--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-138.812</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.21535e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.191</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1916114932947444</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6401405543196917</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.325163521322319</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.157285356156221</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26.42594023751873</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.75144313712272</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 13.461x + -8425.382</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>436.5613412390976</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>459756129.7226777</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.617320643735627e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-124.881</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.16844e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.92</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3163862155468708</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6672988410120807</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.244488088691967</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.135214841455913</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.89517354074312</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.95358244905577</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.136x + -8648.783</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>429.426343755753</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>290537744.422328</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.633929680176825e-05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-115.24</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.14064e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.389</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3418126842168111</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7873243054545538</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.280089896848315</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.335561143644852</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33.42687872252122</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.16898640496976</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.933x + -9004.450</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>423.777566549322</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>303912238.4359277</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.647653998322822e-05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-110.995</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.12067e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.751</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03866112505642204</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6310889820055303</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.058926213036916</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.975505547908519</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30.19127106272634</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.1096533110838</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.705x + -8715.852</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>418.4780451746641</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>456040234.680056</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.660075106136696e-05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-106.298</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.10734e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.038</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1590480294086417</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.530346475396138</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.200895437514181</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.805119031982555</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31.15138677097848</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.20104291829934</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.060x + -8804.113</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>457.1980885449453</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2432192575.5996</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.968994096982682e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6362135409928577</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-102.316</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.09842e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.322</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1420233111535582</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8076149251994229</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.495643479595357</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.574670224228278</v>
+      </c>
+      <c r="J7" t="n">
+        <v>45.87179168723365</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.18963722131048</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 15.015x + -8647.549</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>466.2216449640257</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>980250299.3921894</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.348927935908901e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7179425488705289</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-100.617</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.09092e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.54900000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07830713619269164</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3071860725067974</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.398477207138512</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.015642289022849</v>
+      </c>
+      <c r="J8" t="n">
+        <v>37.09347506303033</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.10652505823433</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.693x + -8328.152</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>465.0648399277428</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>315961879.7105847</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.619582718730847e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7535598306285342</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-92.96100000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.08651e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.782</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4164939112962919</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.133297331941555</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.621305872901047</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.6926529107413</v>
+      </c>
+      <c r="J9" t="n">
+        <v>50.22657284326222</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.61123063991427</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 16.888x + -9523.735</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>462.0454749569959</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>507997005.9589807</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.227522631558258e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7773364585598589</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-93.67200000000003</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.082609999999999e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.98099999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1617325119238948</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.759705859251338</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.565502145397057</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.578594925231208</v>
+      </c>
+      <c r="J10" t="n">
+        <v>52.00445736814248</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.344032132899</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.651x + -8663.695</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>458.0409926564698</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>206302720.2869713</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.999651868526985e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7932244636922485</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-92.05400000000009</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.08056e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.173</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2072955141396269</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5454724906845655</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.331970943090006</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.143726058355128</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41.38384227129414</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.26301697638011</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 15.310x + -8351.491</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>454.1664677363372</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>473653198.5129693</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.830078272135628e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8063690400347214</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +1192,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-121.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.21634e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.754</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3164903587282908</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7778741743617645</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.461623813279092</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.422465636962559</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33.32976497281621</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.96837537932797</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.188x + -8745.798</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>425.556513835281</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>439647509.2972604</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.634380782702551e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-111.737</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.21579e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-76.58</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0139188235977812</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4032493822599827</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.333960457939073</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.169164727500518</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.46758390179824</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.90677899824207</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.974x + -8194.017</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>415.4930371170042</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>413978764.9088309</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.676989275717434e-05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-102.237</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.20277e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.88500000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5934229774499764</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.030465497959012</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.694160515413292</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.955486472502589</v>
+      </c>
+      <c r="J4" t="n">
+        <v>47.28654211276875</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.48824651819594</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.295x + -9494.248</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>419.4491319593897</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>128502580.708563</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.436877730562132e-05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5208876383838603</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-100.225</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.19107e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-77.10599999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4028511991794416</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.023299975134411</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.674980028094986</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.7327423592449</v>
+      </c>
+      <c r="J5" t="n">
+        <v>42.47204809449438</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.48646823592055</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.287x + -9370.291</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>442.898424126861</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>998615699.4737236</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.634526766010167e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6049952232335382</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-98.95000000000005</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.18404e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.31999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3520387347631234</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8529723944085141</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.466325014602316</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.06408751544502</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.23849248096194</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.37210788369278</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.772x + -8952.997</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>459.4419108960251</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2200050254.421949</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.531037011878829e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.7127448382542522</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-97.99800000000005</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.179499999999999e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.48999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3488996412597917</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7785537313279486</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.708690601594925</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.586390090859982</v>
+      </c>
+      <c r="J7" t="n">
+        <v>45.90821696265915</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.28400188530301</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 15.397x + -8631.121</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>456.8288223071426</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>486092885.9156572</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.306173198639828e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7223758203920591</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-94.42200000000003</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.17457e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.657</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4801645341277065</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8020454599199882</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.542292289407071</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.349117361662359</v>
+      </c>
+      <c r="J8" t="n">
+        <v>36.99527892414145</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.47985200944004</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.256x + -9043.425</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>455.5738003963161</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>414419474.7917985</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.741429831853265e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7494979212000059</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-97.20600000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.17208e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.816</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03471175430512569</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1886290392761659</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.150009958138471</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.784617603478716</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31.75053460318929</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.11077642405689</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.709x + -8037.031</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>454.5853986103272</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>108931757.139886</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.192447312401475e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7821872914603254</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-93.70299999999997</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.17053e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.97199999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1947439123320832</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5523444986602706</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.264832899069007</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.251803367504679</v>
+      </c>
+      <c r="J10" t="n">
+        <v>38.65799346646809</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.25853183561952</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.292x + -8291.427</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>451.5707879685751</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>614814743.8409787</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.022111914245131e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7941343882990924</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-91.82900000000006</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.16953e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.111</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.06022194818207349</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4863690710485331</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.420237270551536</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.22968090805138</v>
+      </c>
+      <c r="J11" t="n">
+        <v>39.82159364052018</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.2961015716008</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 15.447x + -8296.650</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>448.5443893143457</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>204222695.5029631</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.889528513827882e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8042280551084774</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-90.75300000000004</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.16839e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-78.25</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1309157165110802</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6414333786593623</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.371880245353843</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.355753039203927</v>
+      </c>
+      <c r="J12" t="n">
+        <v>40.67715977940247</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.34556247412979</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 15.657x + -8334.539</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>445.3617068934848</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>92169324.80456986</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.787832217141882e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8124397277872584</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-86.74799999999993</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.16651e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-78.372</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5461594089392622</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5893925544401728</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.359832687388762</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.384702482976528</v>
+      </c>
+      <c r="J13" t="n">
+        <v>37.79114712261124</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.58584861664701</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 16.762x + -8876.971</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>442.174287418509</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>231743751.0767274</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.706539925316978e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8193441356163379</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-85.71799999999996</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.16679e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-78.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3809619793428631</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.940210419520971</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.696242951974511</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.651337386673285</v>
+      </c>
+      <c r="J14" t="n">
+        <v>56.81998852543433</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.52793233680913</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 16.482x + -8637.507</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>439.0523805817506</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>92283929.4686774</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.634271659427536e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8258247591501469</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-87.33100000000002</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.16595e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-78.61499999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2204231327090241</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7173105553115233</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.082566153931112</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.010475568240889</v>
+      </c>
+      <c r="J15" t="n">
+        <v>35.49957492604283</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.31645639209579</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 15.533x + -8033.736</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>435.8882484891935</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>104529149.8862714</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.574501842928551e-06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8313841030114739</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-85.70400000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.16497e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-78.729</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1734043090905827</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6431014296704807</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.364292639675629</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.284857464935116</v>
+      </c>
+      <c r="J16" t="n">
+        <v>39.69687123002117</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.39821187978183</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 15.887x + -8154.108</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>432.6607238217108</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>274297734.1155606</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.520942983810344e-06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8365537986124532</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-84.77199999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.16677e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-78.84099999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1023786923017569</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.5201476579457995</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.476600907347314</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.995878279674151</v>
+      </c>
+      <c r="J17" t="n">
+        <v>40.23086948456863</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.4205715568302</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 15.986x + -8133.900</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>429.3165494262582</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>203934586.1922266</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.474302652004281e-06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8412734728912257</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-82.55399999999997</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.16473e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-78.952</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3572676105965221</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7560890507750943</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.56462395779619</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.578638123188831</v>
+      </c>
+      <c r="J18" t="n">
+        <v>52.53009133940343</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.58516089805744</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 16.759x + -8471.952</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>425.9215493809027</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>21183066.55456443</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.427282840713248e-06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8460935578739216</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-81.09499999999997</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.16867e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-79.07299999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2099367862275081</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8880466162554737</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.515310175100335</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.495265419909257</v>
+      </c>
+      <c r="J19" t="n">
+        <v>46.63374388710879</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.54973313037205</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 16.586x + -8294.413</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>422.3230347670413</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>56607783.77640617</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.388197784125901e-06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8503685283031174</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-82.12599999999998</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.16924e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-79.17700000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.01368154594398414</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5536990957905542</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.514149773891765</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.532969187758171</v>
+      </c>
+      <c r="J20" t="n">
+        <v>54.16953460278456</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.39231169106921</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 15.861x + -7830.255</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>418.7695825234975</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>250972891.4649639</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.350049975723018e-06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8545821828130712</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-78.28100000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.16894e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-79.301</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3635656862472247</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8332025941300015</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.274057688379306</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.377995221933312</v>
+      </c>
+      <c r="J21" t="n">
+        <v>49.2828086738517</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.61496854372025</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 16.907x + -8297.646</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>415.3545860070256</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>34236904.45462151</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.312118988587916e-06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8588643534098148</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-79.52400000000006</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.17013e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-79.40300000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1041033060454893</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5901341396295071</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.326117725156579</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.970034417693584</v>
+      </c>
+      <c r="J22" t="n">
+        <v>39.48324977154112</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86.50872653162848</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 16.391x + -7948.454</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>411.8290656418306</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>128691416.7346684</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.281866695430897e-06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8624132974589148</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,8 +2430,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-154.9829999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.25343e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-74.611</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2720457344516501</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5572529293545954</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.099907237109413</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.045591311832009</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23.12159672972388</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.3953647282212</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.416x + -7840.930</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>434.9999257535136</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>344819230.5409263</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.616787432361747e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-127.0749999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.20708e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-76.012</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2268987737245904</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6368823274303386</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.268729063557205</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.197811681729863</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.24769433494262</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.74484201939346</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.440x + -8066.219</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>423.8370143989371</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>547836927.5268921</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.656265994921808e-05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-113.0509999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.178079999999999e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.523</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3630593732499043</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9972396494370661</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.575740765283392</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.361346673380489</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33.66970051690187</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.21932323919702</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 15.133x + -8984.526</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>418.7714804008791</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>275201067.4412613</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.669982950005685e-05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-110.6909999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.15806e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.84699999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04427324000057927</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4288234263283882</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.088016781281395</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.048388617719308</v>
+      </c>
+      <c r="J5" t="n">
+        <v>32.71649156956062</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.94346905743005</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.101x + -8216.206</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>433.5745037809186</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1377337842.410501</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.144539877366335e-05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.549404673223865</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-103.889</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.1463e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.111</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1632241141875213</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6023929228274145</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.394722846961558</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.979967496398626</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31.58056057728474</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.23399469050551</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.192x + -8778.693</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>459.553311242398</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1882194165.19316</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.755623996886845e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6691686861868202</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-97.91399999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.13615e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.367</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5699435146274544</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.011273201742436</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.685503940553962</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.683296619601748</v>
+      </c>
+      <c r="J7" t="n">
+        <v>45.9869421948146</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.51320910630089</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.412x + -9402.658</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>457.9437873575273</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>395560895.6460473</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.072688346032543e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.6912128621876305</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-94.75800000000004</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.130670000000001e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.59399999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3388034996971831</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9967164359554841</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.814657303785062</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.666723339112187</v>
+      </c>
+      <c r="J8" t="n">
+        <v>47.8269404575823</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.55911649603661</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.631x + -9405.307</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>459.4159812941938</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>119775122.0151341</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.880674451816313e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7409437104918355</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-96.32500000000005</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.1277e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.816</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2366907644341785</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4167899803093497</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.129201596139299</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.943290000706279</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.19957650124805</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.07449723841992</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.573x + -8063.108</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>458.4407398337984</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2050759825.418768</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.218387483515646e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7791332507737403</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-92.19000000000005</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.12321e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.991</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2206160237111593</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7543313861075586</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.532648826214313</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.682490663789457</v>
+      </c>
+      <c r="J10" t="n">
+        <v>52.62256582177227</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.36674037246492</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.749x + -8648.108</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>454.1219036357127</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>117072889.9099261</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.131163266566401e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7850367555682619</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-88.60199999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.12047e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.163</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4091694089847645</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.574477866256307</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.549948974767799</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.231253077970797</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41.34519349762449</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.56369146988662</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 16.654x + -9064.751</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>450.8553170662203</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>154554559.0861521</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.912314105095442e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8010355879667522</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-84.38499999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.11952e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-78.35299999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.637259481460802</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9660936609081621</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.48128779744172</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.827935325292888</v>
+      </c>
+      <c r="J12" t="n">
+        <v>48.61631945073621</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.68660525809</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 17.273x + -9312.488</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>447.5941925583273</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>177427477.6973688</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.725781819813984e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8162627728454941</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-82.84299999999996</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.11746e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-78.512</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5796616328349538</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6343058820088262</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.512314145170895</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.317249196402199</v>
+      </c>
+      <c r="J13" t="n">
+        <v>44.43721378107117</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.622170643838</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 16.943x + -9025.273</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>443.8448988552323</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>342020752.9353812</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.63263793774982e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8245042456947388</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-84.62100000000009</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.11511e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-78.64400000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.09589835926551951</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8394914168343394</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.570705945470481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.536366543814996</v>
+      </c>
+      <c r="J14" t="n">
+        <v>50.956289445696</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.4417932709521</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 16.082x + -8441.386</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>440.0494036026332</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>159184895.4359874</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.555567234494001e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8317010721692827</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-83.94100000000003</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.11432e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-78.77500000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1115059899106077</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8241650984262582</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.488049813722304</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.285879891882056</v>
+      </c>
+      <c r="J15" t="n">
+        <v>46.01942209834783</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.44160452250371</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 16.081x + -8347.667</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>436.3822431930071</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>470354012.4058977</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.492046342755361e-06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8379316464687732</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-78.07400000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.11416e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-78.937</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4647135923414617</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6639705578297351</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.685470615248416</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.385794665227607</v>
+      </c>
+      <c r="J16" t="n">
+        <v>47.47124749764816</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.72236432383686</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 17.462x + -9018.367</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>432.7070547697845</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>163013896.3609696</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.430512162143117e-06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8442482653894926</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-81.77199999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.11313e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-79.042</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3477365262141789</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.5529316491965853</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.204506388140444</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.041631753494224</v>
+      </c>
+      <c r="J17" t="n">
+        <v>42.44051890047962</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.41701922497259</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 15.970x + -8112.332</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>428.928766008439</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>76658901.32251114</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.386613082874812e-06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8489111888488755</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-81.60999999999996</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.11395e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-79.161</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.206532410750953</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5120631779318011</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.252374548146723</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.457918192885649</v>
+      </c>
+      <c r="J18" t="n">
+        <v>56.97753812005435</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.28313144161756</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 15.393x + -7723.155</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>425.2764764867915</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>155317345.4695542</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.344374033453632e-06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.853593503515818</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-78.74700000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.11415e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-79.30200000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1330858811668987</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4570632257041024</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.092793376310215</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.848939700136619</v>
+      </c>
+      <c r="J19" t="n">
+        <v>40.30521752203344</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.40867727258967</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 15.933x + -7925.510</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>421.6229672675877</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>135787529.6473996</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.301976943813317e-06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8584123172216425</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-77.13200000000006</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.113180000000001e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-79.41500000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1297665175197009</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.565735524987386</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.344986339498656</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.153225000437529</v>
+      </c>
+      <c r="J20" t="n">
+        <v>46.44978303970022</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.51583409920414</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 16.424x + -8100.256</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>418.0042884196412</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>93515649.87172209</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.266278368072416e-06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.862586599675672</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-76.80700000000007</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.11435e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-79.544</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1017203708429545</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5672137690783522</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.37875187598734</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.549378574614573</v>
+      </c>
+      <c r="J21" t="n">
+        <v>62.86242267236202</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.38509718954563</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 15.829x + -7709.902</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>414.4162369724249</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>98336831.56401308</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.232749848994821e-06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8666569399053725</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-73.47200000000004</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.11423e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-79.65600000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1306278689324792</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.6328748845939941</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.4767764927858</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.393417089662345</v>
+      </c>
+      <c r="J22" t="n">
+        <v>55.48930023729125</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86.64470537406686</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 17.057x + -8259.885</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>410.8905802376653</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>35631955.4182388</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.203224322856655e-06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8703108420755646</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +3668,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-148.436</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.87922e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.291</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02101189782293583</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4416031295047814</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.253422903089771</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.829554929011778</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27.53106510200563</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.34901167197908</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.292x + -8200.374</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>441.2503204854718</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>453307118.7463925</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.523184793402742e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-113.721</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.87782e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.417</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2022948526187804</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4694093191168598</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.216195771550979</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.026329615081339</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.41383807915502</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.28775760729498</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 15.413x + -9107.588</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>476.6023147017011</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>227347529.4133855</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.826787225294773e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7363457258037635</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-105.9749999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.84144e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-78.038</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05770519846303718</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6753350119727103</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.46294988078753</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.228208201846874</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38.26377739692781</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.29597584401212</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 15.447x + -8814.496</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>474.03694661931</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>128656884.9781878</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.766313256740211e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8045145645487335</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-99.35599999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.81253e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-78.372</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2463898255991757</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9327750449122331</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.581829270750887</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.348649979974415</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.85928415814353</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.61836106409478</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.924x + -9534.063</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>469.0849278976439</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>238714322.3381775</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.546279619244071e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8234967373181572</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-99.18700000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.79014e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-78.628</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07711677239392996</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3715025133735628</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.273188192489151</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.099177526153265</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38.39836110295903</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.41644623323495</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.968x + -8820.971</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>464.0618202839452</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>266449676.4856685</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.416616707267517e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8359286498442891</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-96.51100000000008</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.77705e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-78.854</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1261868149208826</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5286105061370255</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.324726675539995</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.196136895677287</v>
+      </c>
+      <c r="J7" t="n">
+        <v>39.5511188707784</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.46781189788122</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.200x + -8822.491</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>458.8129218312916</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>29108738.45743059</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.323451476185574e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8457376730006512</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-96.16399999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.76467e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-79.038</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1536918080742448</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.583854032139182</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.284295879553938</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.160212447265749</v>
+      </c>
+      <c r="J8" t="n">
+        <v>40.39249237444133</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.51486193447968</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.420x + -8812.922</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>453.1626101977044</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>179414853.6158305</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.25404088657733e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8534723744850051</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-94.30100000000004</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.7574e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-79.248</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.07135794233975726</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8777163556381857</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.005117324541387</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.968314970434818</v>
+      </c>
+      <c r="J9" t="n">
+        <v>38.33821509162608</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.51034475496964</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 16.398x + -8660.449</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>447.4505321666326</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>82895946.05834448</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.191766518712591e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8609017121513836</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-93.14399999999995</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.74943e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-79.428</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1746615813686714</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5400528925217504</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.180900667657328</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.229148017613586</v>
+      </c>
+      <c r="J10" t="n">
+        <v>39.61458506589467</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.59874183786719</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 16.826x + -8761.127</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>441.9769639623128</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>114951946.6660604</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.14075280656471e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8672568560896207</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-91.59100000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.74377e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-79.59099999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1638014264097569</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6202505999003254</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.442115668568615</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.397534574039562</v>
+      </c>
+      <c r="J11" t="n">
+        <v>44.05801338712136</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.70715520511527</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 17.381x + -8935.365</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>436.7184993165156</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>75285427.38131291</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.100065549795278e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8725612409680905</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +4334,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-107.129</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.74437e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.244</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01505260537279031</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5655120172916728</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9205681126079903</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.894376023837155</v>
+      </c>
+      <c r="J2" t="n">
+        <v>32.21984490610736</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.09884029082536</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.664x + -9168.045</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>444.1272595847075</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>108864793.1901087</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.23384089549512e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5283403986844767</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-93.601</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.76221e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.97</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4191208280561204</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8201220516463597</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.525928095295496</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.904812430422271</v>
+      </c>
+      <c r="J3" t="n">
+        <v>36.42205966339108</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.44781561778335</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.109x + -9613.249</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>483.8378742692371</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>96173839.7698317</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.809131246282537e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7336223625923195</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-92.25099999999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.76744e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-78.206</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1483437519659716</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4608595489542529</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.482466634266881</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.299662476454889</v>
+      </c>
+      <c r="J4" t="n">
+        <v>41.90094506884159</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.31932891105524</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 15.545x + -9084.446</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>481.9175302628286</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>434126598.6003155</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.27596436351776e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7646691931757942</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-89.05499999999995</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.76995e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-78.354</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5705037793440886</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6994848286068222</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.805597269583298</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.268839894697855</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38.70071618893611</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.58067505465303</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.737x + -9693.610</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>480.7478539399942</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>394980255.859816</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.738300323053375e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.804474578142778</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-88.66300000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.77418e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-78.51900000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07890459733344933</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5738289258654355</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.510745159853829</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.556603467005762</v>
+      </c>
+      <c r="J6" t="n">
+        <v>49.81846626164148</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.46714595864923</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.197x + -9243.748</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>476.4086466037708</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>448482705.571925</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.610043817204512e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8160723395709514</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-88.54200000000003</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.77759e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-78.667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04213691763952598</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7224552129789223</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.221023638015017</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.186944186748775</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40.61644537722049</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.38348824761647</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 15.822x + -8893.081</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>471.7079776354223</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>33836282.58977511</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.508835727844292e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8259222514682217</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-85.83799999999997</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.7825e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.82599999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3491018886865117</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7620699783851993</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.298825080717381</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.260718031395355</v>
+      </c>
+      <c r="J8" t="n">
+        <v>46.39635713656119</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.46683111339421</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.196x + -8995.915</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>466.9010668586121</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>252841154.3298536</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.429287957105137e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.834203520639902</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-82.87699999999995</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.78731e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.97</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4075924077423179</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9835335769783613</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.312075041667159</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.58917772440293</v>
+      </c>
+      <c r="J9" t="n">
+        <v>53.92067172313116</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.58083054750514</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 16.737x + -9195.304</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>462.2085125306908</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>150849216.6590624</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.365786026408263e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.841184312411405</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-84.09299999999996</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.79115e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-79.095</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5001868411509627</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.286568009590114</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.049070432317442</v>
+      </c>
+      <c r="J10" t="n">
+        <v>43.02720445839579</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.47075669293118</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 16.214x + -8779.878</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>457.7292824094559</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>59808375.2467428</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.312195813450152e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8473420374072599</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-82.20100000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.7943e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-79.22799999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2337142179290318</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5323350461727602</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.237320821564642</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.108321369535127</v>
+      </c>
+      <c r="J11" t="n">
+        <v>43.8396645646021</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.52072046388218</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 16.447x + -8809.539</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>453.4089835910032</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>59504330.46251216</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.266543799497662e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8527704216938883</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-80.21000000000004</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.79687e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-79.342</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1592045218196105</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8947502627080397</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.688218308443864</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.712888023685584</v>
+      </c>
+      <c r="J12" t="n">
+        <v>58.79283257010837</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.68044798971584</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 17.241x + -9158.798</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>449.3128788115454</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>58519160.6841563</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.228846453558306e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8574119825783549</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-80.28700000000003</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.80072e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-79.452</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1572133842226058</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7072554046623214</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.257823541983323</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.239179019831915</v>
+      </c>
+      <c r="J13" t="n">
+        <v>45.80761059439564</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.59022587957202</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 16.784x + -8804.543</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>445.3372836648231</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>176529882.1420476</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.196660354521983e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8615324941101248</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-80.30300000000005</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.80283e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-79.551</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2501873502243557</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6753983504459924</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.38201129210432</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.071594947626012</v>
+      </c>
+      <c r="J14" t="n">
+        <v>41.86916415303637</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.56760377659262</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 16.673x + -8648.770</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>441.4633788509963</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>32229912.12559871</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.167379872379136e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8653437710121358</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-79.08799999999997</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.80562e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-79.65000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3972886743752337</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7942993864004355</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.482844013892421</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.253182020333465</v>
+      </c>
+      <c r="J15" t="n">
+        <v>47.5707044361684</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.66078674449373</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 17.139x + -8816.128</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>437.6124367348919</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>217606140.6536585</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.142694722031057e-06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.868679340340917</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-78.62199999999996</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.80718e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-79.752</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4474656213682003</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6285925599346588</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.480539308420189</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.185479715788673</v>
+      </c>
+      <c r="J16" t="n">
+        <v>47.96414807483088</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.6944385266701</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 17.314x + -8819.790</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>433.8524003031019</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>36112145.07855842</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.117052348485922e-06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8721326803225858</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-76.26300000000003</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.81131e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-79.858</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4294887429324541</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.07634533454852</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.674459009976488</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.451967401807524</v>
+      </c>
+      <c r="J17" t="n">
+        <v>56.30987101076902</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.77865078601785</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 17.768x + -8974.515</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>430.0687681233816</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>469549170.1307999</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.094444907575688e-06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8753481574775807</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-78.697</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.81229e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-79.967</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.05588083585556243</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4661930612116133</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.169291525295366</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.149914982014108</v>
+      </c>
+      <c r="J18" t="n">
+        <v>44.78677304149869</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.42938387225492</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 16.026x + -7959.370</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>426.3236654765057</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>48188148.78191241</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.070764944305307e-06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8786854289559114</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-75.11499999999995</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.81515e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-80.075</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.09746330265341353</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6404602328060933</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.434250629492104</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.266192964293285</v>
+      </c>
+      <c r="J19" t="n">
+        <v>45.40427527818311</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.69524674808845</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 17.318x + -8556.045</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>422.6080774865547</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>30729510.39641538</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.050392275350101e-06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8816682310091868</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-74.31799999999998</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.8177e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-80.164</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4692193011243914</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8706687167730387</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.612526565466353</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.318028826892592</v>
+      </c>
+      <c r="J20" t="n">
+        <v>52.42411698486022</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.80687561158989</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 17.925x + -8782.754</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>418.8492119872903</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>99699177.8356974</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.033104798877223e-06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8842634293848884</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-74.33799999999997</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.82033e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-80.258</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2156900627528431</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6784744603553692</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.573425921757229</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.255773469270077</v>
+      </c>
+      <c r="J21" t="n">
+        <v>47.30255336691651</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.76109712077208</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 17.671x + -8563.081</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>415.0822496434679</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>189549326.6332638</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.016993736638098e-06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8867052416613772</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-74.12699999999995</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.82364e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-80.37</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1124222209022645</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8083180241574554</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.223807543020304</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.272915579511115</v>
+      </c>
+      <c r="J22" t="n">
+        <v>54.43464134455434</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86.5844236207531</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 16.755x + -8009.531</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>411.336132300142</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>274160802.661543</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>9.982190114390554e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8896292886038379</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +5572,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-201.391</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.01385e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-73.41</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2296364909577362</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6078580228780566</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.237907571267598</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.994196354650039</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.43486932483383</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.66028256898838</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.699x + -7302.502</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>448.0868660230072</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>432120763.4442663</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.524193114130107e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-150.1640000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.09218e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-76.122</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1196414127941215</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.462278794935522</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.242468645785523</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.195021400136902</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.67780053149527</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.72490414119909</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.377x + -7870.420</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>458.0576473385265</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1535254073.316125</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6.600865462276436e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.6221346535876193</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-135.5309999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.06645e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.93000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.01821994632036216</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5148373473266725</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.210613048401512</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.215830137990696</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29.6830906363262</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.87143116814933</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.854x + -7842.512</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>469.9161833437443</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>426543626.2747911</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.583984295924121e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7552828372831227</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-124.5509999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.03645e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-77.367</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5804019335957445</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9604235352681523</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.774213394500648</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.864324209810046</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.39999241015102</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.31820763514392</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.541x + -8701.710</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>467.1531956187354</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>384295557.1347258</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.041696351356739e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7891987726480826</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-121.155</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.01405e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.703</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03819542857772485</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4234819453490237</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.37744107307523</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.334803817236022</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.11137570502797</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.13165010017671</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.789x + -8118.922</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>463.0916462350833</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>566243428.233409</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.78246445523967e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8087308510273754</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-114.4739999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.99915e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.97499999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3275613662899805</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8520832758368355</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.642845625566089</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.611538870481448</v>
+      </c>
+      <c r="J7" t="n">
+        <v>36.76602825141157</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.44123434496925</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.079x + -8744.575</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>458.155366719374</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>335321526.4706919</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.619416189556971e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8226184098124311</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-113.3599999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.98705e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.23399999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1454714267210917</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4344866750626211</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.386862764621113</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.5373564854663</v>
+      </c>
+      <c r="J8" t="n">
+        <v>38.7730148817938</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.29102253757358</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 15.426x + -8232.455</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>453.0897904582574</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>201694822.5567918</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.496395515594004e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8340735195617309</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-106.962</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.97863e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.468</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2193189354326392</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7878455389818507</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.592082700881541</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.377560165337943</v>
+      </c>
+      <c r="J9" t="n">
+        <v>37.22386935567619</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.53411292493462</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 16.511x + -8721.625</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>447.9884789038092</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>206934293.3790737</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.404995852608527e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8432668587166029</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-105.9420000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.97235e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.67400000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6777930583759576</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.523320713106424</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.611409048472505</v>
+      </c>
+      <c r="J10" t="n">
+        <v>42.25804798728812</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.42366930959109</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 16.000x + -8311.734</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>443.0473409330044</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>240801249.3798047</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.334299345676491e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8508238506214266</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-104.413</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.96745e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.842</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.04852635772667549</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8344308259248309</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.519708120697381</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.598031221256674</v>
+      </c>
+      <c r="J11" t="n">
+        <v>43.38457532545887</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.47190368232027</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 16.219x + -8319.006</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>438.4193282355079</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>25806229.035969</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.278349313536701e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8571255385014426</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +6238,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-127.0940000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.0472e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-76.01000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3156890011984848</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.97285090925156</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.440676296746758</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.284959637321605</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33.28894429570712</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.03281935299277</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.419x + -8998.038</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>428.8948341124835</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>281385923.9833325</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.59815863015575e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-114.9109999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.04653e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-76.874</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02214201925965265</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.04633567291082438</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.104321058262387</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.864130830717051</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29.9758687866024</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.86164679763668</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.821x + -8186.698</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>432.850749027939</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1242917534.074502</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.266007038497087e-05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5332057293538877</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-105.343</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.03772e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-77.217</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3550266579802169</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6614387944018564</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.71518255369683</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.511868491765952</v>
+      </c>
+      <c r="J4" t="n">
+        <v>43.59092517424482</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.19508813400054</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 15.036x + -8805.343</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>467.1079398612561</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2385939196.343543</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.385364504891636e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.6775479794518046</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-99.14700000000005</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.02732e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-77.474</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2483070555288152</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5682759174516555</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.539298469417471</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.192189168530405</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.54324884832494</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.40674426826318</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.924x + -9242.404</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>462.8740630068066</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>434719763.9625528</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.149164943798226e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6854413757349739</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-99.7890000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.01979e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.679</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4928887963228729</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.244973010066469</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.073670120981009</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.46227441948014</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.1408049396007</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.824x + -8456.182</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>467.6597870742491</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>340266557.6764494</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.653407641557734e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.7496766293620616</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-94.78200000000004</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.01564e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.88200000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2097552089747076</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6296495062564021</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.273188133789402</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.014345571950377</v>
+      </c>
+      <c r="J7" t="n">
+        <v>35.25798837604948</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.40851752037459</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 15.932x + -9008.677</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>465.6648062293336</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>660870073.005559</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.122843238729958e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7823288999255741</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-91.81600000000003</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.01307e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-78.09</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3753911060973815</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7870533273630577</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.268733421460422</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.973124901537699</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.83401562066883</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.43720129708646</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.061x + -8959.764</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>460.5572545164216</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>59335483.17586935</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.041024618743799e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7881927870888733</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-92.38999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.01034e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.264</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6091395131324718</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.266061034339221</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.338117364586253</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40.54930417069693</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.28508447384245</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 15.402x + -8452.194</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>456.4816585955455</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>31268812.87347665</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.865979968654931e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8014566797072805</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-90.57899999999995</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.01037e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.43000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1766026344237576</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6449775118365028</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.327372377665219</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.236264268371305</v>
+      </c>
+      <c r="J10" t="n">
+        <v>41.98405620538083</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.32324995252912</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.562x + -8434.849</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>453.0450447735507</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>331677476.4595311</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.643433532120073e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8203356288336173</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-87.71500000000003</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.00963e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.592</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.284421217697096</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8095565444205217</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.655394521131121</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.718188531627107</v>
+      </c>
+      <c r="J11" t="n">
+        <v>58.51830501035526</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.48826426941312</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 16.295x + -8755.167</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>448.9862634315634</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>46571901.01023883</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.555444941424885e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8285486454723441</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-84.66300000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.00917e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-78.74299999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5619376580030291</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.016750498543256</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.291088286448889</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.943797504102476</v>
+      </c>
+      <c r="J12" t="n">
+        <v>39.39722636911135</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.602996634245</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 16.847x + -8967.317</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>445.0313496302306</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>221089791.1095856</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.484715450195128e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8355227839241426</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-82.99200000000008</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.00883e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-78.86799999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.611085245803213</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8730512035772793</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.503027664106945</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.355345401316294</v>
+      </c>
+      <c r="J13" t="n">
+        <v>45.29807484081643</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.71849331651104</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 17.441x + -9203.161</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>441.2023387667601</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>101486988.0634213</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.42824167874795e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8413399622211442</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-86.49799999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.00936e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-78.985</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1066815669347054</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4700025549762474</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.355883184469666</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.572368269561976</v>
+      </c>
+      <c r="J14" t="n">
+        <v>53.05740581592507</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.29088641881872</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 15.426x + -7986.190</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>437.4715723862098</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>57449690.51259881</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.379727520644663e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8465578548034421</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-82.43700000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.00865e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-79.127</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.111647529898037</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6689203519740923</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.267260897898484</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.449199406064878</v>
+      </c>
+      <c r="J15" t="n">
+        <v>47.38617085675377</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.50371673617262</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 16.367x + -8419.750</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>433.8090666612601</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>200800953.828605</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.333391361176151e-06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8516630899017905</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-81.62900000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.00941e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-79.258</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3003178330651065</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5285805268160026</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.23920266819028</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.117464031181024</v>
+      </c>
+      <c r="J16" t="n">
+        <v>43.47005633813709</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.42903280883154</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 16.024x + -8153.537</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>430.2380017060291</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>39389064.77154506</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.293232785149028e-06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8562847747424579</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-80.48099999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.0099e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-79.361</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2558097757365574</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6016751344865429</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.289778889475776</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.396437244033415</v>
+      </c>
+      <c r="J17" t="n">
+        <v>48.83467347061129</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.54830245463963</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 16.579x + -8367.410</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>426.6129276690558</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>65467756.19810615</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.261495630592835e-06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8600427131116327</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-78.85100000000006</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.01015e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-79.467</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3584431059084611</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5862267431410751</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.682633211736269</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.306320364720206</v>
+      </c>
+      <c r="J18" t="n">
+        <v>50.56519977932956</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.58297226724598</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 16.748x + -8372.142</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>422.9245303454863</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>167261841.6995843</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.230586387078175e-06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8638017003769267</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-75.75599999999997</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.01147e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-79.596</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3455968090130568</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9200174715224655</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.767535232060444</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.956776949068005</v>
+      </c>
+      <c r="J19" t="n">
+        <v>73.33580906515812</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.76825808540362</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 17.710x + -8793.047</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>419.3080136373871</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>62055996.3369637</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.197927246364865e-06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8678877325700988</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-77.63899999999995</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.01156e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-79.693</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2911520566826355</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5552695067037177</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.10456850307801</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.046627014585492</v>
+      </c>
+      <c r="J20" t="n">
+        <v>41.55609873971333</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.51465982914073</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 16.419x + -8030.453</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>415.5416941202325</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>73608840.73400299</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.173842519935232e-06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8709531020925498</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-76.26400000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.01346e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-79.821</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.250671080922325</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6470678688595063</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.296146435994921</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.33436541593751</v>
+      </c>
+      <c r="J21" t="n">
+        <v>48.09008211628269</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.54094038033492</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 16.544x + -8010.580</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>411.0599239163823</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>106111814.6856551</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.149276738290599e-06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8741729828158392</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-76.65400000000005</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.014219999999999e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-79.92</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1393148318971744</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5807451093120737</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.328568527433896</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.608520608892386</v>
+      </c>
+      <c r="J22" t="n">
+        <v>66.17594065249925</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86.47140388244669</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 16.217x + -7761.131</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>407.4459078658471</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>51632562.71932381</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.1268057007435e-06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8771765429249365</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +7476,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-212.079</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.34048e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-72.634</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09775238428660057</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7116576783443929</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.141752670121127</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.074780039713145</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16.46094679366934</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.29324554001242</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.007x + -6504.175</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>431.3802792910544</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>517134002.377484</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.611346149556508e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-163.888</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.40305e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-75.205</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1869081556360942</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5929183646290453</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.3172577339898</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.138832426653552</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.2745031554246</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.31756945895515</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.209x + -7000.487</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>406.1964822742892</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>531464218.9944366</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.740229790163936e-05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-142.399</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.35659e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.13800000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3500517204795346</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6996287674581867</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.422923069521735</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.881800688283441</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.62407950232634</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.85794459005777</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.809x + -7709.912</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>443.7626362359905</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>943955460.2865905</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.426695995703156e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.6565336410205004</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-131.019</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.30925e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.696</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3216325080779493</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7262974791148865</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.385765969599591</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.893332204520736</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.07318979280422</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.08631888573478</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.617x + -8039.545</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>450.3571189902734</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4626438561.604074</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.084830119527758e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7361942104284004</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-120.7569999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.27303e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.13800000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4231827061669879</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8664650559238887</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.687802618607461</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.296423059158444</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31.16312837963968</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.35350537499718</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.691x + -8539.226</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>448.2740800618595</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>38662165.69008265</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.502778957277981e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.7659092406962532</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-117.977</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.2461e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.485</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0664872769086961</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7093968994475335</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.382848833060943</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.269400803864905</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.25696630349673</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.15776587493272</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 14.890x + -7943.922</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>445.387017325304</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>323432221.225269</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.038708159641297e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7954441693129413</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-113.365</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.22457e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.798</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1435917165607293</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4676814026646209</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.233637622650597</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.209853001165884</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.80413627735691</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.20263531704791</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 15.066x + -7915.946</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>440.9694717024348</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>191695188.0984681</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.811950100208866e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8123805858384038</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-107.6489999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.20873e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.066</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4863849597300355</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9677087449909744</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.68876618002486</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.737051272546962</v>
+      </c>
+      <c r="J9" t="n">
+        <v>41.67158222566433</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.42234109702724</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 15.994x + -8313.245</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>436.1590196059623</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>52198606.42273451</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.659649004426688e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8250361530844489</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-106.513</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.19572e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.333</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.133576586155218</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5004093939842542</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.321593093252559</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.404818545583846</v>
+      </c>
+      <c r="J10" t="n">
+        <v>39.86063127368425</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.2101776795749</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.096x + -7692.415</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>431.4033591607503</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>89153392.15322308</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.539947714236846e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8358601348984783</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-104.591</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.18468e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.536</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1382706410385817</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.581409056877447</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.137981876614404</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.2387694904972</v>
+      </c>
+      <c r="J11" t="n">
+        <v>37.62158200193961</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.23391246743091</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 15.192x + -7635.581</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>426.8422070299947</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>135098491.7655998</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.455402046740741e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.844015986952308</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +8142,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-129.4920000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.190239999999999e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.535</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4341269836425564</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8770698217290915</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.611166485128293</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.726171321750013</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.44217657680807</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.95011125627252</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.124x + -8799.587</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>429.7932192605974</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>562592999.5669701</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.627895485631908e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-114.0500000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.19621e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-76.41800000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4074856843798644</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8052893662018898</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.505632555887714</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.183018310677797</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29.9661756648014</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.09480031582621</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.649x + -8712.208</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>419.6303894013049</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>817488492.7871574</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.672088246815811e-05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5000000000000003</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-109.6369999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.18674e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.767</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2029816572770876</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7437107576065484</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.363498654623092</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.599642291862426</v>
+      </c>
+      <c r="J4" t="n">
+        <v>39.29648469481174</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.05397946992426</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.497x + -8459.160</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>429.617769656206</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>710104774.3432301</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.255706842964694e-05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5379779268763155</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-103.674</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.17863e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-77.03700000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4437706076916035</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6937116245526209</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.454849245616604</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.879215365228066</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30.44454441905064</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.20353949558505</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.070x + -8694.053</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>452.3229894707206</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>808203832.0034522</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6.152092620533742e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6341441226851702</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-99.44299999999998</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.17232e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.259</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4189759137374585</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.222558228199029</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.616154031587023</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.675854820872687</v>
+      </c>
+      <c r="J6" t="n">
+        <v>43.52718987594177</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.46264421811694</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.177x + -9257.357</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>454.7715577815473</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1970217010.584641</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.661555103148826e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6730637111776536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-100.6600000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.16748e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.473</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2287810479190074</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2909553693014067</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.194053249113096</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.881690882143798</v>
+      </c>
+      <c r="J7" t="n">
+        <v>32.24413141500671</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.98322467867696</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 14.241x + -7971.611</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>459.2726757585126</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>372756534.5368027</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.006160791815131e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7358093608090367</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-98.54599999999994</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.16463e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.65900000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.09326881776994159</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5352377549858983</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.312222876269671</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.138215954275578</v>
+      </c>
+      <c r="J8" t="n">
+        <v>36.09636256477264</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.10727891488591</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.696x + -8138.293</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>458.37568208228</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>473829535.3887117</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.330515857217783e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7729457707706573</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-96.54000000000008</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.162660000000001e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-77.81100000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3206300146548768</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6425562784706773</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.402216861111823</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.392039409126852</v>
+      </c>
+      <c r="J9" t="n">
+        <v>41.39457995253967</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.24132441411275</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 15.222x + -8346.133</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>454.9831432895858</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>204470522.9006511</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.115043053145326e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7872666669690823</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-91.80100000000004</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.16143e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-77.982</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4704757754080797</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9385174736945496</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.741258981043819</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.367071551321159</v>
+      </c>
+      <c r="J10" t="n">
+        <v>42.7925121795191</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.57823194614254</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 16.725x + -9121.422</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>451.2452578884005</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>104534850.1738987</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.000572738836259e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7955462512158019</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-92.46900000000005</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.16208e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.142</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.06426427450633361</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6147806978837342</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.304585700646868</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.263897460490562</v>
+      </c>
+      <c r="J11" t="n">
+        <v>39.61757183780524</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.23403615487634</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 15.192x + -8143.608</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>448.0720873457959</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>390125731.3063829</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.826975893216307e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8090303126201446</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-91.28700000000003</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.15941e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-78.27</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3100808111512601</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7215574700022996</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.399708717458724</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.068831105715563</v>
+      </c>
+      <c r="J12" t="n">
+        <v>39.81076461623726</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.27555474661604</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 15.362x + -8155.639</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>444.4760142132259</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>242694676.8129379</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.733726778152612e-06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8167960157979248</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-87.25400000000002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.16025e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-78.407</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2778815103829188</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8456813308983444</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.465722789624489</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.307784678470119</v>
+      </c>
+      <c r="J13" t="n">
+        <v>41.08126219608315</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.61406644922589</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 16.902x + -8934.495</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>441.0341296801473</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>151335285.9289216</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.652955246449384e-06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8239519648011685</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-87.51700000000005</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.16003e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-78.548</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3793314305432155</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7224578856322302</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.407974108401413</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.440022047394589</v>
+      </c>
+      <c r="J14" t="n">
+        <v>47.52595568656239</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.41195667456248</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 15.948x + -8314.579</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>437.5444965927232</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>619785895.9580516</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.583197135291149e-06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8304214642819526</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-87.44300000000004</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.15982e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-78.654</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1850079808415546</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6211224989523683</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.440378818762587</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.28793299546794</v>
+      </c>
+      <c r="J15" t="n">
+        <v>42.33021315199902</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.36764732155075</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 15.753x + -8125.318</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>434.0868146982034</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>159004724.4555343</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.528213643864651e-06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8357033753030848</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-85.584</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.15883e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-78.79600000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2763925948041334</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5953812507390878</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.454093701839376</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.267031003926022</v>
+      </c>
+      <c r="J16" t="n">
+        <v>43.71138836166046</v>
+      </c>
+      <c r="K16" t="n">
+        <v>86.39923131988029</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 15.891x + -8119.982</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>430.6744964949223</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>167257316.4615875</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.469460529271239e-06</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8415589127745084</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-82.74000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.16019e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-78.913</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2915081464087915</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9061904908275671</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.60067523840496</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.830325477844451</v>
+      </c>
+      <c r="J17" t="n">
+        <v>59.84232123027933</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.56823354229601</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 16.676x + -8464.498</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>427.2183042735488</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>73278536.64309131</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.423873628367312e-06</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8463346620118506</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-85.98600000000005</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.16125e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-79.03</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.08553367608119777</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4511436861560143</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.209508652176592</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.274208323575305</v>
+      </c>
+      <c r="J18" t="n">
+        <v>45.02317040776452</v>
+      </c>
+      <c r="K18" t="n">
+        <v>86.19605984370624</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 15.040x + -7507.542</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>423.6906610712998</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>53706620.86468942</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.38354794085521e-06</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.850674296773324</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-83.06800000000004</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5.16195e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-79.139</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2598098467772489</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6718184631646174</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9773069703928212</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.146576179141718</v>
+      </c>
+      <c r="J19" t="n">
+        <v>37.403737808341</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86.37119903640611</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 15.768x + -7814.229</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>420.3418232263168</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>35319509.81477289</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.342587031040738e-06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8552353239604557</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-82.43200000000002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.16325e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-79.258</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.02535125707845608</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5387538266961881</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.336427828124159</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.549917302944029</v>
+      </c>
+      <c r="J20" t="n">
+        <v>54.77269454172064</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.3154575967724</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 15.529x + -7611.577</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>416.8541039567747</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>80745082.35935077</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.305381697007645e-06</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8595145293817911</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-81.73399999999998</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5.16501e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-79.37</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2436970921242774</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6682560515821906</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.339842451990955</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.487079147596895</v>
+      </c>
+      <c r="J21" t="n">
+        <v>55.49866911638667</v>
+      </c>
+      <c r="K21" t="n">
+        <v>86.38709435375804</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 15.838x + -7688.220</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>413.173417094693</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>24083557.43788818</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.273415623210706e-06</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8632859396389144</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-80.53399999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.16635e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-79.488</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5600702658062693</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.335431596250833</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.386473134667395</v>
+      </c>
+      <c r="J22" t="n">
+        <v>49.06020133975996</v>
+      </c>
+      <c r="K22" t="n">
+        <v>86.31899829893688</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 15.544x + -7461.779</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>409.5263881564664</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>122618991.6382949</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.241619927129778e-06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8671466321769243</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +9380,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-246.2620000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.48405e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-71.477</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08917540533169541</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3471414323388183</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.1459857028003</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.954132397868006</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.54704243204864</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.23478723234156</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.430x + -5414.042</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>429.3284156703372</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>402553699.9200533</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.656942896656787e-05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-177.136</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.56439e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-74.845</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0184069568974506</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6847044382186773</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.456079963214183</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.191634385802108</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.62958177097708</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.08416256317115</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.627x + -6445.594</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>421.7191979384372</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1328494992.742595</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.053142505300511e-05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.570871772563797</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-153.125</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.48945e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-76.01000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3604533760222052</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7743064445909836</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.497126154862834</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.627842470879877</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.87766911889256</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.70517038129283</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.316x + -7146.132</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>443.2816248255861</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>165798939.9663967</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.215415351138841e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7355479135058132</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-141.6579999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.42322e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-76.693</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2608720242752646</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4951698017334251</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.15293708568749</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.886380745785861</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.43295414845267</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.79608932309401</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.605x + -7146.514</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>441.6105664394518</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>580112492.5795598</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.32184981880586e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7815517545166534</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-131.116</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.37384e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-77.176</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2971080407960572</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.138437418711877</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.509783129603516</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.560692240341428</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.59713413647124</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.1322096647157</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.791x + -7685.932</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>437.6272727848345</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>47794544.42563547</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.9517164057488e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8059296303825573</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-126.609</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.34091e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-77.55500000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08846537671712368</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5108913846030761</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.130939646268442</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.022654159692959</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25.80948698569293</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.09283679408355</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 14.642x + -7469.247</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>432.7455043802224</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>167540934.2256478</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.740164012349097e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8220898810919908</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-123.917</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.31622e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-77.863</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4546049582765402</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.075151414504331</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.985898241251778</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.01572125230378</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.01793341948847</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.365x + -7190.514</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>427.7264566839125</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>38758243.48460139</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.594085761636233e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8344966119782465</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-117.938</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.29846e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-78.14400000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1549357653185952</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6998680887728033</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.539827081477487</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.564392866790091</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.00297576992922</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.26989989713512</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 15.339x + -7597.017</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>422.9965335576611</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>107188625.7715122</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.490096372647036e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.844076002849017</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-115.861</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.28564e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-78.361</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.08806292461510733</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6883682539826083</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.237438892053168</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.252080060144379</v>
+      </c>
+      <c r="J10" t="n">
+        <v>33.00930684280635</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.27825604431004</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.373x + -7510.589</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>418.6352001544854</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>98272582.88053755</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.415503448633136e-06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.85141449381325</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-110.61</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.27423e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-78.563</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3470963104992334</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.964366898429819</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.528700134325663</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.54653247517536</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.09323503542841</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.57205587394866</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 16.694x + -8100.325</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>414.6717908169821</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13167151.73639226</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.351561634035653e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8580267901229111</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -588,19 +588,19 @@
       <c r="K2" t="n">
         <v>85.75144313712272</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 13.461x + -8425.382</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8425.382353354806</v>
       </c>
       <c r="Y2" t="n">
         <v>436.5613412390976</v>
       </c>
       <c r="Z2" t="n">
-        <v>459756129.7226777</v>
+        <v>138.812</v>
       </c>
       <c r="AA2" t="n">
         <v>1.617320643735627e-05</v>
@@ -640,19 +640,19 @@
       <c r="K3" t="n">
         <v>85.95358244905577</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.136x + -8648.783</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8648.783113050857</v>
       </c>
       <c r="Y3" t="n">
         <v>429.426343755753</v>
       </c>
       <c r="Z3" t="n">
-        <v>290537744.422328</v>
+        <v>124.881</v>
       </c>
       <c r="AA3" t="n">
         <v>1.633929680176825e-05</v>
@@ -692,19 +692,19 @@
       <c r="K4" t="n">
         <v>86.16898640496976</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.933x + -9004.450</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9004.449998165856</v>
       </c>
       <c r="Y4" t="n">
         <v>423.777566549322</v>
       </c>
       <c r="Z4" t="n">
-        <v>303912238.4359277</v>
+        <v>115.24</v>
       </c>
       <c r="AA4" t="n">
         <v>1.647653998322822e-05</v>
@@ -744,19 +744,19 @@
       <c r="K5" t="n">
         <v>86.1096533110838</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.705x + -8715.852</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8715.851842118569</v>
       </c>
       <c r="Y5" t="n">
         <v>418.4780451746641</v>
       </c>
       <c r="Z5" t="n">
-        <v>456040234.680056</v>
+        <v>110.995</v>
       </c>
       <c r="AA5" t="n">
         <v>1.660075106136696e-05</v>
@@ -796,19 +796,19 @@
       <c r="K6" t="n">
         <v>86.20104291829934</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.060x + -8804.113</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8804.112573257338</v>
       </c>
       <c r="Y6" t="n">
         <v>457.1980885449453</v>
       </c>
       <c r="Z6" t="n">
-        <v>2432192575.5996</v>
+        <v>106.298</v>
       </c>
       <c r="AA6" t="n">
         <v>5.968994096982682e-06</v>
@@ -848,19 +848,19 @@
       <c r="K7" t="n">
         <v>86.18963722131048</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 15.015x + -8647.549</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8647.549253121873</v>
       </c>
       <c r="Y7" t="n">
         <v>466.2216449640257</v>
       </c>
       <c r="Z7" t="n">
-        <v>980250299.3921894</v>
+        <v>102.316</v>
       </c>
       <c r="AA7" t="n">
         <v>3.348927935908901e-06</v>
@@ -900,19 +900,19 @@
       <c r="K8" t="n">
         <v>86.10652505823433</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.693x + -8328.152</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8328.152260697088</v>
       </c>
       <c r="Y8" t="n">
         <v>465.0648399277428</v>
       </c>
       <c r="Z8" t="n">
-        <v>315961879.7105847</v>
+        <v>100.617</v>
       </c>
       <c r="AA8" t="n">
         <v>2.619582718730847e-06</v>
@@ -952,19 +952,19 @@
       <c r="K9" t="n">
         <v>86.61123063991427</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 16.888x + -9523.735</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9523.735254483521</v>
       </c>
       <c r="Y9" t="n">
         <v>462.0454749569959</v>
       </c>
       <c r="Z9" t="n">
-        <v>507997005.9589807</v>
+        <v>92.96100000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>2.227522631558258e-06</v>
@@ -1004,19 +1004,19 @@
       <c r="K10" t="n">
         <v>86.344032132899</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.651x + -8663.695</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8663.69464773346</v>
       </c>
       <c r="Y10" t="n">
         <v>458.0409926564698</v>
       </c>
       <c r="Z10" t="n">
-        <v>206302720.2869713</v>
+        <v>93.67200000000003</v>
       </c>
       <c r="AA10" t="n">
         <v>1.999651868526985e-06</v>
@@ -1056,19 +1056,19 @@
       <c r="K11" t="n">
         <v>86.26301697638011</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 15.310x + -8351.491</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8351.490980495348</v>
       </c>
       <c r="Y11" t="n">
         <v>454.1664677363372</v>
       </c>
       <c r="Z11" t="n">
-        <v>473653198.5129693</v>
+        <v>92.05400000000009</v>
       </c>
       <c r="AA11" t="n">
         <v>1.830078272135628e-06</v>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1254,19 +1254,19 @@
       <c r="K2" t="n">
         <v>85.96837537932797</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.188x + -8745.798</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8745.798358997865</v>
       </c>
       <c r="Y2" t="n">
         <v>425.556513835281</v>
       </c>
       <c r="Z2" t="n">
-        <v>439647509.2972604</v>
+        <v>121.05</v>
       </c>
       <c r="AA2" t="n">
         <v>1.634380782702551e-05</v>
@@ -1306,19 +1306,19 @@
       <c r="K3" t="n">
         <v>85.90677899824207</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.974x + -8194.017</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8194.017028003105</v>
       </c>
       <c r="Y3" t="n">
         <v>415.4930371170042</v>
       </c>
       <c r="Z3" t="n">
-        <v>413978764.9088309</v>
+        <v>111.737</v>
       </c>
       <c r="AA3" t="n">
         <v>1.676989275717434e-05</v>
@@ -1358,19 +1358,19 @@
       <c r="K4" t="n">
         <v>86.48824651819594</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.295x + -9494.248</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9494.247686904209</v>
       </c>
       <c r="Y4" t="n">
         <v>419.4491319593897</v>
       </c>
       <c r="Z4" t="n">
-        <v>128502580.708563</v>
+        <v>102.237</v>
       </c>
       <c r="AA4" t="n">
         <v>1.436877730562132e-05</v>
@@ -1410,19 +1410,19 @@
       <c r="K5" t="n">
         <v>86.48646823592055</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.287x + -9370.291</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9370.291333677103</v>
       </c>
       <c r="Y5" t="n">
         <v>442.898424126861</v>
       </c>
       <c r="Z5" t="n">
-        <v>998615699.4737236</v>
+        <v>100.225</v>
       </c>
       <c r="AA5" t="n">
         <v>7.634526766010167e-06</v>
@@ -1462,19 +1462,19 @@
       <c r="K6" t="n">
         <v>86.37210788369278</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.772x + -8952.997</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8952.996738374797</v>
       </c>
       <c r="Y6" t="n">
         <v>459.4419108960251</v>
       </c>
       <c r="Z6" t="n">
-        <v>2200050254.421949</v>
+        <v>98.95000000000005</v>
       </c>
       <c r="AA6" t="n">
         <v>3.531037011878829e-06</v>
@@ -1514,19 +1514,19 @@
       <c r="K7" t="n">
         <v>86.28400188530301</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 15.397x + -8631.121</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8631.120644864346</v>
       </c>
       <c r="Y7" t="n">
         <v>456.8288223071426</v>
       </c>
       <c r="Z7" t="n">
-        <v>486092885.9156572</v>
+        <v>97.99800000000005</v>
       </c>
       <c r="AA7" t="n">
         <v>3.306173198639828e-06</v>
@@ -1566,19 +1566,19 @@
       <c r="K8" t="n">
         <v>86.47985200944004</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.256x + -9043.425</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9043.424900618778</v>
       </c>
       <c r="Y8" t="n">
         <v>455.5738003963161</v>
       </c>
       <c r="Z8" t="n">
-        <v>414419474.7917985</v>
+        <v>94.42200000000003</v>
       </c>
       <c r="AA8" t="n">
         <v>2.741429831853265e-06</v>
@@ -1618,19 +1618,19 @@
       <c r="K9" t="n">
         <v>86.11077642405689</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.709x + -8037.031</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8037.031378340025</v>
       </c>
       <c r="Y9" t="n">
         <v>454.5853986103272</v>
       </c>
       <c r="Z9" t="n">
-        <v>108931757.139886</v>
+        <v>97.20600000000002</v>
       </c>
       <c r="AA9" t="n">
         <v>2.192447312401475e-06</v>
@@ -1670,19 +1670,19 @@
       <c r="K10" t="n">
         <v>86.25853183561952</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.292x + -8291.427</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8291.427047402522</v>
       </c>
       <c r="Y10" t="n">
         <v>451.5707879685751</v>
       </c>
       <c r="Z10" t="n">
-        <v>614814743.8409787</v>
+        <v>93.70299999999997</v>
       </c>
       <c r="AA10" t="n">
         <v>2.022111914245131e-06</v>
@@ -1722,19 +1722,19 @@
       <c r="K11" t="n">
         <v>86.2961015716008</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 15.447x + -8296.650</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8296.650322649335</v>
       </c>
       <c r="Y11" t="n">
         <v>448.5443893143457</v>
       </c>
       <c r="Z11" t="n">
-        <v>204222695.5029631</v>
+        <v>91.82900000000006</v>
       </c>
       <c r="AA11" t="n">
         <v>1.889528513827882e-06</v>
@@ -1774,19 +1774,19 @@
       <c r="K12" t="n">
         <v>86.34556247412979</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 15.657x + -8334.539</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-8334.538598439145</v>
       </c>
       <c r="Y12" t="n">
         <v>445.3617068934848</v>
       </c>
       <c r="Z12" t="n">
-        <v>92169324.80456986</v>
+        <v>90.75300000000004</v>
       </c>
       <c r="AA12" t="n">
         <v>1.787832217141882e-06</v>
@@ -1826,19 +1826,19 @@
       <c r="K13" t="n">
         <v>86.58584861664701</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 16.762x + -8876.971</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-8876.970806251997</v>
       </c>
       <c r="Y13" t="n">
         <v>442.174287418509</v>
       </c>
       <c r="Z13" t="n">
-        <v>231743751.0767274</v>
+        <v>86.74799999999993</v>
       </c>
       <c r="AA13" t="n">
         <v>1.706539925316978e-06</v>
@@ -1878,19 +1878,19 @@
       <c r="K14" t="n">
         <v>86.52793233680913</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 16.482x + -8637.507</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-8637.506802509282</v>
       </c>
       <c r="Y14" t="n">
         <v>439.0523805817506</v>
       </c>
       <c r="Z14" t="n">
-        <v>92283929.4686774</v>
+        <v>85.71799999999996</v>
       </c>
       <c r="AA14" t="n">
         <v>1.634271659427536e-06</v>
@@ -1930,19 +1930,19 @@
       <c r="K15" t="n">
         <v>86.31645639209579</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 15.533x + -8033.736</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-8033.735733587318</v>
       </c>
       <c r="Y15" t="n">
         <v>435.8882484891935</v>
       </c>
       <c r="Z15" t="n">
-        <v>104529149.8862714</v>
+        <v>87.33100000000002</v>
       </c>
       <c r="AA15" t="n">
         <v>1.574501842928551e-06</v>
@@ -1982,19 +1982,19 @@
       <c r="K16" t="n">
         <v>86.39821187978183</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 15.887x + -8154.108</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-8154.107755845124</v>
       </c>
       <c r="Y16" t="n">
         <v>432.6607238217108</v>
       </c>
       <c r="Z16" t="n">
-        <v>274297734.1155606</v>
+        <v>85.70400000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.520942983810344e-06</v>
@@ -2034,19 +2034,19 @@
       <c r="K17" t="n">
         <v>86.4205715568302</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 15.986x + -8133.900</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-8133.899800027603</v>
       </c>
       <c r="Y17" t="n">
         <v>429.3165494262582</v>
       </c>
       <c r="Z17" t="n">
-        <v>203934586.1922266</v>
+        <v>84.77199999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.474302652004281e-06</v>
@@ -2086,19 +2086,19 @@
       <c r="K18" t="n">
         <v>86.58516089805744</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 16.759x + -8471.952</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-8471.952024295244</v>
       </c>
       <c r="Y18" t="n">
         <v>425.9215493809027</v>
       </c>
       <c r="Z18" t="n">
-        <v>21183066.55456443</v>
+        <v>82.55399999999997</v>
       </c>
       <c r="AA18" t="n">
         <v>1.427282840713248e-06</v>
@@ -2138,19 +2138,19 @@
       <c r="K19" t="n">
         <v>86.54973313037205</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 16.586x + -8294.413</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-8294.412934411361</v>
       </c>
       <c r="Y19" t="n">
         <v>422.3230347670413</v>
       </c>
       <c r="Z19" t="n">
-        <v>56607783.77640617</v>
+        <v>81.09499999999997</v>
       </c>
       <c r="AA19" t="n">
         <v>1.388197784125901e-06</v>
@@ -2190,19 +2190,19 @@
       <c r="K20" t="n">
         <v>86.39231169106921</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 15.861x + -7830.255</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-7830.255058443125</v>
       </c>
       <c r="Y20" t="n">
         <v>418.7695825234975</v>
       </c>
       <c r="Z20" t="n">
-        <v>250972891.4649639</v>
+        <v>82.12599999999998</v>
       </c>
       <c r="AA20" t="n">
         <v>1.350049975723018e-06</v>
@@ -2242,19 +2242,19 @@
       <c r="K21" t="n">
         <v>86.61496854372025</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 16.907x + -8297.646</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-8297.645628534941</v>
       </c>
       <c r="Y21" t="n">
         <v>415.3545860070256</v>
       </c>
       <c r="Z21" t="n">
-        <v>34236904.45462151</v>
+        <v>78.28100000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.312118988587916e-06</v>
@@ -2294,19 +2294,19 @@
       <c r="K22" t="n">
         <v>86.50872653162848</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 16.391x + -7948.454</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7948.453721050384</v>
       </c>
       <c r="Y22" t="n">
         <v>411.8290656418306</v>
       </c>
       <c r="Z22" t="n">
-        <v>128691416.7346684</v>
+        <v>79.52400000000006</v>
       </c>
       <c r="AA22" t="n">
         <v>1.281866695430897e-06</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2492,19 +2492,19 @@
       <c r="K2" t="n">
         <v>85.3953647282212</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.416x + -7840.930</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7840.929782597505</v>
       </c>
       <c r="Y2" t="n">
         <v>434.9999257535136</v>
       </c>
       <c r="Z2" t="n">
-        <v>344819230.5409263</v>
+        <v>154.9829999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.616787432361747e-05</v>
@@ -2544,19 +2544,19 @@
       <c r="K3" t="n">
         <v>85.74484201939346</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.440x + -8066.219</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8066.219127042919</v>
       </c>
       <c r="Y3" t="n">
         <v>423.8370143989371</v>
       </c>
       <c r="Z3" t="n">
-        <v>547836927.5268921</v>
+        <v>127.0749999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.656265994921808e-05</v>
@@ -2596,19 +2596,19 @@
       <c r="K4" t="n">
         <v>86.21932323919702</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 15.133x + -8984.526</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8984.526394492035</v>
       </c>
       <c r="Y4" t="n">
         <v>418.7714804008791</v>
       </c>
       <c r="Z4" t="n">
-        <v>275201067.4412613</v>
+        <v>113.0509999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.669982950005685e-05</v>
@@ -2648,19 +2648,19 @@
       <c r="K5" t="n">
         <v>85.94346905743005</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.101x + -8216.206</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8216.205625040062</v>
       </c>
       <c r="Y5" t="n">
         <v>433.5745037809186</v>
       </c>
       <c r="Z5" t="n">
-        <v>1377337842.410501</v>
+        <v>110.6909999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.144539877366335e-05</v>
@@ -2700,19 +2700,19 @@
       <c r="K6" t="n">
         <v>86.23399469050551</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.192x + -8778.693</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8778.693107569165</v>
       </c>
       <c r="Y6" t="n">
         <v>459.553311242398</v>
       </c>
       <c r="Z6" t="n">
-        <v>1882194165.19316</v>
+        <v>103.889</v>
       </c>
       <c r="AA6" t="n">
         <v>4.755623996886845e-06</v>
@@ -2752,19 +2752,19 @@
       <c r="K7" t="n">
         <v>86.51320910630089</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.412x + -9402.658</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9402.657814577398</v>
       </c>
       <c r="Y7" t="n">
         <v>457.9437873575273</v>
       </c>
       <c r="Z7" t="n">
-        <v>395560895.6460473</v>
+        <v>97.91399999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>4.072688346032543e-06</v>
@@ -2804,19 +2804,19 @@
       <c r="K8" t="n">
         <v>86.55911649603661</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.631x + -9405.307</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-9405.307126144153</v>
       </c>
       <c r="Y8" t="n">
         <v>459.4159812941938</v>
       </c>
       <c r="Z8" t="n">
-        <v>119775122.0151341</v>
+        <v>94.75800000000004</v>
       </c>
       <c r="AA8" t="n">
         <v>2.880674451816313e-06</v>
@@ -2856,19 +2856,19 @@
       <c r="K9" t="n">
         <v>86.07449723841992</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.573x + -8063.108</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8063.108053185911</v>
       </c>
       <c r="Y9" t="n">
         <v>458.4407398337984</v>
       </c>
       <c r="Z9" t="n">
-        <v>2050759825.418768</v>
+        <v>96.32500000000005</v>
       </c>
       <c r="AA9" t="n">
         <v>2.218387483515646e-06</v>
@@ -2908,19 +2908,19 @@
       <c r="K10" t="n">
         <v>86.36674037246492</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.749x + -8648.108</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8648.107996158215</v>
       </c>
       <c r="Y10" t="n">
         <v>454.1219036357127</v>
       </c>
       <c r="Z10" t="n">
-        <v>117072889.9099261</v>
+        <v>92.19000000000005</v>
       </c>
       <c r="AA10" t="n">
         <v>2.131163266566401e-06</v>
@@ -2960,19 +2960,19 @@
       <c r="K11" t="n">
         <v>86.56369146988662</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 16.654x + -9064.751</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-9064.751095793868</v>
       </c>
       <c r="Y11" t="n">
         <v>450.8553170662203</v>
       </c>
       <c r="Z11" t="n">
-        <v>154554559.0861521</v>
+        <v>88.60199999999998</v>
       </c>
       <c r="AA11" t="n">
         <v>1.912314105095442e-06</v>
@@ -3012,19 +3012,19 @@
       <c r="K12" t="n">
         <v>86.68660525809</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 17.273x + -9312.488</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9312.487903245348</v>
       </c>
       <c r="Y12" t="n">
         <v>447.5941925583273</v>
       </c>
       <c r="Z12" t="n">
-        <v>177427477.6973688</v>
+        <v>84.38499999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.725781819813984e-06</v>
@@ -3064,19 +3064,19 @@
       <c r="K13" t="n">
         <v>86.622170643838</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 16.943x + -9025.273</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-9025.273366936073</v>
       </c>
       <c r="Y13" t="n">
         <v>443.8448988552323</v>
       </c>
       <c r="Z13" t="n">
-        <v>342020752.9353812</v>
+        <v>82.84299999999996</v>
       </c>
       <c r="AA13" t="n">
         <v>1.63263793774982e-06</v>
@@ -3116,19 +3116,19 @@
       <c r="K14" t="n">
         <v>86.4417932709521</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 16.082x + -8441.386</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-8441.386468294138</v>
       </c>
       <c r="Y14" t="n">
         <v>440.0494036026332</v>
       </c>
       <c r="Z14" t="n">
-        <v>159184895.4359874</v>
+        <v>84.62100000000009</v>
       </c>
       <c r="AA14" t="n">
         <v>1.555567234494001e-06</v>
@@ -3168,19 +3168,19 @@
       <c r="K15" t="n">
         <v>86.44160452250371</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 16.081x + -8347.667</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-8347.666635147394</v>
       </c>
       <c r="Y15" t="n">
         <v>436.3822431930071</v>
       </c>
       <c r="Z15" t="n">
-        <v>470354012.4058977</v>
+        <v>83.94100000000003</v>
       </c>
       <c r="AA15" t="n">
         <v>1.492046342755361e-06</v>
@@ -3220,19 +3220,19 @@
       <c r="K16" t="n">
         <v>86.72236432383686</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 17.462x + -9018.367</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-9018.367276180637</v>
       </c>
       <c r="Y16" t="n">
         <v>432.7070547697845</v>
       </c>
       <c r="Z16" t="n">
-        <v>163013896.3609696</v>
+        <v>78.07400000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.430512162143117e-06</v>
@@ -3272,19 +3272,19 @@
       <c r="K17" t="n">
         <v>86.41701922497259</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 15.970x + -8112.332</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-8112.331798445049</v>
       </c>
       <c r="Y17" t="n">
         <v>428.928766008439</v>
       </c>
       <c r="Z17" t="n">
-        <v>76658901.32251114</v>
+        <v>81.77199999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.386613082874812e-06</v>
@@ -3324,19 +3324,19 @@
       <c r="K18" t="n">
         <v>86.28313144161756</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 15.393x + -7723.155</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-7723.155358266668</v>
       </c>
       <c r="Y18" t="n">
         <v>425.2764764867915</v>
       </c>
       <c r="Z18" t="n">
-        <v>155317345.4695542</v>
+        <v>81.60999999999996</v>
       </c>
       <c r="AA18" t="n">
         <v>1.344374033453632e-06</v>
@@ -3376,19 +3376,19 @@
       <c r="K19" t="n">
         <v>86.40867727258967</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 15.933x + -7925.510</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-7925.510388842446</v>
       </c>
       <c r="Y19" t="n">
         <v>421.6229672675877</v>
       </c>
       <c r="Z19" t="n">
-        <v>135787529.6473996</v>
+        <v>78.74700000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>1.301976943813317e-06</v>
@@ -3428,19 +3428,19 @@
       <c r="K20" t="n">
         <v>86.51583409920414</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 16.424x + -8100.256</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-8100.256490752301</v>
       </c>
       <c r="Y20" t="n">
         <v>418.0042884196412</v>
       </c>
       <c r="Z20" t="n">
-        <v>93515649.87172209</v>
+        <v>77.13200000000006</v>
       </c>
       <c r="AA20" t="n">
         <v>1.266278368072416e-06</v>
@@ -3480,19 +3480,19 @@
       <c r="K21" t="n">
         <v>86.38509718954563</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 15.829x + -7709.902</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-7709.902032735014</v>
       </c>
       <c r="Y21" t="n">
         <v>414.4162369724249</v>
       </c>
       <c r="Z21" t="n">
-        <v>98336831.56401308</v>
+        <v>76.80700000000007</v>
       </c>
       <c r="AA21" t="n">
         <v>1.232749848994821e-06</v>
@@ -3532,19 +3532,19 @@
       <c r="K22" t="n">
         <v>86.64470537406686</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 17.057x + -8259.885</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-8259.885288528591</v>
       </c>
       <c r="Y22" t="n">
         <v>410.8905802376653</v>
       </c>
       <c r="Z22" t="n">
-        <v>35631955.4182388</v>
+        <v>73.47200000000004</v>
       </c>
       <c r="AA22" t="n">
         <v>1.203224322856655e-06</v>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -3730,19 +3730,19 @@
       <c r="K2" t="n">
         <v>85.34901167197908</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.292x + -8200.374</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8200.373625341766</v>
       </c>
       <c r="Y2" t="n">
         <v>441.2503204854718</v>
       </c>
       <c r="Z2" t="n">
-        <v>453307118.7463925</v>
+        <v>148.436</v>
       </c>
       <c r="AA2" t="n">
         <v>1.523184793402742e-05</v>
@@ -3782,19 +3782,19 @@
       <c r="K3" t="n">
         <v>86.28775760729498</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.413x + -9107.588</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9107.587728673427</v>
       </c>
       <c r="Y3" t="n">
         <v>476.6023147017011</v>
       </c>
       <c r="Z3" t="n">
-        <v>227347529.4133855</v>
+        <v>113.721</v>
       </c>
       <c r="AA3" t="n">
         <v>2.826787225294773e-06</v>
@@ -3834,19 +3834,19 @@
       <c r="K4" t="n">
         <v>86.29597584401212</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 15.447x + -8814.496</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8814.495803533349</v>
       </c>
       <c r="Y4" t="n">
         <v>474.03694661931</v>
       </c>
       <c r="Z4" t="n">
-        <v>128656884.9781878</v>
+        <v>105.9749999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.766313256740211e-06</v>
@@ -3886,19 +3886,19 @@
       <c r="K5" t="n">
         <v>86.61836106409478</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.924x + -9534.063</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9534.062981448962</v>
       </c>
       <c r="Y5" t="n">
         <v>469.0849278976439</v>
       </c>
       <c r="Z5" t="n">
-        <v>238714322.3381775</v>
+        <v>99.35599999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.546279619244071e-06</v>
@@ -3938,19 +3938,19 @@
       <c r="K6" t="n">
         <v>86.41644623323495</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.968x + -8820.971</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8820.971473368434</v>
       </c>
       <c r="Y6" t="n">
         <v>464.0618202839452</v>
       </c>
       <c r="Z6" t="n">
-        <v>266449676.4856685</v>
+        <v>99.18700000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.416616707267517e-06</v>
@@ -3990,19 +3990,19 @@
       <c r="K7" t="n">
         <v>86.46781189788122</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.200x + -8822.491</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8822.49052332835</v>
       </c>
       <c r="Y7" t="n">
         <v>458.8129218312916</v>
       </c>
       <c r="Z7" t="n">
-        <v>29108738.45743059</v>
+        <v>96.51100000000008</v>
       </c>
       <c r="AA7" t="n">
         <v>1.323451476185574e-06</v>
@@ -4042,19 +4042,19 @@
       <c r="K8" t="n">
         <v>86.51486193447968</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.420x + -8812.922</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8812.921887403612</v>
       </c>
       <c r="Y8" t="n">
         <v>453.1626101977044</v>
       </c>
       <c r="Z8" t="n">
-        <v>179414853.6158305</v>
+        <v>96.16399999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.25404088657733e-06</v>
@@ -4094,19 +4094,19 @@
       <c r="K9" t="n">
         <v>86.51034475496964</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 16.398x + -8660.449</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8660.448950401082</v>
       </c>
       <c r="Y9" t="n">
         <v>447.4505321666326</v>
       </c>
       <c r="Z9" t="n">
-        <v>82895946.05834448</v>
+        <v>94.30100000000004</v>
       </c>
       <c r="AA9" t="n">
         <v>1.191766518712591e-06</v>
@@ -4146,19 +4146,19 @@
       <c r="K10" t="n">
         <v>86.59874183786719</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 16.826x + -8761.127</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8761.127318496159</v>
       </c>
       <c r="Y10" t="n">
         <v>441.9769639623128</v>
       </c>
       <c r="Z10" t="n">
-        <v>114951946.6660604</v>
+        <v>93.14399999999995</v>
       </c>
       <c r="AA10" t="n">
         <v>1.14075280656471e-06</v>
@@ -4198,19 +4198,19 @@
       <c r="K11" t="n">
         <v>86.70715520511527</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 17.381x + -8935.365</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8935.364647830273</v>
       </c>
       <c r="Y11" t="n">
         <v>436.7184993165156</v>
       </c>
       <c r="Z11" t="n">
-        <v>75285427.38131291</v>
+        <v>91.59100000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.100065549795278e-06</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4396,19 +4396,19 @@
       <c r="K2" t="n">
         <v>86.09884029082536</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.664x + -9168.045</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-9168.045261675268</v>
       </c>
       <c r="Y2" t="n">
         <v>444.1272595847075</v>
       </c>
       <c r="Z2" t="n">
-        <v>108864793.1901087</v>
+        <v>107.129</v>
       </c>
       <c r="AA2" t="n">
         <v>1.23384089549512e-05</v>
@@ -4448,19 +4448,19 @@
       <c r="K3" t="n">
         <v>86.44781561778335</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.109x + -9613.249</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9613.249141578935</v>
       </c>
       <c r="Y3" t="n">
         <v>483.8378742692371</v>
       </c>
       <c r="Z3" t="n">
-        <v>96173839.7698317</v>
+        <v>93.601</v>
       </c>
       <c r="AA3" t="n">
         <v>2.809131246282537e-06</v>
@@ -4500,19 +4500,19 @@
       <c r="K4" t="n">
         <v>86.31932891105524</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 15.545x + -9084.446</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9084.445695273294</v>
       </c>
       <c r="Y4" t="n">
         <v>481.9175302628286</v>
       </c>
       <c r="Z4" t="n">
-        <v>434126598.6003155</v>
+        <v>92.25099999999998</v>
       </c>
       <c r="AA4" t="n">
         <v>2.27596436351776e-06</v>
@@ -4552,19 +4552,19 @@
       <c r="K5" t="n">
         <v>86.58067505465303</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.737x + -9693.610</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9693.609583300185</v>
       </c>
       <c r="Y5" t="n">
         <v>480.7478539399942</v>
       </c>
       <c r="Z5" t="n">
-        <v>394980255.859816</v>
+        <v>89.05499999999995</v>
       </c>
       <c r="AA5" t="n">
         <v>1.738300323053375e-06</v>
@@ -4604,19 +4604,19 @@
       <c r="K6" t="n">
         <v>86.46714595864923</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.197x + -9243.748</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9243.747570538677</v>
       </c>
       <c r="Y6" t="n">
         <v>476.4086466037708</v>
       </c>
       <c r="Z6" t="n">
-        <v>448482705.571925</v>
+        <v>88.66300000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.610043817204512e-06</v>
@@ -4656,19 +4656,19 @@
       <c r="K7" t="n">
         <v>86.38348824761647</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 15.822x + -8893.081</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8893.081304166333</v>
       </c>
       <c r="Y7" t="n">
         <v>471.7079776354223</v>
       </c>
       <c r="Z7" t="n">
-        <v>33836282.58977511</v>
+        <v>88.54200000000003</v>
       </c>
       <c r="AA7" t="n">
         <v>1.508835727844292e-06</v>
@@ -4708,19 +4708,19 @@
       <c r="K8" t="n">
         <v>86.46683111339421</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.196x + -8995.915</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8995.914981161315</v>
       </c>
       <c r="Y8" t="n">
         <v>466.9010668586121</v>
       </c>
       <c r="Z8" t="n">
-        <v>252841154.3298536</v>
+        <v>85.83799999999997</v>
       </c>
       <c r="AA8" t="n">
         <v>1.429287957105137e-06</v>
@@ -4760,19 +4760,19 @@
       <c r="K9" t="n">
         <v>86.58083054750514</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 16.737x + -9195.304</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-9195.303952956188</v>
       </c>
       <c r="Y9" t="n">
         <v>462.2085125306908</v>
       </c>
       <c r="Z9" t="n">
-        <v>150849216.6590624</v>
+        <v>82.87699999999995</v>
       </c>
       <c r="AA9" t="n">
         <v>1.365786026408263e-06</v>
@@ -4812,19 +4812,19 @@
       <c r="K10" t="n">
         <v>86.47075669293118</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 16.214x + -8779.878</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8779.878118726585</v>
       </c>
       <c r="Y10" t="n">
         <v>457.7292824094559</v>
       </c>
       <c r="Z10" t="n">
-        <v>59808375.2467428</v>
+        <v>84.09299999999996</v>
       </c>
       <c r="AA10" t="n">
         <v>1.312195813450152e-06</v>
@@ -4864,19 +4864,19 @@
       <c r="K11" t="n">
         <v>86.52072046388218</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 16.447x + -8809.539</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8809.539496702904</v>
       </c>
       <c r="Y11" t="n">
         <v>453.4089835910032</v>
       </c>
       <c r="Z11" t="n">
-        <v>59504330.46251216</v>
+        <v>82.20100000000002</v>
       </c>
       <c r="AA11" t="n">
         <v>1.266543799497662e-06</v>
@@ -4916,19 +4916,19 @@
       <c r="K12" t="n">
         <v>86.68044798971584</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 17.241x + -9158.798</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-9158.797661151497</v>
       </c>
       <c r="Y12" t="n">
         <v>449.3128788115454</v>
       </c>
       <c r="Z12" t="n">
-        <v>58519160.6841563</v>
+        <v>80.21000000000004</v>
       </c>
       <c r="AA12" t="n">
         <v>1.228846453558306e-06</v>
@@ -4968,19 +4968,19 @@
       <c r="K13" t="n">
         <v>86.59022587957202</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 16.784x + -8804.543</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-8804.542669663158</v>
       </c>
       <c r="Y13" t="n">
         <v>445.3372836648231</v>
       </c>
       <c r="Z13" t="n">
-        <v>176529882.1420476</v>
+        <v>80.28700000000003</v>
       </c>
       <c r="AA13" t="n">
         <v>1.196660354521983e-06</v>
@@ -5020,19 +5020,19 @@
       <c r="K14" t="n">
         <v>86.56760377659262</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 16.673x + -8648.770</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-8648.770055613191</v>
       </c>
       <c r="Y14" t="n">
         <v>441.4633788509963</v>
       </c>
       <c r="Z14" t="n">
-        <v>32229912.12559871</v>
+        <v>80.30300000000005</v>
       </c>
       <c r="AA14" t="n">
         <v>1.167379872379136e-06</v>
@@ -5072,19 +5072,19 @@
       <c r="K15" t="n">
         <v>86.66078674449373</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 17.139x + -8816.128</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-8816.128156542951</v>
       </c>
       <c r="Y15" t="n">
         <v>437.6124367348919</v>
       </c>
       <c r="Z15" t="n">
-        <v>217606140.6536585</v>
+        <v>79.08799999999997</v>
       </c>
       <c r="AA15" t="n">
         <v>1.142694722031057e-06</v>
@@ -5124,19 +5124,19 @@
       <c r="K16" t="n">
         <v>86.6944385266701</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 17.314x + -8819.790</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-8819.790180277078</v>
       </c>
       <c r="Y16" t="n">
         <v>433.8524003031019</v>
       </c>
       <c r="Z16" t="n">
-        <v>36112145.07855842</v>
+        <v>78.62199999999996</v>
       </c>
       <c r="AA16" t="n">
         <v>1.117052348485922e-06</v>
@@ -5176,19 +5176,19 @@
       <c r="K17" t="n">
         <v>86.77865078601785</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 17.768x + -8974.515</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-8974.515075371071</v>
       </c>
       <c r="Y17" t="n">
         <v>430.0687681233816</v>
       </c>
       <c r="Z17" t="n">
-        <v>469549170.1307999</v>
+        <v>76.26300000000003</v>
       </c>
       <c r="AA17" t="n">
         <v>1.094444907575688e-06</v>
@@ -5228,19 +5228,19 @@
       <c r="K18" t="n">
         <v>86.42938387225492</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 16.026x + -7959.370</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-7959.370109641281</v>
       </c>
       <c r="Y18" t="n">
         <v>426.3236654765057</v>
       </c>
       <c r="Z18" t="n">
-        <v>48188148.78191241</v>
+        <v>78.697</v>
       </c>
       <c r="AA18" t="n">
         <v>1.070764944305307e-06</v>
@@ -5280,19 +5280,19 @@
       <c r="K19" t="n">
         <v>86.69524674808845</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 17.318x + -8556.045</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-8556.044908255646</v>
       </c>
       <c r="Y19" t="n">
         <v>422.6080774865547</v>
       </c>
       <c r="Z19" t="n">
-        <v>30729510.39641538</v>
+        <v>75.11499999999995</v>
       </c>
       <c r="AA19" t="n">
         <v>1.050392275350101e-06</v>
@@ -5332,19 +5332,19 @@
       <c r="K20" t="n">
         <v>86.80687561158989</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 17.925x + -8782.754</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-8782.753613832549</v>
       </c>
       <c r="Y20" t="n">
         <v>418.8492119872903</v>
       </c>
       <c r="Z20" t="n">
-        <v>99699177.8356974</v>
+        <v>74.31799999999998</v>
       </c>
       <c r="AA20" t="n">
         <v>1.033104798877223e-06</v>
@@ -5384,19 +5384,19 @@
       <c r="K21" t="n">
         <v>86.76109712077208</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 17.671x + -8563.081</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-8563.08091120807</v>
       </c>
       <c r="Y21" t="n">
         <v>415.0822496434679</v>
       </c>
       <c r="Z21" t="n">
-        <v>189549326.6332638</v>
+        <v>74.33799999999997</v>
       </c>
       <c r="AA21" t="n">
         <v>1.016993736638098e-06</v>
@@ -5436,19 +5436,19 @@
       <c r="K22" t="n">
         <v>86.5844236207531</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 16.755x + -8009.531</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-8009.531316887499</v>
       </c>
       <c r="Y22" t="n">
         <v>411.336132300142</v>
       </c>
       <c r="Z22" t="n">
-        <v>274160802.661543</v>
+        <v>74.12699999999995</v>
       </c>
       <c r="AA22" t="n">
         <v>9.982190114390554e-07</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5634,19 +5634,19 @@
       <c r="K2" t="n">
         <v>84.66028256898838</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.699x + -7302.502</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7302.501598697544</v>
       </c>
       <c r="Y2" t="n">
         <v>448.0868660230072</v>
       </c>
       <c r="Z2" t="n">
-        <v>432120763.4442663</v>
+        <v>201.391</v>
       </c>
       <c r="AA2" t="n">
         <v>1.524193114130107e-05</v>
@@ -5686,19 +5686,19 @@
       <c r="K3" t="n">
         <v>85.72490414119909</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.377x + -7870.420</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7870.419776766566</v>
       </c>
       <c r="Y3" t="n">
         <v>458.0576473385265</v>
       </c>
       <c r="Z3" t="n">
-        <v>1535254073.316125</v>
+        <v>150.1640000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>6.600865462276436e-06</v>
@@ -5738,19 +5738,19 @@
       <c r="K4" t="n">
         <v>85.87143116814933</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.854x + -7842.512</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7842.511579781048</v>
       </c>
       <c r="Y4" t="n">
         <v>469.9161833437443</v>
       </c>
       <c r="Z4" t="n">
-        <v>426543626.2747911</v>
+        <v>135.5309999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>2.583984295924121e-06</v>
@@ -5790,19 +5790,19 @@
       <c r="K5" t="n">
         <v>86.31820763514392</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.541x + -8701.710</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8701.709860191046</v>
       </c>
       <c r="Y5" t="n">
         <v>467.1531956187354</v>
       </c>
       <c r="Z5" t="n">
-        <v>384295557.1347258</v>
+        <v>124.5509999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>2.041696351356739e-06</v>
@@ -5842,19 +5842,19 @@
       <c r="K6" t="n">
         <v>86.13165010017671</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.789x + -8118.922</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8118.921871447683</v>
       </c>
       <c r="Y6" t="n">
         <v>463.0916462350833</v>
       </c>
       <c r="Z6" t="n">
-        <v>566243428.233409</v>
+        <v>121.155</v>
       </c>
       <c r="AA6" t="n">
         <v>1.78246445523967e-06</v>
@@ -5894,19 +5894,19 @@
       <c r="K7" t="n">
         <v>86.44123434496925</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.079x + -8744.575</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8744.574638608035</v>
       </c>
       <c r="Y7" t="n">
         <v>458.155366719374</v>
       </c>
       <c r="Z7" t="n">
-        <v>335321526.4706919</v>
+        <v>114.4739999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.619416189556971e-06</v>
@@ -5946,19 +5946,19 @@
       <c r="K8" t="n">
         <v>86.29102253757358</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 15.426x + -8232.455</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8232.455344380243</v>
       </c>
       <c r="Y8" t="n">
         <v>453.0897904582574</v>
       </c>
       <c r="Z8" t="n">
-        <v>201694822.5567918</v>
+        <v>113.3599999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.496395515594004e-06</v>
@@ -5998,19 +5998,19 @@
       <c r="K9" t="n">
         <v>86.53411292493462</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 16.511x + -8721.625</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8721.625051795852</v>
       </c>
       <c r="Y9" t="n">
         <v>447.9884789038092</v>
       </c>
       <c r="Z9" t="n">
-        <v>206934293.3790737</v>
+        <v>106.962</v>
       </c>
       <c r="AA9" t="n">
         <v>1.404995852608527e-06</v>
@@ -6050,19 +6050,19 @@
       <c r="K10" t="n">
         <v>86.42366930959109</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 16.000x + -8311.734</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8311.733703603246</v>
       </c>
       <c r="Y10" t="n">
         <v>443.0473409330044</v>
       </c>
       <c r="Z10" t="n">
-        <v>240801249.3798047</v>
+        <v>105.9420000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.334299345676491e-06</v>
@@ -6102,19 +6102,19 @@
       <c r="K11" t="n">
         <v>86.47190368232027</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 16.219x + -8319.006</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8319.005571557916</v>
       </c>
       <c r="Y11" t="n">
         <v>438.4193282355079</v>
       </c>
       <c r="Z11" t="n">
-        <v>25806229.035969</v>
+        <v>104.413</v>
       </c>
       <c r="AA11" t="n">
         <v>1.278349313536701e-06</v>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6300,19 +6300,19 @@
       <c r="K2" t="n">
         <v>86.03281935299277</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.419x + -8998.038</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8998.037819848076</v>
       </c>
       <c r="Y2" t="n">
         <v>428.8948341124835</v>
       </c>
       <c r="Z2" t="n">
-        <v>281385923.9833325</v>
+        <v>127.0940000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.59815863015575e-05</v>
@@ -6352,19 +6352,19 @@
       <c r="K3" t="n">
         <v>85.86164679763668</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.821x + -8186.698</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8186.697565978693</v>
       </c>
       <c r="Y3" t="n">
         <v>432.850749027939</v>
       </c>
       <c r="Z3" t="n">
-        <v>1242917534.074502</v>
+        <v>114.9109999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.266007038497087e-05</v>
@@ -6404,19 +6404,19 @@
       <c r="K4" t="n">
         <v>86.19508813400054</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 15.036x + -8805.343</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8805.342610140813</v>
       </c>
       <c r="Y4" t="n">
         <v>467.1079398612561</v>
       </c>
       <c r="Z4" t="n">
-        <v>2385939196.343543</v>
+        <v>105.343</v>
       </c>
       <c r="AA4" t="n">
         <v>4.385364504891636e-06</v>
@@ -6456,19 +6456,19 @@
       <c r="K5" t="n">
         <v>86.40674426826318</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.924x + -9242.404</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9242.403888453036</v>
       </c>
       <c r="Y5" t="n">
         <v>462.8740630068066</v>
       </c>
       <c r="Z5" t="n">
-        <v>434719763.9625528</v>
+        <v>99.14700000000005</v>
       </c>
       <c r="AA5" t="n">
         <v>4.149164943798226e-06</v>
@@ -6508,19 +6508,19 @@
       <c r="K6" t="n">
         <v>86.1408049396007</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.824x + -8456.182</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8456.181561102565</v>
       </c>
       <c r="Y6" t="n">
         <v>467.6597870742491</v>
       </c>
       <c r="Z6" t="n">
-        <v>340266557.6764494</v>
+        <v>99.7890000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>2.653407641557734e-06</v>
@@ -6560,19 +6560,19 @@
       <c r="K7" t="n">
         <v>86.40851752037459</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 15.932x + -9008.677</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9008.67653005546</v>
       </c>
       <c r="Y7" t="n">
         <v>465.6648062293336</v>
       </c>
       <c r="Z7" t="n">
-        <v>660870073.005559</v>
+        <v>94.78200000000004</v>
       </c>
       <c r="AA7" t="n">
         <v>2.122843238729958e-06</v>
@@ -6612,19 +6612,19 @@
       <c r="K8" t="n">
         <v>86.43720129708646</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.061x + -8959.764</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8959.763870917543</v>
       </c>
       <c r="Y8" t="n">
         <v>460.5572545164216</v>
       </c>
       <c r="Z8" t="n">
-        <v>59335483.17586935</v>
+        <v>91.81600000000003</v>
       </c>
       <c r="AA8" t="n">
         <v>2.041024618743799e-06</v>
@@ -6664,19 +6664,19 @@
       <c r="K9" t="n">
         <v>86.28508447384245</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 15.402x + -8452.194</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8452.194266275221</v>
       </c>
       <c r="Y9" t="n">
         <v>456.4816585955455</v>
       </c>
       <c r="Z9" t="n">
-        <v>31268812.87347665</v>
+        <v>92.38999999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.865979968654931e-06</v>
@@ -6716,19 +6716,19 @@
       <c r="K10" t="n">
         <v>86.32324995252912</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.562x + -8434.849</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8434.84913626253</v>
       </c>
       <c r="Y10" t="n">
         <v>453.0450447735507</v>
       </c>
       <c r="Z10" t="n">
-        <v>331677476.4595311</v>
+        <v>90.57899999999995</v>
       </c>
       <c r="AA10" t="n">
         <v>1.643433532120073e-06</v>
@@ -6768,19 +6768,19 @@
       <c r="K11" t="n">
         <v>86.48826426941312</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 16.295x + -8755.167</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8755.166632520968</v>
       </c>
       <c r="Y11" t="n">
         <v>448.9862634315634</v>
       </c>
       <c r="Z11" t="n">
-        <v>46571901.01023883</v>
+        <v>87.71500000000003</v>
       </c>
       <c r="AA11" t="n">
         <v>1.555444941424885e-06</v>
@@ -6820,19 +6820,19 @@
       <c r="K12" t="n">
         <v>86.602996634245</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 16.847x + -8967.317</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-8967.316715429086</v>
       </c>
       <c r="Y12" t="n">
         <v>445.0313496302306</v>
       </c>
       <c r="Z12" t="n">
-        <v>221089791.1095856</v>
+        <v>84.66300000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>1.484715450195128e-06</v>
@@ -6872,19 +6872,19 @@
       <c r="K13" t="n">
         <v>86.71849331651104</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 17.441x + -9203.161</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-9203.16118004487</v>
       </c>
       <c r="Y13" t="n">
         <v>441.2023387667601</v>
       </c>
       <c r="Z13" t="n">
-        <v>101486988.0634213</v>
+        <v>82.99200000000008</v>
       </c>
       <c r="AA13" t="n">
         <v>1.42824167874795e-06</v>
@@ -6924,19 +6924,19 @@
       <c r="K14" t="n">
         <v>86.29088641881872</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 15.426x + -7986.190</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-7986.190497144414</v>
       </c>
       <c r="Y14" t="n">
         <v>437.4715723862098</v>
       </c>
       <c r="Z14" t="n">
-        <v>57449690.51259881</v>
+        <v>86.49799999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>1.379727520644663e-06</v>
@@ -6976,19 +6976,19 @@
       <c r="K15" t="n">
         <v>86.50371673617262</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 16.367x + -8419.750</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-8419.750097659607</v>
       </c>
       <c r="Y15" t="n">
         <v>433.8090666612601</v>
       </c>
       <c r="Z15" t="n">
-        <v>200800953.828605</v>
+        <v>82.43700000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.333391361176151e-06</v>
@@ -7028,19 +7028,19 @@
       <c r="K16" t="n">
         <v>86.42903280883154</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 16.024x + -8153.537</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-8153.537225727913</v>
       </c>
       <c r="Y16" t="n">
         <v>430.2380017060291</v>
       </c>
       <c r="Z16" t="n">
-        <v>39389064.77154506</v>
+        <v>81.62900000000002</v>
       </c>
       <c r="AA16" t="n">
         <v>1.293232785149028e-06</v>
@@ -7080,19 +7080,19 @@
       <c r="K17" t="n">
         <v>86.54830245463963</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 16.579x + -8367.410</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-8367.410371942011</v>
       </c>
       <c r="Y17" t="n">
         <v>426.6129276690558</v>
       </c>
       <c r="Z17" t="n">
-        <v>65467756.19810615</v>
+        <v>80.48099999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.261495630592835e-06</v>
@@ -7132,19 +7132,19 @@
       <c r="K18" t="n">
         <v>86.58297226724598</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 16.748x + -8372.142</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-8372.141872889862</v>
       </c>
       <c r="Y18" t="n">
         <v>422.9245303454863</v>
       </c>
       <c r="Z18" t="n">
-        <v>167261841.6995843</v>
+        <v>78.85100000000006</v>
       </c>
       <c r="AA18" t="n">
         <v>1.230586387078175e-06</v>
@@ -7184,19 +7184,19 @@
       <c r="K19" t="n">
         <v>86.76825808540362</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 17.710x + -8793.047</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-8793.046607036948</v>
       </c>
       <c r="Y19" t="n">
         <v>419.3080136373871</v>
       </c>
       <c r="Z19" t="n">
-        <v>62055996.3369637</v>
+        <v>75.75599999999997</v>
       </c>
       <c r="AA19" t="n">
         <v>1.197927246364865e-06</v>
@@ -7236,19 +7236,19 @@
       <c r="K20" t="n">
         <v>86.51465982914073</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 16.419x + -8030.453</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-8030.453118528424</v>
       </c>
       <c r="Y20" t="n">
         <v>415.5416941202325</v>
       </c>
       <c r="Z20" t="n">
-        <v>73608840.73400299</v>
+        <v>77.63899999999995</v>
       </c>
       <c r="AA20" t="n">
         <v>1.173842519935232e-06</v>
@@ -7288,19 +7288,19 @@
       <c r="K21" t="n">
         <v>86.54094038033492</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 16.544x + -8010.580</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-8010.580184951246</v>
       </c>
       <c r="Y21" t="n">
         <v>411.0599239163823</v>
       </c>
       <c r="Z21" t="n">
-        <v>106111814.6856551</v>
+        <v>76.26400000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.149276738290599e-06</v>
@@ -7340,19 +7340,19 @@
       <c r="K22" t="n">
         <v>86.47140388244669</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 16.217x + -7761.131</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7761.130699727876</v>
       </c>
       <c r="Y22" t="n">
         <v>407.4459078658471</v>
       </c>
       <c r="Z22" t="n">
-        <v>51632562.71932381</v>
+        <v>76.65400000000005</v>
       </c>
       <c r="AA22" t="n">
         <v>1.1268057007435e-06</v>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7538,19 +7538,19 @@
       <c r="K2" t="n">
         <v>84.29324554001242</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.007x + -6504.175</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6504.174744469758</v>
       </c>
       <c r="Y2" t="n">
         <v>431.3802792910544</v>
       </c>
       <c r="Z2" t="n">
-        <v>517134002.377484</v>
+        <v>212.079</v>
       </c>
       <c r="AA2" t="n">
         <v>1.611346149556508e-05</v>
@@ -7590,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.31756945895515</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.209x + -7000.487</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7000.486509476262</v>
       </c>
       <c r="Y3" t="n">
         <v>406.1964822742892</v>
       </c>
       <c r="Z3" t="n">
-        <v>531464218.9944366</v>
+        <v>163.888</v>
       </c>
       <c r="AA3" t="n">
         <v>1.740229790163936e-05</v>
@@ -7642,19 +7642,19 @@
       <c r="K4" t="n">
         <v>85.85794459005777</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.809x + -7709.912</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7709.912167855526</v>
       </c>
       <c r="Y4" t="n">
         <v>443.7626362359905</v>
       </c>
       <c r="Z4" t="n">
-        <v>943955460.2865905</v>
+        <v>142.399</v>
       </c>
       <c r="AA4" t="n">
         <v>5.426695995703156e-06</v>
@@ -7694,19 +7694,19 @@
       <c r="K5" t="n">
         <v>86.08631888573478</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.617x + -8039.545</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8039.545069267775</v>
       </c>
       <c r="Y5" t="n">
         <v>450.3571189902734</v>
       </c>
       <c r="Z5" t="n">
-        <v>4626438561.604074</v>
+        <v>131.019</v>
       </c>
       <c r="AA5" t="n">
         <v>3.084830119527758e-06</v>
@@ -7746,19 +7746,19 @@
       <c r="K6" t="n">
         <v>86.35350537499718</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.691x + -8539.226</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8539.226460839291</v>
       </c>
       <c r="Y6" t="n">
         <v>448.2740800618595</v>
       </c>
       <c r="Z6" t="n">
-        <v>38662165.69008265</v>
+        <v>120.7569999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>2.502778957277981e-06</v>
@@ -7798,19 +7798,19 @@
       <c r="K7" t="n">
         <v>86.15776587493272</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 14.890x + -7943.922</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7943.922326265624</v>
       </c>
       <c r="Y7" t="n">
         <v>445.387017325304</v>
       </c>
       <c r="Z7" t="n">
-        <v>323432221.225269</v>
+        <v>117.977</v>
       </c>
       <c r="AA7" t="n">
         <v>2.038708159641297e-06</v>
@@ -7850,19 +7850,19 @@
       <c r="K8" t="n">
         <v>86.20263531704791</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 15.066x + -7915.946</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7915.945534897673</v>
       </c>
       <c r="Y8" t="n">
         <v>440.9694717024348</v>
       </c>
       <c r="Z8" t="n">
-        <v>191695188.0984681</v>
+        <v>113.365</v>
       </c>
       <c r="AA8" t="n">
         <v>1.811950100208866e-06</v>
@@ -7902,19 +7902,19 @@
       <c r="K9" t="n">
         <v>86.42234109702724</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 15.994x + -8313.245</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8313.244926148822</v>
       </c>
       <c r="Y9" t="n">
         <v>436.1590196059623</v>
       </c>
       <c r="Z9" t="n">
-        <v>52198606.42273451</v>
+        <v>107.6489999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.659649004426688e-06</v>
@@ -7954,19 +7954,19 @@
       <c r="K10" t="n">
         <v>86.2101776795749</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.096x + -7692.415</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7692.415457396726</v>
       </c>
       <c r="Y10" t="n">
         <v>431.4033591607503</v>
       </c>
       <c r="Z10" t="n">
-        <v>89153392.15322308</v>
+        <v>106.513</v>
       </c>
       <c r="AA10" t="n">
         <v>1.539947714236846e-06</v>
@@ -8006,19 +8006,19 @@
       <c r="K11" t="n">
         <v>86.23391246743091</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 15.192x + -7635.581</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7635.581378916427</v>
       </c>
       <c r="Y11" t="n">
         <v>426.8422070299947</v>
       </c>
       <c r="Z11" t="n">
-        <v>135098491.7655998</v>
+        <v>104.591</v>
       </c>
       <c r="AA11" t="n">
         <v>1.455402046740741e-06</v>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -8204,19 +8204,19 @@
       <c r="K2" t="n">
         <v>85.95011125627252</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.124x + -8799.587</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8799.586962586653</v>
       </c>
       <c r="Y2" t="n">
         <v>429.7932192605974</v>
       </c>
       <c r="Z2" t="n">
-        <v>562592999.5669701</v>
+        <v>129.4920000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.627895485631908e-05</v>
@@ -8256,19 +8256,19 @@
       <c r="K3" t="n">
         <v>86.09480031582621</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.649x + -8712.208</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8712.207715790601</v>
       </c>
       <c r="Y3" t="n">
         <v>419.6303894013049</v>
       </c>
       <c r="Z3" t="n">
-        <v>817488492.7871574</v>
+        <v>114.0500000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.672088246815811e-05</v>
@@ -8308,19 +8308,19 @@
       <c r="K4" t="n">
         <v>86.05397946992426</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.497x + -8459.160</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8459.159807644928</v>
       </c>
       <c r="Y4" t="n">
         <v>429.617769656206</v>
       </c>
       <c r="Z4" t="n">
-        <v>710104774.3432301</v>
+        <v>109.6369999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.255706842964694e-05</v>
@@ -8360,19 +8360,19 @@
       <c r="K5" t="n">
         <v>86.20353949558505</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.070x + -8694.053</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8694.053340036611</v>
       </c>
       <c r="Y5" t="n">
         <v>452.3229894707206</v>
       </c>
       <c r="Z5" t="n">
-        <v>808203832.0034522</v>
+        <v>103.674</v>
       </c>
       <c r="AA5" t="n">
         <v>6.152092620533742e-06</v>
@@ -8412,19 +8412,19 @@
       <c r="K6" t="n">
         <v>86.46264421811694</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.177x + -9257.357</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9257.356887068754</v>
       </c>
       <c r="Y6" t="n">
         <v>454.7715577815473</v>
       </c>
       <c r="Z6" t="n">
-        <v>1970217010.584641</v>
+        <v>99.44299999999998</v>
       </c>
       <c r="AA6" t="n">
         <v>4.661555103148826e-06</v>
@@ -8464,19 +8464,19 @@
       <c r="K7" t="n">
         <v>85.98322467867696</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 14.241x + -7971.611</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7971.611483143059</v>
       </c>
       <c r="Y7" t="n">
         <v>459.2726757585126</v>
       </c>
       <c r="Z7" t="n">
-        <v>372756534.5368027</v>
+        <v>100.6600000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>3.006160791815131e-06</v>
@@ -8516,19 +8516,19 @@
       <c r="K8" t="n">
         <v>86.10727891488591</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.696x + -8138.293</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8138.293414799076</v>
       </c>
       <c r="Y8" t="n">
         <v>458.37568208228</v>
       </c>
       <c r="Z8" t="n">
-        <v>473829535.3887117</v>
+        <v>98.54599999999994</v>
       </c>
       <c r="AA8" t="n">
         <v>2.330515857217783e-06</v>
@@ -8568,19 +8568,19 @@
       <c r="K9" t="n">
         <v>86.24132441411275</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 15.222x + -8346.133</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8346.133023764769</v>
       </c>
       <c r="Y9" t="n">
         <v>454.9831432895858</v>
       </c>
       <c r="Z9" t="n">
-        <v>204470522.9006511</v>
+        <v>96.54000000000008</v>
       </c>
       <c r="AA9" t="n">
         <v>2.115043053145326e-06</v>
@@ -8620,19 +8620,19 @@
       <c r="K10" t="n">
         <v>86.57823194614254</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 16.725x + -9121.422</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9121.422450275599</v>
       </c>
       <c r="Y10" t="n">
         <v>451.2452578884005</v>
       </c>
       <c r="Z10" t="n">
-        <v>104534850.1738987</v>
+        <v>91.80100000000004</v>
       </c>
       <c r="AA10" t="n">
         <v>2.000572738836259e-06</v>
@@ -8672,19 +8672,19 @@
       <c r="K11" t="n">
         <v>86.23403615487634</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 15.192x + -8143.608</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8143.608376541416</v>
       </c>
       <c r="Y11" t="n">
         <v>448.0720873457959</v>
       </c>
       <c r="Z11" t="n">
-        <v>390125731.3063829</v>
+        <v>92.46900000000005</v>
       </c>
       <c r="AA11" t="n">
         <v>1.826975893216307e-06</v>
@@ -8724,19 +8724,19 @@
       <c r="K12" t="n">
         <v>86.27555474661604</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 15.362x + -8155.639</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-8155.639213459574</v>
       </c>
       <c r="Y12" t="n">
         <v>444.4760142132259</v>
       </c>
       <c r="Z12" t="n">
-        <v>242694676.8129379</v>
+        <v>91.28700000000003</v>
       </c>
       <c r="AA12" t="n">
         <v>1.733726778152612e-06</v>
@@ -8776,19 +8776,19 @@
       <c r="K13" t="n">
         <v>86.61406644922589</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 16.902x + -8934.495</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-8934.495273070181</v>
       </c>
       <c r="Y13" t="n">
         <v>441.0341296801473</v>
       </c>
       <c r="Z13" t="n">
-        <v>151335285.9289216</v>
+        <v>87.25400000000002</v>
       </c>
       <c r="AA13" t="n">
         <v>1.652955246449384e-06</v>
@@ -8828,19 +8828,19 @@
       <c r="K14" t="n">
         <v>86.41195667456248</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 15.948x + -8314.579</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-8314.579168769395</v>
       </c>
       <c r="Y14" t="n">
         <v>437.5444965927232</v>
       </c>
       <c r="Z14" t="n">
-        <v>619785895.9580516</v>
+        <v>87.51700000000005</v>
       </c>
       <c r="AA14" t="n">
         <v>1.583197135291149e-06</v>
@@ -8880,19 +8880,19 @@
       <c r="K15" t="n">
         <v>86.36764732155075</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 15.753x + -8125.318</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-8125.317972457186</v>
       </c>
       <c r="Y15" t="n">
         <v>434.0868146982034</v>
       </c>
       <c r="Z15" t="n">
-        <v>159004724.4555343</v>
+        <v>87.44300000000004</v>
       </c>
       <c r="AA15" t="n">
         <v>1.528213643864651e-06</v>
@@ -8932,19 +8932,19 @@
       <c r="K16" t="n">
         <v>86.39923131988029</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 15.891x + -8119.982</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-8119.982157234307</v>
       </c>
       <c r="Y16" t="n">
         <v>430.6744964949223</v>
       </c>
       <c r="Z16" t="n">
-        <v>167257316.4615875</v>
+        <v>85.584</v>
       </c>
       <c r="AA16" t="n">
         <v>1.469460529271239e-06</v>
@@ -8984,19 +8984,19 @@
       <c r="K17" t="n">
         <v>86.56823354229601</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 16.676x + -8464.498</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-8464.497698882653</v>
       </c>
       <c r="Y17" t="n">
         <v>427.2183042735488</v>
       </c>
       <c r="Z17" t="n">
-        <v>73278536.64309131</v>
+        <v>82.74000000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>1.423873628367312e-06</v>
@@ -9036,19 +9036,19 @@
       <c r="K18" t="n">
         <v>86.19605984370624</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 15.040x + -7507.542</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-7507.542129849154</v>
       </c>
       <c r="Y18" t="n">
         <v>423.6906610712998</v>
       </c>
       <c r="Z18" t="n">
-        <v>53706620.86468942</v>
+        <v>85.98600000000005</v>
       </c>
       <c r="AA18" t="n">
         <v>1.38354794085521e-06</v>
@@ -9088,19 +9088,19 @@
       <c r="K19" t="n">
         <v>86.37119903640611</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 15.768x + -7814.229</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-7814.228678086119</v>
       </c>
       <c r="Y19" t="n">
         <v>420.3418232263168</v>
       </c>
       <c r="Z19" t="n">
-        <v>35319509.81477289</v>
+        <v>83.06800000000004</v>
       </c>
       <c r="AA19" t="n">
         <v>1.342587031040738e-06</v>
@@ -9140,19 +9140,19 @@
       <c r="K20" t="n">
         <v>86.3154575967724</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 15.529x + -7611.577</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-7611.576853225756</v>
       </c>
       <c r="Y20" t="n">
         <v>416.8541039567747</v>
       </c>
       <c r="Z20" t="n">
-        <v>80745082.35935077</v>
+        <v>82.43200000000002</v>
       </c>
       <c r="AA20" t="n">
         <v>1.305381697007645e-06</v>
@@ -9192,19 +9192,19 @@
       <c r="K21" t="n">
         <v>86.38709435375804</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 15.838x + -7688.220</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-7688.220450246899</v>
       </c>
       <c r="Y21" t="n">
         <v>413.173417094693</v>
       </c>
       <c r="Z21" t="n">
-        <v>24083557.43788818</v>
+        <v>81.73399999999998</v>
       </c>
       <c r="AA21" t="n">
         <v>1.273415623210706e-06</v>
@@ -9244,19 +9244,19 @@
       <c r="K22" t="n">
         <v>86.31899829893688</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 15.544x + -7461.779</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7461.779420541887</v>
       </c>
       <c r="Y22" t="n">
         <v>409.5263881564664</v>
       </c>
       <c r="Z22" t="n">
-        <v>122618991.6382949</v>
+        <v>80.53399999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1.241619927129778e-06</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -9442,19 +9442,19 @@
       <c r="K2" t="n">
         <v>83.23478723234156</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.430x + -5414.042</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5414.041814868423</v>
       </c>
       <c r="Y2" t="n">
         <v>429.3284156703372</v>
       </c>
       <c r="Z2" t="n">
-        <v>402553699.9200533</v>
+        <v>246.2620000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.656942896656787e-05</v>
@@ -9494,19 +9494,19 @@
       <c r="K3" t="n">
         <v>85.08416256317115</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.627x + -6445.594</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6445.594085121489</v>
       </c>
       <c r="Y3" t="n">
         <v>421.7191979384372</v>
       </c>
       <c r="Z3" t="n">
-        <v>1328494992.742595</v>
+        <v>177.136</v>
       </c>
       <c r="AA3" t="n">
         <v>1.053142505300511e-05</v>
@@ -9546,19 +9546,19 @@
       <c r="K4" t="n">
         <v>85.70517038129283</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.316x + -7146.132</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7146.132424742581</v>
       </c>
       <c r="Y4" t="n">
         <v>443.2816248255861</v>
       </c>
       <c r="Z4" t="n">
-        <v>165798939.9663967</v>
+        <v>153.125</v>
       </c>
       <c r="AA4" t="n">
         <v>3.215415351138841e-06</v>
@@ -9598,19 +9598,19 @@
       <c r="K5" t="n">
         <v>85.79608932309401</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.605x + -7146.514</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7146.513889313306</v>
       </c>
       <c r="Y5" t="n">
         <v>441.6105664394518</v>
       </c>
       <c r="Z5" t="n">
-        <v>580112492.5795598</v>
+        <v>141.6579999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>2.32184981880586e-06</v>
@@ -9650,19 +9650,19 @@
       <c r="K6" t="n">
         <v>86.1322096647157</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.791x + -7685.932</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-7685.932461853346</v>
       </c>
       <c r="Y6" t="n">
         <v>437.6272727848345</v>
       </c>
       <c r="Z6" t="n">
-        <v>47794544.42563547</v>
+        <v>131.116</v>
       </c>
       <c r="AA6" t="n">
         <v>1.9517164057488e-06</v>
@@ -9702,19 +9702,19 @@
       <c r="K7" t="n">
         <v>86.09283679408355</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 14.642x + -7469.247</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7469.247115082168</v>
       </c>
       <c r="Y7" t="n">
         <v>432.7455043802224</v>
       </c>
       <c r="Z7" t="n">
-        <v>167540934.2256478</v>
+        <v>126.609</v>
       </c>
       <c r="AA7" t="n">
         <v>1.740164012349097e-06</v>
@@ -9754,19 +9754,19 @@
       <c r="K8" t="n">
         <v>86.01793341948847</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.365x + -7190.514</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7190.513920025728</v>
       </c>
       <c r="Y8" t="n">
         <v>427.7264566839125</v>
       </c>
       <c r="Z8" t="n">
-        <v>38758243.48460139</v>
+        <v>123.917</v>
       </c>
       <c r="AA8" t="n">
         <v>1.594085761636233e-06</v>
@@ -9806,19 +9806,19 @@
       <c r="K9" t="n">
         <v>86.26989989713512</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 15.339x + -7597.017</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7597.017364114158</v>
       </c>
       <c r="Y9" t="n">
         <v>422.9965335576611</v>
       </c>
       <c r="Z9" t="n">
-        <v>107188625.7715122</v>
+        <v>117.938</v>
       </c>
       <c r="AA9" t="n">
         <v>1.490096372647036e-06</v>
@@ -9858,19 +9858,19 @@
       <c r="K10" t="n">
         <v>86.27825604431004</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.373x + -7510.589</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7510.588681929537</v>
       </c>
       <c r="Y10" t="n">
         <v>418.6352001544854</v>
       </c>
       <c r="Z10" t="n">
-        <v>98272582.88053755</v>
+        <v>115.861</v>
       </c>
       <c r="AA10" t="n">
         <v>1.415503448633136e-06</v>
@@ -9910,19 +9910,19 @@
       <c r="K11" t="n">
         <v>86.57205587394866</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 16.694x + -8100.325</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8100.325238554351</v>
       </c>
       <c r="Y11" t="n">
         <v>414.6717908169821</v>
       </c>
       <c r="Z11" t="n">
-        <v>13167151.73639226</v>
+        <v>110.61</v>
       </c>
       <c r="AA11" t="n">
         <v>1.351561634035653e-06</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>85.75144313712272</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.461x + -8425.382</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.46121302656552</v>
       </c>
       <c r="X2" t="n">
         <v>-8425.382353354806</v>
@@ -600,7 +598,7 @@
         <v>436.5613412390976</v>
       </c>
       <c r="Z2" t="n">
-        <v>138.812</v>
+        <v>459756129.7226777</v>
       </c>
       <c r="AA2" t="n">
         <v>1.617320643735627e-05</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>85.95358244905577</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.136x + -8648.783</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.1360820951703</v>
       </c>
       <c r="X3" t="n">
         <v>-8648.783113050857</v>
@@ -652,7 +648,7 @@
         <v>429.426343755753</v>
       </c>
       <c r="Z3" t="n">
-        <v>124.881</v>
+        <v>290537744.422328</v>
       </c>
       <c r="AA3" t="n">
         <v>1.633929680176825e-05</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>86.16898640496976</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.933x + -9004.450</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.93348098541376</v>
       </c>
       <c r="X4" t="n">
         <v>-9004.449998165856</v>
@@ -704,7 +698,7 @@
         <v>423.777566549322</v>
       </c>
       <c r="Z4" t="n">
-        <v>115.24</v>
+        <v>303912238.4359277</v>
       </c>
       <c r="AA4" t="n">
         <v>1.647653998322822e-05</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>86.1096533110838</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.705x + -8715.852</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.70503950702534</v>
       </c>
       <c r="X5" t="n">
         <v>-8715.851842118569</v>
@@ -756,7 +748,7 @@
         <v>418.4780451746641</v>
       </c>
       <c r="Z5" t="n">
-        <v>110.995</v>
+        <v>456040234.680056</v>
       </c>
       <c r="AA5" t="n">
         <v>1.660075106136696e-05</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>86.20104291829934</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.060x + -8804.113</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.05986807852183</v>
       </c>
       <c r="X6" t="n">
         <v>-8804.112573257338</v>
@@ -808,7 +798,7 @@
         <v>457.1980885449453</v>
       </c>
       <c r="Z6" t="n">
-        <v>106.298</v>
+        <v>2432192575.5996</v>
       </c>
       <c r="AA6" t="n">
         <v>5.968994096982682e-06</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>86.18963722131048</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.015x + -8647.549</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.01465623900591</v>
       </c>
       <c r="X7" t="n">
         <v>-8647.549253121873</v>
@@ -860,7 +848,7 @@
         <v>466.2216449640257</v>
       </c>
       <c r="Z7" t="n">
-        <v>102.316</v>
+        <v>980250299.3921894</v>
       </c>
       <c r="AA7" t="n">
         <v>3.348927935908901e-06</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>86.10652505823433</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.693x + -8328.152</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.69318818376992</v>
       </c>
       <c r="X8" t="n">
         <v>-8328.152260697088</v>
@@ -912,7 +898,7 @@
         <v>465.0648399277428</v>
       </c>
       <c r="Z8" t="n">
-        <v>100.617</v>
+        <v>315961879.7105847</v>
       </c>
       <c r="AA8" t="n">
         <v>2.619582718730847e-06</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>86.61123063991427</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.888x + -9523.735</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.88782801410668</v>
       </c>
       <c r="X9" t="n">
         <v>-9523.735254483521</v>
@@ -964,7 +948,7 @@
         <v>462.0454749569959</v>
       </c>
       <c r="Z9" t="n">
-        <v>92.96100000000001</v>
+        <v>507997005.9589807</v>
       </c>
       <c r="AA9" t="n">
         <v>2.227522631558258e-06</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>86.344032132899</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.651x + -8663.695</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.65057452743505</v>
       </c>
       <c r="X10" t="n">
         <v>-8663.69464773346</v>
@@ -1016,7 +998,7 @@
         <v>458.0409926564698</v>
       </c>
       <c r="Z10" t="n">
-        <v>93.67200000000003</v>
+        <v>206302720.2869713</v>
       </c>
       <c r="AA10" t="n">
         <v>1.999651868526985e-06</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>86.26301697638011</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 15.310x + -8351.491</t>
-        </is>
+      <c r="W11" t="n">
+        <v>15.31034815498231</v>
       </c>
       <c r="X11" t="n">
         <v>-8351.490980495348</v>
@@ -1068,7 +1048,7 @@
         <v>454.1664677363372</v>
       </c>
       <c r="Z11" t="n">
-        <v>92.05400000000009</v>
+        <v>473653198.5129693</v>
       </c>
       <c r="AA11" t="n">
         <v>1.830078272135628e-06</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>85.96837537932797</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.188x + -8745.798</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.1881230881079</v>
       </c>
       <c r="X2" t="n">
         <v>-8745.798358997865</v>
@@ -1266,7 +1244,7 @@
         <v>425.556513835281</v>
       </c>
       <c r="Z2" t="n">
-        <v>121.05</v>
+        <v>439647509.2972604</v>
       </c>
       <c r="AA2" t="n">
         <v>1.634380782702551e-05</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>85.90677899824207</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.974x + -8194.017</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.97390290455378</v>
       </c>
       <c r="X3" t="n">
         <v>-8194.017028003105</v>
@@ -1318,7 +1294,7 @@
         <v>415.4930371170042</v>
       </c>
       <c r="Z3" t="n">
-        <v>111.737</v>
+        <v>413978764.9088309</v>
       </c>
       <c r="AA3" t="n">
         <v>1.676989275717434e-05</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>86.48824651819594</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.295x + -9494.248</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.29499757508114</v>
       </c>
       <c r="X4" t="n">
         <v>-9494.247686904209</v>
@@ -1370,7 +1344,7 @@
         <v>419.4491319593897</v>
       </c>
       <c r="Z4" t="n">
-        <v>102.237</v>
+        <v>128502580.708563</v>
       </c>
       <c r="AA4" t="n">
         <v>1.436877730562132e-05</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>86.48646823592055</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.287x + -9370.291</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.28672959154234</v>
       </c>
       <c r="X5" t="n">
         <v>-9370.291333677103</v>
@@ -1422,7 +1394,7 @@
         <v>442.898424126861</v>
       </c>
       <c r="Z5" t="n">
-        <v>100.225</v>
+        <v>998615699.4737236</v>
       </c>
       <c r="AA5" t="n">
         <v>7.634526766010167e-06</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>86.37210788369278</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.772x + -8952.997</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.7720202565853</v>
       </c>
       <c r="X6" t="n">
         <v>-8952.996738374797</v>
@@ -1474,7 +1444,7 @@
         <v>459.4419108960251</v>
       </c>
       <c r="Z6" t="n">
-        <v>98.95000000000005</v>
+        <v>2200050254.421949</v>
       </c>
       <c r="AA6" t="n">
         <v>3.531037011878829e-06</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>86.28400188530301</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.397x + -8631.121</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.39705343960711</v>
       </c>
       <c r="X7" t="n">
         <v>-8631.120644864346</v>
@@ -1526,7 +1494,7 @@
         <v>456.8288223071426</v>
       </c>
       <c r="Z7" t="n">
-        <v>97.99800000000005</v>
+        <v>486092885.9156572</v>
       </c>
       <c r="AA7" t="n">
         <v>3.306173198639828e-06</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>86.47985200944004</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.256x + -9043.425</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.25604123245146</v>
       </c>
       <c r="X8" t="n">
         <v>-9043.424900618778</v>
@@ -1578,7 +1544,7 @@
         <v>455.5738003963161</v>
       </c>
       <c r="Z8" t="n">
-        <v>94.42200000000003</v>
+        <v>414419474.7917985</v>
       </c>
       <c r="AA8" t="n">
         <v>2.741429831853265e-06</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>86.11077642405689</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.709x + -8037.031</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.70929904195229</v>
       </c>
       <c r="X9" t="n">
         <v>-8037.031378340025</v>
@@ -1630,7 +1594,7 @@
         <v>454.5853986103272</v>
       </c>
       <c r="Z9" t="n">
-        <v>97.20600000000002</v>
+        <v>108931757.139886</v>
       </c>
       <c r="AA9" t="n">
         <v>2.192447312401475e-06</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>86.25853183561952</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.292x + -8291.427</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.29194246146126</v>
       </c>
       <c r="X10" t="n">
         <v>-8291.427047402522</v>
@@ -1682,7 +1644,7 @@
         <v>451.5707879685751</v>
       </c>
       <c r="Z10" t="n">
-        <v>93.70299999999997</v>
+        <v>614814743.8409787</v>
       </c>
       <c r="AA10" t="n">
         <v>2.022111914245131e-06</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>86.2961015716008</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 15.447x + -8296.650</t>
-        </is>
+      <c r="W11" t="n">
+        <v>15.44749275968518</v>
       </c>
       <c r="X11" t="n">
         <v>-8296.650322649335</v>
@@ -1734,7 +1694,7 @@
         <v>448.5443893143457</v>
       </c>
       <c r="Z11" t="n">
-        <v>91.82900000000006</v>
+        <v>204222695.5029631</v>
       </c>
       <c r="AA11" t="n">
         <v>1.889528513827882e-06</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>86.34556247412979</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 15.657x + -8334.539</t>
-        </is>
+      <c r="W12" t="n">
+        <v>15.65714622017708</v>
       </c>
       <c r="X12" t="n">
         <v>-8334.538598439145</v>
@@ -1786,7 +1744,7 @@
         <v>445.3617068934848</v>
       </c>
       <c r="Z12" t="n">
-        <v>90.75300000000004</v>
+        <v>92169324.80456986</v>
       </c>
       <c r="AA12" t="n">
         <v>1.787832217141882e-06</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>86.58584861664701</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 16.762x + -8876.971</t>
-        </is>
+      <c r="W13" t="n">
+        <v>16.76198348291728</v>
       </c>
       <c r="X13" t="n">
         <v>-8876.970806251997</v>
@@ -1838,7 +1794,7 @@
         <v>442.174287418509</v>
       </c>
       <c r="Z13" t="n">
-        <v>86.74799999999993</v>
+        <v>231743751.0767274</v>
       </c>
       <c r="AA13" t="n">
         <v>1.706539925316978e-06</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>86.52793233680913</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 16.482x + -8637.507</t>
-        </is>
+      <c r="W14" t="n">
+        <v>16.48171443191587</v>
       </c>
       <c r="X14" t="n">
         <v>-8637.506802509282</v>
@@ -1890,7 +1844,7 @@
         <v>439.0523805817506</v>
       </c>
       <c r="Z14" t="n">
-        <v>85.71799999999996</v>
+        <v>92283929.4686774</v>
       </c>
       <c r="AA14" t="n">
         <v>1.634271659427536e-06</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>86.31645639209579</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 15.533x + -8033.736</t>
-        </is>
+      <c r="W15" t="n">
+        <v>15.53309137840044</v>
       </c>
       <c r="X15" t="n">
         <v>-8033.735733587318</v>
@@ -1942,7 +1894,7 @@
         <v>435.8882484891935</v>
       </c>
       <c r="Z15" t="n">
-        <v>87.33100000000002</v>
+        <v>104529149.8862714</v>
       </c>
       <c r="AA15" t="n">
         <v>1.574501842928551e-06</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>86.39821187978183</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 15.887x + -8154.108</t>
-        </is>
+      <c r="W16" t="n">
+        <v>15.88663313037</v>
       </c>
       <c r="X16" t="n">
         <v>-8154.107755845124</v>
@@ -1994,7 +1944,7 @@
         <v>432.6607238217108</v>
       </c>
       <c r="Z16" t="n">
-        <v>85.70400000000001</v>
+        <v>274297734.1155606</v>
       </c>
       <c r="AA16" t="n">
         <v>1.520942983810344e-06</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>86.4205715568302</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 15.986x + -8133.900</t>
-        </is>
+      <c r="W17" t="n">
+        <v>15.98613355001055</v>
       </c>
       <c r="X17" t="n">
         <v>-8133.899800027603</v>
@@ -2046,7 +1994,7 @@
         <v>429.3165494262582</v>
       </c>
       <c r="Z17" t="n">
-        <v>84.77199999999999</v>
+        <v>203934586.1922266</v>
       </c>
       <c r="AA17" t="n">
         <v>1.474302652004281e-06</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>86.58516089805744</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 16.759x + -8471.952</t>
-        </is>
+      <c r="W18" t="n">
+        <v>16.7585997617742</v>
       </c>
       <c r="X18" t="n">
         <v>-8471.952024295244</v>
@@ -2098,7 +2044,7 @@
         <v>425.9215493809027</v>
       </c>
       <c r="Z18" t="n">
-        <v>82.55399999999997</v>
+        <v>21183066.55456443</v>
       </c>
       <c r="AA18" t="n">
         <v>1.427282840713248e-06</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>86.54973313037205</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 16.586x + -8294.413</t>
-        </is>
+      <c r="W19" t="n">
+        <v>16.5861100823373</v>
       </c>
       <c r="X19" t="n">
         <v>-8294.412934411361</v>
@@ -2150,7 +2094,7 @@
         <v>422.3230347670413</v>
       </c>
       <c r="Z19" t="n">
-        <v>81.09499999999997</v>
+        <v>56607783.77640617</v>
       </c>
       <c r="AA19" t="n">
         <v>1.388197784125901e-06</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>86.39231169106921</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 15.861x + -7830.255</t>
-        </is>
+      <c r="W20" t="n">
+        <v>15.86058272691931</v>
       </c>
       <c r="X20" t="n">
         <v>-7830.255058443125</v>
@@ -2202,7 +2144,7 @@
         <v>418.7695825234975</v>
       </c>
       <c r="Z20" t="n">
-        <v>82.12599999999998</v>
+        <v>250972891.4649639</v>
       </c>
       <c r="AA20" t="n">
         <v>1.350049975723018e-06</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>86.61496854372025</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 16.907x + -8297.646</t>
-        </is>
+      <c r="W21" t="n">
+        <v>16.90651984926625</v>
       </c>
       <c r="X21" t="n">
         <v>-8297.645628534941</v>
@@ -2254,7 +2194,7 @@
         <v>415.3545860070256</v>
       </c>
       <c r="Z21" t="n">
-        <v>78.28100000000001</v>
+        <v>34236904.45462151</v>
       </c>
       <c r="AA21" t="n">
         <v>1.312118988587916e-06</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>86.50872653162848</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 16.391x + -7948.454</t>
-        </is>
+      <c r="W22" t="n">
+        <v>16.39082409335788</v>
       </c>
       <c r="X22" t="n">
         <v>-7948.453721050384</v>
@@ -2306,7 +2244,7 @@
         <v>411.8290656418306</v>
       </c>
       <c r="Z22" t="n">
-        <v>79.52400000000006</v>
+        <v>128691416.7346684</v>
       </c>
       <c r="AA22" t="n">
         <v>1.281866695430897e-06</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>85.3953647282212</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.416x + -7840.930</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.4162655416546</v>
       </c>
       <c r="X2" t="n">
         <v>-7840.929782597505</v>
@@ -2504,7 +2440,7 @@
         <v>434.9999257535136</v>
       </c>
       <c r="Z2" t="n">
-        <v>154.9829999999999</v>
+        <v>344819230.5409263</v>
       </c>
       <c r="AA2" t="n">
         <v>1.616787432361747e-05</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>85.74484201939346</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.440x + -8066.219</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.44025355411804</v>
       </c>
       <c r="X3" t="n">
         <v>-8066.219127042919</v>
@@ -2556,7 +2490,7 @@
         <v>423.8370143989371</v>
       </c>
       <c r="Z3" t="n">
-        <v>127.0749999999999</v>
+        <v>547836927.5268921</v>
       </c>
       <c r="AA3" t="n">
         <v>1.656265994921808e-05</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>86.21932323919702</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 15.133x + -8984.526</t>
-        </is>
+      <c r="W4" t="n">
+        <v>15.13289886314923</v>
       </c>
       <c r="X4" t="n">
         <v>-8984.526394492035</v>
@@ -2608,7 +2540,7 @@
         <v>418.7714804008791</v>
       </c>
       <c r="Z4" t="n">
-        <v>113.0509999999999</v>
+        <v>275201067.4412613</v>
       </c>
       <c r="AA4" t="n">
         <v>1.669982950005685e-05</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>85.94346905743005</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.101x + -8216.206</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.10072163318455</v>
       </c>
       <c r="X5" t="n">
         <v>-8216.205625040062</v>
@@ -2660,7 +2590,7 @@
         <v>433.5745037809186</v>
       </c>
       <c r="Z5" t="n">
-        <v>110.6909999999999</v>
+        <v>1377337842.410501</v>
       </c>
       <c r="AA5" t="n">
         <v>1.144539877366335e-05</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>86.23399469050551</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.192x + -8778.693</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.19202414063634</v>
       </c>
       <c r="X6" t="n">
         <v>-8778.693107569165</v>
@@ -2712,7 +2640,7 @@
         <v>459.553311242398</v>
       </c>
       <c r="Z6" t="n">
-        <v>103.889</v>
+        <v>1882194165.19316</v>
       </c>
       <c r="AA6" t="n">
         <v>4.755623996886845e-06</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>86.51320910630089</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.412x + -9402.658</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.41194814785252</v>
       </c>
       <c r="X7" t="n">
         <v>-9402.657814577398</v>
@@ -2764,7 +2690,7 @@
         <v>457.9437873575273</v>
       </c>
       <c r="Z7" t="n">
-        <v>97.91399999999999</v>
+        <v>395560895.6460473</v>
       </c>
       <c r="AA7" t="n">
         <v>4.072688346032543e-06</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>86.55911649603661</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.631x + -9405.307</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.63145015458909</v>
       </c>
       <c r="X8" t="n">
         <v>-9405.307126144153</v>
@@ -2816,7 +2740,7 @@
         <v>459.4159812941938</v>
       </c>
       <c r="Z8" t="n">
-        <v>94.75800000000004</v>
+        <v>119775122.0151341</v>
       </c>
       <c r="AA8" t="n">
         <v>2.880674451816313e-06</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>86.07449723841992</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.573x + -8063.108</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.57293642754105</v>
       </c>
       <c r="X9" t="n">
         <v>-8063.108053185911</v>
@@ -2868,7 +2790,7 @@
         <v>458.4407398337984</v>
       </c>
       <c r="Z9" t="n">
-        <v>96.32500000000005</v>
+        <v>2050759825.418768</v>
       </c>
       <c r="AA9" t="n">
         <v>2.218387483515646e-06</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>86.36674037246492</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.749x + -8648.108</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.74865738981043</v>
       </c>
       <c r="X10" t="n">
         <v>-8648.107996158215</v>
@@ -2920,7 +2840,7 @@
         <v>454.1219036357127</v>
       </c>
       <c r="Z10" t="n">
-        <v>92.19000000000005</v>
+        <v>117072889.9099261</v>
       </c>
       <c r="AA10" t="n">
         <v>2.131163266566401e-06</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>86.56369146988662</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 16.654x + -9064.751</t>
-        </is>
+      <c r="W11" t="n">
+        <v>16.65364594434075</v>
       </c>
       <c r="X11" t="n">
         <v>-9064.751095793868</v>
@@ -2972,7 +2890,7 @@
         <v>450.8553170662203</v>
       </c>
       <c r="Z11" t="n">
-        <v>88.60199999999998</v>
+        <v>154554559.0861521</v>
       </c>
       <c r="AA11" t="n">
         <v>1.912314105095442e-06</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>86.68660525809</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 17.273x + -9312.488</t>
-        </is>
+      <c r="W12" t="n">
+        <v>17.27288744915598</v>
       </c>
       <c r="X12" t="n">
         <v>-9312.487903245348</v>
@@ -3024,7 +2940,7 @@
         <v>447.5941925583273</v>
       </c>
       <c r="Z12" t="n">
-        <v>84.38499999999999</v>
+        <v>177427477.6973688</v>
       </c>
       <c r="AA12" t="n">
         <v>1.725781819813984e-06</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>86.622170643838</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 16.943x + -9025.273</t>
-        </is>
+      <c r="W13" t="n">
+        <v>16.94265132071409</v>
       </c>
       <c r="X13" t="n">
         <v>-9025.273366936073</v>
@@ -3076,7 +2990,7 @@
         <v>443.8448988552323</v>
       </c>
       <c r="Z13" t="n">
-        <v>82.84299999999996</v>
+        <v>342020752.9353812</v>
       </c>
       <c r="AA13" t="n">
         <v>1.63263793774982e-06</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>86.4417932709521</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 16.082x + -8441.386</t>
-        </is>
+      <c r="W14" t="n">
+        <v>16.08172519812724</v>
       </c>
       <c r="X14" t="n">
         <v>-8441.386468294138</v>
@@ -3128,7 +3040,7 @@
         <v>440.0494036026332</v>
       </c>
       <c r="Z14" t="n">
-        <v>84.62100000000009</v>
+        <v>159184895.4359874</v>
       </c>
       <c r="AA14" t="n">
         <v>1.555567234494001e-06</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>86.44160452250371</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 16.081x + -8347.667</t>
-        </is>
+      <c r="W15" t="n">
+        <v>16.08086997576172</v>
       </c>
       <c r="X15" t="n">
         <v>-8347.666635147394</v>
@@ -3180,7 +3090,7 @@
         <v>436.3822431930071</v>
       </c>
       <c r="Z15" t="n">
-        <v>83.94100000000003</v>
+        <v>470354012.4058977</v>
       </c>
       <c r="AA15" t="n">
         <v>1.492046342755361e-06</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>86.72236432383686</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 17.462x + -9018.367</t>
-        </is>
+      <c r="W16" t="n">
+        <v>17.46175350010721</v>
       </c>
       <c r="X16" t="n">
         <v>-9018.367276180637</v>
@@ -3232,7 +3140,7 @@
         <v>432.7070547697845</v>
       </c>
       <c r="Z16" t="n">
-        <v>78.07400000000001</v>
+        <v>163013896.3609696</v>
       </c>
       <c r="AA16" t="n">
         <v>1.430512162143117e-06</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>86.41701922497259</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 15.970x + -8112.332</t>
-        </is>
+      <c r="W17" t="n">
+        <v>15.97024282799256</v>
       </c>
       <c r="X17" t="n">
         <v>-8112.331798445049</v>
@@ -3284,7 +3190,7 @@
         <v>428.928766008439</v>
       </c>
       <c r="Z17" t="n">
-        <v>81.77199999999999</v>
+        <v>76658901.32251114</v>
       </c>
       <c r="AA17" t="n">
         <v>1.386613082874812e-06</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>86.28313144161756</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 15.393x + -7723.155</t>
-        </is>
+      <c r="W18" t="n">
+        <v>15.3934375115313</v>
       </c>
       <c r="X18" t="n">
         <v>-7723.155358266668</v>
@@ -3336,7 +3240,7 @@
         <v>425.2764764867915</v>
       </c>
       <c r="Z18" t="n">
-        <v>81.60999999999996</v>
+        <v>155317345.4695542</v>
       </c>
       <c r="AA18" t="n">
         <v>1.344374033453632e-06</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>86.40867727258967</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 15.933x + -7925.510</t>
-        </is>
+      <c r="W19" t="n">
+        <v>15.93305002266193</v>
       </c>
       <c r="X19" t="n">
         <v>-7925.510388842446</v>
@@ -3388,7 +3290,7 @@
         <v>421.6229672675877</v>
       </c>
       <c r="Z19" t="n">
-        <v>78.74700000000001</v>
+        <v>135787529.6473996</v>
       </c>
       <c r="AA19" t="n">
         <v>1.301976943813317e-06</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>86.51583409920414</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 16.424x + -8100.256</t>
-        </is>
+      <c r="W20" t="n">
+        <v>16.42434358446324</v>
       </c>
       <c r="X20" t="n">
         <v>-8100.256490752301</v>
@@ -3440,7 +3340,7 @@
         <v>418.0042884196412</v>
       </c>
       <c r="Z20" t="n">
-        <v>77.13200000000006</v>
+        <v>93515649.87172209</v>
       </c>
       <c r="AA20" t="n">
         <v>1.266278368072416e-06</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>86.38509718954563</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 15.829x + -7709.902</t>
-        </is>
+      <c r="W21" t="n">
+        <v>15.82884480380962</v>
       </c>
       <c r="X21" t="n">
         <v>-7709.902032735014</v>
@@ -3492,7 +3390,7 @@
         <v>414.4162369724249</v>
       </c>
       <c r="Z21" t="n">
-        <v>76.80700000000007</v>
+        <v>98336831.56401308</v>
       </c>
       <c r="AA21" t="n">
         <v>1.232749848994821e-06</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>86.64470537406686</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 17.057x + -8259.885</t>
-        </is>
+      <c r="W22" t="n">
+        <v>17.05670425805519</v>
       </c>
       <c r="X22" t="n">
         <v>-8259.885288528591</v>
@@ -3544,7 +3440,7 @@
         <v>410.8905802376653</v>
       </c>
       <c r="Z22" t="n">
-        <v>73.47200000000004</v>
+        <v>35631955.4182388</v>
       </c>
       <c r="AA22" t="n">
         <v>1.203224322856655e-06</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>85.34901167197908</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.292x + -8200.374</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.29198442932583</v>
       </c>
       <c r="X2" t="n">
         <v>-8200.373625341766</v>
@@ -3742,7 +3636,7 @@
         <v>441.2503204854718</v>
       </c>
       <c r="Z2" t="n">
-        <v>148.436</v>
+        <v>453307118.7463925</v>
       </c>
       <c r="AA2" t="n">
         <v>1.523184793402742e-05</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>86.28775760729498</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.413x + -9107.588</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.41267457729695</v>
       </c>
       <c r="X3" t="n">
         <v>-9107.587728673427</v>
@@ -3794,7 +3686,7 @@
         <v>476.6023147017011</v>
       </c>
       <c r="Z3" t="n">
-        <v>113.721</v>
+        <v>227347529.4133855</v>
       </c>
       <c r="AA3" t="n">
         <v>2.826787225294773e-06</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>86.29597584401212</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 15.447x + -8814.496</t>
-        </is>
+      <c r="W4" t="n">
+        <v>15.44696695383033</v>
       </c>
       <c r="X4" t="n">
         <v>-8814.495803533349</v>
@@ -3846,7 +3736,7 @@
         <v>474.03694661931</v>
       </c>
       <c r="Z4" t="n">
-        <v>105.9749999999999</v>
+        <v>128656884.9781878</v>
       </c>
       <c r="AA4" t="n">
         <v>1.766313256740211e-06</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>86.61836106409478</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.924x + -9534.063</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.92352028285748</v>
       </c>
       <c r="X5" t="n">
         <v>-9534.062981448962</v>
@@ -3898,7 +3786,7 @@
         <v>469.0849278976439</v>
       </c>
       <c r="Z5" t="n">
-        <v>99.35599999999999</v>
+        <v>238714322.3381775</v>
       </c>
       <c r="AA5" t="n">
         <v>1.546279619244071e-06</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>86.41644623323495</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.968x + -8820.971</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.96768259864628</v>
       </c>
       <c r="X6" t="n">
         <v>-8820.971473368434</v>
@@ -3950,7 +3836,7 @@
         <v>464.0618202839452</v>
       </c>
       <c r="Z6" t="n">
-        <v>99.18700000000001</v>
+        <v>266449676.4856685</v>
       </c>
       <c r="AA6" t="n">
         <v>1.416616707267517e-06</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>86.46781189788122</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.200x + -8822.491</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.20048960678877</v>
       </c>
       <c r="X7" t="n">
         <v>-8822.49052332835</v>
@@ -4002,7 +3886,7 @@
         <v>458.8129218312916</v>
       </c>
       <c r="Z7" t="n">
-        <v>96.51100000000008</v>
+        <v>29108738.45743059</v>
       </c>
       <c r="AA7" t="n">
         <v>1.323451476185574e-06</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>86.51486193447968</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.420x + -8812.922</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.41975076668417</v>
       </c>
       <c r="X8" t="n">
         <v>-8812.921887403612</v>
@@ -4054,7 +3936,7 @@
         <v>453.1626101977044</v>
       </c>
       <c r="Z8" t="n">
-        <v>96.16399999999999</v>
+        <v>179414853.6158305</v>
       </c>
       <c r="AA8" t="n">
         <v>1.25404088657733e-06</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>86.51034475496964</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.398x + -8660.449</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.39844369081006</v>
       </c>
       <c r="X9" t="n">
         <v>-8660.448950401082</v>
@@ -4106,7 +3986,7 @@
         <v>447.4505321666326</v>
       </c>
       <c r="Z9" t="n">
-        <v>94.30100000000004</v>
+        <v>82895946.05834448</v>
       </c>
       <c r="AA9" t="n">
         <v>1.191766518712591e-06</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>86.59874183786719</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 16.826x + -8761.127</t>
-        </is>
+      <c r="W10" t="n">
+        <v>16.82567386277453</v>
       </c>
       <c r="X10" t="n">
         <v>-8761.127318496159</v>
@@ -4158,7 +4036,7 @@
         <v>441.9769639623128</v>
       </c>
       <c r="Z10" t="n">
-        <v>93.14399999999995</v>
+        <v>114951946.6660604</v>
       </c>
       <c r="AA10" t="n">
         <v>1.14075280656471e-06</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>86.70715520511527</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.381x + -8935.365</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.38092384372241</v>
       </c>
       <c r="X11" t="n">
         <v>-8935.364647830273</v>
@@ -4210,7 +4086,7 @@
         <v>436.7184993165156</v>
       </c>
       <c r="Z11" t="n">
-        <v>91.59100000000001</v>
+        <v>75285427.38131291</v>
       </c>
       <c r="AA11" t="n">
         <v>1.100065549795278e-06</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>86.09884029082536</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.664x + -9168.045</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.66415516767536</v>
       </c>
       <c r="X2" t="n">
         <v>-9168.045261675268</v>
@@ -4408,7 +4282,7 @@
         <v>444.1272595847075</v>
       </c>
       <c r="Z2" t="n">
-        <v>107.129</v>
+        <v>108864793.1901087</v>
       </c>
       <c r="AA2" t="n">
         <v>1.23384089549512e-05</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>86.44781561778335</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.109x + -9613.249</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.10906020334769</v>
       </c>
       <c r="X3" t="n">
         <v>-9613.249141578935</v>
@@ -4460,7 +4332,7 @@
         <v>483.8378742692371</v>
       </c>
       <c r="Z3" t="n">
-        <v>93.601</v>
+        <v>96173839.7698317</v>
       </c>
       <c r="AA3" t="n">
         <v>2.809131246282537e-06</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>86.31932891105524</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 15.545x + -9084.446</t>
-        </is>
+      <c r="W4" t="n">
+        <v>15.54524737775507</v>
       </c>
       <c r="X4" t="n">
         <v>-9084.445695273294</v>
@@ -4512,7 +4382,7 @@
         <v>481.9175302628286</v>
       </c>
       <c r="Z4" t="n">
-        <v>92.25099999999998</v>
+        <v>434126598.6003155</v>
       </c>
       <c r="AA4" t="n">
         <v>2.27596436351776e-06</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>86.58067505465303</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.737x + -9693.610</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.73656181709892</v>
       </c>
       <c r="X5" t="n">
         <v>-9693.609583300185</v>
@@ -4564,7 +4432,7 @@
         <v>480.7478539399942</v>
       </c>
       <c r="Z5" t="n">
-        <v>89.05499999999995</v>
+        <v>394980255.859816</v>
       </c>
       <c r="AA5" t="n">
         <v>1.738300323053375e-06</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>86.46714595864923</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.197x + -9243.748</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.19742807996265</v>
       </c>
       <c r="X6" t="n">
         <v>-9243.747570538677</v>
@@ -4616,7 +4482,7 @@
         <v>476.4086466037708</v>
       </c>
       <c r="Z6" t="n">
-        <v>88.66300000000001</v>
+        <v>448482705.571925</v>
       </c>
       <c r="AA6" t="n">
         <v>1.610043817204512e-06</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>86.38348824761647</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.822x + -8893.081</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.821784017322</v>
       </c>
       <c r="X7" t="n">
         <v>-8893.081304166333</v>
@@ -4668,7 +4532,7 @@
         <v>471.7079776354223</v>
       </c>
       <c r="Z7" t="n">
-        <v>88.54200000000003</v>
+        <v>33836282.58977511</v>
       </c>
       <c r="AA7" t="n">
         <v>1.508835727844292e-06</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>86.46683111339421</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.196x + -8995.915</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.1959810410846</v>
       </c>
       <c r="X8" t="n">
         <v>-8995.914981161315</v>
@@ -4720,7 +4582,7 @@
         <v>466.9010668586121</v>
       </c>
       <c r="Z8" t="n">
-        <v>85.83799999999997</v>
+        <v>252841154.3298536</v>
       </c>
       <c r="AA8" t="n">
         <v>1.429287957105137e-06</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>86.58083054750514</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.737x + -9195.304</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.73732475235285</v>
       </c>
       <c r="X9" t="n">
         <v>-9195.303952956188</v>
@@ -4772,7 +4632,7 @@
         <v>462.2085125306908</v>
       </c>
       <c r="Z9" t="n">
-        <v>82.87699999999995</v>
+        <v>150849216.6590624</v>
       </c>
       <c r="AA9" t="n">
         <v>1.365786026408263e-06</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>86.47075669293118</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 16.214x + -8779.878</t>
-        </is>
+      <c r="W10" t="n">
+        <v>16.2140415656756</v>
       </c>
       <c r="X10" t="n">
         <v>-8779.878118726585</v>
@@ -4824,7 +4682,7 @@
         <v>457.7292824094559</v>
       </c>
       <c r="Z10" t="n">
-        <v>84.09299999999996</v>
+        <v>59808375.2467428</v>
       </c>
       <c r="AA10" t="n">
         <v>1.312195813450152e-06</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>86.52072046388218</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 16.447x + -8809.539</t>
-        </is>
+      <c r="W11" t="n">
+        <v>16.44746716044817</v>
       </c>
       <c r="X11" t="n">
         <v>-8809.539496702904</v>
@@ -4876,7 +4732,7 @@
         <v>453.4089835910032</v>
       </c>
       <c r="Z11" t="n">
-        <v>82.20100000000002</v>
+        <v>59504330.46251216</v>
       </c>
       <c r="AA11" t="n">
         <v>1.266543799497662e-06</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>86.68044798971584</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 17.241x + -9158.798</t>
-        </is>
+      <c r="W12" t="n">
+        <v>17.24077723915691</v>
       </c>
       <c r="X12" t="n">
         <v>-9158.797661151497</v>
@@ -4928,7 +4782,7 @@
         <v>449.3128788115454</v>
       </c>
       <c r="Z12" t="n">
-        <v>80.21000000000004</v>
+        <v>58519160.6841563</v>
       </c>
       <c r="AA12" t="n">
         <v>1.228846453558306e-06</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>86.59022587957202</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 16.784x + -8804.543</t>
-        </is>
+      <c r="W13" t="n">
+        <v>16.78355249768228</v>
       </c>
       <c r="X13" t="n">
         <v>-8804.542669663158</v>
@@ -4980,7 +4832,7 @@
         <v>445.3372836648231</v>
       </c>
       <c r="Z13" t="n">
-        <v>80.28700000000003</v>
+        <v>176529882.1420476</v>
       </c>
       <c r="AA13" t="n">
         <v>1.196660354521983e-06</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>86.56760377659262</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 16.673x + -8648.770</t>
-        </is>
+      <c r="W14" t="n">
+        <v>16.672673637864</v>
       </c>
       <c r="X14" t="n">
         <v>-8648.770055613191</v>
@@ -5032,7 +4882,7 @@
         <v>441.4633788509963</v>
       </c>
       <c r="Z14" t="n">
-        <v>80.30300000000005</v>
+        <v>32229912.12559871</v>
       </c>
       <c r="AA14" t="n">
         <v>1.167379872379136e-06</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>86.66078674449373</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 17.139x + -8816.128</t>
-        </is>
+      <c r="W15" t="n">
+        <v>17.13903556360076</v>
       </c>
       <c r="X15" t="n">
         <v>-8816.128156542951</v>
@@ -5084,7 +4932,7 @@
         <v>437.6124367348919</v>
       </c>
       <c r="Z15" t="n">
-        <v>79.08799999999997</v>
+        <v>217606140.6536585</v>
       </c>
       <c r="AA15" t="n">
         <v>1.142694722031057e-06</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>86.6944385266701</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 17.314x + -8819.790</t>
-        </is>
+      <c r="W16" t="n">
+        <v>17.31391071908497</v>
       </c>
       <c r="X16" t="n">
         <v>-8819.790180277078</v>
@@ -5136,7 +4982,7 @@
         <v>433.8524003031019</v>
       </c>
       <c r="Z16" t="n">
-        <v>78.62199999999996</v>
+        <v>36112145.07855842</v>
       </c>
       <c r="AA16" t="n">
         <v>1.117052348485922e-06</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>86.77865078601785</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 17.768x + -8974.515</t>
-        </is>
+      <c r="W17" t="n">
+        <v>17.76752271114635</v>
       </c>
       <c r="X17" t="n">
         <v>-8974.515075371071</v>
@@ -5188,7 +5032,7 @@
         <v>430.0687681233816</v>
       </c>
       <c r="Z17" t="n">
-        <v>76.26300000000003</v>
+        <v>469549170.1307999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.094444907575688e-06</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>86.42938387225492</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 16.026x + -7959.370</t>
-        </is>
+      <c r="W18" t="n">
+        <v>16.02569019930987</v>
       </c>
       <c r="X18" t="n">
         <v>-7959.370109641281</v>
@@ -5240,7 +5082,7 @@
         <v>426.3236654765057</v>
       </c>
       <c r="Z18" t="n">
-        <v>78.697</v>
+        <v>48188148.78191241</v>
       </c>
       <c r="AA18" t="n">
         <v>1.070764944305307e-06</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>86.69524674808845</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 17.318x + -8556.045</t>
-        </is>
+      <c r="W19" t="n">
+        <v>17.31815447593515</v>
       </c>
       <c r="X19" t="n">
         <v>-8556.044908255646</v>
@@ -5292,7 +5132,7 @@
         <v>422.6080774865547</v>
       </c>
       <c r="Z19" t="n">
-        <v>75.11499999999995</v>
+        <v>30729510.39641538</v>
       </c>
       <c r="AA19" t="n">
         <v>1.050392275350101e-06</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>86.80687561158989</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 17.925x + -8782.754</t>
-        </is>
+      <c r="W20" t="n">
+        <v>17.92490429093078</v>
       </c>
       <c r="X20" t="n">
         <v>-8782.753613832549</v>
@@ -5344,7 +5182,7 @@
         <v>418.8492119872903</v>
       </c>
       <c r="Z20" t="n">
-        <v>74.31799999999998</v>
+        <v>99699177.8356974</v>
       </c>
       <c r="AA20" t="n">
         <v>1.033104798877223e-06</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>86.76109712077208</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 17.671x + -8563.081</t>
-        </is>
+      <c r="W21" t="n">
+        <v>17.67102547793089</v>
       </c>
       <c r="X21" t="n">
         <v>-8563.08091120807</v>
@@ -5396,7 +5232,7 @@
         <v>415.0822496434679</v>
       </c>
       <c r="Z21" t="n">
-        <v>74.33799999999997</v>
+        <v>189549326.6332638</v>
       </c>
       <c r="AA21" t="n">
         <v>1.016993736638098e-06</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>86.5844236207531</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 16.755x + -8009.531</t>
-        </is>
+      <c r="W22" t="n">
+        <v>16.75497371290091</v>
       </c>
       <c r="X22" t="n">
         <v>-8009.531316887499</v>
@@ -5448,7 +5282,7 @@
         <v>411.336132300142</v>
       </c>
       <c r="Z22" t="n">
-        <v>74.12699999999995</v>
+        <v>274160802.661543</v>
       </c>
       <c r="AA22" t="n">
         <v>9.982190114390554e-07</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>84.66028256898838</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.699x + -7302.502</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.6990312958025</v>
       </c>
       <c r="X2" t="n">
         <v>-7302.501598697544</v>
@@ -5646,7 +5478,7 @@
         <v>448.0868660230072</v>
       </c>
       <c r="Z2" t="n">
-        <v>201.391</v>
+        <v>432120763.4442663</v>
       </c>
       <c r="AA2" t="n">
         <v>1.524193114130107e-05</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>85.72490414119909</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.377x + -7870.420</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.37734026843357</v>
       </c>
       <c r="X3" t="n">
         <v>-7870.419776766566</v>
@@ -5698,7 +5528,7 @@
         <v>458.0576473385265</v>
       </c>
       <c r="Z3" t="n">
-        <v>150.1640000000001</v>
+        <v>1535254073.316125</v>
       </c>
       <c r="AA3" t="n">
         <v>6.600865462276436e-06</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.87143116814933</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.854x + -7842.512</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.85385184086968</v>
       </c>
       <c r="X4" t="n">
         <v>-7842.511579781048</v>
@@ -5750,7 +5578,7 @@
         <v>469.9161833437443</v>
       </c>
       <c r="Z4" t="n">
-        <v>135.5309999999999</v>
+        <v>426543626.2747911</v>
       </c>
       <c r="AA4" t="n">
         <v>2.583984295924121e-06</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>86.31820763514392</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.541x + -8701.710</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.54050007974512</v>
       </c>
       <c r="X5" t="n">
         <v>-8701.709860191046</v>
@@ -5802,7 +5628,7 @@
         <v>467.1531956187354</v>
       </c>
       <c r="Z5" t="n">
-        <v>124.5509999999999</v>
+        <v>384295557.1347258</v>
       </c>
       <c r="AA5" t="n">
         <v>2.041696351356739e-06</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>86.13165010017671</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.789x + -8118.922</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.78891432840433</v>
       </c>
       <c r="X6" t="n">
         <v>-8118.921871447683</v>
@@ -5854,7 +5678,7 @@
         <v>463.0916462350833</v>
       </c>
       <c r="Z6" t="n">
-        <v>121.155</v>
+        <v>566243428.233409</v>
       </c>
       <c r="AA6" t="n">
         <v>1.78246445523967e-06</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>86.44123434496925</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.079x + -8744.575</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.07919295827195</v>
       </c>
       <c r="X7" t="n">
         <v>-8744.574638608035</v>
@@ -5906,7 +5728,7 @@
         <v>458.155366719374</v>
       </c>
       <c r="Z7" t="n">
-        <v>114.4739999999999</v>
+        <v>335321526.4706919</v>
       </c>
       <c r="AA7" t="n">
         <v>1.619416189556971e-06</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>86.29102253757358</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 15.426x + -8232.455</t>
-        </is>
+      <c r="W8" t="n">
+        <v>15.42628003873503</v>
       </c>
       <c r="X8" t="n">
         <v>-8232.455344380243</v>
@@ -5958,7 +5778,7 @@
         <v>453.0897904582574</v>
       </c>
       <c r="Z8" t="n">
-        <v>113.3599999999999</v>
+        <v>201694822.5567918</v>
       </c>
       <c r="AA8" t="n">
         <v>1.496395515594004e-06</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>86.53411292493462</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.511x + -8721.625</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.51117767689291</v>
       </c>
       <c r="X9" t="n">
         <v>-8721.625051795852</v>
@@ -6010,7 +5828,7 @@
         <v>447.9884789038092</v>
       </c>
       <c r="Z9" t="n">
-        <v>106.962</v>
+        <v>206934293.3790737</v>
       </c>
       <c r="AA9" t="n">
         <v>1.404995852608527e-06</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>86.42366930959109</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 16.000x + -8311.734</t>
-        </is>
+      <c r="W10" t="n">
+        <v>16.0000165272244</v>
       </c>
       <c r="X10" t="n">
         <v>-8311.733703603246</v>
@@ -6062,7 +5878,7 @@
         <v>443.0473409330044</v>
       </c>
       <c r="Z10" t="n">
-        <v>105.9420000000001</v>
+        <v>240801249.3798047</v>
       </c>
       <c r="AA10" t="n">
         <v>1.334299345676491e-06</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>86.47190368232027</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 16.219x + -8319.006</t>
-        </is>
+      <c r="W11" t="n">
+        <v>16.21932612958744</v>
       </c>
       <c r="X11" t="n">
         <v>-8319.005571557916</v>
@@ -6114,7 +5928,7 @@
         <v>438.4193282355079</v>
       </c>
       <c r="Z11" t="n">
-        <v>104.413</v>
+        <v>25806229.035969</v>
       </c>
       <c r="AA11" t="n">
         <v>1.278349313536701e-06</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>86.03281935299277</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.419x + -8998.038</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.41935528366748</v>
       </c>
       <c r="X2" t="n">
         <v>-8998.037819848076</v>
@@ -6312,7 +6124,7 @@
         <v>428.8948341124835</v>
       </c>
       <c r="Z2" t="n">
-        <v>127.0940000000001</v>
+        <v>281385923.9833325</v>
       </c>
       <c r="AA2" t="n">
         <v>1.59815863015575e-05</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>85.86164679763668</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.821x + -8186.698</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.82098318058108</v>
       </c>
       <c r="X3" t="n">
         <v>-8186.697565978693</v>
@@ -6364,7 +6174,7 @@
         <v>432.850749027939</v>
       </c>
       <c r="Z3" t="n">
-        <v>114.9109999999999</v>
+        <v>1242917534.074502</v>
       </c>
       <c r="AA3" t="n">
         <v>1.266007038497087e-05</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>86.19508813400054</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 15.036x + -8805.343</t>
-        </is>
+      <c r="W4" t="n">
+        <v>15.03622972663303</v>
       </c>
       <c r="X4" t="n">
         <v>-8805.342610140813</v>
@@ -6416,7 +6224,7 @@
         <v>467.1079398612561</v>
       </c>
       <c r="Z4" t="n">
-        <v>105.343</v>
+        <v>2385939196.343543</v>
       </c>
       <c r="AA4" t="n">
         <v>4.385364504891636e-06</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>86.40674426826318</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.924x + -9242.404</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.92445628612508</v>
       </c>
       <c r="X5" t="n">
         <v>-9242.403888453036</v>
@@ -6468,7 +6274,7 @@
         <v>462.8740630068066</v>
       </c>
       <c r="Z5" t="n">
-        <v>99.14700000000005</v>
+        <v>434719763.9625528</v>
       </c>
       <c r="AA5" t="n">
         <v>4.149164943798226e-06</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>86.1408049396007</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.824x + -8456.182</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.8241035214749</v>
       </c>
       <c r="X6" t="n">
         <v>-8456.181561102565</v>
@@ -6520,7 +6324,7 @@
         <v>467.6597870742491</v>
       </c>
       <c r="Z6" t="n">
-        <v>99.7890000000001</v>
+        <v>340266557.6764494</v>
       </c>
       <c r="AA6" t="n">
         <v>2.653407641557734e-06</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>86.40851752037459</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.932x + -9008.677</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.93233944722355</v>
       </c>
       <c r="X7" t="n">
         <v>-9008.67653005546</v>
@@ -6572,7 +6374,7 @@
         <v>465.6648062293336</v>
       </c>
       <c r="Z7" t="n">
-        <v>94.78200000000004</v>
+        <v>660870073.005559</v>
       </c>
       <c r="AA7" t="n">
         <v>2.122843238729958e-06</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>86.43720129708646</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.061x + -8959.764</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.06094456924135</v>
       </c>
       <c r="X8" t="n">
         <v>-8959.763870917543</v>
@@ -6624,7 +6424,7 @@
         <v>460.5572545164216</v>
       </c>
       <c r="Z8" t="n">
-        <v>91.81600000000003</v>
+        <v>59335483.17586935</v>
       </c>
       <c r="AA8" t="n">
         <v>2.041024618743799e-06</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>86.28508447384245</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.402x + -8452.194</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.40155300398406</v>
       </c>
       <c r="X9" t="n">
         <v>-8452.194266275221</v>
@@ -6676,7 +6474,7 @@
         <v>456.4816585955455</v>
       </c>
       <c r="Z9" t="n">
-        <v>92.38999999999999</v>
+        <v>31268812.87347665</v>
       </c>
       <c r="AA9" t="n">
         <v>1.865979968654931e-06</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>86.32324995252912</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.562x + -8434.849</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.56187115866204</v>
       </c>
       <c r="X10" t="n">
         <v>-8434.84913626253</v>
@@ -6728,7 +6524,7 @@
         <v>453.0450447735507</v>
       </c>
       <c r="Z10" t="n">
-        <v>90.57899999999995</v>
+        <v>331677476.4595311</v>
       </c>
       <c r="AA10" t="n">
         <v>1.643433532120073e-06</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>86.48826426941312</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 16.295x + -8755.167</t>
-        </is>
+      <c r="W11" t="n">
+        <v>16.29508015012644</v>
       </c>
       <c r="X11" t="n">
         <v>-8755.166632520968</v>
@@ -6780,7 +6574,7 @@
         <v>448.9862634315634</v>
       </c>
       <c r="Z11" t="n">
-        <v>87.71500000000003</v>
+        <v>46571901.01023883</v>
       </c>
       <c r="AA11" t="n">
         <v>1.555444941424885e-06</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>86.602996634245</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 16.847x + -8967.317</t>
-        </is>
+      <c r="W12" t="n">
+        <v>16.84679782633561</v>
       </c>
       <c r="X12" t="n">
         <v>-8967.316715429086</v>
@@ -6832,7 +6624,7 @@
         <v>445.0313496302306</v>
       </c>
       <c r="Z12" t="n">
-        <v>84.66300000000001</v>
+        <v>221089791.1095856</v>
       </c>
       <c r="AA12" t="n">
         <v>1.484715450195128e-06</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>86.71849331651104</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 17.441x + -9203.161</t>
-        </is>
+      <c r="W13" t="n">
+        <v>17.44110982551324</v>
       </c>
       <c r="X13" t="n">
         <v>-9203.16118004487</v>
@@ -6884,7 +6674,7 @@
         <v>441.2023387667601</v>
       </c>
       <c r="Z13" t="n">
-        <v>82.99200000000008</v>
+        <v>101486988.0634213</v>
       </c>
       <c r="AA13" t="n">
         <v>1.42824167874795e-06</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>86.29088641881872</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 15.426x + -7986.190</t>
-        </is>
+      <c r="W14" t="n">
+        <v>15.42571233335039</v>
       </c>
       <c r="X14" t="n">
         <v>-7986.190497144414</v>
@@ -6936,7 +6724,7 @@
         <v>437.4715723862098</v>
       </c>
       <c r="Z14" t="n">
-        <v>86.49799999999999</v>
+        <v>57449690.51259881</v>
       </c>
       <c r="AA14" t="n">
         <v>1.379727520644663e-06</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>86.50371673617262</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 16.367x + -8419.750</t>
-        </is>
+      <c r="W15" t="n">
+        <v>16.36727953793666</v>
       </c>
       <c r="X15" t="n">
         <v>-8419.750097659607</v>
@@ -6988,7 +6774,7 @@
         <v>433.8090666612601</v>
       </c>
       <c r="Z15" t="n">
-        <v>82.43700000000001</v>
+        <v>200800953.828605</v>
       </c>
       <c r="AA15" t="n">
         <v>1.333391361176151e-06</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>86.42903280883154</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 16.024x + -8153.537</t>
-        </is>
+      <c r="W16" t="n">
+        <v>16.02411061962765</v>
       </c>
       <c r="X16" t="n">
         <v>-8153.537225727913</v>
@@ -7040,7 +6824,7 @@
         <v>430.2380017060291</v>
       </c>
       <c r="Z16" t="n">
-        <v>81.62900000000002</v>
+        <v>39389064.77154506</v>
       </c>
       <c r="AA16" t="n">
         <v>1.293232785149028e-06</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>86.54830245463963</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 16.579x + -8367.410</t>
-        </is>
+      <c r="W17" t="n">
+        <v>16.57921874263137</v>
       </c>
       <c r="X17" t="n">
         <v>-8367.410371942011</v>
@@ -7092,7 +6874,7 @@
         <v>426.6129276690558</v>
       </c>
       <c r="Z17" t="n">
-        <v>80.48099999999999</v>
+        <v>65467756.19810615</v>
       </c>
       <c r="AA17" t="n">
         <v>1.261495630592835e-06</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>86.58297226724598</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 16.748x + -8372.142</t>
-        </is>
+      <c r="W18" t="n">
+        <v>16.74784028843792</v>
       </c>
       <c r="X18" t="n">
         <v>-8372.141872889862</v>
@@ -7144,7 +6924,7 @@
         <v>422.9245303454863</v>
       </c>
       <c r="Z18" t="n">
-        <v>78.85100000000006</v>
+        <v>167261841.6995843</v>
       </c>
       <c r="AA18" t="n">
         <v>1.230586387078175e-06</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>86.76825808540362</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 17.710x + -8793.047</t>
-        </is>
+      <c r="W19" t="n">
+        <v>17.71026477324596</v>
       </c>
       <c r="X19" t="n">
         <v>-8793.046607036948</v>
@@ -7196,7 +6974,7 @@
         <v>419.3080136373871</v>
       </c>
       <c r="Z19" t="n">
-        <v>75.75599999999997</v>
+        <v>62055996.3369637</v>
       </c>
       <c r="AA19" t="n">
         <v>1.197927246364865e-06</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>86.51465982914073</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 16.419x + -8030.453</t>
-        </is>
+      <c r="W20" t="n">
+        <v>16.41879627757449</v>
       </c>
       <c r="X20" t="n">
         <v>-8030.453118528424</v>
@@ -7248,7 +7024,7 @@
         <v>415.5416941202325</v>
       </c>
       <c r="Z20" t="n">
-        <v>77.63899999999995</v>
+        <v>73608840.73400299</v>
       </c>
       <c r="AA20" t="n">
         <v>1.173842519935232e-06</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>86.54094038033492</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 16.544x + -8010.580</t>
-        </is>
+      <c r="W21" t="n">
+        <v>16.54384682346686</v>
       </c>
       <c r="X21" t="n">
         <v>-8010.580184951246</v>
@@ -7300,7 +7074,7 @@
         <v>411.0599239163823</v>
       </c>
       <c r="Z21" t="n">
-        <v>76.26400000000001</v>
+        <v>106111814.6856551</v>
       </c>
       <c r="AA21" t="n">
         <v>1.149276738290599e-06</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>86.47140388244669</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 16.217x + -7761.131</t>
-        </is>
+      <c r="W22" t="n">
+        <v>16.2170229625122</v>
       </c>
       <c r="X22" t="n">
         <v>-7761.130699727876</v>
@@ -7352,7 +7124,7 @@
         <v>407.4459078658471</v>
       </c>
       <c r="Z22" t="n">
-        <v>76.65400000000005</v>
+        <v>51632562.71932381</v>
       </c>
       <c r="AA22" t="n">
         <v>1.1268057007435e-06</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>84.29324554001242</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.007x + -6504.175</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.0067712903218</v>
       </c>
       <c r="X2" t="n">
         <v>-6504.174744469758</v>
@@ -7550,7 +7320,7 @@
         <v>431.3802792910544</v>
       </c>
       <c r="Z2" t="n">
-        <v>212.079</v>
+        <v>517134002.377484</v>
       </c>
       <c r="AA2" t="n">
         <v>1.611346149556508e-05</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.31756945895515</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.209x + -7000.487</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.2090796213082</v>
       </c>
       <c r="X3" t="n">
         <v>-7000.486509476262</v>
@@ -7602,7 +7370,7 @@
         <v>406.1964822742892</v>
       </c>
       <c r="Z3" t="n">
-        <v>163.888</v>
+        <v>531464218.9944366</v>
       </c>
       <c r="AA3" t="n">
         <v>1.740229790163936e-05</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>85.85794459005777</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.809x + -7709.912</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.8085867696154</v>
       </c>
       <c r="X4" t="n">
         <v>-7709.912167855526</v>
@@ -7654,7 +7420,7 @@
         <v>443.7626362359905</v>
       </c>
       <c r="Z4" t="n">
-        <v>142.399</v>
+        <v>943955460.2865905</v>
       </c>
       <c r="AA4" t="n">
         <v>5.426695995703156e-06</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>86.08631888573478</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.617x + -8039.545</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.61709321768785</v>
       </c>
       <c r="X5" t="n">
         <v>-8039.545069267775</v>
@@ -7706,7 +7470,7 @@
         <v>450.3571189902734</v>
       </c>
       <c r="Z5" t="n">
-        <v>131.019</v>
+        <v>4626438561.604074</v>
       </c>
       <c r="AA5" t="n">
         <v>3.084830119527758e-06</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>86.35350537499718</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.691x + -8539.226</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.69134364300222</v>
       </c>
       <c r="X6" t="n">
         <v>-8539.226460839291</v>
@@ -7758,7 +7520,7 @@
         <v>448.2740800618595</v>
       </c>
       <c r="Z6" t="n">
-        <v>120.7569999999999</v>
+        <v>38662165.69008265</v>
       </c>
       <c r="AA6" t="n">
         <v>2.502778957277981e-06</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>86.15776587493272</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 14.890x + -7943.922</t>
-        </is>
+      <c r="W7" t="n">
+        <v>14.88974008794273</v>
       </c>
       <c r="X7" t="n">
         <v>-7943.922326265624</v>
@@ -7810,7 +7570,7 @@
         <v>445.387017325304</v>
       </c>
       <c r="Z7" t="n">
-        <v>117.977</v>
+        <v>323432221.225269</v>
       </c>
       <c r="AA7" t="n">
         <v>2.038708159641297e-06</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>86.20263531704791</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 15.066x + -7915.946</t>
-        </is>
+      <c r="W8" t="n">
+        <v>15.06620187371839</v>
       </c>
       <c r="X8" t="n">
         <v>-7915.945534897673</v>
@@ -7862,7 +7620,7 @@
         <v>440.9694717024348</v>
       </c>
       <c r="Z8" t="n">
-        <v>113.365</v>
+        <v>191695188.0984681</v>
       </c>
       <c r="AA8" t="n">
         <v>1.811950100208866e-06</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>86.42234109702724</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.994x + -8313.245</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.99406103152173</v>
       </c>
       <c r="X9" t="n">
         <v>-8313.244926148822</v>
@@ -7914,7 +7670,7 @@
         <v>436.1590196059623</v>
       </c>
       <c r="Z9" t="n">
-        <v>107.6489999999999</v>
+        <v>52198606.42273451</v>
       </c>
       <c r="AA9" t="n">
         <v>1.659649004426688e-06</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>86.2101776795749</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.096x + -7692.415</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.09627396283187</v>
       </c>
       <c r="X10" t="n">
         <v>-7692.415457396726</v>
@@ -7966,7 +7720,7 @@
         <v>431.4033591607503</v>
       </c>
       <c r="Z10" t="n">
-        <v>106.513</v>
+        <v>89153392.15322308</v>
       </c>
       <c r="AA10" t="n">
         <v>1.539947714236846e-06</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>86.23391246743091</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 15.192x + -7635.581</t>
-        </is>
+      <c r="W11" t="n">
+        <v>15.19169150364624</v>
       </c>
       <c r="X11" t="n">
         <v>-7635.581378916427</v>
@@ -8018,7 +7770,7 @@
         <v>426.8422070299947</v>
       </c>
       <c r="Z11" t="n">
-        <v>104.591</v>
+        <v>135098491.7655998</v>
       </c>
       <c r="AA11" t="n">
         <v>1.455402046740741e-06</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>85.95011125627252</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.124x + -8799.587</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.12392554478488</v>
       </c>
       <c r="X2" t="n">
         <v>-8799.586962586653</v>
@@ -8216,7 +7966,7 @@
         <v>429.7932192605974</v>
       </c>
       <c r="Z2" t="n">
-        <v>129.4920000000001</v>
+        <v>562592999.5669701</v>
       </c>
       <c r="AA2" t="n">
         <v>1.627895485631908e-05</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>86.09480031582621</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.649x + -8712.208</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.64893791468133</v>
       </c>
       <c r="X3" t="n">
         <v>-8712.207715790601</v>
@@ -8268,7 +8016,7 @@
         <v>419.6303894013049</v>
       </c>
       <c r="Z3" t="n">
-        <v>114.0500000000001</v>
+        <v>817488492.7871574</v>
       </c>
       <c r="AA3" t="n">
         <v>1.672088246815811e-05</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>86.05397946992426</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.497x + -8459.160</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.49692457470197</v>
       </c>
       <c r="X4" t="n">
         <v>-8459.159807644928</v>
@@ -8320,7 +8066,7 @@
         <v>429.617769656206</v>
       </c>
       <c r="Z4" t="n">
-        <v>109.6369999999999</v>
+        <v>710104774.3432301</v>
       </c>
       <c r="AA4" t="n">
         <v>1.255706842964694e-05</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>86.20353949558505</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.070x + -8694.053</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.06980062195729</v>
       </c>
       <c r="X5" t="n">
         <v>-8694.053340036611</v>
@@ -8372,7 +8116,7 @@
         <v>452.3229894707206</v>
       </c>
       <c r="Z5" t="n">
-        <v>103.674</v>
+        <v>808203832.0034522</v>
       </c>
       <c r="AA5" t="n">
         <v>6.152092620533742e-06</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>86.46264421811694</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.177x + -9257.357</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.17676239454528</v>
       </c>
       <c r="X6" t="n">
         <v>-9257.356887068754</v>
@@ -8424,7 +8166,7 @@
         <v>454.7715577815473</v>
       </c>
       <c r="Z6" t="n">
-        <v>99.44299999999998</v>
+        <v>1970217010.584641</v>
       </c>
       <c r="AA6" t="n">
         <v>4.661555103148826e-06</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>85.98322467867696</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 14.241x + -7971.611</t>
-        </is>
+      <c r="W7" t="n">
+        <v>14.24074725219623</v>
       </c>
       <c r="X7" t="n">
         <v>-7971.611483143059</v>
@@ -8476,7 +8216,7 @@
         <v>459.2726757585126</v>
       </c>
       <c r="Z7" t="n">
-        <v>100.6600000000001</v>
+        <v>372756534.5368027</v>
       </c>
       <c r="AA7" t="n">
         <v>3.006160791815131e-06</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>86.10727891488591</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.696x + -8138.293</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.69604241525118</v>
       </c>
       <c r="X8" t="n">
         <v>-8138.293414799076</v>
@@ -8528,7 +8266,7 @@
         <v>458.37568208228</v>
       </c>
       <c r="Z8" t="n">
-        <v>98.54599999999994</v>
+        <v>473829535.3887117</v>
       </c>
       <c r="AA8" t="n">
         <v>2.330515857217783e-06</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>86.24132441411275</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.222x + -8346.133</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.22173524286037</v>
       </c>
       <c r="X9" t="n">
         <v>-8346.133023764769</v>
@@ -8580,7 +8316,7 @@
         <v>454.9831432895858</v>
       </c>
       <c r="Z9" t="n">
-        <v>96.54000000000008</v>
+        <v>204470522.9006511</v>
       </c>
       <c r="AA9" t="n">
         <v>2.115043053145326e-06</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>86.57823194614254</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 16.725x + -9121.422</t>
-        </is>
+      <c r="W10" t="n">
+        <v>16.72458364745447</v>
       </c>
       <c r="X10" t="n">
         <v>-9121.422450275599</v>
@@ -8632,7 +8366,7 @@
         <v>451.2452578884005</v>
       </c>
       <c r="Z10" t="n">
-        <v>91.80100000000004</v>
+        <v>104534850.1738987</v>
       </c>
       <c r="AA10" t="n">
         <v>2.000572738836259e-06</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>86.23403615487634</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 15.192x + -8143.608</t>
-        </is>
+      <c r="W11" t="n">
+        <v>15.19219189203601</v>
       </c>
       <c r="X11" t="n">
         <v>-8143.608376541416</v>
@@ -8684,7 +8416,7 @@
         <v>448.0720873457959</v>
       </c>
       <c r="Z11" t="n">
-        <v>92.46900000000005</v>
+        <v>390125731.3063829</v>
       </c>
       <c r="AA11" t="n">
         <v>1.826975893216307e-06</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>86.27555474661604</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 15.362x + -8155.639</t>
-        </is>
+      <c r="W12" t="n">
+        <v>15.36203429133054</v>
       </c>
       <c r="X12" t="n">
         <v>-8155.639213459574</v>
@@ -8736,7 +8466,7 @@
         <v>444.4760142132259</v>
       </c>
       <c r="Z12" t="n">
-        <v>91.28700000000003</v>
+        <v>242694676.8129379</v>
       </c>
       <c r="AA12" t="n">
         <v>1.733726778152612e-06</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>86.61406644922589</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 16.902x + -8934.495</t>
-        </is>
+      <c r="W13" t="n">
+        <v>16.90200504411959</v>
       </c>
       <c r="X13" t="n">
         <v>-8934.495273070181</v>
@@ -8788,7 +8516,7 @@
         <v>441.0341296801473</v>
       </c>
       <c r="Z13" t="n">
-        <v>87.25400000000002</v>
+        <v>151335285.9289216</v>
       </c>
       <c r="AA13" t="n">
         <v>1.652955246449384e-06</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>86.41195667456248</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 15.948x + -8314.579</t>
-        </is>
+      <c r="W14" t="n">
+        <v>15.94765071620183</v>
       </c>
       <c r="X14" t="n">
         <v>-8314.579168769395</v>
@@ -8840,7 +8566,7 @@
         <v>437.5444965927232</v>
       </c>
       <c r="Z14" t="n">
-        <v>87.51700000000005</v>
+        <v>619785895.9580516</v>
       </c>
       <c r="AA14" t="n">
         <v>1.583197135291149e-06</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>86.36764732155075</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 15.753x + -8125.318</t>
-        </is>
+      <c r="W15" t="n">
+        <v>15.75260017528404</v>
       </c>
       <c r="X15" t="n">
         <v>-8125.317972457186</v>
@@ -8892,7 +8616,7 @@
         <v>434.0868146982034</v>
       </c>
       <c r="Z15" t="n">
-        <v>87.44300000000004</v>
+        <v>159004724.4555343</v>
       </c>
       <c r="AA15" t="n">
         <v>1.528213643864651e-06</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>86.39923131988029</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 15.891x + -8119.982</t>
-        </is>
+      <c r="W16" t="n">
+        <v>15.89114278155018</v>
       </c>
       <c r="X16" t="n">
         <v>-8119.982157234307</v>
@@ -8944,7 +8666,7 @@
         <v>430.6744964949223</v>
       </c>
       <c r="Z16" t="n">
-        <v>85.584</v>
+        <v>167257316.4615875</v>
       </c>
       <c r="AA16" t="n">
         <v>1.469460529271239e-06</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>86.56823354229601</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 16.676x + -8464.498</t>
-        </is>
+      <c r="W17" t="n">
+        <v>16.67574058292641</v>
       </c>
       <c r="X17" t="n">
         <v>-8464.497698882653</v>
@@ -8996,7 +8716,7 @@
         <v>427.2183042735488</v>
       </c>
       <c r="Z17" t="n">
-        <v>82.74000000000001</v>
+        <v>73278536.64309131</v>
       </c>
       <c r="AA17" t="n">
         <v>1.423873628367312e-06</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>86.19605984370624</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 15.040x + -7507.542</t>
-        </is>
+      <c r="W18" t="n">
+        <v>15.04008201906049</v>
       </c>
       <c r="X18" t="n">
         <v>-7507.542129849154</v>
@@ -9048,7 +8766,7 @@
         <v>423.6906610712998</v>
       </c>
       <c r="Z18" t="n">
-        <v>85.98600000000005</v>
+        <v>53706620.86468942</v>
       </c>
       <c r="AA18" t="n">
         <v>1.38354794085521e-06</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>86.37119903640611</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 15.768x + -7814.229</t>
-        </is>
+      <c r="W19" t="n">
+        <v>15.76805951364126</v>
       </c>
       <c r="X19" t="n">
         <v>-7814.228678086119</v>
@@ -9100,7 +8816,7 @@
         <v>420.3418232263168</v>
       </c>
       <c r="Z19" t="n">
-        <v>83.06800000000004</v>
+        <v>35319509.81477289</v>
       </c>
       <c r="AA19" t="n">
         <v>1.342587031040738e-06</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>86.3154575967724</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 15.529x + -7611.577</t>
-        </is>
+      <c r="W20" t="n">
+        <v>15.52886908561989</v>
       </c>
       <c r="X20" t="n">
         <v>-7611.576853225756</v>
@@ -9152,7 +8866,7 @@
         <v>416.8541039567747</v>
       </c>
       <c r="Z20" t="n">
-        <v>82.43200000000002</v>
+        <v>80745082.35935077</v>
       </c>
       <c r="AA20" t="n">
         <v>1.305381697007645e-06</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>86.38709435375804</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 15.838x + -7688.220</t>
-        </is>
+      <c r="W21" t="n">
+        <v>15.83761802685178</v>
       </c>
       <c r="X21" t="n">
         <v>-7688.220450246899</v>
@@ -9204,7 +8916,7 @@
         <v>413.173417094693</v>
       </c>
       <c r="Z21" t="n">
-        <v>81.73399999999998</v>
+        <v>24083557.43788818</v>
       </c>
       <c r="AA21" t="n">
         <v>1.273415623210706e-06</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>86.31899829893688</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 15.544x + -7461.779</t>
-        </is>
+      <c r="W22" t="n">
+        <v>15.54384732010938</v>
       </c>
       <c r="X22" t="n">
         <v>-7461.779420541887</v>
@@ -9256,7 +8966,7 @@
         <v>409.5263881564664</v>
       </c>
       <c r="Z22" t="n">
-        <v>80.53399999999999</v>
+        <v>122618991.6382949</v>
       </c>
       <c r="AA22" t="n">
         <v>1.241619927129778e-06</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>83.23478723234156</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.430x + -5414.042</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.429781238972879</v>
       </c>
       <c r="X2" t="n">
         <v>-5414.041814868423</v>
@@ -9454,7 +9162,7 @@
         <v>429.3284156703372</v>
       </c>
       <c r="Z2" t="n">
-        <v>246.2620000000001</v>
+        <v>402553699.9200533</v>
       </c>
       <c r="AA2" t="n">
         <v>1.656942896656787e-05</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>85.08416256317115</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.627x + -6445.594</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.62673141074112</v>
       </c>
       <c r="X3" t="n">
         <v>-6445.594085121489</v>
@@ -9506,7 +9212,7 @@
         <v>421.7191979384372</v>
       </c>
       <c r="Z3" t="n">
-        <v>177.136</v>
+        <v>1328494992.742595</v>
       </c>
       <c r="AA3" t="n">
         <v>1.053142505300511e-05</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>85.70517038129283</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.316x + -7146.132</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.3156451929969</v>
       </c>
       <c r="X4" t="n">
         <v>-7146.132424742581</v>
@@ -9558,7 +9262,7 @@
         <v>443.2816248255861</v>
       </c>
       <c r="Z4" t="n">
-        <v>153.125</v>
+        <v>165798939.9663967</v>
       </c>
       <c r="AA4" t="n">
         <v>3.215415351138841e-06</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>85.79608932309401</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.605x + -7146.514</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.60469582453691</v>
       </c>
       <c r="X5" t="n">
         <v>-7146.513889313306</v>
@@ -9610,7 +9312,7 @@
         <v>441.6105664394518</v>
       </c>
       <c r="Z5" t="n">
-        <v>141.6579999999999</v>
+        <v>580112492.5795598</v>
       </c>
       <c r="AA5" t="n">
         <v>2.32184981880586e-06</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>86.1322096647157</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.791x + -7685.932</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.79106039914917</v>
       </c>
       <c r="X6" t="n">
         <v>-7685.932461853346</v>
@@ -9662,7 +9362,7 @@
         <v>437.6272727848345</v>
       </c>
       <c r="Z6" t="n">
-        <v>131.116</v>
+        <v>47794544.42563547</v>
       </c>
       <c r="AA6" t="n">
         <v>1.9517164057488e-06</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>86.09283679408355</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 14.642x + -7469.247</t>
-        </is>
+      <c r="W7" t="n">
+        <v>14.6415533226027</v>
       </c>
       <c r="X7" t="n">
         <v>-7469.247115082168</v>
@@ -9714,7 +9412,7 @@
         <v>432.7455043802224</v>
       </c>
       <c r="Z7" t="n">
-        <v>126.609</v>
+        <v>167540934.2256478</v>
       </c>
       <c r="AA7" t="n">
         <v>1.740164012349097e-06</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>86.01793341948847</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.365x + -7190.514</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.36527923318814</v>
       </c>
       <c r="X8" t="n">
         <v>-7190.513920025728</v>
@@ -9766,7 +9462,7 @@
         <v>427.7264566839125</v>
       </c>
       <c r="Z8" t="n">
-        <v>123.917</v>
+        <v>38758243.48460139</v>
       </c>
       <c r="AA8" t="n">
         <v>1.594085761636233e-06</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>86.26989989713512</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.339x + -7597.017</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.33867958993862</v>
       </c>
       <c r="X9" t="n">
         <v>-7597.017364114158</v>
@@ -9818,7 +9512,7 @@
         <v>422.9965335576611</v>
       </c>
       <c r="Z9" t="n">
-        <v>117.938</v>
+        <v>107188625.7715122</v>
       </c>
       <c r="AA9" t="n">
         <v>1.490096372647036e-06</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>86.27825604431004</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.373x + -7510.589</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.37321574682725</v>
       </c>
       <c r="X10" t="n">
         <v>-7510.588681929537</v>
@@ -9870,7 +9562,7 @@
         <v>418.6352001544854</v>
       </c>
       <c r="Z10" t="n">
-        <v>115.861</v>
+        <v>98272582.88053755</v>
       </c>
       <c r="AA10" t="n">
         <v>1.415503448633136e-06</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>86.57205587394866</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 16.694x + -8100.325</t>
-        </is>
+      <c r="W11" t="n">
+        <v>16.69437940080897</v>
       </c>
       <c r="X11" t="n">
         <v>-8100.325238554351</v>
@@ -9922,7 +9612,7 @@
         <v>414.6717908169821</v>
       </c>
       <c r="Z11" t="n">
-        <v>110.61</v>
+        <v>13167151.73639226</v>
       </c>
       <c r="AA11" t="n">
         <v>1.351561634035653e-06</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-138.812</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-124.881</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-115.24</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-110.995</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-106.298</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-102.316</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-100.617</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-92.96100000000001</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-93.67200000000003</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-92.05400000000009</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-148.436</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-113.721</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-105.9749999999999</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-99.35599999999999</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-99.18700000000001</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-96.51100000000008</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-96.16399999999999</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-94.30100000000004</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-93.14399999999995</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-91.59100000000001</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-201.391</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-150.1640000000001</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-135.5309999999999</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-124.5509999999999</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-121.155</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-114.4739999999999</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-113.3599999999999</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-106.962</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-105.9420000000001</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-104.413</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-212.079</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-163.888</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-142.399</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-131.019</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-120.7569999999999</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-117.977</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-113.365</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-107.6489999999999</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-106.513</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-104.591</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-246.2620000000001</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-177.136</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-153.125</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-141.6579999999999</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-131.116</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-126.609</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-123.917</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-117.938</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-115.861</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-110.61</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-138.812</v>
+        <v>202.047</v>
       </c>
       <c r="D2" t="n">
         <v>5.21535e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-124.881</v>
+        <v>191.839</v>
       </c>
       <c r="D3" t="n">
         <v>5.16844e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-115.24</v>
+        <v>185.659</v>
       </c>
       <c r="D4" t="n">
         <v>5.14064e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-110.995</v>
+        <v>177.7169999999999</v>
       </c>
       <c r="D5" t="n">
         <v>5.12067e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-106.298</v>
+        <v>173.469</v>
       </c>
       <c r="D6" t="n">
         <v>5.10734e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-102.316</v>
+        <v>168.0309999999999</v>
       </c>
       <c r="D7" t="n">
         <v>5.09842e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-100.617</v>
+        <v>162.943</v>
       </c>
       <c r="D8" t="n">
         <v>5.09092e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-92.96100000000001</v>
+        <v>163.156</v>
       </c>
       <c r="D9" t="n">
         <v>5.08651e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-93.67200000000003</v>
+        <v>155.971</v>
       </c>
       <c r="D10" t="n">
         <v>5.082609999999999e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-92.05400000000009</v>
+        <v>152.0339999999999</v>
       </c>
       <c r="D11" t="n">
         <v>5.08056e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-121.05</v>
+        <v>204.684</v>
       </c>
       <c r="D2" t="n">
         <v>5.21634e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-111.737</v>
+        <v>178.233</v>
       </c>
       <c r="D3" t="n">
         <v>5.21579e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-102.237</v>
+        <v>177.282</v>
       </c>
       <c r="D4" t="n">
         <v>5.20277e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-100.225</v>
+        <v>172.5309999999999</v>
       </c>
       <c r="D5" t="n">
         <v>5.19107e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-98.95000000000005</v>
+        <v>166.1299999999999</v>
       </c>
       <c r="D6" t="n">
         <v>5.18404e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-97.99800000000005</v>
+        <v>162.554</v>
       </c>
       <c r="D7" t="n">
         <v>5.179499999999999e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-94.42200000000003</v>
+        <v>160.9569999999999</v>
       </c>
       <c r="D8" t="n">
         <v>5.17457e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-97.20600000000002</v>
+        <v>153.128</v>
       </c>
       <c r="D9" t="n">
         <v>5.17208e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-93.70299999999997</v>
+        <v>151.991</v>
       </c>
       <c r="D10" t="n">
         <v>5.17053e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-91.82900000000006</v>
+        <v>149.975</v>
       </c>
       <c r="D11" t="n">
         <v>5.16953e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-90.75300000000004</v>
+        <v>146.2569999999999</v>
       </c>
       <c r="D12" t="n">
         <v>5.16839e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-86.74799999999993</v>
+        <v>147.52</v>
       </c>
       <c r="D13" t="n">
         <v>5.16651e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-85.71799999999996</v>
+        <v>144.762</v>
       </c>
       <c r="D14" t="n">
         <v>5.16679e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-87.33100000000002</v>
+        <v>139.8</v>
       </c>
       <c r="D15" t="n">
         <v>5.16595e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-85.70400000000001</v>
+        <v>138.576</v>
       </c>
       <c r="D16" t="n">
         <v>5.16497e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-84.77199999999999</v>
+        <v>136.36</v>
       </c>
       <c r="D17" t="n">
         <v>5.16677e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-82.55399999999997</v>
+        <v>136.257</v>
       </c>
       <c r="D18" t="n">
         <v>5.16473e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-81.09499999999997</v>
+        <v>134.044</v>
       </c>
       <c r="D19" t="n">
         <v>5.16867e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-82.12599999999998</v>
+        <v>129.803</v>
       </c>
       <c r="D20" t="n">
         <v>5.16924e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-78.28100000000001</v>
+        <v>130.119</v>
       </c>
       <c r="D21" t="n">
         <v>5.16894e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-79.52400000000006</v>
+        <v>126.468</v>
       </c>
       <c r="D22" t="n">
         <v>5.17013e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-154.9829999999999</v>
+        <v>210.712</v>
       </c>
       <c r="D2" t="n">
         <v>5.25343e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-127.0749999999999</v>
+        <v>183.956</v>
       </c>
       <c r="D3" t="n">
         <v>5.20708e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-113.0509999999999</v>
+        <v>180.083</v>
       </c>
       <c r="D4" t="n">
         <v>5.178079999999999e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-110.6909999999999</v>
+        <v>172.3580000000001</v>
       </c>
       <c r="D5" t="n">
         <v>5.15806e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-103.889</v>
+        <v>170.711</v>
       </c>
       <c r="D6" t="n">
         <v>5.1463e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-97.91399999999999</v>
+        <v>168.984</v>
       </c>
       <c r="D7" t="n">
         <v>5.13615e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-94.75800000000004</v>
+        <v>165.126</v>
       </c>
       <c r="D8" t="n">
         <v>5.130670000000001e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-96.32500000000005</v>
+        <v>156.348</v>
       </c>
       <c r="D9" t="n">
         <v>5.1277e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-92.19000000000005</v>
+        <v>155.3</v>
       </c>
       <c r="D10" t="n">
         <v>5.12321e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-88.60199999999998</v>
+        <v>153.829</v>
       </c>
       <c r="D11" t="n">
         <v>5.12047e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-84.38499999999999</v>
+        <v>151.853</v>
       </c>
       <c r="D12" t="n">
         <v>5.11952e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-82.84299999999996</v>
+        <v>148.809</v>
       </c>
       <c r="D13" t="n">
         <v>5.11746e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-84.62100000000009</v>
+        <v>143.251</v>
       </c>
       <c r="D14" t="n">
         <v>5.11511e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-83.94100000000003</v>
+        <v>139.908</v>
       </c>
       <c r="D15" t="n">
         <v>5.11432e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-78.07400000000001</v>
+        <v>140.885</v>
       </c>
       <c r="D16" t="n">
         <v>5.11416e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-81.77199999999999</v>
+        <v>134.765</v>
       </c>
       <c r="D17" t="n">
         <v>5.11313e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-81.60999999999996</v>
+        <v>131.494</v>
       </c>
       <c r="D18" t="n">
         <v>5.11395e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-78.74700000000001</v>
+        <v>129.931</v>
       </c>
       <c r="D19" t="n">
         <v>5.11415e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-77.13200000000006</v>
+        <v>128.692</v>
       </c>
       <c r="D20" t="n">
         <v>5.113180000000001e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-76.80700000000007</v>
+        <v>125.114</v>
       </c>
       <c r="D21" t="n">
         <v>5.11435e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-73.47200000000004</v>
+        <v>125.383</v>
       </c>
       <c r="D22" t="n">
         <v>5.11423e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-148.436</v>
+        <v>238.871</v>
       </c>
       <c r="D2" t="n">
         <v>4.87922e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-113.721</v>
+        <v>173.854</v>
       </c>
       <c r="D3" t="n">
         <v>4.87782e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-105.9749999999999</v>
+        <v>158.3100000000001</v>
       </c>
       <c r="D4" t="n">
         <v>4.84144e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-99.35599999999999</v>
+        <v>154.839</v>
       </c>
       <c r="D5" t="n">
         <v>4.81253e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-99.18700000000001</v>
+        <v>147.86</v>
       </c>
       <c r="D6" t="n">
         <v>4.79014e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-96.51100000000008</v>
+        <v>144.188</v>
       </c>
       <c r="D7" t="n">
         <v>4.77705e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-96.16399999999999</v>
+        <v>140.3050000000001</v>
       </c>
       <c r="D8" t="n">
         <v>4.76467e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-94.30100000000004</v>
+        <v>135.5</v>
       </c>
       <c r="D9" t="n">
         <v>4.7574e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-93.14399999999995</v>
+        <v>131.688</v>
       </c>
       <c r="D10" t="n">
         <v>4.74943e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-91.59100000000001</v>
+        <v>128.871</v>
       </c>
       <c r="D11" t="n">
         <v>4.74377e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-107.129</v>
+        <v>204.016</v>
       </c>
       <c r="D2" t="n">
         <v>4.74437e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-93.601</v>
+        <v>179.986</v>
       </c>
       <c r="D3" t="n">
         <v>4.76221e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-92.25099999999998</v>
+        <v>170.772</v>
       </c>
       <c r="D4" t="n">
         <v>4.76744e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-89.05499999999995</v>
+        <v>168.457</v>
       </c>
       <c r="D5" t="n">
         <v>4.76995e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-88.66300000000001</v>
+        <v>162.661</v>
       </c>
       <c r="D6" t="n">
         <v>4.77418e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-88.54200000000003</v>
+        <v>157.551</v>
       </c>
       <c r="D7" t="n">
         <v>4.77759e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-85.83799999999997</v>
+        <v>154.458</v>
       </c>
       <c r="D8" t="n">
         <v>4.7825e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-82.87699999999995</v>
+        <v>152.2860000000001</v>
       </c>
       <c r="D9" t="n">
         <v>4.78731e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-84.09299999999996</v>
+        <v>147.229</v>
       </c>
       <c r="D10" t="n">
         <v>4.79115e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-82.20100000000002</v>
+        <v>144.8179999999999</v>
       </c>
       <c r="D11" t="n">
         <v>4.7943e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-80.21000000000004</v>
+        <v>143.027</v>
       </c>
       <c r="D12" t="n">
         <v>4.79687e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-80.28700000000003</v>
+        <v>139.073</v>
       </c>
       <c r="D13" t="n">
         <v>4.80072e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-80.30300000000005</v>
+        <v>136.257</v>
       </c>
       <c r="D14" t="n">
         <v>4.80283e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-79.08799999999997</v>
+        <v>134.838</v>
       </c>
       <c r="D15" t="n">
         <v>4.80562e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-78.62199999999996</v>
+        <v>132.256</v>
       </c>
       <c r="D16" t="n">
         <v>4.80718e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-76.26300000000003</v>
+        <v>131.183</v>
       </c>
       <c r="D17" t="n">
         <v>4.81131e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-78.697</v>
+        <v>125.34</v>
       </c>
       <c r="D18" t="n">
         <v>4.81229e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-75.11499999999995</v>
+        <v>125.903</v>
       </c>
       <c r="D19" t="n">
         <v>4.81515e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-74.31799999999998</v>
+        <v>124.379</v>
       </c>
       <c r="D20" t="n">
         <v>4.8177e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-74.33799999999997</v>
+        <v>121.612</v>
       </c>
       <c r="D21" t="n">
         <v>4.82033e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-74.12699999999995</v>
+        <v>118.135</v>
       </c>
       <c r="D22" t="n">
         <v>4.82364e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-201.391</v>
+        <v>253.4470000000001</v>
       </c>
       <c r="D2" t="n">
         <v>5.01385e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-150.1640000000001</v>
+        <v>172.7979999999999</v>
       </c>
       <c r="D3" t="n">
         <v>5.09218e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-135.5309999999999</v>
+        <v>155.4710000000001</v>
       </c>
       <c r="D4" t="n">
         <v>5.06645e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-124.5509999999999</v>
+        <v>151.967</v>
       </c>
       <c r="D5" t="n">
         <v>5.03645e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-121.155</v>
+        <v>144.878</v>
       </c>
       <c r="D6" t="n">
         <v>5.01405e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-114.4739999999999</v>
+        <v>143.576</v>
       </c>
       <c r="D7" t="n">
         <v>4.99915e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-113.3599999999999</v>
+        <v>136.6940000000001</v>
       </c>
       <c r="D8" t="n">
         <v>4.98705e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-106.962</v>
+        <v>135.736</v>
       </c>
       <c r="D9" t="n">
         <v>4.97863e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-105.9420000000001</v>
+        <v>130.203</v>
       </c>
       <c r="D10" t="n">
         <v>4.97235e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-104.413</v>
+        <v>127.462</v>
       </c>
       <c r="D11" t="n">
         <v>4.96745e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-127.0940000000001</v>
+        <v>204.199</v>
       </c>
       <c r="D2" t="n">
         <v>5.0472e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-114.9109999999999</v>
+        <v>176.8770000000001</v>
       </c>
       <c r="D3" t="n">
         <v>5.04653e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-105.343</v>
+        <v>173.34</v>
       </c>
       <c r="D4" t="n">
         <v>5.03772e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-99.14700000000005</v>
+        <v>170.826</v>
       </c>
       <c r="D5" t="n">
         <v>5.02732e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-99.7890000000001</v>
+        <v>163.6229999999999</v>
       </c>
       <c r="D6" t="n">
         <v>5.01979e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-94.78200000000004</v>
+        <v>163.093</v>
       </c>
       <c r="D7" t="n">
         <v>5.01564e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-91.81600000000003</v>
+        <v>159.327</v>
       </c>
       <c r="D8" t="n">
         <v>5.01307e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-92.38999999999999</v>
+        <v>153.55</v>
       </c>
       <c r="D9" t="n">
         <v>5.01034e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-90.57899999999995</v>
+        <v>149.8440000000001</v>
       </c>
       <c r="D10" t="n">
         <v>5.01037e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-87.71500000000003</v>
+        <v>147.658</v>
       </c>
       <c r="D11" t="n">
         <v>5.00963e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-84.66300000000001</v>
+        <v>146.007</v>
       </c>
       <c r="D12" t="n">
         <v>5.00917e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-82.99200000000008</v>
+        <v>143.929</v>
       </c>
       <c r="D13" t="n">
         <v>5.00883e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-86.49799999999999</v>
+        <v>137.064</v>
       </c>
       <c r="D14" t="n">
         <v>5.00936e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-82.43700000000001</v>
+        <v>136.907</v>
       </c>
       <c r="D15" t="n">
         <v>5.00865e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-81.62900000000002</v>
+        <v>133.383</v>
       </c>
       <c r="D16" t="n">
         <v>5.00941e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-80.48099999999999</v>
+        <v>132.185</v>
       </c>
       <c r="D17" t="n">
         <v>5.0099e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-78.85100000000006</v>
+        <v>130.94</v>
       </c>
       <c r="D18" t="n">
         <v>5.01015e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-75.75599999999997</v>
+        <v>130.161</v>
       </c>
       <c r="D19" t="n">
         <v>5.01147e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-77.63899999999995</v>
+        <v>126.241</v>
       </c>
       <c r="D20" t="n">
         <v>5.01156e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-76.26400000000001</v>
+        <v>123.382</v>
       </c>
       <c r="D21" t="n">
         <v>5.01346e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-76.65400000000005</v>
+        <v>120.958</v>
       </c>
       <c r="D22" t="n">
         <v>5.014219999999999e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-212.079</v>
+        <v>236.601</v>
       </c>
       <c r="D2" t="n">
         <v>5.34048e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-163.888</v>
+        <v>170.455</v>
       </c>
       <c r="D3" t="n">
         <v>5.40305e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-142.399</v>
+        <v>158.9570000000001</v>
       </c>
       <c r="D4" t="n">
         <v>5.35659e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-131.019</v>
+        <v>153.12</v>
       </c>
       <c r="D5" t="n">
         <v>5.30925e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-120.7569999999999</v>
+        <v>150.159</v>
       </c>
       <c r="D6" t="n">
         <v>5.27303e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-117.977</v>
+        <v>143.3390000000001</v>
       </c>
       <c r="D7" t="n">
         <v>5.2461e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-113.365</v>
+        <v>139.069</v>
       </c>
       <c r="D8" t="n">
         <v>5.22457e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-107.6489999999999</v>
+        <v>137.652</v>
       </c>
       <c r="D9" t="n">
         <v>5.20873e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-106.513</v>
+        <v>130.743</v>
       </c>
       <c r="D10" t="n">
         <v>5.19572e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-104.591</v>
+        <v>127.131</v>
       </c>
       <c r="D11" t="n">
         <v>5.18468e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-129.4920000000001</v>
+        <v>204.609</v>
       </c>
       <c r="D2" t="n">
         <v>5.190239999999999e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-114.0500000000001</v>
+        <v>180.717</v>
       </c>
       <c r="D3" t="n">
         <v>5.19621e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-109.6369999999999</v>
+        <v>172.316</v>
       </c>
       <c r="D4" t="n">
         <v>5.18674e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-103.674</v>
+        <v>169.34</v>
       </c>
       <c r="D5" t="n">
         <v>5.17863e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-99.44299999999998</v>
+        <v>167.161</v>
       </c>
       <c r="D6" t="n">
         <v>5.17232e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-100.6600000000001</v>
+        <v>158.897</v>
       </c>
       <c r="D7" t="n">
         <v>5.16748e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-98.54599999999994</v>
+        <v>155.76</v>
       </c>
       <c r="D8" t="n">
         <v>5.16463e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-96.54000000000008</v>
+        <v>153.4829999999999</v>
       </c>
       <c r="D9" t="n">
         <v>5.162660000000001e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-91.80100000000004</v>
+        <v>152.814</v>
       </c>
       <c r="D10" t="n">
         <v>5.16143e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-92.46900000000005</v>
+        <v>147.194</v>
       </c>
       <c r="D11" t="n">
         <v>5.16208e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-91.28700000000003</v>
+        <v>144.9469999999999</v>
       </c>
       <c r="D12" t="n">
         <v>5.15941e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-87.25400000000002</v>
+        <v>145.48</v>
       </c>
       <c r="D13" t="n">
         <v>5.16025e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-87.51700000000005</v>
+        <v>140.832</v>
       </c>
       <c r="D14" t="n">
         <v>5.16003e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-87.44300000000004</v>
+        <v>137.995</v>
       </c>
       <c r="D15" t="n">
         <v>5.15982e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-85.584</v>
+        <v>136.198</v>
       </c>
       <c r="D16" t="n">
         <v>5.15883e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-82.74000000000001</v>
+        <v>135.462</v>
       </c>
       <c r="D17" t="n">
         <v>5.16019e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-85.98600000000005</v>
+        <v>128.85</v>
       </c>
       <c r="D18" t="n">
         <v>5.16125e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-83.06800000000004</v>
+        <v>128.679</v>
       </c>
       <c r="D19" t="n">
         <v>5.16195e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-82.43200000000002</v>
+        <v>125.838</v>
       </c>
       <c r="D20" t="n">
         <v>5.16325e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-81.73399999999998</v>
+        <v>123.924</v>
       </c>
       <c r="D21" t="n">
         <v>5.16501e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-80.53399999999999</v>
+        <v>121.6420000000001</v>
       </c>
       <c r="D22" t="n">
         <v>5.16635e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-246.2620000000001</v>
+        <v>230.223</v>
       </c>
       <c r="D2" t="n">
         <v>5.48405e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-177.136</v>
+        <v>155.771</v>
       </c>
       <c r="D3" t="n">
         <v>5.56439e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-153.125</v>
+        <v>142.388</v>
       </c>
       <c r="D4" t="n">
         <v>5.48945e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-141.6579999999999</v>
+        <v>134.357</v>
       </c>
       <c r="D5" t="n">
         <v>5.42322e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-131.116</v>
+        <v>131.894</v>
       </c>
       <c r="D6" t="n">
         <v>5.37384e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-126.609</v>
+        <v>126.794</v>
       </c>
       <c r="D7" t="n">
         <v>5.34091e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-123.917</v>
+        <v>121.5</v>
       </c>
       <c r="D8" t="n">
         <v>5.31622e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-117.938</v>
+        <v>119.83</v>
       </c>
       <c r="D9" t="n">
         <v>5.29846e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-115.861</v>
+        <v>116.121</v>
       </c>
       <c r="D10" t="n">
         <v>5.28564e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-110.61</v>
+        <v>116.015</v>
       </c>
       <c r="D11" t="n">
         <v>5.27423e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>202.047</v>
       </c>
+      <c r="C2" t="n">
+        <v>1972.717110813929</v>
+      </c>
       <c r="D2" t="n">
         <v>5.21535e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>191.839</v>
       </c>
+      <c r="C3" t="n">
+        <v>1980.368333197129</v>
+      </c>
       <c r="D3" t="n">
         <v>5.16844e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>185.659</v>
       </c>
+      <c r="C4" t="n">
+        <v>2207.485243168651</v>
+      </c>
       <c r="D4" t="n">
         <v>5.14064e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>177.7169999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>2354.843385729282</v>
+      </c>
       <c r="D5" t="n">
         <v>5.12067e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>173.469</v>
       </c>
+      <c r="C6" t="n">
+        <v>2535.044767899375</v>
+      </c>
       <c r="D6" t="n">
         <v>5.10734e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>168.0309999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>2879.715069958469</v>
+      </c>
       <c r="D7" t="n">
         <v>5.09842e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>162.943</v>
       </c>
+      <c r="C8" t="n">
+        <v>2806.187277743682</v>
+      </c>
       <c r="D8" t="n">
         <v>5.09092e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>163.156</v>
       </c>
+      <c r="C9" t="n">
+        <v>3936.959637485385</v>
+      </c>
       <c r="D9" t="n">
         <v>5.08651e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>155.971</v>
       </c>
+      <c r="C10" t="n">
+        <v>4041.901958464363</v>
+      </c>
       <c r="D10" t="n">
         <v>5.082609999999999e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>152.0339999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4041.276218715817</v>
       </c>
       <c r="D11" t="n">
         <v>5.08056e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>204.684</v>
       </c>
+      <c r="C2" t="n">
+        <v>2015.699649272424</v>
+      </c>
       <c r="D2" t="n">
         <v>5.21634e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>178.233</v>
       </c>
+      <c r="C3" t="n">
+        <v>1559.50462520739</v>
+      </c>
       <c r="D3" t="n">
         <v>5.21579e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>177.282</v>
       </c>
+      <c r="C4" t="n">
+        <v>1775.418227523338</v>
+      </c>
       <c r="D4" t="n">
         <v>5.20277e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>172.5309999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>1844.755126791277</v>
+      </c>
       <c r="D5" t="n">
         <v>5.19107e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>166.1299999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>1845.530256939678</v>
+      </c>
       <c r="D6" t="n">
         <v>5.18404e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>162.554</v>
       </c>
+      <c r="C7" t="n">
+        <v>1818.071030531702</v>
+      </c>
       <c r="D7" t="n">
         <v>5.179499999999999e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>160.9569999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>1982.141926072397</v>
+      </c>
       <c r="D8" t="n">
         <v>5.17457e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>153.128</v>
       </c>
+      <c r="C9" t="n">
+        <v>1884.96580207776</v>
+      </c>
       <c r="D9" t="n">
         <v>5.17208e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>151.991</v>
       </c>
+      <c r="C10" t="n">
+        <v>1987.482295056813</v>
+      </c>
       <c r="D10" t="n">
         <v>5.17053e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>149.975</v>
       </c>
+      <c r="C11" t="n">
+        <v>2104.045801778465</v>
+      </c>
       <c r="D11" t="n">
         <v>5.16953e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>146.2569999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>2120.823043393012</v>
+      </c>
       <c r="D12" t="n">
         <v>5.16839e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>147.52</v>
       </c>
+      <c r="C13" t="n">
+        <v>2394.449246603403</v>
+      </c>
       <c r="D13" t="n">
         <v>5.16651e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>144.762</v>
       </c>
+      <c r="C14" t="n">
+        <v>2522.790410277687</v>
+      </c>
       <c r="D14" t="n">
         <v>5.16679e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>139.8</v>
       </c>
+      <c r="C15" t="n">
+        <v>2197.558626170416</v>
+      </c>
       <c r="D15" t="n">
         <v>5.16595e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>138.576</v>
       </c>
+      <c r="C16" t="n">
+        <v>2346.725954416556</v>
+      </c>
       <c r="D16" t="n">
         <v>5.16497e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>136.36</v>
       </c>
+      <c r="C17" t="n">
+        <v>2483.370304598448</v>
+      </c>
       <c r="D17" t="n">
         <v>5.16677e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>136.257</v>
       </c>
+      <c r="C18" t="n">
+        <v>2739.812287832403</v>
+      </c>
       <c r="D18" t="n">
         <v>5.16473e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>134.044</v>
       </c>
+      <c r="C19" t="n">
+        <v>2960.214309813253</v>
+      </c>
       <c r="D19" t="n">
         <v>5.16867e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>129.803</v>
       </c>
+      <c r="C20" t="n">
+        <v>2777.478584746372</v>
+      </c>
       <c r="D20" t="n">
         <v>5.16924e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>130.119</v>
       </c>
+      <c r="C21" t="n">
+        <v>3459.04638822465</v>
+      </c>
       <c r="D21" t="n">
         <v>5.16894e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>126.468</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3323.625718269403</v>
       </c>
       <c r="D22" t="n">
         <v>5.17013e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>210.712</v>
       </c>
+      <c r="C2" t="n">
+        <v>2443.022122058087</v>
+      </c>
       <c r="D2" t="n">
         <v>5.25343e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>183.956</v>
       </c>
+      <c r="C3" t="n">
+        <v>1881.795198538124</v>
+      </c>
       <c r="D3" t="n">
         <v>5.20708e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>180.083</v>
       </c>
+      <c r="C4" t="n">
+        <v>2006.825306675156</v>
+      </c>
       <c r="D4" t="n">
         <v>5.178079999999999e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>172.3580000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>1862.654439184312</v>
+      </c>
       <c r="D5" t="n">
         <v>5.15806e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>170.711</v>
       </c>
+      <c r="C6" t="n">
+        <v>2144.759345960296</v>
+      </c>
       <c r="D6" t="n">
         <v>5.1463e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>168.984</v>
       </c>
+      <c r="C7" t="n">
+        <v>2470.29770624601</v>
+      </c>
       <c r="D7" t="n">
         <v>5.13615e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>165.126</v>
       </c>
+      <c r="C8" t="n">
+        <v>2838.549238372652</v>
+      </c>
       <c r="D8" t="n">
         <v>5.130670000000001e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>156.348</v>
       </c>
+      <c r="C9" t="n">
+        <v>2345.306160628545</v>
+      </c>
       <c r="D9" t="n">
         <v>5.1277e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>155.3</v>
       </c>
+      <c r="C10" t="n">
+        <v>2716.370026637733</v>
+      </c>
       <c r="D10" t="n">
         <v>5.12321e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>153.829</v>
       </c>
+      <c r="C11" t="n">
+        <v>3162.890249078233</v>
+      </c>
       <c r="D11" t="n">
         <v>5.12047e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>151.853</v>
       </c>
+      <c r="C12" t="n">
+        <v>3803.780707247504</v>
+      </c>
       <c r="D12" t="n">
         <v>5.11952e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>148.809</v>
       </c>
+      <c r="C13" t="n">
+        <v>3835.991789269505</v>
+      </c>
       <c r="D13" t="n">
         <v>5.11746e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>143.251</v>
       </c>
+      <c r="C14" t="n">
+        <v>3581.006606013594</v>
+      </c>
       <c r="D14" t="n">
         <v>5.11511e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>139.908</v>
       </c>
+      <c r="C15" t="n">
+        <v>3500.545385437597</v>
+      </c>
       <c r="D15" t="n">
         <v>5.11432e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>140.885</v>
       </c>
+      <c r="C16" t="n">
+        <v>5379.397985353458</v>
+      </c>
       <c r="D16" t="n">
         <v>5.11416e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>134.765</v>
       </c>
+      <c r="C17" t="n">
+        <v>4168.43453661371</v>
+      </c>
       <c r="D17" t="n">
         <v>5.11313e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>131.494</v>
       </c>
+      <c r="C18" t="n">
+        <v>4114.545733306368</v>
+      </c>
       <c r="D18" t="n">
         <v>5.11395e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>129.931</v>
       </c>
+      <c r="C19" t="n">
+        <v>5146.301988592404</v>
+      </c>
       <c r="D19" t="n">
         <v>5.11415e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>128.692</v>
       </c>
+      <c r="C20" t="n">
+        <v>6147.891385208427</v>
+      </c>
       <c r="D20" t="n">
         <v>5.113180000000001e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>125.114</v>
       </c>
+      <c r="C21" t="n">
+        <v>5571.476546349876</v>
+      </c>
       <c r="D21" t="n">
         <v>5.11435e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>125.383</v>
+      </c>
+      <c r="C22" t="n">
+        <v>14113.91529533627</v>
       </c>
       <c r="D22" t="n">
         <v>5.11423e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>238.871</v>
       </c>
+      <c r="C2" t="n">
+        <v>340321.951364356</v>
+      </c>
       <c r="D2" t="n">
         <v>4.87922e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>173.854</v>
       </c>
+      <c r="C3" t="n">
+        <v>7350.681253906602</v>
+      </c>
       <c r="D3" t="n">
         <v>4.87782e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>158.3100000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>5911.816410356815</v>
+      </c>
       <c r="D4" t="n">
         <v>4.84144e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>154.839</v>
       </c>
+      <c r="C5" t="n">
+        <v>12802.90385764884</v>
+      </c>
       <c r="D5" t="n">
         <v>4.81253e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>147.86</v>
       </c>
+      <c r="C6" t="n">
+        <v>11173.95576282563</v>
+      </c>
       <c r="D6" t="n">
         <v>4.79014e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>144.188</v>
       </c>
+      <c r="C7" t="n">
+        <v>23984.28333720245</v>
+      </c>
       <c r="D7" t="n">
         <v>4.77705e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>140.3050000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>30951.24511083157</v>
+      </c>
       <c r="D8" t="n">
         <v>4.76467e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>135.5</v>
       </c>
+      <c r="C9" t="n">
+        <v>9795.185135625718</v>
+      </c>
       <c r="D9" t="n">
         <v>4.7574e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>131.688</v>
       </c>
+      <c r="C10" t="n">
+        <v>6688.243746949493</v>
+      </c>
       <c r="D10" t="n">
         <v>4.74943e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>128.871</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4424.986444492507</v>
       </c>
       <c r="D11" t="n">
         <v>4.74377e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>204.016</v>
       </c>
+      <c r="C2" t="n">
+        <v>2193.410189933743</v>
+      </c>
       <c r="D2" t="n">
         <v>4.74437e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>179.986</v>
       </c>
+      <c r="C3" t="n">
+        <v>1766.412761321959</v>
+      </c>
       <c r="D3" t="n">
         <v>4.76221e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>170.772</v>
       </c>
+      <c r="C4" t="n">
+        <v>1670.622892437571</v>
+      </c>
       <c r="D4" t="n">
         <v>4.76744e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>168.457</v>
       </c>
+      <c r="C5" t="n">
+        <v>1848.967490156394</v>
+      </c>
       <c r="D5" t="n">
         <v>4.76995e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>162.661</v>
       </c>
+      <c r="C6" t="n">
+        <v>1885.460714115447</v>
+      </c>
       <c r="D6" t="n">
         <v>4.77418e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>157.551</v>
       </c>
+      <c r="C7" t="n">
+        <v>1867.435334102583</v>
+      </c>
       <c r="D7" t="n">
         <v>4.77759e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>154.458</v>
       </c>
+      <c r="C8" t="n">
+        <v>2097.153442623491</v>
+      </c>
       <c r="D8" t="n">
         <v>4.7825e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>152.2860000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>2259.493796952537</v>
+      </c>
       <c r="D9" t="n">
         <v>4.78731e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>147.229</v>
       </c>
+      <c r="C10" t="n">
+        <v>2168.654204125118</v>
+      </c>
       <c r="D10" t="n">
         <v>4.79115e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>144.8179999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>2336.18711812594</v>
+      </c>
       <c r="D11" t="n">
         <v>4.7943e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>143.027</v>
       </c>
+      <c r="C12" t="n">
+        <v>2717.931807715625</v>
+      </c>
       <c r="D12" t="n">
         <v>4.79687e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>139.073</v>
       </c>
+      <c r="C13" t="n">
+        <v>2658.538869423347</v>
+      </c>
       <c r="D13" t="n">
         <v>4.80072e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>136.257</v>
       </c>
+      <c r="C14" t="n">
+        <v>2748.098465187131</v>
+      </c>
       <c r="D14" t="n">
         <v>4.80283e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>134.838</v>
       </c>
+      <c r="C15" t="n">
+        <v>3051.922530153669</v>
+      </c>
       <c r="D15" t="n">
         <v>4.80562e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>132.256</v>
       </c>
+      <c r="C16" t="n">
+        <v>3145.334200218892</v>
+      </c>
       <c r="D16" t="n">
         <v>4.80718e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>131.183</v>
       </c>
+      <c r="C17" t="n">
+        <v>3746.665378270208</v>
+      </c>
       <c r="D17" t="n">
         <v>4.81131e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>125.34</v>
       </c>
+      <c r="C18" t="n">
+        <v>3235.965318226253</v>
+      </c>
       <c r="D18" t="n">
         <v>4.81229e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>125.903</v>
       </c>
+      <c r="C19" t="n">
+        <v>4446.505391276554</v>
+      </c>
       <c r="D19" t="n">
         <v>4.81515e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>124.379</v>
       </c>
+      <c r="C20" t="n">
+        <v>4745.908666976865</v>
+      </c>
       <c r="D20" t="n">
         <v>4.8177e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>121.612</v>
       </c>
+      <c r="C21" t="n">
+        <v>4937.222861326731</v>
+      </c>
       <c r="D21" t="n">
         <v>4.82033e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>118.135</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5130.27763745067</v>
       </c>
       <c r="D22" t="n">
         <v>4.82364e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>253.4470000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>9712.441537246896</v>
+      </c>
       <c r="D2" t="n">
         <v>5.01385e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>172.7979999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>2514.02706019984</v>
+      </c>
       <c r="D3" t="n">
         <v>5.09218e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>155.4710000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>2128.497791866364</v>
+      </c>
       <c r="D4" t="n">
         <v>5.06645e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>151.967</v>
       </c>
+      <c r="C5" t="n">
+        <v>2456.865003077657</v>
+      </c>
       <c r="D5" t="n">
         <v>5.03645e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>144.878</v>
       </c>
+      <c r="C6" t="n">
+        <v>2403.746262807377</v>
+      </c>
       <c r="D6" t="n">
         <v>5.01405e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>143.576</v>
       </c>
+      <c r="C7" t="n">
+        <v>3227.28228631922</v>
+      </c>
       <c r="D7" t="n">
         <v>4.99915e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>136.6940000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>3097.351402879</v>
+      </c>
       <c r="D8" t="n">
         <v>4.98705e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>135.736</v>
       </c>
+      <c r="C9" t="n">
+        <v>4344.412642038901</v>
+      </c>
       <c r="D9" t="n">
         <v>4.97863e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>130.203</v>
       </c>
+      <c r="C10" t="n">
+        <v>4326.67114295874</v>
+      </c>
       <c r="D10" t="n">
         <v>4.97235e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>127.462</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5820.423495345805</v>
       </c>
       <c r="D11" t="n">
         <v>4.96745e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>204.199</v>
       </c>
+      <c r="C2" t="n">
+        <v>3461.007778542659</v>
+      </c>
       <c r="D2" t="n">
         <v>5.0472e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>176.8770000000001</v>
       </c>
+      <c r="C3" t="n">
+        <v>2264.691023561652</v>
+      </c>
       <c r="D3" t="n">
         <v>5.04653e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>173.34</v>
       </c>
+      <c r="C4" t="n">
+        <v>2476.71303068313</v>
+      </c>
       <c r="D4" t="n">
         <v>5.03772e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>170.826</v>
       </c>
+      <c r="C5" t="n">
+        <v>2759.976934762906</v>
+      </c>
       <c r="D5" t="n">
         <v>5.02732e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>163.6229999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>2784.619769844362</v>
+      </c>
       <c r="D6" t="n">
         <v>5.01979e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>163.093</v>
       </c>
+      <c r="C7" t="n">
+        <v>3424.879602073352</v>
+      </c>
       <c r="D7" t="n">
         <v>5.01564e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>159.327</v>
       </c>
+      <c r="C8" t="n">
+        <v>4015.521543252151</v>
+      </c>
       <c r="D8" t="n">
         <v>5.01307e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>153.55</v>
       </c>
+      <c r="C9" t="n">
+        <v>4033.568957050852</v>
+      </c>
       <c r="D9" t="n">
         <v>5.01034e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>149.8440000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>4493.624835817146</v>
+      </c>
       <c r="D10" t="n">
         <v>5.01037e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>147.658</v>
       </c>
+      <c r="C11" t="n">
+        <v>6255.680034399322</v>
+      </c>
       <c r="D11" t="n">
         <v>5.00963e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>146.007</v>
       </c>
+      <c r="C12" t="n">
+        <v>8707.695405574887</v>
+      </c>
       <c r="D12" t="n">
         <v>5.00917e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>143.929</v>
       </c>
+      <c r="C13" t="n">
+        <v>15052.19451143153</v>
+      </c>
       <c r="D13" t="n">
         <v>5.00883e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>137.064</v>
       </c>
+      <c r="C14" t="n">
+        <v>7190.932387284072</v>
+      </c>
       <c r="D14" t="n">
         <v>5.00936e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>136.907</v>
       </c>
+      <c r="C15" t="n">
+        <v>13633.77140933025</v>
+      </c>
       <c r="D15" t="n">
         <v>5.00865e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>133.383</v>
       </c>
+      <c r="C16" t="n">
+        <v>15574.02291838962</v>
+      </c>
       <c r="D16" t="n">
         <v>5.00941e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>132.185</v>
       </c>
+      <c r="C17" t="n">
+        <v>40695.98885527576</v>
+      </c>
       <c r="D17" t="n">
         <v>5.0099e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>130.94</v>
       </c>
+      <c r="C18" t="n">
+        <v>56144.58527776378</v>
+      </c>
       <c r="D18" t="n">
         <v>5.01015e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>130.161</v>
       </c>
+      <c r="C19" t="n">
+        <v>16069.21448984618</v>
+      </c>
       <c r="D19" t="n">
         <v>5.01147e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>126.241</v>
       </c>
+      <c r="C20" t="n">
+        <v>17374.17108945834</v>
+      </c>
       <c r="D20" t="n">
         <v>5.01156e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>123.382</v>
       </c>
+      <c r="C21" t="n">
+        <v>4470.811765823927</v>
+      </c>
       <c r="D21" t="n">
         <v>5.01346e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>120.958</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4716.107823525852</v>
       </c>
       <c r="D22" t="n">
         <v>5.014219999999999e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>236.601</v>
       </c>
+      <c r="C2" t="n">
+        <v>10849.95401912157</v>
+      </c>
       <c r="D2" t="n">
         <v>5.34048e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>170.455</v>
       </c>
+      <c r="C3" t="n">
+        <v>2809.29987121525</v>
+      </c>
       <c r="D3" t="n">
         <v>5.40305e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>158.9570000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>2883.770561290855</v>
+      </c>
       <c r="D4" t="n">
         <v>5.35659e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>153.12</v>
       </c>
+      <c r="C5" t="n">
+        <v>3120.367929413724</v>
+      </c>
       <c r="D5" t="n">
         <v>5.30925e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>150.159</v>
       </c>
+      <c r="C6" t="n">
+        <v>4346.541105931205</v>
+      </c>
       <c r="D6" t="n">
         <v>5.27303e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>143.3390000000001</v>
       </c>
+      <c r="C7" t="n">
+        <v>3796.890149702368</v>
+      </c>
       <c r="D7" t="n">
         <v>5.2461e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>139.069</v>
       </c>
+      <c r="C8" t="n">
+        <v>4469.171754588876</v>
+      </c>
       <c r="D8" t="n">
         <v>5.22457e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>137.652</v>
       </c>
+      <c r="C9" t="n">
+        <v>7239.578167571793</v>
+      </c>
       <c r="D9" t="n">
         <v>5.20873e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>130.743</v>
       </c>
+      <c r="C10" t="n">
+        <v>6529.135578827382</v>
+      </c>
       <c r="D10" t="n">
         <v>5.19572e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>127.131</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8573.512692480415</v>
       </c>
       <c r="D11" t="n">
         <v>5.18468e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>204.609</v>
       </c>
+      <c r="C2" t="n">
+        <v>2948.970386066969</v>
+      </c>
       <c r="D2" t="n">
         <v>5.190239999999999e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>180.717</v>
       </c>
+      <c r="C3" t="n">
+        <v>2250.855064130742</v>
+      </c>
       <c r="D3" t="n">
         <v>5.19621e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>172.316</v>
       </c>
+      <c r="C4" t="n">
+        <v>2206.426015560342</v>
+      </c>
       <c r="D4" t="n">
         <v>5.18674e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>169.34</v>
       </c>
+      <c r="C5" t="n">
+        <v>2495.057765517849</v>
+      </c>
       <c r="D5" t="n">
         <v>5.17863e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>167.161</v>
       </c>
+      <c r="C6" t="n">
+        <v>2917.927256853559</v>
+      </c>
       <c r="D6" t="n">
         <v>5.17232e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>158.897</v>
       </c>
+      <c r="C7" t="n">
+        <v>2457.67301370019</v>
+      </c>
       <c r="D7" t="n">
         <v>5.16748e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>155.76</v>
       </c>
+      <c r="C8" t="n">
+        <v>2789.431781076364</v>
+      </c>
       <c r="D8" t="n">
         <v>5.16463e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>153.4829999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>3164.910395846828</v>
+      </c>
       <c r="D9" t="n">
         <v>5.162660000000001e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>152.814</v>
       </c>
+      <c r="C10" t="n">
+        <v>4173.86513155786</v>
+      </c>
       <c r="D10" t="n">
         <v>5.16143e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>147.194</v>
       </c>
+      <c r="C11" t="n">
+        <v>3515.580968325159</v>
+      </c>
       <c r="D11" t="n">
         <v>5.16208e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>144.9469999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>4336.707488317524</v>
+      </c>
       <c r="D12" t="n">
         <v>5.15941e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>145.48</v>
       </c>
+      <c r="C13" t="n">
+        <v>5897.401500342778</v>
+      </c>
       <c r="D13" t="n">
         <v>5.16025e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>140.832</v>
       </c>
+      <c r="C14" t="n">
+        <v>5119.518301372334</v>
+      </c>
       <c r="D14" t="n">
         <v>5.16003e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>137.995</v>
       </c>
+      <c r="C15" t="n">
+        <v>5502.17692584668</v>
+      </c>
       <c r="D15" t="n">
         <v>5.15982e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>136.198</v>
       </c>
+      <c r="C16" t="n">
+        <v>6101.916316768395</v>
+      </c>
       <c r="D16" t="n">
         <v>5.15883e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>135.462</v>
       </c>
+      <c r="C17" t="n">
+        <v>8736.951074557814</v>
+      </c>
       <c r="D17" t="n">
         <v>5.16019e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>128.85</v>
       </c>
+      <c r="C18" t="n">
+        <v>6123.04995350059</v>
+      </c>
       <c r="D18" t="n">
         <v>5.16125e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>128.679</v>
       </c>
+      <c r="C19" t="n">
+        <v>7408.147174937479</v>
+      </c>
       <c r="D19" t="n">
         <v>5.16195e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>125.838</v>
       </c>
+      <c r="C20" t="n">
+        <v>6034.159285409603</v>
+      </c>
       <c r="D20" t="n">
         <v>5.16325e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>123.924</v>
       </c>
+      <c r="C21" t="n">
+        <v>9122.136470036678</v>
+      </c>
       <c r="D21" t="n">
         <v>5.16501e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>121.6420000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>11032.2537902185</v>
       </c>
       <c r="D22" t="n">
         <v>5.16635e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>230.223</v>
       </c>
+      <c r="C2" t="n">
+        <v>5285.511024311179</v>
+      </c>
       <c r="D2" t="n">
         <v>5.48405e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>155.771</v>
       </c>
+      <c r="C3" t="n">
+        <v>4282.118939193942</v>
+      </c>
       <c r="D3" t="n">
         <v>5.56439e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>142.388</v>
       </c>
+      <c r="C4" t="n">
+        <v>3520.405250645829</v>
+      </c>
       <c r="D4" t="n">
         <v>5.48945e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>134.357</v>
       </c>
+      <c r="C5" t="n">
+        <v>3329.111661980908</v>
+      </c>
       <c r="D5" t="n">
         <v>5.42322e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>131.894</v>
       </c>
+      <c r="C6" t="n">
+        <v>5195.245441610477</v>
+      </c>
       <c r="D6" t="n">
         <v>5.37384e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>126.794</v>
       </c>
+      <c r="C7" t="n">
+        <v>5834.028242625387</v>
+      </c>
       <c r="D7" t="n">
         <v>5.34091e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>121.5</v>
       </c>
+      <c r="C8" t="n">
+        <v>5019.872522976677</v>
+      </c>
       <c r="D8" t="n">
         <v>5.31622e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>119.83</v>
       </c>
+      <c r="C9" t="n">
+        <v>10622.36278624191</v>
+      </c>
       <c r="D9" t="n">
         <v>5.29846e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>116.121</v>
       </c>
+      <c r="C10" t="n">
+        <v>18519.94843822597</v>
+      </c>
       <c r="D10" t="n">
         <v>5.28564e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>116.015</v>
+      </c>
+      <c r="C11" t="n">
+        <v>39941.23628897461</v>
       </c>
       <c r="D11" t="n">
         <v>5.27423e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
@@ -565,7 +565,7 @@
         <v>202.047</v>
       </c>
       <c r="C2" t="n">
-        <v>1972.717110813929</v>
+        <v>344.3911103236727</v>
       </c>
       <c r="D2" t="n">
         <v>5.21535e-07</v>
@@ -598,16 +598,13 @@
         <v>-8425.382353354806</v>
       </c>
       <c r="Y2" t="n">
-        <v>436.5613412390976</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>459756129.7226777</v>
+        <v>229.9006229273865</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.617320643735627e-05</v>
+        <v>9.390468004277009e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.8754728658495474</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>191.839</v>
       </c>
       <c r="C3" t="n">
-        <v>1980.368333197129</v>
+        <v>403.3256277427941</v>
       </c>
       <c r="D3" t="n">
         <v>5.16844e-07</v>
@@ -651,16 +648,13 @@
         <v>-8648.783113050857</v>
       </c>
       <c r="Y3" t="n">
-        <v>429.426343755753</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>290537744.422328</v>
+        <v>157.4216849829879</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.633929680176825e-05</v>
+        <v>6.638799756616554e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.8738426745704772</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>185.659</v>
       </c>
       <c r="C4" t="n">
-        <v>2207.485243168651</v>
+        <v>441.9545660513697</v>
       </c>
       <c r="D4" t="n">
         <v>5.14064e-07</v>
@@ -704,16 +698,13 @@
         <v>-9004.449998165856</v>
       </c>
       <c r="Y4" t="n">
-        <v>423.777566549322</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>303912238.4359277</v>
+        <v>110.0034723264628</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.647653998322822e-05</v>
+        <v>5.493802959491138e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.8733102871555355</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>177.7169999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>2354.843385729282</v>
+        <v>177.7169999999999</v>
       </c>
       <c r="D5" t="n">
         <v>5.12067e-07</v>
@@ -756,11 +747,10 @@
       <c r="X5" t="n">
         <v>-8715.851842118569</v>
       </c>
-      <c r="Y5" t="n">
-        <v>418.4780451746641</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>456040234.680056</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.660075106136696e-05</v>
@@ -777,7 +767,7 @@
         <v>173.469</v>
       </c>
       <c r="C6" t="n">
-        <v>2535.044767899375</v>
+        <v>390.052536981051</v>
       </c>
       <c r="D6" t="n">
         <v>5.10734e-07</v>
@@ -810,16 +800,13 @@
         <v>-8804.112573257338</v>
       </c>
       <c r="Y6" t="n">
-        <v>457.1980885449453</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2432192575.5996</v>
+        <v>148.8850888462575</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.968994096982682e-06</v>
+        <v>6.257610626092362e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6362135409928577</v>
+        <v>0.8792937976244373</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +817,7 @@
         <v>168.0309999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>2879.715069958469</v>
+        <v>168.0309999999999</v>
       </c>
       <c r="D7" t="n">
         <v>5.09842e-07</v>
@@ -862,11 +849,10 @@
       <c r="X7" t="n">
         <v>-8647.549253121873</v>
       </c>
-      <c r="Y7" t="n">
-        <v>466.2216449640257</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>980250299.3921894</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>3.348927935908901e-06</v>
@@ -883,7 +869,7 @@
         <v>162.943</v>
       </c>
       <c r="C8" t="n">
-        <v>2806.187277743682</v>
+        <v>462.7892024750278</v>
       </c>
       <c r="D8" t="n">
         <v>5.09092e-07</v>
@@ -916,16 +902,13 @@
         <v>-8328.152260697088</v>
       </c>
       <c r="Y8" t="n">
-        <v>465.0648399277428</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>315961879.7105847</v>
+        <v>60.56521440817603</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.619582718730847e-06</v>
+        <v>4.454127271989648e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7535598306285342</v>
+        <v>0.8764884833998486</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +919,7 @@
         <v>163.156</v>
       </c>
       <c r="C9" t="n">
-        <v>3936.959637485385</v>
+        <v>392.9621891418261</v>
       </c>
       <c r="D9" t="n">
         <v>5.08651e-07</v>
@@ -969,16 +952,13 @@
         <v>-9523.735254483521</v>
       </c>
       <c r="Y9" t="n">
-        <v>462.0454749569959</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>507997005.9589807</v>
+        <v>125.1098390792133</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.227522631558258e-06</v>
+        <v>5.438059972178863e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7773364585598589</v>
+        <v>0.8841174156044891</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +969,7 @@
         <v>155.971</v>
       </c>
       <c r="C10" t="n">
-        <v>4041.901958464363</v>
+        <v>406.7885019146118</v>
       </c>
       <c r="D10" t="n">
         <v>5.082609999999999e-07</v>
@@ -1022,16 +1002,13 @@
         <v>-8663.69464773346</v>
       </c>
       <c r="Y10" t="n">
-        <v>458.0409926564698</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>206302720.2869713</v>
+        <v>105.4024587408428</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.999651868526985e-06</v>
+        <v>5.277029393332828e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7932244636922485</v>
+        <v>0.8807965771361188</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1019,7 @@
         <v>152.0339999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>4041.276218715817</v>
+        <v>152.0339999999999</v>
       </c>
       <c r="D11" t="n">
         <v>5.08056e-07</v>
@@ -1074,11 +1051,10 @@
       <c r="X11" t="n">
         <v>-8351.490980495348</v>
       </c>
-      <c r="Y11" t="n">
-        <v>454.1664677363372</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>473653198.5129693</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>1.830078272135628e-06</v>
@@ -1241,7 +1217,7 @@
         <v>204.684</v>
       </c>
       <c r="C2" t="n">
-        <v>2015.699649272424</v>
+        <v>333.0270070311045</v>
       </c>
       <c r="D2" t="n">
         <v>5.21634e-07</v>
@@ -1274,16 +1250,13 @@
         <v>-8745.798358997865</v>
       </c>
       <c r="Y2" t="n">
-        <v>425.556513835281</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>439647509.2972604</v>
+        <v>223.0084259902413</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.634380782702551e-05</v>
+        <v>7.410451648377995e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.8919967201928634</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1267,7 @@
         <v>178.233</v>
       </c>
       <c r="C3" t="n">
-        <v>1559.50462520739</v>
+        <v>387.3411781734849</v>
       </c>
       <c r="D3" t="n">
         <v>5.21579e-07</v>
@@ -1327,16 +1300,13 @@
         <v>-8194.017028003105</v>
       </c>
       <c r="Y3" t="n">
-        <v>415.4930371170042</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>413978764.9088309</v>
+        <v>157.4197865639987</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.676989275717434e-05</v>
+        <v>7.407614133219286e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.8703510490126979</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1317,7 @@
         <v>177.282</v>
       </c>
       <c r="C4" t="n">
-        <v>1775.418227523338</v>
+        <v>177.282</v>
       </c>
       <c r="D4" t="n">
         <v>5.20277e-07</v>
@@ -1379,11 +1349,10 @@
       <c r="X4" t="n">
         <v>-9494.247686904209</v>
       </c>
-      <c r="Y4" t="n">
-        <v>419.4491319593897</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>128502580.708563</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>1.436877730562132e-05</v>
@@ -1400,7 +1369,7 @@
         <v>172.5309999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>1844.755126791277</v>
+        <v>529.6243631490713</v>
       </c>
       <c r="D5" t="n">
         <v>5.19107e-07</v>
@@ -1433,16 +1402,13 @@
         <v>-9370.291333677103</v>
       </c>
       <c r="Y5" t="n">
-        <v>442.898424126861</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>998615699.4737236</v>
+        <v>0.3241863592358062</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.634526766010167e-06</v>
+        <v>4.41672142289782e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6049952232335382</v>
+        <v>0.8598474278637736</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1419,7 @@
         <v>166.1299999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>1845.530256939678</v>
+        <v>387.7967086525374</v>
       </c>
       <c r="D6" t="n">
         <v>5.18404e-07</v>
@@ -1486,16 +1452,13 @@
         <v>-8952.996738374797</v>
       </c>
       <c r="Y6" t="n">
-        <v>459.4419108960251</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2200050254.421949</v>
+        <v>138.0677563262086</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.531037011878829e-06</v>
+        <v>6.34141649426861e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7127448382542522</v>
+        <v>0.8774412860110926</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1469,7 @@
         <v>162.554</v>
       </c>
       <c r="C7" t="n">
-        <v>1818.071030531702</v>
+        <v>376.4243304700689</v>
       </c>
       <c r="D7" t="n">
         <v>5.179499999999999e-07</v>
@@ -1539,16 +1502,13 @@
         <v>-8631.120644864346</v>
       </c>
       <c r="Y7" t="n">
-        <v>456.8288223071426</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>486092885.9156572</v>
+        <v>144.0083939977964</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.306173198639828e-06</v>
+        <v>6.259567773943016e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7223758203920591</v>
+        <v>0.8811408823484378</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1519,7 @@
         <v>160.9569999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1982.141926072397</v>
+        <v>374.4413837960556</v>
       </c>
       <c r="D8" t="n">
         <v>5.17457e-07</v>
@@ -1592,16 +1552,13 @@
         <v>-9043.424900618778</v>
       </c>
       <c r="Y8" t="n">
-        <v>455.5738003963161</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>414419474.7917985</v>
+        <v>141.2392026920833</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.741429831853265e-06</v>
+        <v>6.269339490577508e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7494979212000059</v>
+        <v>0.8814009597784864</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1569,7 @@
         <v>153.128</v>
       </c>
       <c r="C9" t="n">
-        <v>1884.96580207776</v>
+        <v>366.9710549971194</v>
       </c>
       <c r="D9" t="n">
         <v>5.17208e-07</v>
@@ -1645,16 +1602,13 @@
         <v>-8037.031378340025</v>
       </c>
       <c r="Y9" t="n">
-        <v>454.5853986103272</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>108931757.139886</v>
+        <v>142.9133771970071</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.192447312401475e-06</v>
+        <v>6.054270864660105e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7821872914603254</v>
+        <v>0.8849298712682626</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1619,7 @@
         <v>151.991</v>
       </c>
       <c r="C10" t="n">
-        <v>1987.482295056813</v>
+        <v>404.9512013180006</v>
       </c>
       <c r="D10" t="n">
         <v>5.17053e-07</v>
@@ -1698,16 +1652,13 @@
         <v>-8291.427047402522</v>
       </c>
       <c r="Y10" t="n">
-        <v>451.5707879685751</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>614814743.8409787</v>
+        <v>98.40911146387889</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.022111914245131e-06</v>
+        <v>4.899836239363002e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7941343882990924</v>
+        <v>0.8847338045899777</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1669,7 @@
         <v>149.975</v>
       </c>
       <c r="C11" t="n">
-        <v>2104.045801778465</v>
+        <v>365.2470051404855</v>
       </c>
       <c r="D11" t="n">
         <v>5.16953e-07</v>
@@ -1751,16 +1702,13 @@
         <v>-8296.650322649335</v>
       </c>
       <c r="Y11" t="n">
-        <v>448.5443893143457</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>204222695.5029631</v>
+        <v>135.5088901740925</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.889528513827882e-06</v>
+        <v>5.663009006004826e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8042280551084774</v>
+        <v>0.8899018259419662</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1719,7 @@
         <v>146.2569999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>2120.823043393012</v>
+        <v>146.2569999999999</v>
       </c>
       <c r="D12" t="n">
         <v>5.16839e-07</v>
@@ -1803,11 +1751,10 @@
       <c r="X12" t="n">
         <v>-8334.538598439145</v>
       </c>
-      <c r="Y12" t="n">
-        <v>445.3617068934848</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>92169324.80456986</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>1.787832217141882e-06</v>
@@ -1824,7 +1771,7 @@
         <v>147.52</v>
       </c>
       <c r="C13" t="n">
-        <v>2394.449246603403</v>
+        <v>386.5370260168108</v>
       </c>
       <c r="D13" t="n">
         <v>5.16651e-07</v>
@@ -1857,16 +1804,13 @@
         <v>-8876.970806251997</v>
       </c>
       <c r="Y13" t="n">
-        <v>442.174287418509</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>231743751.0767274</v>
+        <v>104.5847440824063</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.706539925316978e-06</v>
+        <v>5.136521040146e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8193441356163379</v>
+        <v>0.8865342640098314</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1821,7 @@
         <v>144.762</v>
       </c>
       <c r="C14" t="n">
-        <v>2522.790410277687</v>
+        <v>380.210065905066</v>
       </c>
       <c r="D14" t="n">
         <v>5.16679e-07</v>
@@ -1910,16 +1854,13 @@
         <v>-8637.506802509282</v>
       </c>
       <c r="Y14" t="n">
-        <v>439.0523805817506</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>92283929.4686774</v>
+        <v>105.7573589779639</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.634271659427536e-06</v>
+        <v>4.86561674479868e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8258247591501469</v>
+        <v>0.8918869563566058</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1871,7 @@
         <v>139.8</v>
       </c>
       <c r="C15" t="n">
-        <v>2197.558626170416</v>
+        <v>375.3800781796061</v>
       </c>
       <c r="D15" t="n">
         <v>5.16595e-07</v>
@@ -1963,16 +1904,13 @@
         <v>-8033.735733587318</v>
       </c>
       <c r="Y15" t="n">
-        <v>435.8882484891935</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>104529149.8862714</v>
+        <v>107.1930694323915</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.574501842928551e-06</v>
+        <v>4.887625925854153e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8313841030114739</v>
+        <v>0.8929718765991993</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1921,7 @@
         <v>138.576</v>
       </c>
       <c r="C16" t="n">
-        <v>2346.725954416556</v>
+        <v>411.7916117839802</v>
       </c>
       <c r="D16" t="n">
         <v>5.16497e-07</v>
@@ -2016,16 +1954,13 @@
         <v>-8154.107755845124</v>
       </c>
       <c r="Y16" t="n">
-        <v>432.6607238217108</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>274297734.1155606</v>
+        <v>65.4312068768817</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.520942983810344e-06</v>
+        <v>4.230956079471146e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8365537986124532</v>
+        <v>0.8891324299389712</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1971,7 @@
         <v>136.36</v>
       </c>
       <c r="C17" t="n">
-        <v>2483.370304598448</v>
+        <v>367.7910074746194</v>
       </c>
       <c r="D17" t="n">
         <v>5.16677e-07</v>
@@ -2069,16 +2004,13 @@
         <v>-8133.899800027603</v>
       </c>
       <c r="Y17" t="n">
-        <v>429.3165494262582</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>203934586.1922266</v>
+        <v>106.6031614154839</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.474302652004281e-06</v>
+        <v>4.979385093718369e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8412734728912257</v>
+        <v>0.8926286489021307</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2021,7 @@
         <v>136.257</v>
       </c>
       <c r="C18" t="n">
-        <v>2739.812287832403</v>
+        <v>415.4012094342916</v>
       </c>
       <c r="D18" t="n">
         <v>5.16473e-07</v>
@@ -2122,16 +2054,13 @@
         <v>-8471.952024295244</v>
       </c>
       <c r="Y18" t="n">
-        <v>425.9215493809027</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>21183066.55456443</v>
+        <v>78.53895455267042</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.427282840713248e-06</v>
+        <v>1.850504210320341e-08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8460935578739216</v>
+        <v>0.7905346964649813</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2071,7 @@
         <v>134.044</v>
       </c>
       <c r="C19" t="n">
-        <v>2960.214309813253</v>
+        <v>333.8276886751332</v>
       </c>
       <c r="D19" t="n">
         <v>5.16867e-07</v>
@@ -2175,16 +2104,13 @@
         <v>-8294.412934411361</v>
       </c>
       <c r="Y19" t="n">
-        <v>422.3230347670413</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>56607783.77640617</v>
+        <v>132.139441229088</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.388197784125901e-06</v>
+        <v>5.234154315022335e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8503685283031174</v>
+        <v>0.9011701638633079</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2121,7 @@
         <v>129.803</v>
       </c>
       <c r="C20" t="n">
-        <v>2777.478584746372</v>
+        <v>467.0369166354093</v>
       </c>
       <c r="D20" t="n">
         <v>5.16924e-07</v>
@@ -2228,16 +2154,13 @@
         <v>-7830.255058443125</v>
       </c>
       <c r="Y20" t="n">
-        <v>418.7695825234975</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>250972891.4649639</v>
+        <v>23.12963728663417</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.350049975723018e-06</v>
+        <v>2.449391648522401e-08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8545821828130712</v>
+        <v>0.7537748643487034</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2171,7 @@
         <v>130.119</v>
       </c>
       <c r="C21" t="n">
-        <v>3459.04638822465</v>
+        <v>360.0790886762683</v>
       </c>
       <c r="D21" t="n">
         <v>5.16894e-07</v>
@@ -2281,16 +2204,13 @@
         <v>-8297.645628534941</v>
       </c>
       <c r="Y21" t="n">
-        <v>415.3545860070256</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>34236904.45462151</v>
+        <v>119.6879713770479</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.312118988587916e-06</v>
+        <v>2.266384538245927e-08</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8588643534098148</v>
+        <v>0.7941595699682489</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2221,7 @@
         <v>126.468</v>
       </c>
       <c r="C22" t="n">
-        <v>3323.625718269403</v>
+        <v>356.1223838441292</v>
       </c>
       <c r="D22" t="n">
         <v>5.17013e-07</v>
@@ -2334,16 +2254,13 @@
         <v>-7948.453721050384</v>
       </c>
       <c r="Y22" t="n">
-        <v>411.8290656418306</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>128691416.7346684</v>
+        <v>119.3617090422799</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.281866695430897e-06</v>
+        <v>2.262536145671332e-08</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8624132974589148</v>
+        <v>0.7951882469836797</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2417,7 @@
         <v>210.712</v>
       </c>
       <c r="C2" t="n">
-        <v>2443.022122058087</v>
+        <v>210.712</v>
       </c>
       <c r="D2" t="n">
         <v>5.25343e-07</v>
@@ -2532,11 +2449,10 @@
       <c r="X2" t="n">
         <v>-7840.929782597505</v>
       </c>
-      <c r="Y2" t="n">
-        <v>434.9999257535136</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>344819230.5409263</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>1.616787432361747e-05</v>
@@ -2553,7 +2469,7 @@
         <v>183.956</v>
       </c>
       <c r="C3" t="n">
-        <v>1881.795198538124</v>
+        <v>363.6497639271059</v>
       </c>
       <c r="D3" t="n">
         <v>5.20708e-07</v>
@@ -2586,16 +2502,13 @@
         <v>-8066.219127042919</v>
       </c>
       <c r="Y3" t="n">
-        <v>423.8370143989371</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>547836927.5268921</v>
+        <v>191.0132913280065</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.656265994921808e-05</v>
+        <v>7.905519892743868e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.875464542001318</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2519,7 @@
         <v>180.083</v>
       </c>
       <c r="C4" t="n">
-        <v>2006.825306675156</v>
+        <v>387.0542451777099</v>
       </c>
       <c r="D4" t="n">
         <v>5.178079999999999e-07</v>
@@ -2639,16 +2552,13 @@
         <v>-8984.526394492035</v>
       </c>
       <c r="Y4" t="n">
-        <v>418.7714804008791</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>275201067.4412613</v>
+        <v>159.9096847103525</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.669982950005685e-05</v>
+        <v>6.9129023585624e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.875124314175641</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2569,7 @@
         <v>172.3580000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1862.654439184312</v>
+        <v>393.2590477592757</v>
       </c>
       <c r="D5" t="n">
         <v>5.15806e-07</v>
@@ -2692,16 +2602,13 @@
         <v>-8216.205625040062</v>
       </c>
       <c r="Y5" t="n">
-        <v>433.5745037809186</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1377337842.410501</v>
+        <v>146.8984825696081</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.144539877366335e-05</v>
+        <v>6.370404615978873e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.549404673223865</v>
+        <v>0.8771097234591843</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2619,7 @@
         <v>170.711</v>
       </c>
       <c r="C6" t="n">
-        <v>2144.759345960296</v>
+        <v>390.2476918822101</v>
       </c>
       <c r="D6" t="n">
         <v>5.1463e-07</v>
@@ -2745,16 +2652,13 @@
         <v>-8778.693107569165</v>
       </c>
       <c r="Y6" t="n">
-        <v>459.553311242398</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1882194165.19316</v>
+        <v>142.06375932202</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.755623996886845e-06</v>
+        <v>5.750435024820161e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6691686861868202</v>
+        <v>0.88292339022861</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2669,7 @@
         <v>168.984</v>
       </c>
       <c r="C7" t="n">
-        <v>2470.29770624601</v>
+        <v>383.2824836663607</v>
       </c>
       <c r="D7" t="n">
         <v>5.13615e-07</v>
@@ -2798,16 +2702,13 @@
         <v>-9402.657814577398</v>
       </c>
       <c r="Y7" t="n">
-        <v>457.9437873575273</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>395560895.6460473</v>
+        <v>142.5645284873783</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.072688346032543e-06</v>
+        <v>5.67972254819635e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6912128621876305</v>
+        <v>0.8863457788451515</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2719,7 @@
         <v>165.126</v>
       </c>
       <c r="C8" t="n">
-        <v>2838.549238372652</v>
+        <v>458.7931246357018</v>
       </c>
       <c r="D8" t="n">
         <v>5.130670000000001e-07</v>
@@ -2851,16 +2752,13 @@
         <v>-9405.307126144153</v>
       </c>
       <c r="Y8" t="n">
-        <v>459.4159812941938</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>119775122.0151341</v>
+        <v>59.02804183650778</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.880674451816313e-06</v>
+        <v>4.354462815013564e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7409437104918355</v>
+        <v>0.8776529971076544</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2769,7 @@
         <v>156.348</v>
       </c>
       <c r="C9" t="n">
-        <v>2345.306160628545</v>
+        <v>383.7329921473025</v>
       </c>
       <c r="D9" t="n">
         <v>5.1277e-07</v>
@@ -2904,16 +2802,13 @@
         <v>-8063.108053185911</v>
       </c>
       <c r="Y9" t="n">
-        <v>458.4407398337984</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2050759825.418768</v>
+        <v>130.3980580756192</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.218387483515646e-06</v>
+        <v>5.660710440691972e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7791332507737403</v>
+        <v>0.8841113583034919</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2819,7 @@
         <v>155.3</v>
       </c>
       <c r="C10" t="n">
-        <v>2716.370026637733</v>
+        <v>155.3</v>
       </c>
       <c r="D10" t="n">
         <v>5.12321e-07</v>
@@ -2956,11 +2851,10 @@
       <c r="X10" t="n">
         <v>-8648.107996158215</v>
       </c>
-      <c r="Y10" t="n">
-        <v>454.1219036357127</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>117072889.9099261</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>2.131163266566401e-06</v>
@@ -2977,7 +2871,7 @@
         <v>153.829</v>
       </c>
       <c r="C11" t="n">
-        <v>3162.890249078233</v>
+        <v>444.3917867001123</v>
       </c>
       <c r="D11" t="n">
         <v>5.12047e-07</v>
@@ -3010,16 +2904,13 @@
         <v>-9064.751095793868</v>
       </c>
       <c r="Y11" t="n">
-        <v>450.8553170662203</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>154554559.0861521</v>
+        <v>56.67532839650912</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.912314105095442e-06</v>
+        <v>4.23478689178182e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8010355879667522</v>
+        <v>0.881795207234946</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2921,7 @@
         <v>151.853</v>
       </c>
       <c r="C12" t="n">
-        <v>3803.780707247504</v>
+        <v>386.1374707202639</v>
       </c>
       <c r="D12" t="n">
         <v>5.11952e-07</v>
@@ -3063,16 +2954,13 @@
         <v>-9312.487903245348</v>
       </c>
       <c r="Y12" t="n">
-        <v>447.5941925583273</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>177427477.6973688</v>
+        <v>110.2976991947266</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.725781819813984e-06</v>
+        <v>4.874724432965449e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8162627728454941</v>
+        <v>0.8911650437145543</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2971,7 @@
         <v>148.809</v>
       </c>
       <c r="C13" t="n">
-        <v>3835.991789269505</v>
+        <v>148.809</v>
       </c>
       <c r="D13" t="n">
         <v>5.11746e-07</v>
@@ -3115,11 +3003,10 @@
       <c r="X13" t="n">
         <v>-9025.273366936073</v>
       </c>
-      <c r="Y13" t="n">
-        <v>443.8448988552323</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>342020752.9353812</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>1.63263793774982e-06</v>
@@ -3136,7 +3023,7 @@
         <v>143.251</v>
       </c>
       <c r="C14" t="n">
-        <v>3581.006606013594</v>
+        <v>143.251</v>
       </c>
       <c r="D14" t="n">
         <v>5.11511e-07</v>
@@ -3168,11 +3055,10 @@
       <c r="X14" t="n">
         <v>-8441.386468294138</v>
       </c>
-      <c r="Y14" t="n">
-        <v>440.0494036026332</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>159184895.4359874</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>1.555567234494001e-06</v>
@@ -3189,7 +3075,7 @@
         <v>139.908</v>
       </c>
       <c r="C15" t="n">
-        <v>3500.545385437597</v>
+        <v>427.361725617272</v>
       </c>
       <c r="D15" t="n">
         <v>5.11432e-07</v>
@@ -3222,16 +3108,13 @@
         <v>-8347.666635147394</v>
       </c>
       <c r="Y15" t="n">
-        <v>436.3822431930071</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>470354012.4058977</v>
+        <v>53.72911812333076</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.492046342755361e-06</v>
+        <v>3.967303247131936e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8379316464687732</v>
+        <v>0.8890166261869491</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3125,7 @@
         <v>140.885</v>
       </c>
       <c r="C16" t="n">
-        <v>5379.397985353458</v>
+        <v>442.8692696758281</v>
       </c>
       <c r="D16" t="n">
         <v>5.11416e-07</v>
@@ -3275,16 +3158,13 @@
         <v>-9018.367276180637</v>
       </c>
       <c r="Y16" t="n">
-        <v>432.7070547697845</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>163013896.3609696</v>
+        <v>33.02922131950001</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.430512162143117e-06</v>
+        <v>3.664617131412577e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8442482653894926</v>
+        <v>0.8885975038958073</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3175,7 @@
         <v>134.765</v>
       </c>
       <c r="C17" t="n">
-        <v>4168.43453661371</v>
+        <v>396.6407040101756</v>
       </c>
       <c r="D17" t="n">
         <v>5.11313e-07</v>
@@ -3328,16 +3208,13 @@
         <v>-8112.331798445049</v>
       </c>
       <c r="Y17" t="n">
-        <v>428.928766008439</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>76658901.32251114</v>
+        <v>75.44817053871354</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.386613082874812e-06</v>
+        <v>4.181993003410859e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8489111888488755</v>
+        <v>0.8940987488573682</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3225,7 @@
         <v>131.494</v>
       </c>
       <c r="C18" t="n">
-        <v>4114.545733306368</v>
+        <v>131.494</v>
       </c>
       <c r="D18" t="n">
         <v>5.11395e-07</v>
@@ -3380,11 +3257,10 @@
       <c r="X18" t="n">
         <v>-7723.155358266668</v>
       </c>
-      <c r="Y18" t="n">
-        <v>425.2764764867915</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>155317345.4695542</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.344374033453632e-06</v>
@@ -3401,7 +3277,7 @@
         <v>129.931</v>
       </c>
       <c r="C19" t="n">
-        <v>5146.301988592404</v>
+        <v>416.9211472387407</v>
       </c>
       <c r="D19" t="n">
         <v>5.11415e-07</v>
@@ -3434,16 +3310,13 @@
         <v>-7925.510388842446</v>
       </c>
       <c r="Y19" t="n">
-        <v>421.6229672675877</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>135787529.6473996</v>
+        <v>45.59886413900296</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.301976943813317e-06</v>
+        <v>3.748221525319169e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8584123172216425</v>
+        <v>0.8931765201238405</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3327,7 @@
         <v>128.692</v>
       </c>
       <c r="C20" t="n">
-        <v>6147.891385208427</v>
+        <v>397.2027845337354</v>
       </c>
       <c r="D20" t="n">
         <v>5.113180000000001e-07</v>
@@ -3487,16 +3360,13 @@
         <v>-8100.256490752301</v>
       </c>
       <c r="Y20" t="n">
-        <v>418.0042884196412</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>93515649.87172209</v>
+        <v>91.7719657082217</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.266278368072416e-06</v>
+        <v>2.983980878070751e-08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.862586599675672</v>
+        <v>0.7636308922401035</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3377,7 @@
         <v>125.114</v>
       </c>
       <c r="C21" t="n">
-        <v>5571.476546349876</v>
+        <v>396.9955436015437</v>
       </c>
       <c r="D21" t="n">
         <v>5.11435e-07</v>
@@ -3540,16 +3410,13 @@
         <v>-7709.902032735014</v>
       </c>
       <c r="Y21" t="n">
-        <v>414.4162369724249</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>98336831.56401308</v>
+        <v>93.03109718082503</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.232749848994821e-06</v>
+        <v>4.6267670528128e-08</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8666569399053725</v>
+        <v>0.7343990011673772</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3427,7 @@
         <v>125.383</v>
       </c>
       <c r="C22" t="n">
-        <v>14113.91529533627</v>
+        <v>393.2974255438315</v>
       </c>
       <c r="D22" t="n">
         <v>5.11423e-07</v>
@@ -3593,16 +3460,13 @@
         <v>-8259.885288528591</v>
       </c>
       <c r="Y22" t="n">
-        <v>410.8905802376653</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>35631955.4182388</v>
+        <v>55.98906642483281</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.203224322856655e-06</v>
+        <v>3.687056364749095e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8703108420755646</v>
+        <v>0.9004620741576727</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3623,7 @@
         <v>238.871</v>
       </c>
       <c r="C2" t="n">
-        <v>340321.951364356</v>
+        <v>325.7049933330659</v>
       </c>
       <c r="D2" t="n">
         <v>4.87922e-07</v>
@@ -3792,16 +3656,13 @@
         <v>-8200.373625341766</v>
       </c>
       <c r="Y2" t="n">
-        <v>441.2503204854718</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>453307118.7463925</v>
+        <v>242.1786016804024</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.523184793402742e-05</v>
+        <v>4.056861174184744e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.9328979066333302</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3673,7 @@
         <v>173.854</v>
       </c>
       <c r="C3" t="n">
-        <v>7350.681253906602</v>
+        <v>304.1970272889869</v>
       </c>
       <c r="D3" t="n">
         <v>4.87782e-07</v>
@@ -3845,16 +3706,13 @@
         <v>-9107.587728673427</v>
       </c>
       <c r="Y3" t="n">
-        <v>476.6023147017011</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>227347529.4133855</v>
+        <v>237.7114894748159</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.826787225294773e-06</v>
+        <v>7.43709630984683e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7363457258037635</v>
+        <v>0.9005567507759799</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3723,7 @@
         <v>158.3100000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>5911.816410356815</v>
+        <v>482.9546466120261</v>
       </c>
       <c r="D4" t="n">
         <v>4.84144e-07</v>
@@ -3898,16 +3756,13 @@
         <v>-8814.495803533349</v>
       </c>
       <c r="Y4" t="n">
-        <v>474.03694661931</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>128656884.9781878</v>
+        <v>42.75312280156238</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.766313256740211e-06</v>
+        <v>3.75090618562822e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8045145645487335</v>
+        <v>0.8816567426619194</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3773,7 @@
         <v>154.839</v>
       </c>
       <c r="C5" t="n">
-        <v>12802.90385764884</v>
+        <v>446.7091493264989</v>
       </c>
       <c r="D5" t="n">
         <v>4.81253e-07</v>
@@ -3951,16 +3806,13 @@
         <v>-9534.062981448962</v>
       </c>
       <c r="Y5" t="n">
-        <v>469.0849278976439</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>238714322.3381775</v>
+        <v>72.57092775892666</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.546279619244071e-06</v>
+        <v>4.211302805758928e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8234967373181572</v>
+        <v>0.8834007791854758</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3823,7 @@
         <v>147.86</v>
       </c>
       <c r="C6" t="n">
-        <v>11173.95576282563</v>
+        <v>368.9668466882758</v>
       </c>
       <c r="D6" t="n">
         <v>4.79014e-07</v>
@@ -4004,16 +3856,13 @@
         <v>-8820.971473368434</v>
       </c>
       <c r="Y6" t="n">
-        <v>464.0618202839452</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>266449676.4856685</v>
+        <v>144.8544539254593</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.416616707267517e-06</v>
+        <v>5.140868309727292e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8359286498442891</v>
+        <v>0.895471127643144</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3873,7 @@
         <v>144.188</v>
       </c>
       <c r="C7" t="n">
-        <v>23984.28333720245</v>
+        <v>371.2024076802504</v>
       </c>
       <c r="D7" t="n">
         <v>4.77705e-07</v>
@@ -4057,16 +3906,13 @@
         <v>-8822.49052332835</v>
       </c>
       <c r="Y7" t="n">
-        <v>458.8129218312916</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>29108738.45743059</v>
+        <v>135.3112536506113</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.323451476185574e-06</v>
+        <v>4.823014132585008e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8457376730006512</v>
+        <v>0.8979351380162091</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3923,7 @@
         <v>140.3050000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>30951.24511083157</v>
+        <v>287.0887637740387</v>
       </c>
       <c r="D8" t="n">
         <v>4.76467e-07</v>
@@ -4110,16 +3956,13 @@
         <v>-8812.921887403612</v>
       </c>
       <c r="Y8" t="n">
-        <v>453.1626101977044</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>179414853.6158305</v>
+        <v>214.804272242354</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.25404088657733e-06</v>
+        <v>6.641244788193796e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8534723744850051</v>
+        <v>0.9109185952838685</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3973,7 @@
         <v>135.5</v>
       </c>
       <c r="C9" t="n">
-        <v>9795.185135625718</v>
+        <v>280.8981722421294</v>
       </c>
       <c r="D9" t="n">
         <v>4.7574e-07</v>
@@ -4163,16 +4006,13 @@
         <v>-8660.448950401082</v>
       </c>
       <c r="Y9" t="n">
-        <v>447.4505321666326</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>82895946.05834448</v>
+        <v>213.5984595748785</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.191766518712591e-06</v>
+        <v>6.461728324893254e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8609017121513836</v>
+        <v>0.9144262595446954</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4023,7 @@
         <v>131.688</v>
       </c>
       <c r="C10" t="n">
-        <v>6688.243746949493</v>
+        <v>416.7538539347299</v>
       </c>
       <c r="D10" t="n">
         <v>4.74943e-07</v>
@@ -4216,16 +4056,13 @@
         <v>-8761.127318496159</v>
       </c>
       <c r="Y10" t="n">
-        <v>441.9769639623128</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>114951946.6660604</v>
+        <v>67.3293447905464</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.14075280656471e-06</v>
+        <v>3.659841981598257e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8672568560896207</v>
+        <v>0.8978041382884377</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4073,7 @@
         <v>128.871</v>
       </c>
       <c r="C11" t="n">
-        <v>4424.986444492507</v>
+        <v>128.871</v>
       </c>
       <c r="D11" t="n">
         <v>4.74377e-07</v>
@@ -4268,11 +4105,10 @@
       <c r="X11" t="n">
         <v>-8935.364647830273</v>
       </c>
-      <c r="Y11" t="n">
-        <v>436.7184993165156</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>75285427.38131291</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>1.100065549795278e-06</v>
@@ -4435,7 +4271,7 @@
         <v>204.016</v>
       </c>
       <c r="C2" t="n">
-        <v>2193.410189933743</v>
+        <v>339.7673869785584</v>
       </c>
       <c r="D2" t="n">
         <v>4.74437e-07</v>
@@ -4468,16 +4304,13 @@
         <v>-9168.045261675268</v>
       </c>
       <c r="Y2" t="n">
-        <v>444.1272595847075</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>108864793.1901087</v>
+        <v>227.6297222373055</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.23384089549512e-05</v>
+        <v>6.765482307061953e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5283403986844767</v>
+        <v>0.8973218605203542</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4321,7 @@
         <v>179.986</v>
       </c>
       <c r="C3" t="n">
-        <v>1766.412761321959</v>
+        <v>545.4438493538568</v>
       </c>
       <c r="D3" t="n">
         <v>4.76221e-07</v>
@@ -4521,16 +4354,13 @@
         <v>-9613.249141578935</v>
       </c>
       <c r="Y3" t="n">
-        <v>483.8378742692371</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>96173839.7698317</v>
+        <v>5.090338729739035</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.809131246282537e-06</v>
+        <v>4.15435445458743e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7336223625923195</v>
+        <v>0.8635069527063824</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4371,7 @@
         <v>170.772</v>
       </c>
       <c r="C4" t="n">
-        <v>1670.622892437571</v>
+        <v>170.772</v>
       </c>
       <c r="D4" t="n">
         <v>4.76744e-07</v>
@@ -4573,11 +4403,10 @@
       <c r="X4" t="n">
         <v>-9084.445695273294</v>
       </c>
-      <c r="Y4" t="n">
-        <v>481.9175302628286</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>434126598.6003155</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>2.27596436351776e-06</v>
@@ -4594,7 +4423,7 @@
         <v>168.457</v>
       </c>
       <c r="C5" t="n">
-        <v>1848.967490156394</v>
+        <v>406.6017632401113</v>
       </c>
       <c r="D5" t="n">
         <v>4.76995e-07</v>
@@ -4627,16 +4456,13 @@
         <v>-9693.609583300185</v>
       </c>
       <c r="Y5" t="n">
-        <v>480.7478539399942</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>394980255.859816</v>
+        <v>132.7331362219924</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.738300323053375e-06</v>
+        <v>5.695351319661394e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.804474578142778</v>
+        <v>0.8813365593857625</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4473,7 @@
         <v>162.661</v>
       </c>
       <c r="C6" t="n">
-        <v>1885.460714115447</v>
+        <v>406.2738152706561</v>
       </c>
       <c r="D6" t="n">
         <v>4.77418e-07</v>
@@ -4680,16 +4506,13 @@
         <v>-9243.747570538677</v>
       </c>
       <c r="Y6" t="n">
-        <v>476.4086466037708</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>448482705.571925</v>
+        <v>125.6010462418734</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.610043817204512e-06</v>
+        <v>5.601616956506803e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8160723395709514</v>
+        <v>0.8798569487772685</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4523,7 @@
         <v>157.551</v>
       </c>
       <c r="C7" t="n">
-        <v>1867.435334102583</v>
+        <v>399.7025898207946</v>
       </c>
       <c r="D7" t="n">
         <v>4.77759e-07</v>
@@ -4733,16 +4556,13 @@
         <v>-8893.081304166333</v>
       </c>
       <c r="Y7" t="n">
-        <v>471.7079776354223</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>33836282.58977511</v>
+        <v>126.2454133521194</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.508835727844292e-06</v>
+        <v>5.591008815793764e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8259222514682217</v>
+        <v>0.8820880142600872</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4573,7 @@
         <v>154.458</v>
       </c>
       <c r="C8" t="n">
-        <v>2097.153442623491</v>
+        <v>454.5802147907395</v>
       </c>
       <c r="D8" t="n">
         <v>4.7825e-07</v>
@@ -4786,16 +4606,13 @@
         <v>-8995.914981161315</v>
       </c>
       <c r="Y8" t="n">
-        <v>466.9010668586121</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>252841154.3298536</v>
+        <v>62.85781446360237</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.429287957105137e-06</v>
+        <v>4.318403669988344e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.834203520639902</v>
+        <v>0.8807109063840068</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4623,7 @@
         <v>152.2860000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>2259.493796952537</v>
+        <v>447.7860286787588</v>
       </c>
       <c r="D9" t="n">
         <v>4.78731e-07</v>
@@ -4839,16 +4656,13 @@
         <v>-9195.303952956188</v>
       </c>
       <c r="Y9" t="n">
-        <v>462.2085125306908</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>150849216.6590624</v>
+        <v>63.21278608061525</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.365786026408263e-06</v>
+        <v>4.26423877519813e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.841184312411405</v>
+        <v>0.8824390103783448</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4673,7 @@
         <v>147.229</v>
       </c>
       <c r="C10" t="n">
-        <v>2168.654204125118</v>
+        <v>377.5822135698467</v>
       </c>
       <c r="D10" t="n">
         <v>4.79115e-07</v>
@@ -4892,16 +4706,13 @@
         <v>-8779.878118726585</v>
       </c>
       <c r="Y10" t="n">
-        <v>457.7292824094559</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>59808375.2467428</v>
+        <v>130.2489205555841</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.312195813450152e-06</v>
+        <v>5.411212466037764e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8473420374072599</v>
+        <v>0.8896215833422135</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4723,7 @@
         <v>144.8179999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>2336.18711812594</v>
+        <v>364.4430241317015</v>
       </c>
       <c r="D11" t="n">
         <v>4.7943e-07</v>
@@ -4945,16 +4756,13 @@
         <v>-8809.539496702904</v>
       </c>
       <c r="Y11" t="n">
-        <v>453.4089835910032</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>59504330.46251216</v>
+        <v>137.5253703308194</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.266543799497662e-06</v>
+        <v>5.423682510497587e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8527704216938883</v>
+        <v>0.8927123680662962</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4773,7 @@
         <v>143.027</v>
       </c>
       <c r="C12" t="n">
-        <v>2717.931807715625</v>
+        <v>376.6154018659058</v>
       </c>
       <c r="D12" t="n">
         <v>4.79687e-07</v>
@@ -4998,16 +4806,13 @@
         <v>-9158.797661151497</v>
       </c>
       <c r="Y12" t="n">
-        <v>449.3128788115454</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>58519160.6841563</v>
+        <v>119.627608249827</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.228846453558306e-06</v>
+        <v>5.017775854070988e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8574119825783549</v>
+        <v>0.8923761719398211</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4823,7 @@
         <v>139.073</v>
       </c>
       <c r="C13" t="n">
-        <v>2658.538869423347</v>
+        <v>363.5623590380698</v>
       </c>
       <c r="D13" t="n">
         <v>4.80072e-07</v>
@@ -5051,16 +4856,13 @@
         <v>-8804.542669663158</v>
       </c>
       <c r="Y13" t="n">
-        <v>445.3372836648231</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>176529882.1420476</v>
+        <v>127.6784616255033</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.196660354521983e-06</v>
+        <v>5.078501271788473e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8615324941101248</v>
+        <v>0.8951702270571552</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4873,7 @@
         <v>136.257</v>
       </c>
       <c r="C14" t="n">
-        <v>2748.098465187131</v>
+        <v>136.257</v>
       </c>
       <c r="D14" t="n">
         <v>4.80283e-07</v>
@@ -5103,11 +4905,10 @@
       <c r="X14" t="n">
         <v>-8648.770055613191</v>
       </c>
-      <c r="Y14" t="n">
-        <v>441.4633788509963</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>32229912.12559871</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>1.167379872379136e-06</v>
@@ -5124,7 +4925,7 @@
         <v>134.838</v>
       </c>
       <c r="C15" t="n">
-        <v>3051.922530153669</v>
+        <v>134.838</v>
       </c>
       <c r="D15" t="n">
         <v>4.80562e-07</v>
@@ -5156,11 +4957,10 @@
       <c r="X15" t="n">
         <v>-8816.128156542951</v>
       </c>
-      <c r="Y15" t="n">
-        <v>437.6124367348919</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>217606140.6536585</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>1.142694722031057e-06</v>
@@ -5177,7 +4977,7 @@
         <v>132.256</v>
       </c>
       <c r="C16" t="n">
-        <v>3145.334200218892</v>
+        <v>434.3350146136094</v>
       </c>
       <c r="D16" t="n">
         <v>4.80718e-07</v>
@@ -5210,16 +5010,13 @@
         <v>-8819.790180277078</v>
       </c>
       <c r="Y16" t="n">
-        <v>433.8524003031019</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>36112145.07855842</v>
+        <v>41.96535895806021</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.117052348485922e-06</v>
+        <v>3.717141678169611e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8721326803225858</v>
+        <v>0.8913862327854897</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5027,7 @@
         <v>131.183</v>
       </c>
       <c r="C17" t="n">
-        <v>3746.665378270208</v>
+        <v>428.2356030756833</v>
       </c>
       <c r="D17" t="n">
         <v>4.81131e-07</v>
@@ -5263,16 +5060,13 @@
         <v>-8974.515075371071</v>
       </c>
       <c r="Y17" t="n">
-        <v>430.0687681233816</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>469549170.1307999</v>
+        <v>43.32431791440263</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.094444907575688e-06</v>
+        <v>3.767883063831334e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8753481574775807</v>
+        <v>0.8910213894939077</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5077,7 @@
         <v>125.34</v>
       </c>
       <c r="C18" t="n">
-        <v>3235.965318226253</v>
+        <v>422.1333723723887</v>
       </c>
       <c r="D18" t="n">
         <v>4.81229e-07</v>
@@ -5316,16 +5110,13 @@
         <v>-7959.370109641281</v>
       </c>
       <c r="Y18" t="n">
-        <v>426.3236654765057</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>48188148.78191241</v>
+        <v>44.42852924781555</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.070764944305307e-06</v>
+        <v>3.670667510141318e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8786854289559114</v>
+        <v>0.8933290145824563</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5127,7 @@
         <v>125.903</v>
       </c>
       <c r="C19" t="n">
-        <v>4446.505391276554</v>
+        <v>125.903</v>
       </c>
       <c r="D19" t="n">
         <v>4.81515e-07</v>
@@ -5368,11 +5159,10 @@
       <c r="X19" t="n">
         <v>-8556.044908255646</v>
       </c>
-      <c r="Y19" t="n">
-        <v>422.6080774865547</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>30729510.39641538</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>1.050392275350101e-06</v>
@@ -5389,7 +5179,7 @@
         <v>124.379</v>
       </c>
       <c r="C20" t="n">
-        <v>4745.908666976865</v>
+        <v>412.6613142454954</v>
       </c>
       <c r="D20" t="n">
         <v>4.8177e-07</v>
@@ -5422,16 +5212,13 @@
         <v>-8782.753613832549</v>
       </c>
       <c r="Y20" t="n">
-        <v>418.8492119872903</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>99699177.8356974</v>
+        <v>45.25610951578229</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.033104798877223e-06</v>
+        <v>3.59188969117282e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8842634293848884</v>
+        <v>0.8976406298994852</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5229,7 @@
         <v>121.612</v>
       </c>
       <c r="C21" t="n">
-        <v>4937.222861326731</v>
+        <v>121.612</v>
       </c>
       <c r="D21" t="n">
         <v>4.82033e-07</v>
@@ -5474,11 +5261,10 @@
       <c r="X21" t="n">
         <v>-8563.08091120807</v>
       </c>
-      <c r="Y21" t="n">
-        <v>415.0822496434679</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>189549326.6332638</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>1.016993736638098e-06</v>
@@ -5495,7 +5281,7 @@
         <v>118.135</v>
       </c>
       <c r="C22" t="n">
-        <v>5130.27763745067</v>
+        <v>420.0459236117385</v>
       </c>
       <c r="D22" t="n">
         <v>4.82364e-07</v>
@@ -5528,16 +5314,13 @@
         <v>-8009.531316887499</v>
       </c>
       <c r="Y22" t="n">
-        <v>411.336132300142</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>274160802.661543</v>
+        <v>63.42875406905142</v>
       </c>
       <c r="AA22" t="n">
-        <v>9.982190114390554e-07</v>
+        <v>3.608567983255995e-08</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8896292886038379</v>
+        <v>0.7420350641531359</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5477,7 @@
         <v>253.4470000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>9712.441537246896</v>
+        <v>323.6833219809552</v>
       </c>
       <c r="D2" t="n">
         <v>5.01385e-07</v>
@@ -5727,16 +5510,13 @@
         <v>-7302.501598697544</v>
       </c>
       <c r="Y2" t="n">
-        <v>448.0868660230072</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>432120763.4442663</v>
+        <v>252.1795368991039</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.524193114130107e-05</v>
+        <v>4.500194215210243e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.9255377633340059</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5527,7 @@
         <v>172.7979999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>2514.02706019984</v>
+        <v>313.5667666526824</v>
       </c>
       <c r="D3" t="n">
         <v>5.09218e-07</v>
@@ -5780,16 +5560,13 @@
         <v>-7870.419776766566</v>
       </c>
       <c r="Y3" t="n">
-        <v>458.0576473385265</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1535254073.316125</v>
+        <v>230.7278090774557</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.600865462276436e-06</v>
+        <v>8.272025430990645e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6221346535876193</v>
+        <v>0.8894968651357756</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5577,7 @@
         <v>155.4710000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>2128.497791866364</v>
+        <v>155.4710000000001</v>
       </c>
       <c r="D4" t="n">
         <v>5.06645e-07</v>
@@ -5832,11 +5609,10 @@
       <c r="X4" t="n">
         <v>-7842.511579781048</v>
       </c>
-      <c r="Y4" t="n">
-        <v>469.9161833437443</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>426543626.2747911</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>2.583984295924121e-06</v>
@@ -5853,7 +5629,7 @@
         <v>151.967</v>
       </c>
       <c r="C5" t="n">
-        <v>2456.865003077657</v>
+        <v>457.0052237107581</v>
       </c>
       <c r="D5" t="n">
         <v>5.03645e-07</v>
@@ -5886,16 +5662,13 @@
         <v>-8701.709860191046</v>
       </c>
       <c r="Y5" t="n">
-        <v>467.1531956187354</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>384295557.1347258</v>
+        <v>62.85769452869913</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.041696351356739e-06</v>
+        <v>4.417970883099724e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7891987726480826</v>
+        <v>0.8765965063282908</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5679,7 @@
         <v>144.878</v>
       </c>
       <c r="C6" t="n">
-        <v>2403.746262807377</v>
+        <v>317.920333750284</v>
       </c>
       <c r="D6" t="n">
         <v>5.01405e-07</v>
@@ -5939,16 +5712,13 @@
         <v>-8118.921871447683</v>
       </c>
       <c r="Y6" t="n">
-        <v>463.0916462350833</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>566243428.233409</v>
+        <v>199.7382618915078</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.78246445523967e-06</v>
+        <v>7.627806507445807e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8087308510273754</v>
+        <v>0.8892077299740936</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5729,7 @@
         <v>143.576</v>
       </c>
       <c r="C7" t="n">
-        <v>3227.28228631922</v>
+        <v>310.1760714150536</v>
       </c>
       <c r="D7" t="n">
         <v>4.99915e-07</v>
@@ -5992,16 +5762,13 @@
         <v>-8744.574638608035</v>
       </c>
       <c r="Y7" t="n">
-        <v>458.155366719374</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>335321526.4706919</v>
+        <v>200.1258072265054</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.619416189556971e-06</v>
+        <v>7.266994107913307e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8226184098124311</v>
+        <v>0.8943795164601346</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5779,7 @@
         <v>136.6940000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>3097.351402879</v>
+        <v>360.460017708268</v>
       </c>
       <c r="D8" t="n">
         <v>4.98705e-07</v>
@@ -6045,16 +5812,13 @@
         <v>-8232.455344380243</v>
       </c>
       <c r="Y8" t="n">
-        <v>453.0897904582574</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>201694822.5567918</v>
+        <v>140.2920926504446</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.496395515594004e-06</v>
+        <v>5.322911086374246e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8340735195617309</v>
+        <v>0.8929410544962458</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5829,7 @@
         <v>135.736</v>
       </c>
       <c r="C9" t="n">
-        <v>4344.412642038901</v>
+        <v>367.9301536037434</v>
       </c>
       <c r="D9" t="n">
         <v>4.97863e-07</v>
@@ -6098,16 +5862,13 @@
         <v>-8721.625051795852</v>
       </c>
       <c r="Y9" t="n">
-        <v>447.9884789038092</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>206934293.3790737</v>
+        <v>126.1254858314337</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.404995852608527e-06</v>
+        <v>5.015497944676026e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8432668587166029</v>
+        <v>0.8935478057307703</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5879,7 @@
         <v>130.203</v>
       </c>
       <c r="C10" t="n">
-        <v>4326.67114295874</v>
+        <v>460.4555701481956</v>
       </c>
       <c r="D10" t="n">
         <v>4.97235e-07</v>
@@ -6151,16 +5912,13 @@
         <v>-8311.733703603246</v>
       </c>
       <c r="Y10" t="n">
-        <v>443.0473409330044</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>240801249.3798047</v>
+        <v>25.92151326303559</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.334299345676491e-06</v>
+        <v>3.611210191295035e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8508238506214266</v>
+        <v>0.8845680238162228</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5929,7 @@
         <v>127.462</v>
       </c>
       <c r="C11" t="n">
-        <v>5820.423495345805</v>
+        <v>402.0098709142263</v>
       </c>
       <c r="D11" t="n">
         <v>4.96745e-07</v>
@@ -6204,16 +5962,13 @@
         <v>-8319.005571557916</v>
       </c>
       <c r="Y11" t="n">
-        <v>438.4193282355079</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>25806229.035969</v>
+        <v>78.7297734199192</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.278349313536701e-06</v>
+        <v>4.152595767305368e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8571255385014426</v>
+        <v>0.8924075463604643</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6125,7 @@
         <v>204.199</v>
       </c>
       <c r="C2" t="n">
-        <v>3461.007778542659</v>
+        <v>333.7383590532926</v>
       </c>
       <c r="D2" t="n">
         <v>5.0472e-07</v>
@@ -6403,16 +6158,13 @@
         <v>-8998.037819848076</v>
       </c>
       <c r="Y2" t="n">
-        <v>428.8948341124835</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>281385923.9833325</v>
+        <v>227.8923884778532</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.59815863015575e-05</v>
+        <v>7.174809799371125e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.8949663818215458</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6175,7 @@
         <v>176.8770000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>2264.691023561652</v>
+        <v>387.5551363556407</v>
       </c>
       <c r="D3" t="n">
         <v>5.04653e-07</v>
@@ -6456,16 +6208,13 @@
         <v>-8186.697565978693</v>
       </c>
       <c r="Y3" t="n">
-        <v>432.850749027939</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1242917534.074502</v>
+        <v>160.9870642315289</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.266007038497087e-05</v>
+        <v>6.711205719375123e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5332057293538877</v>
+        <v>0.8772008645347179</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6225,7 @@
         <v>173.34</v>
       </c>
       <c r="C4" t="n">
-        <v>2476.71303068313</v>
+        <v>400.9949357415367</v>
       </c>
       <c r="D4" t="n">
         <v>5.03772e-07</v>
@@ -6509,16 +6258,13 @@
         <v>-8805.342610140813</v>
       </c>
       <c r="Y4" t="n">
-        <v>467.1079398612561</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2385939196.343543</v>
+        <v>141.1293764231992</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.385364504891636e-06</v>
+        <v>6.334030138377831e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6775479794518046</v>
+        <v>0.8754536965500936</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6275,7 @@
         <v>170.826</v>
       </c>
       <c r="C5" t="n">
-        <v>2759.976934762906</v>
+        <v>392.2677837302621</v>
       </c>
       <c r="D5" t="n">
         <v>5.02732e-07</v>
@@ -6562,16 +6308,13 @@
         <v>-9242.403888453036</v>
       </c>
       <c r="Y5" t="n">
-        <v>462.8740630068066</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>434719763.9625528</v>
+        <v>143.348287769841</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.149164943798226e-06</v>
+        <v>6.117988579171726e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6854413757349739</v>
+        <v>0.8794014137901353</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6325,7 @@
         <v>163.6229999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>2784.619769844362</v>
+        <v>383.3607839776258</v>
       </c>
       <c r="D6" t="n">
         <v>5.01979e-07</v>
@@ -6615,16 +6358,13 @@
         <v>-8456.181561102565</v>
       </c>
       <c r="Y6" t="n">
-        <v>467.6597870742491</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>340266557.6764494</v>
+        <v>145.5312488458853</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.653407641557734e-06</v>
+        <v>5.871513314987725e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7496766293620616</v>
+        <v>0.8840918118655955</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6375,7 @@
         <v>163.093</v>
       </c>
       <c r="C7" t="n">
-        <v>3424.879602073352</v>
+        <v>387.6260250837857</v>
       </c>
       <c r="D7" t="n">
         <v>5.01564e-07</v>
@@ -6668,16 +6408,13 @@
         <v>-9008.67653005546</v>
       </c>
       <c r="Y7" t="n">
-        <v>465.6648062293336</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>660870073.005559</v>
+        <v>134.3057081927186</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.122843238729958e-06</v>
+        <v>5.606485186376758e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7823288999255741</v>
+        <v>0.8848035359512456</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6425,7 @@
         <v>159.327</v>
       </c>
       <c r="C8" t="n">
-        <v>4015.521543252151</v>
+        <v>455.9313743831524</v>
       </c>
       <c r="D8" t="n">
         <v>5.01307e-07</v>
@@ -6721,16 +6458,13 @@
         <v>-8959.763870917543</v>
       </c>
       <c r="Y8" t="n">
-        <v>460.5572545164216</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>59335483.17586935</v>
+        <v>57.65119156154392</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.041024618743799e-06</v>
+        <v>4.211153819740203e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7881927870888733</v>
+        <v>0.8805665605047152</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6475,7 @@
         <v>153.55</v>
       </c>
       <c r="C9" t="n">
-        <v>4033.568957050852</v>
+        <v>397.0440654776713</v>
       </c>
       <c r="D9" t="n">
         <v>5.01034e-07</v>
@@ -6774,16 +6508,13 @@
         <v>-8452.194266275221</v>
       </c>
       <c r="Y9" t="n">
-        <v>456.4816585955455</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>31268812.87347665</v>
+        <v>110.7907600203852</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.865979968654931e-06</v>
+        <v>4.797901593959666e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8014566797072805</v>
+        <v>0.8901034585781992</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6525,7 @@
         <v>149.8440000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>4493.624835817146</v>
+        <v>429.3531783039456</v>
       </c>
       <c r="D10" t="n">
         <v>5.01037e-07</v>
@@ -6827,16 +6558,13 @@
         <v>-8434.84913626253</v>
       </c>
       <c r="Y10" t="n">
-        <v>453.0450447735507</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>331677476.4595311</v>
+        <v>72.71740707250895</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.643433532120073e-06</v>
+        <v>4.262832680057284e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8203356288336173</v>
+        <v>0.8868177966141216</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6575,7 @@
         <v>147.658</v>
       </c>
       <c r="C11" t="n">
-        <v>6255.680034399322</v>
+        <v>458.4268044693984</v>
       </c>
       <c r="D11" t="n">
         <v>5.00963e-07</v>
@@ -6880,16 +6608,13 @@
         <v>-8755.166632520968</v>
       </c>
       <c r="Y11" t="n">
-        <v>448.9862634315634</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>46571901.01023883</v>
+        <v>37.62722075934894</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.555444941424885e-06</v>
+        <v>3.793623224996956e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8285486454723441</v>
+        <v>0.8849402216654799</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6625,7 @@
         <v>146.007</v>
       </c>
       <c r="C12" t="n">
-        <v>8707.695405574887</v>
+        <v>456.3851345786028</v>
       </c>
       <c r="D12" t="n">
         <v>5.00917e-07</v>
@@ -6933,16 +6658,13 @@
         <v>-8967.316715429086</v>
       </c>
       <c r="Y12" t="n">
-        <v>445.0313496302306</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>221089791.1095856</v>
+        <v>33.9692222050665</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.484715450195128e-06</v>
+        <v>3.709304132998158e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8355227839241426</v>
+        <v>0.8852089676178069</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6675,7 @@
         <v>143.929</v>
       </c>
       <c r="C13" t="n">
-        <v>15052.19451143153</v>
+        <v>488.2389712823329</v>
       </c>
       <c r="D13" t="n">
         <v>5.00883e-07</v>
@@ -6986,16 +6708,13 @@
         <v>-9203.16118004487</v>
       </c>
       <c r="Y13" t="n">
-        <v>441.2023387667601</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>101486988.0634213</v>
+        <v>0.09894328438015956</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.42824167874795e-06</v>
+        <v>3.815731746779896e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8413399622211442</v>
+        <v>0.8746576657290869</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6725,7 @@
         <v>137.064</v>
       </c>
       <c r="C14" t="n">
-        <v>7190.932387284072</v>
+        <v>434.2215184145222</v>
       </c>
       <c r="D14" t="n">
         <v>5.00936e-07</v>
@@ -7039,16 +6758,13 @@
         <v>-7986.190497144414</v>
       </c>
       <c r="Y14" t="n">
-        <v>437.4715723862098</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>57449690.51259881</v>
+        <v>46.80144374133224</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.379727520644663e-06</v>
+        <v>3.741252969916298e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8465578548034421</v>
+        <v>0.8903701046201471</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6775,7 @@
         <v>136.907</v>
       </c>
       <c r="C15" t="n">
-        <v>13633.77140933025</v>
+        <v>136.907</v>
       </c>
       <c r="D15" t="n">
         <v>5.00865e-07</v>
@@ -7091,11 +6807,10 @@
       <c r="X15" t="n">
         <v>-8419.750097659607</v>
       </c>
-      <c r="Y15" t="n">
-        <v>433.8090666612601</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>200800953.828605</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>1.333391361176151e-06</v>
@@ -7112,7 +6827,7 @@
         <v>133.383</v>
       </c>
       <c r="C16" t="n">
-        <v>15574.02291838962</v>
+        <v>133.383</v>
       </c>
       <c r="D16" t="n">
         <v>5.00941e-07</v>
@@ -7144,11 +6859,10 @@
       <c r="X16" t="n">
         <v>-8153.537225727913</v>
       </c>
-      <c r="Y16" t="n">
-        <v>430.2380017060291</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>39389064.77154506</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>1.293232785149028e-06</v>
@@ -7165,7 +6879,7 @@
         <v>132.185</v>
       </c>
       <c r="C17" t="n">
-        <v>40695.98885527576</v>
+        <v>132.185</v>
       </c>
       <c r="D17" t="n">
         <v>5.0099e-07</v>
@@ -7197,11 +6911,10 @@
       <c r="X17" t="n">
         <v>-8367.410371942011</v>
       </c>
-      <c r="Y17" t="n">
-        <v>426.6129276690558</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>65467756.19810615</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1.261495630592835e-06</v>
@@ -7218,7 +6931,7 @@
         <v>130.94</v>
       </c>
       <c r="C18" t="n">
-        <v>56144.58527776378</v>
+        <v>130.94</v>
       </c>
       <c r="D18" t="n">
         <v>5.01015e-07</v>
@@ -7250,11 +6963,10 @@
       <c r="X18" t="n">
         <v>-8372.141872889862</v>
       </c>
-      <c r="Y18" t="n">
-        <v>422.9245303454863</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>167261841.6995843</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.230586387078175e-06</v>
@@ -7271,7 +6983,7 @@
         <v>130.161</v>
       </c>
       <c r="C19" t="n">
-        <v>16069.21448984618</v>
+        <v>377.3320098041998</v>
       </c>
       <c r="D19" t="n">
         <v>5.01147e-07</v>
@@ -7304,16 +7016,13 @@
         <v>-8793.046607036948</v>
       </c>
       <c r="Y19" t="n">
-        <v>419.3080136373871</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>62055996.3369637</v>
+        <v>81.90682373251711</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.197927246364865e-06</v>
+        <v>3.970662628894026e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8678877325700988</v>
+        <v>0.902757749613458</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +7033,7 @@
         <v>126.241</v>
       </c>
       <c r="C20" t="n">
-        <v>17374.17108945834</v>
+        <v>395.8857910650998</v>
       </c>
       <c r="D20" t="n">
         <v>5.01156e-07</v>
@@ -7357,16 +7066,13 @@
         <v>-8030.453118528424</v>
       </c>
       <c r="Y20" t="n">
-        <v>415.5416941202325</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>73608840.73400299</v>
+        <v>87.26921127112581</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.173842519935232e-06</v>
+        <v>2.22853880313042e-08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8709531020925498</v>
+        <v>0.7832100861549512</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7083,7 @@
         <v>123.382</v>
       </c>
       <c r="C21" t="n">
-        <v>4470.811765823927</v>
+        <v>123.382</v>
       </c>
       <c r="D21" t="n">
         <v>5.01346e-07</v>
@@ -7409,11 +7115,10 @@
       <c r="X21" t="n">
         <v>-8010.580184951246</v>
       </c>
-      <c r="Y21" t="n">
-        <v>411.0599239163823</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>106111814.6856551</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>1.149276738290599e-06</v>
@@ -7430,7 +7135,7 @@
         <v>120.958</v>
       </c>
       <c r="C22" t="n">
-        <v>4716.107823525852</v>
+        <v>242.6668779791709</v>
       </c>
       <c r="D22" t="n">
         <v>5.014219999999999e-07</v>
@@ -7463,16 +7168,13 @@
         <v>-7761.130699727876</v>
       </c>
       <c r="Y22" t="n">
-        <v>407.4459078658471</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>51632562.71932381</v>
+        <v>206.0151794279648</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.1268057007435e-06</v>
+        <v>6.30284402484601e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8771765429249365</v>
+        <v>0.9301641275216251</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7331,7 @@
         <v>236.601</v>
       </c>
       <c r="C2" t="n">
-        <v>10849.95401912157</v>
+        <v>236.601</v>
       </c>
       <c r="D2" t="n">
         <v>5.34048e-07</v>
@@ -7661,11 +7363,10 @@
       <c r="X2" t="n">
         <v>-6504.174744469758</v>
       </c>
-      <c r="Y2" t="n">
-        <v>431.3802792910544</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>517134002.377484</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>1.611346149556508e-05</v>
@@ -7682,7 +7383,7 @@
         <v>170.455</v>
       </c>
       <c r="C3" t="n">
-        <v>2809.29987121525</v>
+        <v>307.6917454527425</v>
       </c>
       <c r="D3" t="n">
         <v>5.40305e-07</v>
@@ -7715,16 +7416,13 @@
         <v>-7000.486509476262</v>
       </c>
       <c r="Y3" t="n">
-        <v>406.1964822742892</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>531464218.9944366</v>
+        <v>220.2713085346376</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.740229790163936e-05</v>
+        <v>7.998855821040033e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.8920745773425226</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7433,7 @@
         <v>158.9570000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>2883.770561290855</v>
+        <v>300.2928279138742</v>
       </c>
       <c r="D4" t="n">
         <v>5.35659e-07</v>
@@ -7768,16 +7466,13 @@
         <v>-7709.912167855526</v>
       </c>
       <c r="Y4" t="n">
-        <v>443.7626362359905</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>943955460.2865905</v>
+        <v>220.9215905703833</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.426695995703156e-06</v>
+        <v>9.908621478266132e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.6565336410205004</v>
+        <v>0.8809801679421293</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7483,7 @@
         <v>153.12</v>
       </c>
       <c r="C5" t="n">
-        <v>3120.367929413724</v>
+        <v>290.28846621865</v>
       </c>
       <c r="D5" t="n">
         <v>5.30925e-07</v>
@@ -7821,16 +7516,13 @@
         <v>-8039.545069267775</v>
       </c>
       <c r="Y5" t="n">
-        <v>450.3571189902734</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4626438561.604074</v>
+        <v>222.8676787012344</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.084830119527758e-06</v>
+        <v>8.946108326433836e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7361942104284004</v>
+        <v>0.8913342300585392</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7533,7 @@
         <v>150.159</v>
       </c>
       <c r="C6" t="n">
-        <v>4346.541105931205</v>
+        <v>282.3453121881905</v>
       </c>
       <c r="D6" t="n">
         <v>5.27303e-07</v>
@@ -7874,16 +7566,13 @@
         <v>-8539.226460839291</v>
       </c>
       <c r="Y6" t="n">
-        <v>448.2740800618595</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>38662165.69008265</v>
+        <v>224.7749118053001</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.502778957277981e-06</v>
+        <v>9.036364808205926e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7659092406962532</v>
+        <v>0.8934104973528855</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7583,7 @@
         <v>143.3390000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>3796.890149702368</v>
+        <v>275.8369465036677</v>
       </c>
       <c r="D7" t="n">
         <v>5.2461e-07</v>
@@ -7927,16 +7616,13 @@
         <v>-7943.922326265624</v>
       </c>
       <c r="Y7" t="n">
-        <v>445.387017325304</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>323432221.225269</v>
+        <v>223.0535162443924</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.038708159641297e-06</v>
+        <v>8.009662984263437e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7954441693129413</v>
+        <v>0.9028878973696812</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7633,7 @@
         <v>139.069</v>
       </c>
       <c r="C8" t="n">
-        <v>4469.171754588876</v>
+        <v>270.6415675273945</v>
       </c>
       <c r="D8" t="n">
         <v>5.22457e-07</v>
@@ -7980,16 +7666,13 @@
         <v>-7915.945534897673</v>
       </c>
       <c r="Y8" t="n">
-        <v>440.9694717024348</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>191695188.0984681</v>
+        <v>223.231093909834</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.811950100208866e-06</v>
+        <v>8.769866838194908e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8123805858384038</v>
+        <v>0.8989800812589358</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7683,7 @@
         <v>137.652</v>
       </c>
       <c r="C9" t="n">
-        <v>7239.578167571793</v>
+        <v>263.4319410469334</v>
       </c>
       <c r="D9" t="n">
         <v>5.20873e-07</v>
@@ -8033,16 +7716,13 @@
         <v>-8313.244926148822</v>
       </c>
       <c r="Y9" t="n">
-        <v>436.1590196059623</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>52198606.42273451</v>
+        <v>221.1800551701652</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.659649004426688e-06</v>
+        <v>7.482622911118262e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8250361530844489</v>
+        <v>0.9105021387614715</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7733,7 @@
         <v>130.743</v>
       </c>
       <c r="C10" t="n">
-        <v>6529.135578827382</v>
+        <v>257.7315705111645</v>
       </c>
       <c r="D10" t="n">
         <v>5.19572e-07</v>
@@ -8086,16 +7766,13 @@
         <v>-7692.415457396726</v>
       </c>
       <c r="Y10" t="n">
-        <v>431.4033591607503</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>89153392.15322308</v>
+        <v>221.3412966422295</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.539947714236846e-06</v>
+        <v>7.8410061893477e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8358601348984783</v>
+        <v>0.910109379973956</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7783,7 @@
         <v>127.131</v>
       </c>
       <c r="C11" t="n">
-        <v>8573.512692480415</v>
+        <v>253.5332798399539</v>
       </c>
       <c r="D11" t="n">
         <v>5.18468e-07</v>
@@ -8139,16 +7816,13 @@
         <v>-7635.581378916427</v>
       </c>
       <c r="Y11" t="n">
-        <v>426.8422070299947</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>135098491.7655998</v>
+        <v>219.3866016645426</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.455402046740741e-06</v>
+        <v>7.313061727398261e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.844015986952308</v>
+        <v>0.9168531593108472</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7979,7 @@
         <v>204.609</v>
       </c>
       <c r="C2" t="n">
-        <v>2948.970386066969</v>
+        <v>333.7421800405776</v>
       </c>
       <c r="D2" t="n">
         <v>5.190239999999999e-07</v>
@@ -8338,16 +8012,13 @@
         <v>-8799.586962586653</v>
       </c>
       <c r="Y2" t="n">
-        <v>429.7932192605974</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>562592999.5669701</v>
+        <v>227.2043173257353</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.627895485631908e-05</v>
+        <v>7.415790909173874e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.892209389826914</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +8029,7 @@
         <v>180.717</v>
       </c>
       <c r="C3" t="n">
-        <v>2250.855064130742</v>
+        <v>406.6459735239791</v>
       </c>
       <c r="D3" t="n">
         <v>5.19621e-07</v>
@@ -8391,16 +8062,13 @@
         <v>-8712.207715790601</v>
       </c>
       <c r="Y3" t="n">
-        <v>419.6303894013049</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>817488492.7871574</v>
+        <v>139.8248128091584</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.672088246815811e-05</v>
+        <v>6.131392653100676e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5000000000000003</v>
+        <v>0.8761863054589144</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8079,7 @@
         <v>172.316</v>
       </c>
       <c r="C4" t="n">
-        <v>2206.426015560342</v>
+        <v>397.8591615662288</v>
       </c>
       <c r="D4" t="n">
         <v>5.18674e-07</v>
@@ -8444,16 +8112,13 @@
         <v>-8459.159807644928</v>
       </c>
       <c r="Y4" t="n">
-        <v>429.617769656206</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>710104774.3432301</v>
+        <v>141.394852709049</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.255706842964694e-05</v>
+        <v>5.936200708988308e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5379779268763155</v>
+        <v>0.8804858813101721</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8129,7 @@
         <v>169.34</v>
       </c>
       <c r="C5" t="n">
-        <v>2495.057765517849</v>
+        <v>530.7556491734686</v>
       </c>
       <c r="D5" t="n">
         <v>5.17863e-07</v>
@@ -8497,16 +8162,13 @@
         <v>-8694.053340036611</v>
       </c>
       <c r="Y5" t="n">
-        <v>452.3229894707206</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>808203832.0034522</v>
+        <v>1.205207069750095</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.152092620533742e-06</v>
+        <v>4.204855398689917e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6341441226851702</v>
+        <v>0.8627178882205535</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8179,7 @@
         <v>167.161</v>
       </c>
       <c r="C6" t="n">
-        <v>2917.927256853559</v>
+        <v>517.3195051347097</v>
       </c>
       <c r="D6" t="n">
         <v>5.17232e-07</v>
@@ -8550,16 +8212,13 @@
         <v>-9257.356887068754</v>
       </c>
       <c r="Y6" t="n">
-        <v>454.7715577815473</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1970217010.584641</v>
+        <v>7.418480364888201</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.661555103148826e-06</v>
+        <v>4.010189250164338e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6730637111776536</v>
+        <v>0.8682984528808602</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8229,7 @@
         <v>158.897</v>
       </c>
       <c r="C7" t="n">
-        <v>2457.67301370019</v>
+        <v>396.6151230536615</v>
       </c>
       <c r="D7" t="n">
         <v>5.16748e-07</v>
@@ -8603,16 +8262,13 @@
         <v>-7971.611483143059</v>
       </c>
       <c r="Y7" t="n">
-        <v>459.2726757585126</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>372756534.5368027</v>
+        <v>123.5819524822922</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.006160791815131e-06</v>
+        <v>5.580689771780757e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7358093608090367</v>
+        <v>0.8813409558600329</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8279,7 @@
         <v>155.76</v>
       </c>
       <c r="C8" t="n">
-        <v>2789.431781076364</v>
+        <v>389.398452558566</v>
       </c>
       <c r="D8" t="n">
         <v>5.16463e-07</v>
@@ -8656,16 +8312,13 @@
         <v>-8138.293414799076</v>
       </c>
       <c r="Y8" t="n">
-        <v>458.37568208228</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>473829535.3887117</v>
+        <v>124.7574524670185</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.330515857217783e-06</v>
+        <v>5.54003427037018e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7729457707706573</v>
+        <v>0.8830618283321697</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8329,7 @@
         <v>153.4829999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>3164.910395846828</v>
+        <v>153.4829999999999</v>
       </c>
       <c r="D9" t="n">
         <v>5.162660000000001e-07</v>
@@ -8708,11 +8361,10 @@
       <c r="X9" t="n">
         <v>-8346.133023764769</v>
       </c>
-      <c r="Y9" t="n">
-        <v>454.9831432895858</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>204470522.9006511</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>2.115043053145326e-06</v>
@@ -8729,7 +8381,7 @@
         <v>152.814</v>
       </c>
       <c r="C10" t="n">
-        <v>4173.86513155786</v>
+        <v>152.814</v>
       </c>
       <c r="D10" t="n">
         <v>5.16143e-07</v>
@@ -8761,11 +8413,10 @@
       <c r="X10" t="n">
         <v>-9121.422450275599</v>
       </c>
-      <c r="Y10" t="n">
-        <v>451.2452578884005</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>104534850.1738987</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>2.000572738836259e-06</v>
@@ -8782,7 +8433,7 @@
         <v>147.194</v>
       </c>
       <c r="C11" t="n">
-        <v>3515.580968325159</v>
+        <v>358.3160349785629</v>
       </c>
       <c r="D11" t="n">
         <v>5.16208e-07</v>
@@ -8815,16 +8466,13 @@
         <v>-8143.608376541416</v>
       </c>
       <c r="Y11" t="n">
-        <v>448.0720873457959</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>390125731.3063829</v>
+        <v>141.1282560027825</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.826975893216307e-06</v>
+        <v>5.637330948850109e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8090303126201446</v>
+        <v>0.8923681297970864</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8483,7 @@
         <v>144.9469999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>4336.707488317524</v>
+        <v>393.2511289055929</v>
       </c>
       <c r="D12" t="n">
         <v>5.15941e-07</v>
@@ -8868,16 +8516,13 @@
         <v>-8155.639213459574</v>
       </c>
       <c r="Y12" t="n">
-        <v>444.4760142132259</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>242694676.8129379</v>
+        <v>99.59046985793617</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.733726778152612e-06</v>
+        <v>4.69699916975905e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8167960157979248</v>
+        <v>0.8907493303389157</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8533,7 @@
         <v>145.48</v>
       </c>
       <c r="C13" t="n">
-        <v>5897.401500342778</v>
+        <v>424.5484234291735</v>
       </c>
       <c r="D13" t="n">
         <v>5.16025e-07</v>
@@ -8921,16 +8566,13 @@
         <v>-8934.495273070181</v>
       </c>
       <c r="Y13" t="n">
-        <v>441.0341296801473</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>151335285.9289216</v>
+        <v>63.07391247671142</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.652955246449384e-06</v>
+        <v>4.273598507811043e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8239519648011685</v>
+        <v>0.8849312902537186</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8583,7 @@
         <v>140.832</v>
       </c>
       <c r="C14" t="n">
-        <v>5119.518301372334</v>
+        <v>140.832</v>
       </c>
       <c r="D14" t="n">
         <v>5.16003e-07</v>
@@ -8973,11 +8615,10 @@
       <c r="X14" t="n">
         <v>-8314.579168769395</v>
       </c>
-      <c r="Y14" t="n">
-        <v>437.5444965927232</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>619785895.9580516</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>1.583197135291149e-06</v>
@@ -8994,7 +8635,7 @@
         <v>137.995</v>
       </c>
       <c r="C15" t="n">
-        <v>5502.17692584668</v>
+        <v>409.5404736692715</v>
       </c>
       <c r="D15" t="n">
         <v>5.15982e-07</v>
@@ -9027,16 +8668,13 @@
         <v>-8125.317972457186</v>
       </c>
       <c r="Y15" t="n">
-        <v>434.0868146982034</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>159004724.4555343</v>
+        <v>69.20627253984094</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.528213643864651e-06</v>
+        <v>4.174501091509376e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8357033753030848</v>
+        <v>0.8907022372085974</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8685,7 @@
         <v>136.198</v>
       </c>
       <c r="C16" t="n">
-        <v>6101.916316768395</v>
+        <v>419.169734472589</v>
       </c>
       <c r="D16" t="n">
         <v>5.15883e-07</v>
@@ -9080,16 +8718,13 @@
         <v>-8119.982157234307</v>
       </c>
       <c r="Y16" t="n">
-        <v>430.6744964949223</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>167257316.4615875</v>
+        <v>80.11166277418602</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.469460529271239e-06</v>
+        <v>1.826632434904228e-08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8415589127745084</v>
+        <v>0.7905655511727179</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8735,7 @@
         <v>135.462</v>
       </c>
       <c r="C17" t="n">
-        <v>8736.951074557814</v>
+        <v>135.462</v>
       </c>
       <c r="D17" t="n">
         <v>5.16019e-07</v>
@@ -9132,11 +8767,10 @@
       <c r="X17" t="n">
         <v>-8464.497698882653</v>
       </c>
-      <c r="Y17" t="n">
-        <v>427.2183042735488</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>73278536.64309131</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1.423873628367312e-06</v>
@@ -9153,7 +8787,7 @@
         <v>128.85</v>
       </c>
       <c r="C18" t="n">
-        <v>6123.04995350059</v>
+        <v>498.3512950132838</v>
       </c>
       <c r="D18" t="n">
         <v>5.16125e-07</v>
@@ -9186,16 +8820,13 @@
         <v>-7507.542129849154</v>
       </c>
       <c r="Y18" t="n">
-        <v>423.6906610712998</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>53706620.86468942</v>
+        <v>4.318141355633743</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.38354794085521e-06</v>
+        <v>3.918891604463265e-08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.850674296773324</v>
+        <v>0.7140455141465991</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8837,7 @@
         <v>128.679</v>
       </c>
       <c r="C19" t="n">
-        <v>7408.147174937479</v>
+        <v>420.4362557923385</v>
       </c>
       <c r="D19" t="n">
         <v>5.16195e-07</v>
@@ -9239,16 +8870,13 @@
         <v>-7814.228678086119</v>
       </c>
       <c r="Y19" t="n">
-        <v>420.3418232263168</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>35319509.81477289</v>
+        <v>40.83394559870862</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.342587031040738e-06</v>
+        <v>3.653105197658538e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8552353239604557</v>
+        <v>0.8940978275469788</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8887,7 @@
         <v>125.838</v>
       </c>
       <c r="C20" t="n">
-        <v>6034.159285409603</v>
+        <v>381.9111972965312</v>
       </c>
       <c r="D20" t="n">
         <v>5.16325e-07</v>
@@ -9292,16 +8920,13 @@
         <v>-7611.576853225756</v>
       </c>
       <c r="Y20" t="n">
-        <v>416.8541039567747</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>80745082.35935077</v>
+        <v>75.83070001575803</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.305381697007645e-06</v>
+        <v>4.080322871783889e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8595145293817911</v>
+        <v>0.8990971811547871</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8937,7 @@
         <v>123.924</v>
       </c>
       <c r="C21" t="n">
-        <v>9122.136470036678</v>
+        <v>383.8729147054056</v>
       </c>
       <c r="D21" t="n">
         <v>5.16501e-07</v>
@@ -9345,16 +8970,13 @@
         <v>-7688.220450246899</v>
       </c>
       <c r="Y21" t="n">
-        <v>413.173417094693</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>24083557.43788818</v>
+        <v>69.3957914278527</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.273415623210706e-06</v>
+        <v>4.008907648031505e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8632859396389144</v>
+        <v>0.8987504464267437</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8987,7 @@
         <v>121.6420000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>11032.2537902185</v>
+        <v>367.4489439492795</v>
       </c>
       <c r="D22" t="n">
         <v>5.16635e-07</v>
@@ -9398,16 +9020,13 @@
         <v>-7461.779420541887</v>
       </c>
       <c r="Y22" t="n">
-        <v>409.5263881564664</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>122618991.6382949</v>
+        <v>81.53535160518707</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.241619927129778e-06</v>
+        <v>4.184498841114459e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8671466321769243</v>
+        <v>0.9008264610054592</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9183,7 @@
         <v>230.223</v>
       </c>
       <c r="C2" t="n">
-        <v>5285.511024311179</v>
+        <v>318.6762908569275</v>
       </c>
       <c r="D2" t="n">
         <v>5.48405e-07</v>
@@ -9597,16 +9216,13 @@
         <v>-5414.041814868423</v>
       </c>
       <c r="Y2" t="n">
-        <v>429.3284156703372</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>402553699.9200533</v>
+        <v>223.6363416046415</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.656942896656787e-05</v>
+        <v>3.341432782033877e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.9390762822440303</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9233,7 @@
         <v>155.771</v>
       </c>
       <c r="C3" t="n">
-        <v>4282.118939193942</v>
+        <v>281.2050578839725</v>
       </c>
       <c r="D3" t="n">
         <v>5.56439e-07</v>
@@ -9650,16 +9266,13 @@
         <v>-6445.594085121489</v>
       </c>
       <c r="Y3" t="n">
-        <v>421.7191979384372</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1328494992.742595</v>
+        <v>231.3452517081248</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.053142505300511e-05</v>
+        <v>8.069067949366617e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.570871772563797</v>
+        <v>0.8999087974728303</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9283,7 @@
         <v>142.388</v>
       </c>
       <c r="C4" t="n">
-        <v>3520.405250645829</v>
+        <v>274.9206344129435</v>
       </c>
       <c r="D4" t="n">
         <v>5.48945e-07</v>
@@ -9703,16 +9316,13 @@
         <v>-7146.132424742581</v>
       </c>
       <c r="Y4" t="n">
-        <v>443.2816248255861</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>165798939.9663967</v>
+        <v>227.2879308200891</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.215415351138841e-06</v>
+        <v>8.837082347473839e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7355479135058132</v>
+        <v>0.8952620395798013</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9333,7 @@
         <v>134.357</v>
       </c>
       <c r="C5" t="n">
-        <v>3329.111661980908</v>
+        <v>272.340117382444</v>
       </c>
       <c r="D5" t="n">
         <v>5.42322e-07</v>
@@ -9756,16 +9366,13 @@
         <v>-7146.513889313306</v>
       </c>
       <c r="Y5" t="n">
-        <v>441.6105664394518</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>580112492.5795598</v>
+        <v>222.6717965081064</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.32184981880586e-06</v>
+        <v>8.373627419559294e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7815517545166534</v>
+        <v>0.8998280601798566</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9383,7 @@
         <v>131.894</v>
       </c>
       <c r="C6" t="n">
-        <v>5195.245441610477</v>
+        <v>262.8184441995215</v>
       </c>
       <c r="D6" t="n">
         <v>5.37384e-07</v>
@@ -9809,16 +9416,13 @@
         <v>-7685.932461853346</v>
       </c>
       <c r="Y6" t="n">
-        <v>437.6272727848345</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>47794544.42563547</v>
+        <v>224.7462366581939</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9517164057488e-06</v>
+        <v>8.043829150533915e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8059296303825573</v>
+        <v>0.9060893027203227</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9433,7 @@
         <v>126.794</v>
       </c>
       <c r="C7" t="n">
-        <v>5834.028242625387</v>
+        <v>256.3464491092914</v>
       </c>
       <c r="D7" t="n">
         <v>5.34091e-07</v>
@@ -9862,16 +9466,13 @@
         <v>-7469.247115082168</v>
       </c>
       <c r="Y7" t="n">
-        <v>432.7455043802224</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>167540934.2256478</v>
+        <v>223.9275679417528</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.740164012349097e-06</v>
+        <v>7.727730312684295e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8220898810919908</v>
+        <v>0.9110341542815975</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9483,7 @@
         <v>121.5</v>
       </c>
       <c r="C8" t="n">
-        <v>5019.872522976677</v>
+        <v>250.596257992918</v>
       </c>
       <c r="D8" t="n">
         <v>5.31622e-07</v>
@@ -9915,16 +9516,13 @@
         <v>-7190.513920025728</v>
       </c>
       <c r="Y8" t="n">
-        <v>427.7264566839125</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>38758243.48460139</v>
+        <v>222.9776757650925</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.594085761636233e-06</v>
+        <v>7.606002976191019e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8344966119782465</v>
+        <v>0.9141653567392408</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9533,7 @@
         <v>119.83</v>
       </c>
       <c r="C9" t="n">
-        <v>10622.36278624191</v>
+        <v>242.8081298746673</v>
       </c>
       <c r="D9" t="n">
         <v>5.29846e-07</v>
@@ -9968,16 +9566,13 @@
         <v>-7597.017364114158</v>
       </c>
       <c r="Y9" t="n">
-        <v>422.9965335576611</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>107188625.7715122</v>
+        <v>224.117781748786</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.490096372647036e-06</v>
+        <v>7.507951925369305e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.844076002849017</v>
+        <v>0.916976180910871</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9583,7 @@
         <v>116.121</v>
       </c>
       <c r="C10" t="n">
-        <v>18519.94843822597</v>
+        <v>238.6319366151209</v>
       </c>
       <c r="D10" t="n">
         <v>5.28564e-07</v>
@@ -10021,16 +9616,13 @@
         <v>-7510.588681929537</v>
       </c>
       <c r="Y10" t="n">
-        <v>418.6352001544854</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>98272582.88053755</v>
+        <v>222.7389122939269</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.415503448633136e-06</v>
+        <v>7.38618453373546e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.85141449381325</v>
+        <v>0.9195498165967417</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9633,7 @@
         <v>116.015</v>
       </c>
       <c r="C11" t="n">
-        <v>39941.23628897461</v>
+        <v>116.015</v>
       </c>
       <c r="D11" t="n">
         <v>5.27423e-07</v>
@@ -10073,11 +9665,10 @@
       <c r="X11" t="n">
         <v>-8100.325238554351</v>
       </c>
-      <c r="Y11" t="n">
-        <v>414.6717908169821</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>13167151.73639226</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>1.351561634035653e-06</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
@@ -565,7 +565,7 @@
         <v>202.047</v>
       </c>
       <c r="C2" t="n">
-        <v>344.3911103236727</v>
+        <v>344.391113968732</v>
       </c>
       <c r="D2" t="n">
         <v>5.21535e-07</v>
@@ -574,16 +574,16 @@
         <v>-75.191</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1916114932947444</v>
+        <v>0.1916114932947508</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6401405543196917</v>
+        <v>0.6401405543196615</v>
       </c>
       <c r="H2" t="n">
         <v>1.325163521322319</v>
       </c>
       <c r="I2" t="n">
-        <v>2.157285356156221</v>
+        <v>2.15728535615622</v>
       </c>
       <c r="J2" t="n">
         <v>26.42594023751873</v>
@@ -592,19 +592,19 @@
         <v>85.75144313712272</v>
       </c>
       <c r="W2" t="n">
-        <v>13.46121302656552</v>
+        <v>13.4612130265655</v>
       </c>
       <c r="X2" t="n">
-        <v>-8425.382353354806</v>
+        <v>-8425.382353354793</v>
       </c>
       <c r="Y2" t="n">
-        <v>229.9006229273865</v>
+        <v>229.9006078340155</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.390468004277009e-09</v>
+        <v>9.390464970288625e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8754728658495474</v>
+        <v>0.8754728802098124</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
         <v>191.839</v>
       </c>
       <c r="C3" t="n">
-        <v>403.3256277427941</v>
+        <v>403.3256387227924</v>
       </c>
       <c r="D3" t="n">
         <v>5.16844e-07</v>
@@ -627,7 +627,7 @@
         <v>0.3163862155468708</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6672988410120807</v>
+        <v>0.6672988410120961</v>
       </c>
       <c r="H3" t="n">
         <v>1.244488088691967</v>
@@ -636,25 +636,25 @@
         <v>2.135214841455913</v>
       </c>
       <c r="J3" t="n">
-        <v>27.89517354074312</v>
+        <v>27.89517354074306</v>
       </c>
       <c r="K3" t="n">
-        <v>85.95358244905577</v>
+        <v>85.95358244905579</v>
       </c>
       <c r="W3" t="n">
-        <v>14.1360820951703</v>
+        <v>14.13608209517033</v>
       </c>
       <c r="X3" t="n">
-        <v>-8648.783113050857</v>
+        <v>-8648.783113050877</v>
       </c>
       <c r="Y3" t="n">
-        <v>157.4216849829879</v>
+        <v>157.4216700417161</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.638799756616554e-09</v>
+        <v>6.638798901483142e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8738426745704772</v>
+        <v>0.8738426742760733</v>
       </c>
     </row>
     <row r="4">
@@ -665,7 +665,7 @@
         <v>185.659</v>
       </c>
       <c r="C4" t="n">
-        <v>441.9545660513697</v>
+        <v>441.9545613422773</v>
       </c>
       <c r="D4" t="n">
         <v>5.14064e-07</v>
@@ -674,13 +674,13 @@
         <v>-76.389</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3418126842168111</v>
+        <v>0.3418126842168303</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7873243054545538</v>
+        <v>0.787324305454534</v>
       </c>
       <c r="H4" t="n">
-        <v>1.280089896848315</v>
+        <v>1.280089896848301</v>
       </c>
       <c r="I4" t="n">
         <v>2.335561143644852</v>
@@ -692,19 +692,19 @@
         <v>86.16898640496976</v>
       </c>
       <c r="W4" t="n">
-        <v>14.93348098541376</v>
+        <v>14.93348098541377</v>
       </c>
       <c r="X4" t="n">
-        <v>-9004.449998165856</v>
+        <v>-9004.449998165865</v>
       </c>
       <c r="Y4" t="n">
-        <v>110.0034723264628</v>
+        <v>110.0034760628821</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.493802959491138e-09</v>
+        <v>5.493802419722268e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8733102871555355</v>
+        <v>0.8733102946857125</v>
       </c>
     </row>
     <row r="5">
@@ -724,13 +724,13 @@
         <v>-76.751</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03866112505642204</v>
+        <v>0.03866112505641388</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6310889820055303</v>
+        <v>0.631088982005509</v>
       </c>
       <c r="H5" t="n">
-        <v>1.058926213036916</v>
+        <v>1.058926213036913</v>
       </c>
       <c r="I5" t="n">
         <v>1.975505547908519</v>
@@ -742,10 +742,10 @@
         <v>86.1096533110838</v>
       </c>
       <c r="W5" t="n">
-        <v>14.70503950702534</v>
+        <v>14.70503950702535</v>
       </c>
       <c r="X5" t="n">
-        <v>-8715.851842118569</v>
+        <v>-8715.851842118578</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>1.660075106136696e-05</v>
+        <v>1.660187505309909e-05</v>
       </c>
       <c r="AB5" t="n">
         <v>0.5000000000000001</v>
@@ -767,7 +767,7 @@
         <v>173.469</v>
       </c>
       <c r="C6" t="n">
-        <v>390.052536981051</v>
+        <v>390.0525450344726</v>
       </c>
       <c r="D6" t="n">
         <v>5.10734e-07</v>
@@ -776,37 +776,37 @@
         <v>-77.038</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1590480294086417</v>
+        <v>0.1590480294086399</v>
       </c>
       <c r="G6" t="n">
-        <v>0.530346475396138</v>
+        <v>0.530346475396146</v>
       </c>
       <c r="H6" t="n">
         <v>1.200895437514181</v>
       </c>
       <c r="I6" t="n">
-        <v>1.805119031982555</v>
+        <v>1.805119031982562</v>
       </c>
       <c r="J6" t="n">
-        <v>31.15138677097848</v>
+        <v>31.15138677097838</v>
       </c>
       <c r="K6" t="n">
         <v>86.20104291829934</v>
       </c>
       <c r="W6" t="n">
-        <v>15.05986807852183</v>
+        <v>15.05986807852182</v>
       </c>
       <c r="X6" t="n">
-        <v>-8804.112573257338</v>
+        <v>-8804.112573257327</v>
       </c>
       <c r="Y6" t="n">
-        <v>148.8850888462575</v>
+        <v>148.8850777608197</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.257610626092362e-09</v>
+        <v>6.257609979652605e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8792937976244373</v>
+        <v>0.8792938015861804</v>
       </c>
     </row>
     <row r="7">
@@ -826,28 +826,28 @@
         <v>-77.322</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1420233111535582</v>
+        <v>0.1420233111535636</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8076149251994229</v>
+        <v>0.8076149251994346</v>
       </c>
       <c r="H7" t="n">
         <v>1.495643479595357</v>
       </c>
       <c r="I7" t="n">
-        <v>2.574670224228278</v>
+        <v>2.574670224228298</v>
       </c>
       <c r="J7" t="n">
-        <v>45.87179168723365</v>
+        <v>45.8717916872337</v>
       </c>
       <c r="K7" t="n">
-        <v>86.18963722131048</v>
+        <v>86.18963722131049</v>
       </c>
       <c r="W7" t="n">
-        <v>15.01465623900591</v>
+        <v>15.01465623900593</v>
       </c>
       <c r="X7" t="n">
-        <v>-8647.549253121873</v>
+        <v>-8647.549253121884</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>3.348927935908901e-06</v>
+        <v>4.220743708817354e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.7179425488705289</v>
+        <v>0.6849916157015855</v>
       </c>
     </row>
     <row r="8">
@@ -869,7 +869,7 @@
         <v>162.943</v>
       </c>
       <c r="C8" t="n">
-        <v>462.7892024750278</v>
+        <v>462.789221501918</v>
       </c>
       <c r="D8" t="n">
         <v>5.09092e-07</v>
@@ -878,37 +878,37 @@
         <v>-77.54900000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07830713619269164</v>
+        <v>0.07830713619269372</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3071860725067974</v>
+        <v>0.3071860725068022</v>
       </c>
       <c r="H8" t="n">
-        <v>1.398477207138512</v>
+        <v>1.398477207138516</v>
       </c>
       <c r="I8" t="n">
-        <v>2.015642289022849</v>
+        <v>2.015642289022921</v>
       </c>
       <c r="J8" t="n">
         <v>37.09347506303033</v>
       </c>
       <c r="K8" t="n">
-        <v>86.10652505823433</v>
+        <v>86.10652505823431</v>
       </c>
       <c r="W8" t="n">
-        <v>14.69318818376992</v>
+        <v>14.69318818376991</v>
       </c>
       <c r="X8" t="n">
-        <v>-8328.152260697088</v>
+        <v>-8328.152260697079</v>
       </c>
       <c r="Y8" t="n">
-        <v>60.56521440817603</v>
+        <v>60.56518800376531</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.454127271989648e-09</v>
+        <v>4.45412765456922e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8764884833998486</v>
+        <v>0.8764884642052987</v>
       </c>
     </row>
     <row r="9">
@@ -919,7 +919,7 @@
         <v>163.156</v>
       </c>
       <c r="C9" t="n">
-        <v>392.9621891418261</v>
+        <v>392.9621903175844</v>
       </c>
       <c r="D9" t="n">
         <v>5.08651e-07</v>
@@ -928,37 +928,37 @@
         <v>-77.782</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4164939112962919</v>
+        <v>0.4164939112962885</v>
       </c>
       <c r="G9" t="n">
         <v>1.133297331941555</v>
       </c>
       <c r="H9" t="n">
-        <v>1.621305872901047</v>
+        <v>1.621305872901055</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6926529107413</v>
+        <v>2.692652910741343</v>
       </c>
       <c r="J9" t="n">
-        <v>50.22657284326222</v>
+        <v>50.22657284326226</v>
       </c>
       <c r="K9" t="n">
         <v>86.61123063991427</v>
       </c>
       <c r="W9" t="n">
-        <v>16.88782801410668</v>
+        <v>16.88782801410665</v>
       </c>
       <c r="X9" t="n">
-        <v>-9523.735254483521</v>
+        <v>-9523.735254483508</v>
       </c>
       <c r="Y9" t="n">
-        <v>125.1098390792133</v>
+        <v>125.1098427284256</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.438059972178863e-09</v>
+        <v>5.438060306922006e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8841174156044891</v>
+        <v>0.8841174214021877</v>
       </c>
     </row>
     <row r="10">
@@ -969,7 +969,7 @@
         <v>155.971</v>
       </c>
       <c r="C10" t="n">
-        <v>406.7885019146118</v>
+        <v>406.7885075627921</v>
       </c>
       <c r="D10" t="n">
         <v>5.082609999999999e-07</v>
@@ -978,19 +978,19 @@
         <v>-77.98099999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1617325119238948</v>
+        <v>0.1617325119238919</v>
       </c>
       <c r="G10" t="n">
         <v>0.759705859251338</v>
       </c>
       <c r="H10" t="n">
-        <v>1.565502145397057</v>
+        <v>1.565502145397079</v>
       </c>
       <c r="I10" t="n">
-        <v>2.578594925231208</v>
+        <v>2.578594925231223</v>
       </c>
       <c r="J10" t="n">
-        <v>52.00445736814248</v>
+        <v>52.00445736814253</v>
       </c>
       <c r="K10" t="n">
         <v>86.344032132899</v>
@@ -999,16 +999,16 @@
         <v>15.65057452743505</v>
       </c>
       <c r="X10" t="n">
-        <v>-8663.69464773346</v>
+        <v>-8663.694647733459</v>
       </c>
       <c r="Y10" t="n">
-        <v>105.4024587408428</v>
+        <v>105.4024575105026</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.277029393332828e-09</v>
+        <v>5.277030531419358e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8807965771361188</v>
+        <v>0.8807965602109382</v>
       </c>
     </row>
     <row r="11">
@@ -1028,28 +1028,28 @@
         <v>-78.173</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2072955141396269</v>
+        <v>0.2072955141396304</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5454724906845655</v>
+        <v>0.5454724906845972</v>
       </c>
       <c r="H11" t="n">
-        <v>1.331970943090006</v>
+        <v>1.33197094309005</v>
       </c>
       <c r="I11" t="n">
         <v>2.143726058355128</v>
       </c>
       <c r="J11" t="n">
-        <v>41.38384227129414</v>
+        <v>41.38384227129446</v>
       </c>
       <c r="K11" t="n">
-        <v>86.26301697638011</v>
+        <v>86.2630169763801</v>
       </c>
       <c r="W11" t="n">
-        <v>15.31034815498231</v>
+        <v>15.3103481549823</v>
       </c>
       <c r="X11" t="n">
-        <v>-8351.490980495348</v>
+        <v>-8351.490980495342</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>1.830078272135628e-06</v>
+        <v>1.82926307452483e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8063690400347214</v>
+        <v>0.8064383751236831</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1217,7 @@
         <v>204.684</v>
       </c>
       <c r="C2" t="n">
-        <v>333.0270070311045</v>
+        <v>333.0270055230043</v>
       </c>
       <c r="D2" t="n">
         <v>5.21634e-07</v>
@@ -1226,19 +1226,19 @@
         <v>-75.754</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3164903587282908</v>
+        <v>0.3164903587282932</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7778741743617645</v>
+        <v>0.7778741743617876</v>
       </c>
       <c r="H2" t="n">
         <v>1.461623813279092</v>
       </c>
       <c r="I2" t="n">
-        <v>2.422465636962559</v>
+        <v>2.422465636962534</v>
       </c>
       <c r="J2" t="n">
-        <v>33.32976497281621</v>
+        <v>33.32976497281615</v>
       </c>
       <c r="K2" t="n">
         <v>85.96837537932797</v>
@@ -1247,16 +1247,16 @@
         <v>14.1881230881079</v>
       </c>
       <c r="X2" t="n">
-        <v>-8745.798358997865</v>
+        <v>-8745.798358997863</v>
       </c>
       <c r="Y2" t="n">
-        <v>223.0084259902413</v>
+        <v>223.0084257518495</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.410451648377995e-09</v>
+        <v>7.410451186857469e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8919967201928634</v>
+        <v>0.8919967224851825</v>
       </c>
     </row>
     <row r="3">
@@ -1267,7 +1267,7 @@
         <v>178.233</v>
       </c>
       <c r="C3" t="n">
-        <v>387.3411781734849</v>
+        <v>387.3411747194574</v>
       </c>
       <c r="D3" t="n">
         <v>5.21579e-07</v>
@@ -1276,16 +1276,16 @@
         <v>-76.58</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0139188235977812</v>
+        <v>0.01391882359777785</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4032493822599827</v>
+        <v>0.403249382259977</v>
       </c>
       <c r="H3" t="n">
         <v>1.333960457939073</v>
       </c>
       <c r="I3" t="n">
-        <v>2.169164727500518</v>
+        <v>2.169164727500503</v>
       </c>
       <c r="J3" t="n">
         <v>31.46758390179824</v>
@@ -1294,19 +1294,19 @@
         <v>85.90677899824207</v>
       </c>
       <c r="W3" t="n">
-        <v>13.97390290455378</v>
+        <v>13.97390290455383</v>
       </c>
       <c r="X3" t="n">
-        <v>-8194.017028003105</v>
+        <v>-8194.01702800314</v>
       </c>
       <c r="Y3" t="n">
-        <v>157.4197865639987</v>
+        <v>157.4197792984946</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.407614133219286e-09</v>
+        <v>7.407610361741133e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8703510490126979</v>
+        <v>0.8703510827243802</v>
       </c>
     </row>
     <row r="4">
@@ -1326,28 +1326,28 @@
         <v>-76.88500000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5934229774499764</v>
+        <v>0.5934229774499765</v>
       </c>
       <c r="G4" t="n">
         <v>1.030465497959012</v>
       </c>
       <c r="H4" t="n">
-        <v>1.694160515413292</v>
+        <v>1.694160515413319</v>
       </c>
       <c r="I4" t="n">
-        <v>2.955486472502589</v>
+        <v>2.955486472502577</v>
       </c>
       <c r="J4" t="n">
-        <v>47.28654211276875</v>
+        <v>47.28654211276874</v>
       </c>
       <c r="K4" t="n">
         <v>86.48824651819594</v>
       </c>
       <c r="W4" t="n">
-        <v>16.29499757508114</v>
+        <v>16.29499757508112</v>
       </c>
       <c r="X4" t="n">
-        <v>-9494.247686904209</v>
+        <v>-9494.247686904198</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>1.436877730562132e-05</v>
+        <v>1.437528063277675e-05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5208876383838603</v>
+        <v>0.5208293852394846</v>
       </c>
     </row>
     <row r="5">
@@ -1369,7 +1369,7 @@
         <v>172.5309999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>529.6243631490713</v>
+        <v>529.6243125367926</v>
       </c>
       <c r="D5" t="n">
         <v>5.19107e-07</v>
@@ -1378,37 +1378,37 @@
         <v>-77.10599999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4028511991794416</v>
+        <v>0.4028511991794392</v>
       </c>
       <c r="G5" t="n">
-        <v>1.023299975134411</v>
+        <v>1.023299975134475</v>
       </c>
       <c r="H5" t="n">
-        <v>1.674980028094986</v>
+        <v>1.674980028094982</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7327423592449</v>
+        <v>2.732742359244883</v>
       </c>
       <c r="J5" t="n">
-        <v>42.47204809449438</v>
+        <v>42.47204809449417</v>
       </c>
       <c r="K5" t="n">
-        <v>86.48646823592055</v>
+        <v>86.48646823592057</v>
       </c>
       <c r="W5" t="n">
-        <v>16.28672959154234</v>
+        <v>16.28672959154239</v>
       </c>
       <c r="X5" t="n">
-        <v>-9370.291333677103</v>
+        <v>-9370.291333677133</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3241863592358062</v>
+        <v>0.3241789192435256</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.41672142289782e-09</v>
+        <v>4.416717263785596e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8598474278637736</v>
+        <v>0.8598474793700015</v>
       </c>
     </row>
     <row r="6">
@@ -1419,7 +1419,7 @@
         <v>166.1299999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>387.7967086525374</v>
+        <v>387.7967054166649</v>
       </c>
       <c r="D6" t="n">
         <v>5.18404e-07</v>
@@ -1431,34 +1431,34 @@
         <v>0.3520387347631234</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8529723944085141</v>
+        <v>0.8529723944084484</v>
       </c>
       <c r="H6" t="n">
-        <v>1.466325014602316</v>
+        <v>1.466325014602286</v>
       </c>
       <c r="I6" t="n">
-        <v>2.06408751544502</v>
+        <v>2.064087515445013</v>
       </c>
       <c r="J6" t="n">
-        <v>35.23849248096194</v>
+        <v>35.23849248096204</v>
       </c>
       <c r="K6" t="n">
-        <v>86.37210788369278</v>
+        <v>86.37210788369279</v>
       </c>
       <c r="W6" t="n">
-        <v>15.7720202565853</v>
+        <v>15.77202025658535</v>
       </c>
       <c r="X6" t="n">
-        <v>-8952.996738374797</v>
+        <v>-8952.996738374826</v>
       </c>
       <c r="Y6" t="n">
-        <v>138.0677563262086</v>
+        <v>138.0677664450951</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.34141649426861e-09</v>
+        <v>6.341418106734412e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8774412860110926</v>
+        <v>0.8774412708113917</v>
       </c>
     </row>
     <row r="7">
@@ -1469,7 +1469,7 @@
         <v>162.554</v>
       </c>
       <c r="C7" t="n">
-        <v>376.4243304700689</v>
+        <v>376.4243365919004</v>
       </c>
       <c r="D7" t="n">
         <v>5.179499999999999e-07</v>
@@ -1478,16 +1478,16 @@
         <v>-77.48999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3488996412597917</v>
+        <v>0.3488996412597922</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7785537313279486</v>
+        <v>0.7785537313279134</v>
       </c>
       <c r="H7" t="n">
-        <v>1.708690601594925</v>
+        <v>1.708690601594952</v>
       </c>
       <c r="I7" t="n">
-        <v>2.586390090859982</v>
+        <v>2.586390090860013</v>
       </c>
       <c r="J7" t="n">
         <v>45.90821696265915</v>
@@ -1496,19 +1496,19 @@
         <v>86.28400188530301</v>
       </c>
       <c r="W7" t="n">
-        <v>15.39705343960711</v>
+        <v>15.39705343960712</v>
       </c>
       <c r="X7" t="n">
-        <v>-8631.120644864346</v>
+        <v>-8631.120644864357</v>
       </c>
       <c r="Y7" t="n">
-        <v>144.0083939977964</v>
+        <v>144.0083830735583</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.259567773943016e-09</v>
+        <v>6.259567105913664e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8811408823484378</v>
+        <v>0.8811408785020909</v>
       </c>
     </row>
     <row r="8">
@@ -1519,7 +1519,7 @@
         <v>160.9569999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>374.4413837960556</v>
+        <v>374.4413740723473</v>
       </c>
       <c r="D8" t="n">
         <v>5.17457e-07</v>
@@ -1528,37 +1528,37 @@
         <v>-77.657</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4801645341277065</v>
+        <v>0.4801645341277064</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8020454599199882</v>
+        <v>0.8020454599199758</v>
       </c>
       <c r="H8" t="n">
-        <v>1.542292289407071</v>
+        <v>1.542292289407025</v>
       </c>
       <c r="I8" t="n">
-        <v>2.349117361662359</v>
+        <v>2.349117361662363</v>
       </c>
       <c r="J8" t="n">
-        <v>36.99527892414145</v>
+        <v>36.99527892414148</v>
       </c>
       <c r="K8" t="n">
         <v>86.47985200944004</v>
       </c>
       <c r="W8" t="n">
-        <v>16.25604123245146</v>
+        <v>16.25604123245145</v>
       </c>
       <c r="X8" t="n">
-        <v>-9043.424900618778</v>
+        <v>-9043.424900618773</v>
       </c>
       <c r="Y8" t="n">
-        <v>141.2392026920833</v>
+        <v>141.2392074967616</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.269339490577508e-09</v>
+        <v>6.269338301692185e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8814009597784864</v>
+        <v>0.8814009762837013</v>
       </c>
     </row>
     <row r="9">
@@ -1569,7 +1569,7 @@
         <v>153.128</v>
       </c>
       <c r="C9" t="n">
-        <v>366.9710549971194</v>
+        <v>366.9710401942912</v>
       </c>
       <c r="D9" t="n">
         <v>5.17208e-07</v>
@@ -1578,19 +1578,19 @@
         <v>-77.816</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03471175430512569</v>
+        <v>0.0347117543051103</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1886290392761659</v>
+        <v>0.1886290392761678</v>
       </c>
       <c r="H9" t="n">
-        <v>1.150009958138471</v>
+        <v>1.150009958138461</v>
       </c>
       <c r="I9" t="n">
-        <v>1.784617603478716</v>
+        <v>1.784617603478775</v>
       </c>
       <c r="J9" t="n">
-        <v>31.75053460318929</v>
+        <v>31.75053460318937</v>
       </c>
       <c r="K9" t="n">
         <v>86.11077642405689</v>
@@ -1599,16 +1599,16 @@
         <v>14.70929904195229</v>
       </c>
       <c r="X9" t="n">
-        <v>-8037.031378340025</v>
+        <v>-8037.031378340022</v>
       </c>
       <c r="Y9" t="n">
-        <v>142.9133771970071</v>
+        <v>142.9133812711353</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.054270864660105e-09</v>
+        <v>6.054268481942603e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8849298712682626</v>
+        <v>0.8849298881465186</v>
       </c>
     </row>
     <row r="10">
@@ -1619,7 +1619,7 @@
         <v>151.991</v>
       </c>
       <c r="C10" t="n">
-        <v>404.9512013180006</v>
+        <v>404.9511613765343</v>
       </c>
       <c r="D10" t="n">
         <v>5.17053e-07</v>
@@ -1631,34 +1631,34 @@
         <v>0.1947439123320832</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5523444986602706</v>
+        <v>0.552344498660277</v>
       </c>
       <c r="H10" t="n">
-        <v>1.264832899069007</v>
+        <v>1.264832899068977</v>
       </c>
       <c r="I10" t="n">
-        <v>2.251803367504679</v>
+        <v>2.251803367504654</v>
       </c>
       <c r="J10" t="n">
-        <v>38.65799346646809</v>
+        <v>38.65799346646835</v>
       </c>
       <c r="K10" t="n">
-        <v>86.25853183561952</v>
+        <v>86.25853183561949</v>
       </c>
       <c r="W10" t="n">
-        <v>15.29194246146126</v>
+        <v>15.29194246146117</v>
       </c>
       <c r="X10" t="n">
-        <v>-8291.427047402522</v>
+        <v>-8291.427047402467</v>
       </c>
       <c r="Y10" t="n">
-        <v>98.40911146387889</v>
+        <v>98.40913603165963</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.899836239363002e-09</v>
+        <v>4.899836276904541e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8847338045899777</v>
+        <v>0.8847337800179376</v>
       </c>
     </row>
     <row r="11">
@@ -1669,7 +1669,7 @@
         <v>149.975</v>
       </c>
       <c r="C11" t="n">
-        <v>365.2470051404855</v>
+        <v>365.2469915445549</v>
       </c>
       <c r="D11" t="n">
         <v>5.16953e-07</v>
@@ -1678,37 +1678,37 @@
         <v>-78.111</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06022194818207349</v>
+        <v>0.06022194818207346</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4863690710485331</v>
+        <v>0.4863690710485205</v>
       </c>
       <c r="H11" t="n">
-        <v>1.420237270551536</v>
+        <v>1.420237270551522</v>
       </c>
       <c r="I11" t="n">
-        <v>2.22968090805138</v>
+        <v>2.229680908051382</v>
       </c>
       <c r="J11" t="n">
-        <v>39.82159364052018</v>
+        <v>39.82159364052011</v>
       </c>
       <c r="K11" t="n">
-        <v>86.2961015716008</v>
+        <v>86.29610157160081</v>
       </c>
       <c r="W11" t="n">
-        <v>15.44749275968518</v>
+        <v>15.44749275968521</v>
       </c>
       <c r="X11" t="n">
-        <v>-8296.650322649335</v>
+        <v>-8296.650322649351</v>
       </c>
       <c r="Y11" t="n">
-        <v>135.5088901740925</v>
+        <v>135.5089098159176</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.663009006004826e-09</v>
+        <v>5.663009758989823e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8899018259419662</v>
+        <v>0.889901826217492</v>
       </c>
     </row>
     <row r="12">
@@ -1728,28 +1728,28 @@
         <v>-78.25</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1309157165110802</v>
+        <v>0.1309157165111011</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6414333786593623</v>
+        <v>0.6414333786593798</v>
       </c>
       <c r="H12" t="n">
         <v>1.371880245353843</v>
       </c>
       <c r="I12" t="n">
-        <v>2.355753039203927</v>
+        <v>2.355753039203926</v>
       </c>
       <c r="J12" t="n">
-        <v>40.67715977940247</v>
+        <v>40.67715977940261</v>
       </c>
       <c r="K12" t="n">
-        <v>86.34556247412979</v>
+        <v>86.34556247412981</v>
       </c>
       <c r="W12" t="n">
-        <v>15.65714622017708</v>
+        <v>15.65714622017713</v>
       </c>
       <c r="X12" t="n">
-        <v>-8334.538598439145</v>
+        <v>-8334.538598439181</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>1.787832217141882e-06</v>
+        <v>1.788476675270854e-06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8124397277872584</v>
+        <v>0.8123856688928689</v>
       </c>
     </row>
     <row r="13">
@@ -1771,7 +1771,7 @@
         <v>147.52</v>
       </c>
       <c r="C13" t="n">
-        <v>386.5370260168108</v>
+        <v>386.5370120516294</v>
       </c>
       <c r="D13" t="n">
         <v>5.16651e-07</v>
@@ -1780,37 +1780,37 @@
         <v>-78.372</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5461594089392622</v>
+        <v>0.5461594089392623</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5893925544401728</v>
+        <v>0.5893925544402342</v>
       </c>
       <c r="H13" t="n">
-        <v>1.359832687388762</v>
+        <v>1.359832687388742</v>
       </c>
       <c r="I13" t="n">
-        <v>2.384702482976528</v>
+        <v>2.384702482976529</v>
       </c>
       <c r="J13" t="n">
-        <v>37.79114712261124</v>
+        <v>37.79114712261118</v>
       </c>
       <c r="K13" t="n">
-        <v>86.58584861664701</v>
+        <v>86.585848616647</v>
       </c>
       <c r="W13" t="n">
-        <v>16.76198348291728</v>
+        <v>16.76198348291727</v>
       </c>
       <c r="X13" t="n">
-        <v>-8876.970806251997</v>
+        <v>-8876.970806251993</v>
       </c>
       <c r="Y13" t="n">
-        <v>104.5847440824063</v>
+        <v>104.5847558314836</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.136521040146e-09</v>
+        <v>5.136520999938164e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8865342640098314</v>
+        <v>0.8865342650504305</v>
       </c>
     </row>
     <row r="14">
@@ -1821,7 +1821,7 @@
         <v>144.762</v>
       </c>
       <c r="C14" t="n">
-        <v>380.210065905066</v>
+        <v>380.2100530506711</v>
       </c>
       <c r="D14" t="n">
         <v>5.16679e-07</v>
@@ -1830,37 +1830,37 @@
         <v>-78.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3809619793428631</v>
+        <v>0.3809619793428616</v>
       </c>
       <c r="G14" t="n">
-        <v>0.940210419520971</v>
+        <v>0.9402104195210098</v>
       </c>
       <c r="H14" t="n">
         <v>1.696242951974511</v>
       </c>
       <c r="I14" t="n">
-        <v>2.651337386673285</v>
+        <v>2.651337386673217</v>
       </c>
       <c r="J14" t="n">
         <v>56.81998852543433</v>
       </c>
       <c r="K14" t="n">
-        <v>86.52793233680913</v>
+        <v>86.52793233680912</v>
       </c>
       <c r="W14" t="n">
-        <v>16.48171443191587</v>
+        <v>16.48171443191585</v>
       </c>
       <c r="X14" t="n">
-        <v>-8637.506802509282</v>
+        <v>-8637.506802509266</v>
       </c>
       <c r="Y14" t="n">
-        <v>105.7573589779639</v>
+        <v>105.7573635614998</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.86561674479868e-09</v>
+        <v>4.865615713464103e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8918869563566058</v>
+        <v>0.8918869719684813</v>
       </c>
     </row>
     <row r="15">
@@ -1871,7 +1871,7 @@
         <v>139.8</v>
       </c>
       <c r="C15" t="n">
-        <v>375.3800781796061</v>
+        <v>375.3800280398298</v>
       </c>
       <c r="D15" t="n">
         <v>5.16595e-07</v>
@@ -1880,22 +1880,22 @@
         <v>-78.61499999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2204231327090241</v>
+        <v>0.2204231327090239</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7173105553115233</v>
+        <v>0.7173105553115798</v>
       </c>
       <c r="H15" t="n">
-        <v>1.082566153931112</v>
+        <v>1.082566153931102</v>
       </c>
       <c r="I15" t="n">
-        <v>2.010475568240889</v>
+        <v>2.010475568240903</v>
       </c>
       <c r="J15" t="n">
-        <v>35.49957492604283</v>
+        <v>35.49957492604278</v>
       </c>
       <c r="K15" t="n">
-        <v>86.31645639209579</v>
+        <v>86.31645639209577</v>
       </c>
       <c r="W15" t="n">
         <v>15.53309137840044</v>
@@ -1904,13 +1904,13 @@
         <v>-8033.735733587318</v>
       </c>
       <c r="Y15" t="n">
-        <v>107.1930694323915</v>
+        <v>107.1930919853709</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.887625925854153e-09</v>
+        <v>4.887624187810668e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8929718765991993</v>
+        <v>0.8929718632103733</v>
       </c>
     </row>
     <row r="16">
@@ -1921,7 +1921,7 @@
         <v>138.576</v>
       </c>
       <c r="C16" t="n">
-        <v>411.7916117839802</v>
+        <v>411.7915779642389</v>
       </c>
       <c r="D16" t="n">
         <v>5.16497e-07</v>
@@ -1930,37 +1930,37 @@
         <v>-78.729</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1734043090905827</v>
+        <v>0.1734043090905769</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6431014296704807</v>
+        <v>0.6431014296704793</v>
       </c>
       <c r="H16" t="n">
-        <v>1.364292639675629</v>
+        <v>1.364292639675652</v>
       </c>
       <c r="I16" t="n">
-        <v>2.284857464935116</v>
+        <v>2.284857464935117</v>
       </c>
       <c r="J16" t="n">
-        <v>39.69687123002117</v>
+        <v>39.69687123002108</v>
       </c>
       <c r="K16" t="n">
-        <v>86.39821187978183</v>
+        <v>86.39821187978181</v>
       </c>
       <c r="W16" t="n">
-        <v>15.88663313037</v>
+        <v>15.88663313036996</v>
       </c>
       <c r="X16" t="n">
-        <v>-8154.107755845124</v>
+        <v>-8154.107755845103</v>
       </c>
       <c r="Y16" t="n">
-        <v>65.4312068768817</v>
+        <v>65.43123283614408</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.230956079471146e-09</v>
+        <v>4.23095565099949e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8891324299389712</v>
+        <v>0.8891324480553866</v>
       </c>
     </row>
     <row r="17">
@@ -1971,7 +1971,7 @@
         <v>136.36</v>
       </c>
       <c r="C17" t="n">
-        <v>367.7910074746194</v>
+        <v>367.7910198302857</v>
       </c>
       <c r="D17" t="n">
         <v>5.16677e-07</v>
@@ -1980,37 +1980,37 @@
         <v>-78.84099999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1023786923017569</v>
+        <v>0.1023786923017589</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5201476579457995</v>
+        <v>0.5201476579457887</v>
       </c>
       <c r="H17" t="n">
-        <v>1.476600907347314</v>
+        <v>1.476600907347289</v>
       </c>
       <c r="I17" t="n">
-        <v>1.995878279674151</v>
+        <v>1.99587827967409</v>
       </c>
       <c r="J17" t="n">
         <v>40.23086948456863</v>
       </c>
       <c r="K17" t="n">
-        <v>86.4205715568302</v>
+        <v>86.42057155683021</v>
       </c>
       <c r="W17" t="n">
-        <v>15.98613355001055</v>
+        <v>15.98613355001057</v>
       </c>
       <c r="X17" t="n">
-        <v>-8133.899800027603</v>
+        <v>-8133.899800027616</v>
       </c>
       <c r="Y17" t="n">
-        <v>106.6031614154839</v>
+        <v>106.6031485407682</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.979385093718369e-09</v>
+        <v>4.97938461285699e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8926286489021307</v>
+        <v>0.8926286522661564</v>
       </c>
     </row>
     <row r="18">
@@ -2021,7 +2021,7 @@
         <v>136.257</v>
       </c>
       <c r="C18" t="n">
-        <v>415.4012094342916</v>
+        <v>415.4012112236608</v>
       </c>
       <c r="D18" t="n">
         <v>5.16473e-07</v>
@@ -2030,37 +2030,37 @@
         <v>-78.952</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3572676105965221</v>
+        <v>0.3572676105965167</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7560890507750943</v>
+        <v>0.7560890507750961</v>
       </c>
       <c r="H18" t="n">
-        <v>1.56462395779619</v>
+        <v>1.564623957796175</v>
       </c>
       <c r="I18" t="n">
-        <v>2.578638123188831</v>
+        <v>2.57863812318887</v>
       </c>
       <c r="J18" t="n">
-        <v>52.53009133940343</v>
+        <v>52.53009133940348</v>
       </c>
       <c r="K18" t="n">
         <v>86.58516089805744</v>
       </c>
       <c r="W18" t="n">
-        <v>16.7585997617742</v>
+        <v>16.75859976177421</v>
       </c>
       <c r="X18" t="n">
         <v>-8471.952024295244</v>
       </c>
       <c r="Y18" t="n">
-        <v>78.53895455267042</v>
+        <v>78.53894212244809</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.850504210320341e-08</v>
+        <v>1.850502738646332e-08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.7905346964649813</v>
+        <v>0.790534747744792</v>
       </c>
     </row>
     <row r="19">
@@ -2071,7 +2071,7 @@
         <v>134.044</v>
       </c>
       <c r="C19" t="n">
-        <v>333.8276886751332</v>
+        <v>333.8276888130184</v>
       </c>
       <c r="D19" t="n">
         <v>5.16867e-07</v>
@@ -2083,34 +2083,34 @@
         <v>0.2099367862275081</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8880466162554737</v>
+        <v>0.8880466162554762</v>
       </c>
       <c r="H19" t="n">
-        <v>1.515310175100335</v>
+        <v>1.51531017510031</v>
       </c>
       <c r="I19" t="n">
-        <v>2.495265419909257</v>
+        <v>2.495265419909244</v>
       </c>
       <c r="J19" t="n">
-        <v>46.63374388710879</v>
+        <v>46.63374388710874</v>
       </c>
       <c r="K19" t="n">
-        <v>86.54973313037205</v>
+        <v>86.54973313037206</v>
       </c>
       <c r="W19" t="n">
-        <v>16.5861100823373</v>
+        <v>16.58611008233738</v>
       </c>
       <c r="X19" t="n">
-        <v>-8294.412934411361</v>
+        <v>-8294.412934411406</v>
       </c>
       <c r="Y19" t="n">
-        <v>132.139441229088</v>
+        <v>132.1394400731704</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.234154315022335e-09</v>
+        <v>5.234154284672732e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9011701638633079</v>
+        <v>0.901170161063104</v>
       </c>
     </row>
     <row r="20">
@@ -2121,7 +2121,7 @@
         <v>129.803</v>
       </c>
       <c r="C20" t="n">
-        <v>467.0369166354093</v>
+        <v>467.0374295778074</v>
       </c>
       <c r="D20" t="n">
         <v>5.16924e-07</v>
@@ -2130,37 +2130,37 @@
         <v>-79.17700000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01368154594398414</v>
+        <v>0.0136815459439828</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5536990957905542</v>
+        <v>0.5536990957905706</v>
       </c>
       <c r="H20" t="n">
-        <v>1.514149773891765</v>
+        <v>1.51414977389177</v>
       </c>
       <c r="I20" t="n">
-        <v>2.532969187758171</v>
+        <v>2.532969187758172</v>
       </c>
       <c r="J20" t="n">
-        <v>54.16953460278456</v>
+        <v>54.16953460278455</v>
       </c>
       <c r="K20" t="n">
         <v>86.39231169106921</v>
       </c>
       <c r="W20" t="n">
-        <v>15.86058272691931</v>
+        <v>15.8605827269193</v>
       </c>
       <c r="X20" t="n">
-        <v>-7830.255058443125</v>
+        <v>-7830.255058443121</v>
       </c>
       <c r="Y20" t="n">
-        <v>23.12963728663417</v>
+        <v>23.12892322752857</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.449391648522401e-08</v>
+        <v>2.449353073360224e-08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.7537748643487034</v>
+        <v>0.7537757322678628</v>
       </c>
     </row>
     <row r="21">
@@ -2171,7 +2171,7 @@
         <v>130.119</v>
       </c>
       <c r="C21" t="n">
-        <v>360.0790886762683</v>
+        <v>360.079115643257</v>
       </c>
       <c r="D21" t="n">
         <v>5.16894e-07</v>
@@ -2180,37 +2180,37 @@
         <v>-79.301</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3635656862472247</v>
+        <v>0.3635656862472216</v>
       </c>
       <c r="G21" t="n">
         <v>0.8332025941300015</v>
       </c>
       <c r="H21" t="n">
-        <v>1.274057688379306</v>
+        <v>1.27405768837931</v>
       </c>
       <c r="I21" t="n">
         <v>2.377995221933312</v>
       </c>
       <c r="J21" t="n">
-        <v>49.2828086738517</v>
+        <v>49.28280867385168</v>
       </c>
       <c r="K21" t="n">
-        <v>86.61496854372025</v>
+        <v>86.61496854372024</v>
       </c>
       <c r="W21" t="n">
-        <v>16.90651984926625</v>
+        <v>16.9065198492662</v>
       </c>
       <c r="X21" t="n">
-        <v>-8297.645628534941</v>
+        <v>-8297.645628534912</v>
       </c>
       <c r="Y21" t="n">
-        <v>119.6879713770479</v>
+        <v>119.6879432405711</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.266384538245927e-08</v>
+        <v>2.266384180022669e-08</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.7941595699682489</v>
+        <v>0.7941595694737776</v>
       </c>
     </row>
     <row r="22">
@@ -2221,7 +2221,7 @@
         <v>126.468</v>
       </c>
       <c r="C22" t="n">
-        <v>356.1223838441292</v>
+        <v>356.1223834070836</v>
       </c>
       <c r="D22" t="n">
         <v>5.17013e-07</v>
@@ -2230,19 +2230,19 @@
         <v>-79.40300000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1041033060454893</v>
+        <v>0.1041033060454829</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5901341396295071</v>
+        <v>0.5901341396294604</v>
       </c>
       <c r="H22" t="n">
-        <v>1.326117725156579</v>
+        <v>1.32611772515657</v>
       </c>
       <c r="I22" t="n">
-        <v>1.970034417693584</v>
+        <v>1.970034417693592</v>
       </c>
       <c r="J22" t="n">
-        <v>39.48324977154112</v>
+        <v>39.4832497715412</v>
       </c>
       <c r="K22" t="n">
         <v>86.50872653162848</v>
@@ -2254,13 +2254,13 @@
         <v>-7948.453721050384</v>
       </c>
       <c r="Y22" t="n">
-        <v>119.3617090422799</v>
+        <v>119.3616963016755</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.262536145671332e-08</v>
+        <v>2.262534013321325e-08</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.7951882469836797</v>
+        <v>0.795188307249609</v>
       </c>
     </row>
   </sheetData>
@@ -2426,28 +2426,28 @@
         <v>-74.611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2720457344516501</v>
+        <v>0.2720457344516437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5572529293545954</v>
+        <v>0.5572529293546007</v>
       </c>
       <c r="H2" t="n">
-        <v>1.099907237109413</v>
+        <v>1.099907237109436</v>
       </c>
       <c r="I2" t="n">
-        <v>2.045591311832009</v>
+        <v>2.045591311831987</v>
       </c>
       <c r="J2" t="n">
-        <v>23.12159672972388</v>
+        <v>23.12159672972395</v>
       </c>
       <c r="K2" t="n">
-        <v>85.3953647282212</v>
+        <v>85.39536472822121</v>
       </c>
       <c r="W2" t="n">
-        <v>12.4162655416546</v>
+        <v>12.41626554165463</v>
       </c>
       <c r="X2" t="n">
-        <v>-7840.929782597505</v>
+        <v>-7840.929782597527</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>1.616787432361747e-05</v>
+        <v>1.61678743359162e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>0.5000000000000001</v>
@@ -2469,7 +2469,7 @@
         <v>183.956</v>
       </c>
       <c r="C3" t="n">
-        <v>363.6497639271059</v>
+        <v>363.6497547221265</v>
       </c>
       <c r="D3" t="n">
         <v>5.20708e-07</v>
@@ -2478,37 +2478,37 @@
         <v>-76.012</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2268987737245904</v>
+        <v>0.2268987737245975</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6368823274303386</v>
+        <v>0.6368823274303759</v>
       </c>
       <c r="H3" t="n">
-        <v>1.268729063557205</v>
+        <v>1.268729063557225</v>
       </c>
       <c r="I3" t="n">
-        <v>2.197811681729863</v>
+        <v>2.197811681729848</v>
       </c>
       <c r="J3" t="n">
-        <v>30.24769433494262</v>
+        <v>30.24769433494263</v>
       </c>
       <c r="K3" t="n">
-        <v>85.74484201939346</v>
+        <v>85.74484201939345</v>
       </c>
       <c r="W3" t="n">
         <v>13.44025355411804</v>
       </c>
       <c r="X3" t="n">
-        <v>-8066.219127042919</v>
+        <v>-8066.219127042916</v>
       </c>
       <c r="Y3" t="n">
-        <v>191.0132913280065</v>
+        <v>191.0133012066292</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.905519892743868e-09</v>
+        <v>7.905520432140107e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.875464542001318</v>
+        <v>0.8754645405653402</v>
       </c>
     </row>
     <row r="4">
@@ -2519,7 +2519,7 @@
         <v>180.083</v>
       </c>
       <c r="C4" t="n">
-        <v>387.0542451777099</v>
+        <v>387.0542433685881</v>
       </c>
       <c r="D4" t="n">
         <v>5.178079999999999e-07</v>
@@ -2531,34 +2531,34 @@
         <v>0.3630593732499043</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9972396494370661</v>
+        <v>0.9972396494370659</v>
       </c>
       <c r="H4" t="n">
-        <v>1.575740765283392</v>
+        <v>1.575740765283397</v>
       </c>
       <c r="I4" t="n">
-        <v>2.361346673380489</v>
+        <v>2.361346673380483</v>
       </c>
       <c r="J4" t="n">
-        <v>33.66970051690187</v>
+        <v>33.66970051690188</v>
       </c>
       <c r="K4" t="n">
-        <v>86.21932323919702</v>
+        <v>86.21932323919701</v>
       </c>
       <c r="W4" t="n">
-        <v>15.13289886314923</v>
+        <v>15.1328988631492</v>
       </c>
       <c r="X4" t="n">
-        <v>-8984.526394492035</v>
+        <v>-8984.526394492013</v>
       </c>
       <c r="Y4" t="n">
-        <v>159.9096847103525</v>
+        <v>159.9096871759979</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.9129023585624e-09</v>
+        <v>6.912902421749697e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.875124314175641</v>
+        <v>0.8751243143808325</v>
       </c>
     </row>
     <row r="5">
@@ -2569,7 +2569,7 @@
         <v>172.3580000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>393.2590477592757</v>
+        <v>393.2590386044641</v>
       </c>
       <c r="D5" t="n">
         <v>5.15806e-07</v>
@@ -2578,19 +2578,19 @@
         <v>-76.84699999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04427324000057927</v>
+        <v>0.04427324000057926</v>
       </c>
       <c r="G5" t="n">
         <v>0.4288234263283882</v>
       </c>
       <c r="H5" t="n">
-        <v>1.088016781281395</v>
+        <v>1.088016781281365</v>
       </c>
       <c r="I5" t="n">
-        <v>2.048388617719308</v>
+        <v>2.048388617719314</v>
       </c>
       <c r="J5" t="n">
-        <v>32.71649156956062</v>
+        <v>32.7164915695606</v>
       </c>
       <c r="K5" t="n">
         <v>85.94346905743005</v>
@@ -2602,13 +2602,13 @@
         <v>-8216.205625040062</v>
       </c>
       <c r="Y5" t="n">
-        <v>146.8984825696081</v>
+        <v>146.898476784162</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.370404615978873e-09</v>
+        <v>6.370403006032022e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8771097234591843</v>
+        <v>0.8771097177957955</v>
       </c>
     </row>
     <row r="6">
@@ -2619,7 +2619,7 @@
         <v>170.711</v>
       </c>
       <c r="C6" t="n">
-        <v>390.2476918822101</v>
+        <v>390.2476932266832</v>
       </c>
       <c r="D6" t="n">
         <v>5.1463e-07</v>
@@ -2628,37 +2628,37 @@
         <v>-77.111</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1632241141875213</v>
+        <v>0.1632241141875192</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6023929228274145</v>
+        <v>0.6023929228274406</v>
       </c>
       <c r="H6" t="n">
-        <v>1.394722846961558</v>
+        <v>1.394722846961592</v>
       </c>
       <c r="I6" t="n">
-        <v>1.979967496398626</v>
+        <v>1.979967496398638</v>
       </c>
       <c r="J6" t="n">
-        <v>31.58056057728474</v>
+        <v>31.58056057728472</v>
       </c>
       <c r="K6" t="n">
-        <v>86.23399469050551</v>
+        <v>86.2339946905055</v>
       </c>
       <c r="W6" t="n">
-        <v>15.19202414063634</v>
+        <v>15.1920241406363</v>
       </c>
       <c r="X6" t="n">
-        <v>-8778.693107569165</v>
+        <v>-8778.693107569135</v>
       </c>
       <c r="Y6" t="n">
-        <v>142.06375932202</v>
+        <v>142.0637608296033</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.750435024820161e-09</v>
+        <v>5.750435092777831e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.88292339022861</v>
+        <v>0.8829233951345242</v>
       </c>
     </row>
     <row r="7">
@@ -2669,7 +2669,7 @@
         <v>168.984</v>
       </c>
       <c r="C7" t="n">
-        <v>383.2824836663607</v>
+        <v>383.2824838252924</v>
       </c>
       <c r="D7" t="n">
         <v>5.13615e-07</v>
@@ -2678,37 +2678,37 @@
         <v>-77.367</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5699435146274544</v>
+        <v>0.5699435146274735</v>
       </c>
       <c r="G7" t="n">
-        <v>1.011273201742436</v>
+        <v>1.011273201742432</v>
       </c>
       <c r="H7" t="n">
         <v>1.685503940553962</v>
       </c>
       <c r="I7" t="n">
-        <v>2.683296619601748</v>
+        <v>2.68329661960172</v>
       </c>
       <c r="J7" t="n">
-        <v>45.9869421948146</v>
+        <v>45.98694219481419</v>
       </c>
       <c r="K7" t="n">
         <v>86.51320910630089</v>
       </c>
       <c r="W7" t="n">
-        <v>16.41194814785252</v>
+        <v>16.41194814785253</v>
       </c>
       <c r="X7" t="n">
-        <v>-9402.657814577398</v>
+        <v>-9402.657814577411</v>
       </c>
       <c r="Y7" t="n">
-        <v>142.5645284873783</v>
+        <v>142.564527343569</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.67972254819635e-09</v>
+        <v>5.679722261742771e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8863457788451515</v>
+        <v>0.8863457807567284</v>
       </c>
     </row>
     <row r="8">
@@ -2719,7 +2719,7 @@
         <v>165.126</v>
       </c>
       <c r="C8" t="n">
-        <v>458.7931246357018</v>
+        <v>458.7931325398323</v>
       </c>
       <c r="D8" t="n">
         <v>5.130670000000001e-07</v>
@@ -2731,16 +2731,16 @@
         <v>0.3388034996971831</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9967164359554841</v>
+        <v>0.996716435955491</v>
       </c>
       <c r="H8" t="n">
-        <v>1.814657303785062</v>
+        <v>1.814657303785136</v>
       </c>
       <c r="I8" t="n">
-        <v>2.666723339112187</v>
+        <v>2.666723339112169</v>
       </c>
       <c r="J8" t="n">
-        <v>47.8269404575823</v>
+        <v>47.82694045758274</v>
       </c>
       <c r="K8" t="n">
         <v>86.55911649603661</v>
@@ -2749,16 +2749,16 @@
         <v>16.63145015458909</v>
       </c>
       <c r="X8" t="n">
-        <v>-9405.307126144153</v>
+        <v>-9405.307126144156</v>
       </c>
       <c r="Y8" t="n">
-        <v>59.02804183650778</v>
+        <v>59.02803660977627</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.354462815013564e-09</v>
+        <v>4.354464015178583e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8776529971076544</v>
+        <v>0.877652969565531</v>
       </c>
     </row>
     <row r="9">
@@ -2769,7 +2769,7 @@
         <v>156.348</v>
       </c>
       <c r="C9" t="n">
-        <v>383.7329921473025</v>
+        <v>383.7329874695934</v>
       </c>
       <c r="D9" t="n">
         <v>5.1277e-07</v>
@@ -2778,37 +2778,37 @@
         <v>-77.816</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2366907644341785</v>
+        <v>0.2366907644341796</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4167899803093497</v>
+        <v>0.4167899803093619</v>
       </c>
       <c r="H9" t="n">
-        <v>1.129201596139299</v>
+        <v>1.129201596139296</v>
       </c>
       <c r="I9" t="n">
-        <v>1.943290000706279</v>
+        <v>1.943290000706262</v>
       </c>
       <c r="J9" t="n">
-        <v>35.19957650124805</v>
+        <v>35.19957650124807</v>
       </c>
       <c r="K9" t="n">
-        <v>86.07449723841992</v>
+        <v>86.07449723841991</v>
       </c>
       <c r="W9" t="n">
-        <v>14.57293642754105</v>
+        <v>14.57293642754102</v>
       </c>
       <c r="X9" t="n">
-        <v>-8063.108053185911</v>
+        <v>-8063.108053185894</v>
       </c>
       <c r="Y9" t="n">
-        <v>130.3980580756192</v>
+        <v>130.3980433726214</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.660710440691972e-09</v>
+        <v>5.66070795484045e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8841113583034919</v>
+        <v>0.8841113566439921</v>
       </c>
     </row>
     <row r="10">
@@ -2828,28 +2828,28 @@
         <v>-77.991</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2206160237111593</v>
+        <v>0.2206160237111546</v>
       </c>
       <c r="G10" t="n">
         <v>0.7543313861075586</v>
       </c>
       <c r="H10" t="n">
-        <v>1.532648826214313</v>
+        <v>1.532648826214294</v>
       </c>
       <c r="I10" t="n">
         <v>2.682490663789457</v>
       </c>
       <c r="J10" t="n">
-        <v>52.62256582177227</v>
+        <v>52.62256582177207</v>
       </c>
       <c r="K10" t="n">
         <v>86.36674037246492</v>
       </c>
       <c r="W10" t="n">
-        <v>15.74865738981043</v>
+        <v>15.7486573898104</v>
       </c>
       <c r="X10" t="n">
-        <v>-8648.107996158215</v>
+        <v>-8648.107996158202</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>2.131163266566401e-06</v>
+        <v>2.008806029530213e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7850367555682619</v>
+        <v>0.7937327979097901</v>
       </c>
     </row>
     <row r="11">
@@ -2871,7 +2871,7 @@
         <v>153.829</v>
       </c>
       <c r="C11" t="n">
-        <v>444.3917867001123</v>
+        <v>444.3917420657357</v>
       </c>
       <c r="D11" t="n">
         <v>5.12047e-07</v>
@@ -2880,37 +2880,37 @@
         <v>-78.163</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4091694089847645</v>
+        <v>0.4091694089847748</v>
       </c>
       <c r="G11" t="n">
-        <v>0.574477866256307</v>
+        <v>0.5744778662563396</v>
       </c>
       <c r="H11" t="n">
         <v>1.549948974767799</v>
       </c>
       <c r="I11" t="n">
-        <v>2.231253077970797</v>
+        <v>2.231253077970798</v>
       </c>
       <c r="J11" t="n">
         <v>41.34519349762449</v>
       </c>
       <c r="K11" t="n">
-        <v>86.56369146988662</v>
+        <v>86.56369146988663</v>
       </c>
       <c r="W11" t="n">
-        <v>16.65364594434075</v>
+        <v>16.65364594434083</v>
       </c>
       <c r="X11" t="n">
-        <v>-9064.751095793868</v>
+        <v>-9064.751095793925</v>
       </c>
       <c r="Y11" t="n">
-        <v>56.67532839650912</v>
+        <v>56.6753550132556</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.23478689178182e-09</v>
+        <v>4.234785720362304e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.881795207234946</v>
+        <v>0.8817952064412825</v>
       </c>
     </row>
     <row r="12">
@@ -2921,7 +2921,7 @@
         <v>151.853</v>
       </c>
       <c r="C12" t="n">
-        <v>386.1374707202639</v>
+        <v>386.1374916957523</v>
       </c>
       <c r="D12" t="n">
         <v>5.11952e-07</v>
@@ -2930,10 +2930,10 @@
         <v>-78.35299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.637259481460802</v>
+        <v>0.6372594814608188</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9660936609081621</v>
+        <v>0.9660936609081548</v>
       </c>
       <c r="H12" t="n">
         <v>1.48128779744172</v>
@@ -2942,7 +2942,7 @@
         <v>2.827935325292888</v>
       </c>
       <c r="J12" t="n">
-        <v>48.61631945073621</v>
+        <v>48.61631945073572</v>
       </c>
       <c r="K12" t="n">
         <v>86.68660525809</v>
@@ -2951,16 +2951,16 @@
         <v>17.27288744915598</v>
       </c>
       <c r="X12" t="n">
-        <v>-9312.487903245348</v>
+        <v>-9312.487903245345</v>
       </c>
       <c r="Y12" t="n">
-        <v>110.2976991947266</v>
+        <v>110.297681648891</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.874724432965449e-09</v>
+        <v>4.87472494368755e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8911650437145543</v>
+        <v>0.891165036856356</v>
       </c>
     </row>
     <row r="13">
@@ -2980,28 +2980,28 @@
         <v>-78.512</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5796616328349538</v>
+        <v>0.579661632834932</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6343058820088262</v>
+        <v>0.6343058820088076</v>
       </c>
       <c r="H13" t="n">
-        <v>1.512314145170895</v>
+        <v>1.512314145170923</v>
       </c>
       <c r="I13" t="n">
-        <v>2.317249196402199</v>
+        <v>2.317249196402248</v>
       </c>
       <c r="J13" t="n">
-        <v>44.43721378107117</v>
+        <v>44.43721378107116</v>
       </c>
       <c r="K13" t="n">
         <v>86.622170643838</v>
       </c>
       <c r="W13" t="n">
-        <v>16.94265132071409</v>
+        <v>16.9426513207141</v>
       </c>
       <c r="X13" t="n">
-        <v>-9025.273366936073</v>
+        <v>-9025.273366936079</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>1.63263793774982e-06</v>
+        <v>1.633045491742949e-06</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8245042456947388</v>
+        <v>0.8244671470022109</v>
       </c>
     </row>
     <row r="14">
@@ -3032,13 +3032,13 @@
         <v>-78.64400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09589835926551951</v>
+        <v>0.09589835926551953</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8394914168343394</v>
+        <v>0.8394914168343167</v>
       </c>
       <c r="H14" t="n">
-        <v>1.570705945470481</v>
+        <v>1.570705945470442</v>
       </c>
       <c r="I14" t="n">
         <v>2.536366543814996</v>
@@ -3050,10 +3050,10 @@
         <v>86.4417932709521</v>
       </c>
       <c r="W14" t="n">
-        <v>16.08172519812724</v>
+        <v>16.08172519812722</v>
       </c>
       <c r="X14" t="n">
-        <v>-8441.386468294138</v>
+        <v>-8441.386468294122</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>1.555567234494001e-06</v>
+        <v>1.555156473695115e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8317010721692827</v>
+        <v>0.8317407133534666</v>
       </c>
     </row>
     <row r="15">
@@ -3075,7 +3075,7 @@
         <v>139.908</v>
       </c>
       <c r="C15" t="n">
-        <v>427.361725617272</v>
+        <v>427.3617248965816</v>
       </c>
       <c r="D15" t="n">
         <v>5.11432e-07</v>
@@ -3084,37 +3084,37 @@
         <v>-78.77500000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1115059899106077</v>
+        <v>0.1115059899106161</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8241650984262582</v>
+        <v>0.8241650984262513</v>
       </c>
       <c r="H15" t="n">
         <v>1.488049813722304</v>
       </c>
       <c r="I15" t="n">
-        <v>2.285879891882056</v>
+        <v>2.285879891882137</v>
       </c>
       <c r="J15" t="n">
-        <v>46.01942209834783</v>
+        <v>46.01942209834789</v>
       </c>
       <c r="K15" t="n">
-        <v>86.44160452250371</v>
+        <v>86.4416045225037</v>
       </c>
       <c r="W15" t="n">
-        <v>16.08086997576172</v>
+        <v>16.08086997576169</v>
       </c>
       <c r="X15" t="n">
-        <v>-8347.666635147394</v>
+        <v>-8347.666635147372</v>
       </c>
       <c r="Y15" t="n">
-        <v>53.72911812333076</v>
+        <v>53.72914852306968</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.967303247131936e-09</v>
+        <v>3.96730562527593e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8890166261869491</v>
+        <v>0.8890166425849961</v>
       </c>
     </row>
     <row r="16">
@@ -3125,7 +3125,7 @@
         <v>140.885</v>
       </c>
       <c r="C16" t="n">
-        <v>442.8692696758281</v>
+        <v>442.8690835133963</v>
       </c>
       <c r="D16" t="n">
         <v>5.11416e-07</v>
@@ -3134,37 +3134,37 @@
         <v>-78.937</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4647135923414617</v>
+        <v>0.4647135923414618</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6639705578297351</v>
+        <v>0.6639705578297354</v>
       </c>
       <c r="H16" t="n">
-        <v>1.685470615248416</v>
+        <v>1.68547061524846</v>
       </c>
       <c r="I16" t="n">
         <v>2.385794665227607</v>
       </c>
       <c r="J16" t="n">
-        <v>47.47124749764816</v>
+        <v>47.47124749764789</v>
       </c>
       <c r="K16" t="n">
-        <v>86.72236432383686</v>
+        <v>86.72236432383684</v>
       </c>
       <c r="W16" t="n">
-        <v>17.46175350010721</v>
+        <v>17.46175350010711</v>
       </c>
       <c r="X16" t="n">
-        <v>-9018.367276180637</v>
+        <v>-9018.367276180579</v>
       </c>
       <c r="Y16" t="n">
-        <v>33.02922131950001</v>
+        <v>33.02976585294689</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.664617131412577e-09</v>
+        <v>3.6646680318347e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8885975038958073</v>
+        <v>0.8885971133413211</v>
       </c>
     </row>
     <row r="17">
@@ -3175,7 +3175,7 @@
         <v>134.765</v>
       </c>
       <c r="C17" t="n">
-        <v>396.6407040101756</v>
+        <v>396.6406713053481</v>
       </c>
       <c r="D17" t="n">
         <v>5.11313e-07</v>
@@ -3184,19 +3184,19 @@
         <v>-79.042</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3477365262141789</v>
+        <v>0.3477365262142145</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5529316491965853</v>
+        <v>0.5529316491965903</v>
       </c>
       <c r="H17" t="n">
-        <v>1.204506388140444</v>
+        <v>1.204506388140443</v>
       </c>
       <c r="I17" t="n">
-        <v>2.041631753494224</v>
+        <v>2.041631753494221</v>
       </c>
       <c r="J17" t="n">
-        <v>42.44051890047962</v>
+        <v>42.44051890048005</v>
       </c>
       <c r="K17" t="n">
         <v>86.41701922497259</v>
@@ -3205,16 +3205,16 @@
         <v>15.97024282799256</v>
       </c>
       <c r="X17" t="n">
-        <v>-8112.331798445049</v>
+        <v>-8112.33179844505</v>
       </c>
       <c r="Y17" t="n">
-        <v>75.44817053871354</v>
+        <v>75.44823366840062</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.181993003410859e-09</v>
+        <v>4.181996194230989e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8940987488573682</v>
+        <v>0.8940987670535485</v>
       </c>
     </row>
     <row r="18">
@@ -3234,19 +3234,19 @@
         <v>-79.161</v>
       </c>
       <c r="F18" t="n">
-        <v>0.206532410750953</v>
+        <v>0.2065324107509542</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5120631779318011</v>
+        <v>0.5120631779318133</v>
       </c>
       <c r="H18" t="n">
-        <v>1.252374548146723</v>
+        <v>1.252374548146775</v>
       </c>
       <c r="I18" t="n">
         <v>2.457918192885649</v>
       </c>
       <c r="J18" t="n">
-        <v>56.97753812005435</v>
+        <v>56.97753812005433</v>
       </c>
       <c r="K18" t="n">
         <v>86.28313144161756</v>
@@ -3255,7 +3255,7 @@
         <v>15.3934375115313</v>
       </c>
       <c r="X18" t="n">
-        <v>-7723.155358266668</v>
+        <v>-7723.15535826667</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>1.344374033453632e-06</v>
+        <v>1.344172234978167e-06</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.853593503515818</v>
+        <v>0.8536164952250157</v>
       </c>
     </row>
     <row r="19">
@@ -3277,7 +3277,7 @@
         <v>129.931</v>
       </c>
       <c r="C19" t="n">
-        <v>416.9211472387407</v>
+        <v>416.9211306037764</v>
       </c>
       <c r="D19" t="n">
         <v>5.11415e-07</v>
@@ -3286,37 +3286,37 @@
         <v>-79.30200000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1330858811668987</v>
+        <v>0.1330858811668914</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4570632257041024</v>
+        <v>0.4570632257040505</v>
       </c>
       <c r="H19" t="n">
         <v>1.092793376310215</v>
       </c>
       <c r="I19" t="n">
-        <v>1.848939700136619</v>
+        <v>1.848939700136615</v>
       </c>
       <c r="J19" t="n">
-        <v>40.30521752203344</v>
+        <v>40.30521752203354</v>
       </c>
       <c r="K19" t="n">
-        <v>86.40867727258967</v>
+        <v>86.40867727258966</v>
       </c>
       <c r="W19" t="n">
-        <v>15.93305002266193</v>
+        <v>15.9330500226619</v>
       </c>
       <c r="X19" t="n">
-        <v>-7925.510388842446</v>
+        <v>-7925.510388842426</v>
       </c>
       <c r="Y19" t="n">
-        <v>45.59886413900296</v>
+        <v>45.59883408696484</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.748221525319169e-09</v>
+        <v>3.748221195700228e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8931765201238405</v>
+        <v>0.8931764030270641</v>
       </c>
     </row>
     <row r="20">
@@ -3327,7 +3327,7 @@
         <v>128.692</v>
       </c>
       <c r="C20" t="n">
-        <v>397.2027845337354</v>
+        <v>397.202793076122</v>
       </c>
       <c r="D20" t="n">
         <v>5.113180000000001e-07</v>
@@ -3339,34 +3339,34 @@
         <v>0.1297665175197009</v>
       </c>
       <c r="G20" t="n">
-        <v>0.565735524987386</v>
+        <v>0.5657355249873937</v>
       </c>
       <c r="H20" t="n">
-        <v>1.344986339498656</v>
+        <v>1.344986339498661</v>
       </c>
       <c r="I20" t="n">
-        <v>2.153225000437529</v>
+        <v>2.153225000437606</v>
       </c>
       <c r="J20" t="n">
-        <v>46.44978303970022</v>
+        <v>46.44978303970057</v>
       </c>
       <c r="K20" t="n">
-        <v>86.51583409920414</v>
+        <v>86.51583409920416</v>
       </c>
       <c r="W20" t="n">
-        <v>16.42434358446324</v>
+        <v>16.42434358446329</v>
       </c>
       <c r="X20" t="n">
-        <v>-8100.256490752301</v>
+        <v>-8100.256490752329</v>
       </c>
       <c r="Y20" t="n">
-        <v>91.7719657082217</v>
+        <v>91.77194030896482</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.983980878070751e-08</v>
+        <v>2.983976772289966e-08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.7636308922401035</v>
+        <v>0.7636309787707771</v>
       </c>
     </row>
     <row r="21">
@@ -3377,7 +3377,7 @@
         <v>125.114</v>
       </c>
       <c r="C21" t="n">
-        <v>396.9955436015437</v>
+        <v>396.9955233739875</v>
       </c>
       <c r="D21" t="n">
         <v>5.11435e-07</v>
@@ -3386,37 +3386,37 @@
         <v>-79.544</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1017203708429545</v>
+        <v>0.1017203708429481</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5672137690783522</v>
+        <v>0.5672137690783452</v>
       </c>
       <c r="H21" t="n">
-        <v>1.37875187598734</v>
+        <v>1.378751875987282</v>
       </c>
       <c r="I21" t="n">
-        <v>2.549378574614573</v>
+        <v>2.549378574614653</v>
       </c>
       <c r="J21" t="n">
-        <v>62.86242267236202</v>
+        <v>62.86242267236146</v>
       </c>
       <c r="K21" t="n">
-        <v>86.38509718954563</v>
+        <v>86.38509718954566</v>
       </c>
       <c r="W21" t="n">
-        <v>15.82884480380962</v>
+        <v>15.82884480380971</v>
       </c>
       <c r="X21" t="n">
-        <v>-7709.902032735014</v>
+        <v>-7709.902032735069</v>
       </c>
       <c r="Y21" t="n">
-        <v>93.03109718082503</v>
+        <v>93.03111347132511</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.6267670528128e-08</v>
+        <v>4.626765849711758e-08</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.7343990011673772</v>
+        <v>0.7343990254680249</v>
       </c>
     </row>
     <row r="22">
@@ -3427,7 +3427,7 @@
         <v>125.383</v>
       </c>
       <c r="C22" t="n">
-        <v>393.2974255438315</v>
+        <v>393.297396083376</v>
       </c>
       <c r="D22" t="n">
         <v>5.11423e-07</v>
@@ -3436,19 +3436,19 @@
         <v>-79.65600000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1306278689324792</v>
+        <v>0.1306278689324751</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6328748845939941</v>
+        <v>0.632874884593983</v>
       </c>
       <c r="H22" t="n">
         <v>1.4767764927858</v>
       </c>
       <c r="I22" t="n">
-        <v>2.393417089662345</v>
+        <v>2.393417089662365</v>
       </c>
       <c r="J22" t="n">
-        <v>55.48930023729125</v>
+        <v>55.48930023729062</v>
       </c>
       <c r="K22" t="n">
         <v>86.64470537406686</v>
@@ -3460,13 +3460,13 @@
         <v>-8259.885288528591</v>
       </c>
       <c r="Y22" t="n">
-        <v>55.98906642483281</v>
+        <v>55.98905151635061</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.687056364749095e-09</v>
+        <v>3.687047499124076e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9004620741576727</v>
+        <v>0.9004621972677983</v>
       </c>
     </row>
   </sheetData>
@@ -3623,7 +3623,7 @@
         <v>238.871</v>
       </c>
       <c r="C2" t="n">
-        <v>325.7049933330659</v>
+        <v>325.7049731563766</v>
       </c>
       <c r="D2" t="n">
         <v>4.87922e-07</v>
@@ -3632,37 +3632,37 @@
         <v>-75.291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02101189782293583</v>
+        <v>0.02101189782293665</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4416031295047814</v>
+        <v>0.4416031295047559</v>
       </c>
       <c r="H2" t="n">
-        <v>1.253422903089771</v>
+        <v>1.253422903089767</v>
       </c>
       <c r="I2" t="n">
-        <v>1.829554929011778</v>
+        <v>1.829554929011708</v>
       </c>
       <c r="J2" t="n">
-        <v>27.53106510200563</v>
+        <v>27.53106510200568</v>
       </c>
       <c r="K2" t="n">
-        <v>85.34901167197908</v>
+        <v>85.34901167197907</v>
       </c>
       <c r="W2" t="n">
-        <v>12.29198442932583</v>
+        <v>12.29198442932581</v>
       </c>
       <c r="X2" t="n">
-        <v>-8200.373625341766</v>
+        <v>-8200.373625341748</v>
       </c>
       <c r="Y2" t="n">
-        <v>242.1786016804024</v>
+        <v>242.1785808988342</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.056861174184744e-09</v>
+        <v>4.0568605612986e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9328979066333302</v>
+        <v>0.9328979490642934</v>
       </c>
     </row>
     <row r="3">
@@ -3673,7 +3673,7 @@
         <v>173.854</v>
       </c>
       <c r="C3" t="n">
-        <v>304.1970272889869</v>
+        <v>304.1970270758579</v>
       </c>
       <c r="D3" t="n">
         <v>4.87782e-07</v>
@@ -3682,19 +3682,19 @@
         <v>-77.417</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2022948526187804</v>
+        <v>0.2022948526187776</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4694093191168598</v>
+        <v>0.4694093191168597</v>
       </c>
       <c r="H3" t="n">
-        <v>1.216195771550979</v>
+        <v>1.216195771550984</v>
       </c>
       <c r="I3" t="n">
-        <v>2.026329615081339</v>
+        <v>2.026329615081373</v>
       </c>
       <c r="J3" t="n">
-        <v>31.41383807915502</v>
+        <v>31.413838079155</v>
       </c>
       <c r="K3" t="n">
         <v>86.28775760729498</v>
@@ -3703,16 +3703,16 @@
         <v>15.41267457729695</v>
       </c>
       <c r="X3" t="n">
-        <v>-9107.587728673427</v>
+        <v>-9107.587728673425</v>
       </c>
       <c r="Y3" t="n">
-        <v>237.7114894748159</v>
+        <v>237.7114903220558</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.43709630984683e-09</v>
+        <v>7.437096324568277e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9005567507759799</v>
+        <v>0.9005567520160501</v>
       </c>
     </row>
     <row r="4">
@@ -3723,7 +3723,7 @@
         <v>158.3100000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>482.9546466120261</v>
+        <v>482.954627828173</v>
       </c>
       <c r="D4" t="n">
         <v>4.84144e-07</v>
@@ -3732,37 +3732,37 @@
         <v>-78.038</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05770519846303718</v>
+        <v>0.0577051984630322</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6753350119727103</v>
+        <v>0.6753350119726891</v>
       </c>
       <c r="H4" t="n">
-        <v>1.46294988078753</v>
+        <v>1.462949880787509</v>
       </c>
       <c r="I4" t="n">
-        <v>2.228208201846874</v>
+        <v>2.228208201846877</v>
       </c>
       <c r="J4" t="n">
-        <v>38.26377739692781</v>
+        <v>38.26377739692784</v>
       </c>
       <c r="K4" t="n">
         <v>86.29597584401212</v>
       </c>
       <c r="W4" t="n">
-        <v>15.44696695383033</v>
+        <v>15.44696695383032</v>
       </c>
       <c r="X4" t="n">
-        <v>-8814.495803533349</v>
+        <v>-8814.495803533346</v>
       </c>
       <c r="Y4" t="n">
-        <v>42.75312280156238</v>
+        <v>42.75314916788184</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.75090618562822e-09</v>
+        <v>3.750906368241167e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8816567426619194</v>
+        <v>0.8816567695562842</v>
       </c>
     </row>
     <row r="5">
@@ -3773,7 +3773,7 @@
         <v>154.839</v>
       </c>
       <c r="C5" t="n">
-        <v>446.7091493264989</v>
+        <v>446.709143098156</v>
       </c>
       <c r="D5" t="n">
         <v>4.81253e-07</v>
@@ -3785,16 +3785,16 @@
         <v>0.2463898255991757</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9327750449122331</v>
+        <v>0.9327750449122383</v>
       </c>
       <c r="H5" t="n">
-        <v>1.581829270750887</v>
+        <v>1.58182927075096</v>
       </c>
       <c r="I5" t="n">
-        <v>2.348649979974415</v>
+        <v>2.348649979974319</v>
       </c>
       <c r="J5" t="n">
-        <v>36.85928415814353</v>
+        <v>36.85928415814359</v>
       </c>
       <c r="K5" t="n">
         <v>86.61836106409478</v>
@@ -3806,13 +3806,13 @@
         <v>-9534.062981448962</v>
       </c>
       <c r="Y5" t="n">
-        <v>72.57092775892666</v>
+        <v>72.57093426314468</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.211302805758928e-09</v>
+        <v>4.21130179896689e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8834007791854758</v>
+        <v>0.8834008086826522</v>
       </c>
     </row>
     <row r="6">
@@ -3823,7 +3823,7 @@
         <v>147.86</v>
       </c>
       <c r="C6" t="n">
-        <v>368.9668466882758</v>
+        <v>368.9668498255512</v>
       </c>
       <c r="D6" t="n">
         <v>4.79014e-07</v>
@@ -3832,19 +3832,19 @@
         <v>-78.628</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07711677239392996</v>
+        <v>0.07711677239394175</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3715025133735628</v>
+        <v>0.3715025133735476</v>
       </c>
       <c r="H6" t="n">
         <v>1.273188192489151</v>
       </c>
       <c r="I6" t="n">
-        <v>2.099177526153265</v>
+        <v>2.099177526153221</v>
       </c>
       <c r="J6" t="n">
-        <v>38.39836110295903</v>
+        <v>38.39836110295906</v>
       </c>
       <c r="K6" t="n">
         <v>86.41644623323495</v>
@@ -3853,16 +3853,16 @@
         <v>15.96768259864628</v>
       </c>
       <c r="X6" t="n">
-        <v>-8820.971473368434</v>
+        <v>-8820.97147336844</v>
       </c>
       <c r="Y6" t="n">
-        <v>144.8544539254593</v>
+        <v>144.8544544199808</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.140868309727292e-09</v>
+        <v>5.140868590765824e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.895471127643144</v>
+        <v>0.8954711303316567</v>
       </c>
     </row>
     <row r="7">
@@ -3873,7 +3873,7 @@
         <v>144.188</v>
       </c>
       <c r="C7" t="n">
-        <v>371.2024076802504</v>
+        <v>371.2024190474932</v>
       </c>
       <c r="D7" t="n">
         <v>4.77705e-07</v>
@@ -3882,37 +3882,37 @@
         <v>-78.854</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1261868149208826</v>
+        <v>0.1261868149208869</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5286105061370255</v>
+        <v>0.5286105061370348</v>
       </c>
       <c r="H7" t="n">
-        <v>1.324726675539995</v>
+        <v>1.324726675540119</v>
       </c>
       <c r="I7" t="n">
-        <v>2.196136895677287</v>
+        <v>2.196136895677293</v>
       </c>
       <c r="J7" t="n">
-        <v>39.5511188707784</v>
+        <v>39.55111887077848</v>
       </c>
       <c r="K7" t="n">
         <v>86.46781189788122</v>
       </c>
       <c r="W7" t="n">
-        <v>16.20048960678877</v>
+        <v>16.20048960678876</v>
       </c>
       <c r="X7" t="n">
-        <v>-8822.49052332835</v>
+        <v>-8822.490523328337</v>
       </c>
       <c r="Y7" t="n">
-        <v>135.3112536506113</v>
+        <v>135.3112369998083</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.823014132585008e-09</v>
+        <v>4.823013576349e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8979351380162091</v>
+        <v>0.8979351306034531</v>
       </c>
     </row>
     <row r="8">
@@ -3923,7 +3923,7 @@
         <v>140.3050000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>287.0887637740387</v>
+        <v>287.0887483015436</v>
       </c>
       <c r="D8" t="n">
         <v>4.76467e-07</v>
@@ -3932,37 +3932,37 @@
         <v>-79.038</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1536918080742448</v>
+        <v>0.1536918080742441</v>
       </c>
       <c r="G8" t="n">
-        <v>0.583854032139182</v>
+        <v>0.5838540321391755</v>
       </c>
       <c r="H8" t="n">
-        <v>1.284295879553938</v>
+        <v>1.284295879553887</v>
       </c>
       <c r="I8" t="n">
         <v>2.160212447265749</v>
       </c>
       <c r="J8" t="n">
-        <v>40.39249237444133</v>
+        <v>40.39249237444132</v>
       </c>
       <c r="K8" t="n">
         <v>86.51486193447968</v>
       </c>
       <c r="W8" t="n">
-        <v>16.41975076668417</v>
+        <v>16.41975076668421</v>
       </c>
       <c r="X8" t="n">
-        <v>-8812.921887403612</v>
+        <v>-8812.921887403641</v>
       </c>
       <c r="Y8" t="n">
-        <v>214.804272242354</v>
+        <v>214.8042785166869</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.641244788193796e-09</v>
+        <v>6.641242705775471e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9109185952838685</v>
+        <v>0.9109186072599155</v>
       </c>
     </row>
     <row r="9">
@@ -3973,7 +3973,7 @@
         <v>135.5</v>
       </c>
       <c r="C9" t="n">
-        <v>280.8981722421294</v>
+        <v>280.8981827421281</v>
       </c>
       <c r="D9" t="n">
         <v>4.7574e-07</v>
@@ -3982,16 +3982,16 @@
         <v>-79.248</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07135794233975726</v>
+        <v>0.07135794233975419</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8777163556381857</v>
+        <v>0.8777163556382003</v>
       </c>
       <c r="H9" t="n">
         <v>1.005117324541387</v>
       </c>
       <c r="I9" t="n">
-        <v>1.968314970434818</v>
+        <v>1.968314970434821</v>
       </c>
       <c r="J9" t="n">
         <v>38.33821509162608</v>
@@ -4000,19 +4000,19 @@
         <v>86.51034475496964</v>
       </c>
       <c r="W9" t="n">
-        <v>16.39844369081006</v>
+        <v>16.39844369081007</v>
       </c>
       <c r="X9" t="n">
         <v>-8660.448950401082</v>
       </c>
       <c r="Y9" t="n">
-        <v>213.5984595748785</v>
+        <v>213.5984532662007</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.461728324893254e-09</v>
+        <v>6.46172908367481e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9144262595446954</v>
+        <v>0.9144262548162821</v>
       </c>
     </row>
     <row r="10">
@@ -4023,7 +4023,7 @@
         <v>131.688</v>
       </c>
       <c r="C10" t="n">
-        <v>416.7538539347299</v>
+        <v>416.7549660407801</v>
       </c>
       <c r="D10" t="n">
         <v>4.74943e-07</v>
@@ -4035,13 +4035,13 @@
         <v>0.1746615813686714</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5400528925217504</v>
+        <v>0.5400528925217368</v>
       </c>
       <c r="H10" t="n">
-        <v>1.180900667657328</v>
+        <v>1.180900667657341</v>
       </c>
       <c r="I10" t="n">
-        <v>2.229148017613586</v>
+        <v>2.229148017613615</v>
       </c>
       <c r="J10" t="n">
         <v>39.61458506589467</v>
@@ -4050,19 +4050,19 @@
         <v>86.59874183786719</v>
       </c>
       <c r="W10" t="n">
-        <v>16.82567386277453</v>
+        <v>16.82567386277451</v>
       </c>
       <c r="X10" t="n">
-        <v>-8761.127318496159</v>
+        <v>-8761.127318496148</v>
       </c>
       <c r="Y10" t="n">
-        <v>67.3293447905464</v>
+        <v>67.32813421914891</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.659841981598257e-09</v>
+        <v>3.659839296772036e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8978041382884377</v>
+        <v>0.897803684055882</v>
       </c>
     </row>
     <row r="11">
@@ -4082,28 +4082,28 @@
         <v>-79.59099999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1638014264097569</v>
+        <v>0.1638014264097591</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6202505999003254</v>
+        <v>0.6202505999003139</v>
       </c>
       <c r="H11" t="n">
-        <v>1.442115668568615</v>
+        <v>1.442115668568622</v>
       </c>
       <c r="I11" t="n">
-        <v>2.397534574039562</v>
+        <v>2.397534574039566</v>
       </c>
       <c r="J11" t="n">
-        <v>44.05801338712136</v>
+        <v>44.05801338712176</v>
       </c>
       <c r="K11" t="n">
         <v>86.70715520511527</v>
       </c>
       <c r="W11" t="n">
-        <v>17.38092384372241</v>
+        <v>17.38092384372242</v>
       </c>
       <c r="X11" t="n">
-        <v>-8935.364647830273</v>
+        <v>-8935.364647830284</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>1.100065549795278e-06</v>
+        <v>1.099953370601029e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8725612409680905</v>
+        <v>0.8725767453339982</v>
       </c>
     </row>
   </sheetData>
@@ -4271,7 +4271,7 @@
         <v>204.016</v>
       </c>
       <c r="C2" t="n">
-        <v>339.7673869785584</v>
+        <v>339.7673915117572</v>
       </c>
       <c r="D2" t="n">
         <v>4.74437e-07</v>
@@ -4283,34 +4283,34 @@
         <v>0.01505260537279031</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5655120172916728</v>
+        <v>0.5655120172916673</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9205681126079903</v>
+        <v>0.9205681126079864</v>
       </c>
       <c r="I2" t="n">
         <v>1.894376023837155</v>
       </c>
       <c r="J2" t="n">
-        <v>32.21984490610736</v>
+        <v>32.21984490610738</v>
       </c>
       <c r="K2" t="n">
-        <v>86.09884029082536</v>
+        <v>86.09884029082535</v>
       </c>
       <c r="W2" t="n">
-        <v>14.66415516767536</v>
+        <v>14.66415516767532</v>
       </c>
       <c r="X2" t="n">
-        <v>-9168.045261675268</v>
+        <v>-9168.045261675235</v>
       </c>
       <c r="Y2" t="n">
-        <v>227.6297222373055</v>
+        <v>227.62971714997</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.765482307061953e-09</v>
+        <v>6.765482074525139e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8973218605203542</v>
+        <v>0.8973218597833352</v>
       </c>
     </row>
     <row r="3">
@@ -4321,7 +4321,7 @@
         <v>179.986</v>
       </c>
       <c r="C3" t="n">
-        <v>545.4438493538568</v>
+        <v>545.4437429207192</v>
       </c>
       <c r="D3" t="n">
         <v>4.76221e-07</v>
@@ -4330,37 +4330,37 @@
         <v>-77.97</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4191208280561204</v>
+        <v>0.4191208280561057</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8201220516463597</v>
+        <v>0.8201220516463859</v>
       </c>
       <c r="H3" t="n">
-        <v>1.525928095295496</v>
+        <v>1.525928095295393</v>
       </c>
       <c r="I3" t="n">
-        <v>1.904812430422271</v>
+        <v>1.9048124304223</v>
       </c>
       <c r="J3" t="n">
-        <v>36.42205966339108</v>
+        <v>36.42205966339107</v>
       </c>
       <c r="K3" t="n">
         <v>86.44781561778335</v>
       </c>
       <c r="W3" t="n">
-        <v>16.10906020334769</v>
+        <v>16.10906020334771</v>
       </c>
       <c r="X3" t="n">
-        <v>-9613.249141578935</v>
+        <v>-9613.249141578946</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.090338729739035</v>
+        <v>5.090451761353048</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.15435445458743e-09</v>
+        <v>4.154361632402995e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8635069527063824</v>
+        <v>0.8635068304305556</v>
       </c>
     </row>
     <row r="4">
@@ -4380,28 +4380,28 @@
         <v>-78.206</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1483437519659716</v>
+        <v>0.148343751965978</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4608595489542529</v>
+        <v>0.460859548954253</v>
       </c>
       <c r="H4" t="n">
-        <v>1.482466634266881</v>
+        <v>1.482466634266912</v>
       </c>
       <c r="I4" t="n">
-        <v>2.299662476454889</v>
+        <v>2.299662476454884</v>
       </c>
       <c r="J4" t="n">
-        <v>41.90094506884159</v>
+        <v>41.90094506884206</v>
       </c>
       <c r="K4" t="n">
-        <v>86.31932891105524</v>
+        <v>86.31932891105522</v>
       </c>
       <c r="W4" t="n">
-        <v>15.54524737775507</v>
+        <v>15.54524737775506</v>
       </c>
       <c r="X4" t="n">
-        <v>-9084.445695273294</v>
+        <v>-9084.445695273291</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>2.27596436351776e-06</v>
+        <v>2.108621816786985e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7646691931757942</v>
+        <v>0.7758179574145685</v>
       </c>
     </row>
     <row r="5">
@@ -4423,7 +4423,7 @@
         <v>168.457</v>
       </c>
       <c r="C5" t="n">
-        <v>406.6017632401113</v>
+        <v>406.6017607657085</v>
       </c>
       <c r="D5" t="n">
         <v>4.76995e-07</v>
@@ -4432,37 +4432,37 @@
         <v>-78.354</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5705037793440886</v>
+        <v>0.5705037793441028</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6994848286068222</v>
+        <v>0.6994848286068229</v>
       </c>
       <c r="H5" t="n">
-        <v>1.805597269583298</v>
+        <v>1.805597269583352</v>
       </c>
       <c r="I5" t="n">
-        <v>2.268839894697855</v>
+        <v>2.26883989469789</v>
       </c>
       <c r="J5" t="n">
-        <v>38.70071618893611</v>
+        <v>38.7007161889357</v>
       </c>
       <c r="K5" t="n">
         <v>86.58067505465303</v>
       </c>
       <c r="W5" t="n">
-        <v>16.73656181709892</v>
+        <v>16.73656181709891</v>
       </c>
       <c r="X5" t="n">
-        <v>-9693.609583300185</v>
+        <v>-9693.609583300173</v>
       </c>
       <c r="Y5" t="n">
-        <v>132.7331362219924</v>
+        <v>132.7331384905397</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.695351319661394e-09</v>
+        <v>5.695351405186227e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8813365593857625</v>
+        <v>0.8813365588996349</v>
       </c>
     </row>
     <row r="6">
@@ -4473,7 +4473,7 @@
         <v>162.661</v>
       </c>
       <c r="C6" t="n">
-        <v>406.2738152706561</v>
+        <v>406.273815992463</v>
       </c>
       <c r="D6" t="n">
         <v>4.77418e-07</v>
@@ -4482,37 +4482,37 @@
         <v>-78.51900000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07890459733344933</v>
+        <v>0.07890459733344735</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5738289258654355</v>
+        <v>0.5738289258654301</v>
       </c>
       <c r="H6" t="n">
-        <v>1.510745159853829</v>
+        <v>1.510745159853823</v>
       </c>
       <c r="I6" t="n">
-        <v>2.556603467005762</v>
+        <v>2.556603467005759</v>
       </c>
       <c r="J6" t="n">
-        <v>49.81846626164148</v>
+        <v>49.81846626164151</v>
       </c>
       <c r="K6" t="n">
-        <v>86.46714595864923</v>
+        <v>86.46714595864921</v>
       </c>
       <c r="W6" t="n">
-        <v>16.19742807996265</v>
+        <v>16.19742807996264</v>
       </c>
       <c r="X6" t="n">
-        <v>-9243.747570538677</v>
+        <v>-9243.747570538662</v>
       </c>
       <c r="Y6" t="n">
-        <v>125.6010462418734</v>
+        <v>125.6010440117387</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.601616956506803e-09</v>
+        <v>5.601616685752391e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8798569487772685</v>
+        <v>0.8798569496078067</v>
       </c>
     </row>
     <row r="7">
@@ -4523,7 +4523,7 @@
         <v>157.551</v>
       </c>
       <c r="C7" t="n">
-        <v>399.7025898207946</v>
+        <v>399.7025901384902</v>
       </c>
       <c r="D7" t="n">
         <v>4.77759e-07</v>
@@ -4532,37 +4532,37 @@
         <v>-78.667</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04213691763952598</v>
+        <v>0.04213691763952981</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7224552129789223</v>
+        <v>0.7224552129789302</v>
       </c>
       <c r="H7" t="n">
-        <v>1.221023638015017</v>
+        <v>1.221023638015037</v>
       </c>
       <c r="I7" t="n">
-        <v>2.186944186748775</v>
+        <v>2.186944186748772</v>
       </c>
       <c r="J7" t="n">
-        <v>40.61644537722049</v>
+        <v>40.61644537722056</v>
       </c>
       <c r="K7" t="n">
-        <v>86.38348824761647</v>
+        <v>86.38348824761646</v>
       </c>
       <c r="W7" t="n">
-        <v>15.821784017322</v>
+        <v>15.82178401732196</v>
       </c>
       <c r="X7" t="n">
-        <v>-8893.081304166333</v>
+        <v>-8893.081304166308</v>
       </c>
       <c r="Y7" t="n">
-        <v>126.2454133521194</v>
+        <v>126.2454138186359</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.591008815793764e-09</v>
+        <v>5.591008823193338e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8820880142600872</v>
+        <v>0.8820880148708538</v>
       </c>
     </row>
     <row r="8">
@@ -4573,7 +4573,7 @@
         <v>154.458</v>
       </c>
       <c r="C8" t="n">
-        <v>454.5802147907395</v>
+        <v>454.5802129485559</v>
       </c>
       <c r="D8" t="n">
         <v>4.7825e-07</v>
@@ -4582,19 +4582,19 @@
         <v>-78.82599999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3491018886865117</v>
+        <v>0.349101888686514</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7620699783851993</v>
+        <v>0.7620699783851991</v>
       </c>
       <c r="H8" t="n">
-        <v>1.298825080717381</v>
+        <v>1.298825080717362</v>
       </c>
       <c r="I8" t="n">
-        <v>2.260718031395355</v>
+        <v>2.26071803139541</v>
       </c>
       <c r="J8" t="n">
-        <v>46.39635713656119</v>
+        <v>46.39635713656086</v>
       </c>
       <c r="K8" t="n">
         <v>86.46683111339421</v>
@@ -4606,13 +4606,13 @@
         <v>-8995.914981161315</v>
       </c>
       <c r="Y8" t="n">
-        <v>62.85781446360237</v>
+        <v>62.85782621046351</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.318403669988344e-09</v>
+        <v>4.318404936688555e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8807109063840068</v>
+        <v>0.8807108876398066</v>
       </c>
     </row>
     <row r="9">
@@ -4623,7 +4623,7 @@
         <v>152.2860000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>447.7860286787588</v>
+        <v>447.7860395649757</v>
       </c>
       <c r="D9" t="n">
         <v>4.78731e-07</v>
@@ -4632,37 +4632,37 @@
         <v>-78.97</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4075924077423179</v>
+        <v>0.4075924077423284</v>
       </c>
       <c r="G9" t="n">
         <v>0.9835335769783613</v>
       </c>
       <c r="H9" t="n">
-        <v>1.312075041667159</v>
+        <v>1.312075041667175</v>
       </c>
       <c r="I9" t="n">
-        <v>2.58917772440293</v>
+        <v>2.589177724402965</v>
       </c>
       <c r="J9" t="n">
-        <v>53.92067172313116</v>
+        <v>53.92067172313102</v>
       </c>
       <c r="K9" t="n">
         <v>86.58083054750514</v>
       </c>
       <c r="W9" t="n">
-        <v>16.73732475235285</v>
+        <v>16.73732475235289</v>
       </c>
       <c r="X9" t="n">
-        <v>-9195.303952956188</v>
+        <v>-9195.303952956219</v>
       </c>
       <c r="Y9" t="n">
-        <v>63.21278608061525</v>
+        <v>63.21275819828529</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.26423877519813e-09</v>
+        <v>4.264236366324386e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8824390103783448</v>
+        <v>0.8824390453702067</v>
       </c>
     </row>
     <row r="10">
@@ -4673,7 +4673,7 @@
         <v>147.229</v>
       </c>
       <c r="C10" t="n">
-        <v>377.5822135698467</v>
+        <v>377.5822051909706</v>
       </c>
       <c r="D10" t="n">
         <v>4.79115e-07</v>
@@ -4685,34 +4685,34 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5001868411509627</v>
+        <v>0.5001868411509414</v>
       </c>
       <c r="H10" t="n">
-        <v>1.286568009590114</v>
+        <v>1.286568009590191</v>
       </c>
       <c r="I10" t="n">
         <v>2.049070432317442</v>
       </c>
       <c r="J10" t="n">
-        <v>43.02720445839579</v>
+        <v>43.02720445839577</v>
       </c>
       <c r="K10" t="n">
-        <v>86.47075669293118</v>
+        <v>86.47075669293119</v>
       </c>
       <c r="W10" t="n">
-        <v>16.2140415656756</v>
+        <v>16.21404156567568</v>
       </c>
       <c r="X10" t="n">
-        <v>-8779.878118726585</v>
+        <v>-8779.878118726641</v>
       </c>
       <c r="Y10" t="n">
-        <v>130.2489205555841</v>
+        <v>130.2489308556262</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.411212466037764e-09</v>
+        <v>5.411212777996565e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8896215833422135</v>
+        <v>0.8896215836910858</v>
       </c>
     </row>
     <row r="11">
@@ -4723,7 +4723,7 @@
         <v>144.8179999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>364.4430241317015</v>
+        <v>364.443028444642</v>
       </c>
       <c r="D11" t="n">
         <v>4.7943e-07</v>
@@ -4732,37 +4732,37 @@
         <v>-79.22799999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2337142179290318</v>
+        <v>0.2337142179290277</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5323350461727602</v>
+        <v>0.5323350461727298</v>
       </c>
       <c r="H11" t="n">
-        <v>1.237320821564642</v>
+        <v>1.237320821564611</v>
       </c>
       <c r="I11" t="n">
-        <v>2.108321369535127</v>
+        <v>2.108321369535186</v>
       </c>
       <c r="J11" t="n">
-        <v>43.8396645646021</v>
+        <v>43.83966456460248</v>
       </c>
       <c r="K11" t="n">
-        <v>86.52072046388218</v>
+        <v>86.52072046388217</v>
       </c>
       <c r="W11" t="n">
-        <v>16.44746716044817</v>
+        <v>16.44746716044814</v>
       </c>
       <c r="X11" t="n">
-        <v>-8809.539496702904</v>
+        <v>-8809.539496702882</v>
       </c>
       <c r="Y11" t="n">
-        <v>137.5253703308194</v>
+        <v>137.5253713015156</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.423682510497587e-09</v>
+        <v>5.423682791954497e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8927123680662962</v>
+        <v>0.8927123748996728</v>
       </c>
     </row>
     <row r="12">
@@ -4773,7 +4773,7 @@
         <v>143.027</v>
       </c>
       <c r="C12" t="n">
-        <v>376.6154018659058</v>
+        <v>376.6154028300266</v>
       </c>
       <c r="D12" t="n">
         <v>4.79687e-07</v>
@@ -4782,37 +4782,37 @@
         <v>-79.342</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1592045218196105</v>
+        <v>0.1592045218196064</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8947502627080397</v>
+        <v>0.8947502627080933</v>
       </c>
       <c r="H12" t="n">
         <v>1.688218308443864</v>
       </c>
       <c r="I12" t="n">
-        <v>2.712888023685584</v>
+        <v>2.712888023685589</v>
       </c>
       <c r="J12" t="n">
-        <v>58.79283257010837</v>
+        <v>58.79283257010831</v>
       </c>
       <c r="K12" t="n">
-        <v>86.68044798971584</v>
+        <v>86.68044798971583</v>
       </c>
       <c r="W12" t="n">
-        <v>17.24077723915691</v>
+        <v>17.24077723915688</v>
       </c>
       <c r="X12" t="n">
-        <v>-9158.797661151497</v>
+        <v>-9158.797661151482</v>
       </c>
       <c r="Y12" t="n">
-        <v>119.627608249827</v>
+        <v>119.6276056669041</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.017775854070988e-09</v>
+        <v>5.017775697294179e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8923761719398211</v>
+        <v>0.8923761709504064</v>
       </c>
     </row>
     <row r="13">
@@ -4823,7 +4823,7 @@
         <v>139.073</v>
       </c>
       <c r="C13" t="n">
-        <v>363.5623590380698</v>
+        <v>363.5623564540439</v>
       </c>
       <c r="D13" t="n">
         <v>4.80072e-07</v>
@@ -4832,37 +4832,37 @@
         <v>-79.452</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1572133842226058</v>
+        <v>0.1572133842226027</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7072554046623214</v>
+        <v>0.7072554046623157</v>
       </c>
       <c r="H13" t="n">
         <v>1.257823541983323</v>
       </c>
       <c r="I13" t="n">
-        <v>2.239179019831915</v>
+        <v>2.239179019831898</v>
       </c>
       <c r="J13" t="n">
-        <v>45.80761059439564</v>
+        <v>45.80761059439575</v>
       </c>
       <c r="K13" t="n">
         <v>86.59022587957202</v>
       </c>
       <c r="W13" t="n">
-        <v>16.78355249768228</v>
+        <v>16.78355249768229</v>
       </c>
       <c r="X13" t="n">
-        <v>-8804.542669663158</v>
+        <v>-8804.542669663162</v>
       </c>
       <c r="Y13" t="n">
-        <v>127.6784616255033</v>
+        <v>127.6784655278801</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.078501271788473e-09</v>
+        <v>5.078501443711879e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8951702270571552</v>
+        <v>0.8951702284522829</v>
       </c>
     </row>
     <row r="14">
@@ -4882,28 +4882,28 @@
         <v>-79.551</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2501873502243557</v>
+        <v>0.2501873502243586</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6753983504459924</v>
+        <v>0.67539835044602</v>
       </c>
       <c r="H14" t="n">
-        <v>1.38201129210432</v>
+        <v>1.382011292104346</v>
       </c>
       <c r="I14" t="n">
         <v>2.071594947626012</v>
       </c>
       <c r="J14" t="n">
-        <v>41.86916415303637</v>
+        <v>41.86916415303664</v>
       </c>
       <c r="K14" t="n">
         <v>86.56760377659262</v>
       </c>
       <c r="W14" t="n">
-        <v>16.672673637864</v>
+        <v>16.67267363786399</v>
       </c>
       <c r="X14" t="n">
-        <v>-8648.770055613191</v>
+        <v>-8648.770055613189</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>1.167379872379136e-06</v>
+        <v>1.167821929997529e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8653437710121358</v>
+        <v>0.8652862177508325</v>
       </c>
     </row>
     <row r="15">
@@ -4934,28 +4934,28 @@
         <v>-79.65000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3972886743752337</v>
+        <v>0.3972886743752359</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7942993864004355</v>
+        <v>0.7942993864004582</v>
       </c>
       <c r="H15" t="n">
-        <v>1.482844013892421</v>
+        <v>1.482844013892448</v>
       </c>
       <c r="I15" t="n">
-        <v>2.253182020333465</v>
+        <v>2.253182020333484</v>
       </c>
       <c r="J15" t="n">
-        <v>47.5707044361684</v>
+        <v>47.57070443616836</v>
       </c>
       <c r="K15" t="n">
         <v>86.66078674449373</v>
       </c>
       <c r="W15" t="n">
-        <v>17.13903556360076</v>
+        <v>17.1390355636008</v>
       </c>
       <c r="X15" t="n">
-        <v>-8816.128156542951</v>
+        <v>-8816.12815654298</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>1.142694722031057e-06</v>
+        <v>1.142508673360783e-06</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.868679340340917</v>
+        <v>0.8686630851541256</v>
       </c>
     </row>
     <row r="16">
@@ -4977,7 +4977,7 @@
         <v>132.256</v>
       </c>
       <c r="C16" t="n">
-        <v>434.3350146136094</v>
+        <v>434.3350075823903</v>
       </c>
       <c r="D16" t="n">
         <v>4.80718e-07</v>
@@ -4986,37 +4986,37 @@
         <v>-79.752</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4474656213682003</v>
+        <v>0.4474656213682247</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6285925599346588</v>
+        <v>0.6285925599346665</v>
       </c>
       <c r="H16" t="n">
-        <v>1.480539308420189</v>
+        <v>1.480539308420188</v>
       </c>
       <c r="I16" t="n">
         <v>2.185479715788673</v>
       </c>
       <c r="J16" t="n">
-        <v>47.96414807483088</v>
+        <v>47.96414807483092</v>
       </c>
       <c r="K16" t="n">
         <v>86.6944385266701</v>
       </c>
       <c r="W16" t="n">
-        <v>17.31391071908497</v>
+        <v>17.31391071908502</v>
       </c>
       <c r="X16" t="n">
-        <v>-8819.790180277078</v>
+        <v>-8819.790180277114</v>
       </c>
       <c r="Y16" t="n">
-        <v>41.96535895806021</v>
+        <v>41.96540858969528</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.717141678169611e-09</v>
+        <v>3.717144591561439e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8913862327854897</v>
+        <v>0.8913861930648297</v>
       </c>
     </row>
     <row r="17">
@@ -5027,7 +5027,7 @@
         <v>131.183</v>
       </c>
       <c r="C17" t="n">
-        <v>428.2356030756833</v>
+        <v>428.2355587257581</v>
       </c>
       <c r="D17" t="n">
         <v>4.81131e-07</v>
@@ -5036,37 +5036,37 @@
         <v>-79.858</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4294887429324541</v>
+        <v>0.4294887429324486</v>
       </c>
       <c r="G17" t="n">
         <v>1.07634533454852</v>
       </c>
       <c r="H17" t="n">
-        <v>1.674459009976488</v>
+        <v>1.674459009976527</v>
       </c>
       <c r="I17" t="n">
-        <v>2.451967401807524</v>
+        <v>2.451967401807525</v>
       </c>
       <c r="J17" t="n">
-        <v>56.30987101076902</v>
+        <v>56.309871010769</v>
       </c>
       <c r="K17" t="n">
-        <v>86.77865078601785</v>
+        <v>86.77865078601783</v>
       </c>
       <c r="W17" t="n">
-        <v>17.76752271114635</v>
+        <v>17.76752271114627</v>
       </c>
       <c r="X17" t="n">
-        <v>-8974.515075371071</v>
+        <v>-8974.515075371022</v>
       </c>
       <c r="Y17" t="n">
-        <v>43.32431791440263</v>
+        <v>43.32440942517029</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.767883063831334e-09</v>
+        <v>3.767885052608444e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8910213894939077</v>
+        <v>0.8910214825866947</v>
       </c>
     </row>
     <row r="18">
@@ -5077,7 +5077,7 @@
         <v>125.34</v>
       </c>
       <c r="C18" t="n">
-        <v>422.1333723723887</v>
+        <v>422.1333534979912</v>
       </c>
       <c r="D18" t="n">
         <v>4.81229e-07</v>
@@ -5086,37 +5086,37 @@
         <v>-79.967</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05588083585556243</v>
+        <v>0.05588083585556246</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4661930612116133</v>
+        <v>0.4661930612116028</v>
       </c>
       <c r="H18" t="n">
-        <v>1.169291525295366</v>
+        <v>1.16929152529535</v>
       </c>
       <c r="I18" t="n">
-        <v>2.149914982014108</v>
+        <v>2.149914982014107</v>
       </c>
       <c r="J18" t="n">
-        <v>44.78677304149869</v>
+        <v>44.78677304149863</v>
       </c>
       <c r="K18" t="n">
-        <v>86.42938387225492</v>
+        <v>86.42938387225493</v>
       </c>
       <c r="W18" t="n">
-        <v>16.02569019930987</v>
+        <v>16.02569019930992</v>
       </c>
       <c r="X18" t="n">
-        <v>-7959.370109641281</v>
+        <v>-7959.370109641308</v>
       </c>
       <c r="Y18" t="n">
-        <v>44.42852924781555</v>
+        <v>44.42855496384536</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.670667510141318e-09</v>
+        <v>3.670666051254952e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8933290145824563</v>
+        <v>0.8933290900848907</v>
       </c>
     </row>
     <row r="19">
@@ -5136,28 +5136,28 @@
         <v>-80.075</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09746330265341353</v>
+        <v>0.09746330265341825</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6404602328060933</v>
+        <v>0.6404602328060932</v>
       </c>
       <c r="H19" t="n">
-        <v>1.434250629492104</v>
+        <v>1.434250629492077</v>
       </c>
       <c r="I19" t="n">
-        <v>2.266192964293285</v>
+        <v>2.266192964293286</v>
       </c>
       <c r="J19" t="n">
-        <v>45.40427527818311</v>
+        <v>45.40427527818315</v>
       </c>
       <c r="K19" t="n">
-        <v>86.69524674808845</v>
+        <v>86.69524674808844</v>
       </c>
       <c r="W19" t="n">
-        <v>17.31815447593515</v>
+        <v>17.3181544759351</v>
       </c>
       <c r="X19" t="n">
-        <v>-8556.044908255646</v>
+        <v>-8556.044908255617</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>1.050392275350101e-06</v>
+        <v>1.050242303279527e-06</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8816682310091868</v>
+        <v>0.881690009753528</v>
       </c>
     </row>
     <row r="20">
@@ -5179,7 +5179,7 @@
         <v>124.379</v>
       </c>
       <c r="C20" t="n">
-        <v>412.6613142454954</v>
+        <v>412.6612349702912</v>
       </c>
       <c r="D20" t="n">
         <v>4.8177e-07</v>
@@ -5188,37 +5188,37 @@
         <v>-80.164</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4692193011243914</v>
+        <v>0.469219301124402</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8706687167730387</v>
+        <v>0.8706687167730299</v>
       </c>
       <c r="H20" t="n">
-        <v>1.612526565466353</v>
+        <v>1.612526565466324</v>
       </c>
       <c r="I20" t="n">
-        <v>2.318028826892592</v>
+        <v>2.318028826892607</v>
       </c>
       <c r="J20" t="n">
-        <v>52.42411698486022</v>
+        <v>52.42411698485977</v>
       </c>
       <c r="K20" t="n">
-        <v>86.80687561158989</v>
+        <v>86.8068756115899</v>
       </c>
       <c r="W20" t="n">
-        <v>17.92490429093078</v>
+        <v>17.92490429093083</v>
       </c>
       <c r="X20" t="n">
-        <v>-8782.753613832549</v>
+        <v>-8782.753613832576</v>
       </c>
       <c r="Y20" t="n">
-        <v>45.25610951578229</v>
+        <v>45.2562653823698</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.59188969117282e-09</v>
+        <v>3.5918961981375e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8976406298994852</v>
+        <v>0.8976405750522507</v>
       </c>
     </row>
     <row r="21">
@@ -5238,28 +5238,28 @@
         <v>-80.258</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2156900627528431</v>
+        <v>0.2156900627528445</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6784744603553692</v>
+        <v>0.6784744603553857</v>
       </c>
       <c r="H21" t="n">
         <v>1.573425921757229</v>
       </c>
       <c r="I21" t="n">
-        <v>2.255773469270077</v>
+        <v>2.255773469270133</v>
       </c>
       <c r="J21" t="n">
-        <v>47.30255336691651</v>
+        <v>47.30255336691628</v>
       </c>
       <c r="K21" t="n">
-        <v>86.76109712077208</v>
+        <v>86.76109712077206</v>
       </c>
       <c r="W21" t="n">
-        <v>17.67102547793089</v>
+        <v>17.67102547793088</v>
       </c>
       <c r="X21" t="n">
-        <v>-8563.08091120807</v>
+        <v>-8563.080911208064</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>1.016993736638098e-06</v>
+        <v>1.016299550097014e-06</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8867052416613772</v>
+        <v>0.8868167974633608</v>
       </c>
     </row>
     <row r="22">
@@ -5281,7 +5281,7 @@
         <v>118.135</v>
       </c>
       <c r="C22" t="n">
-        <v>420.0459236117385</v>
+        <v>420.0459190327686</v>
       </c>
       <c r="D22" t="n">
         <v>4.82364e-07</v>
@@ -5290,37 +5290,37 @@
         <v>-80.37</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1124222209022645</v>
+        <v>0.1124222209022626</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8083180241574554</v>
+        <v>0.8083180241574842</v>
       </c>
       <c r="H22" t="n">
-        <v>1.223807543020304</v>
+        <v>1.223807543020327</v>
       </c>
       <c r="I22" t="n">
-        <v>2.272915579511115</v>
+        <v>2.272915579511114</v>
       </c>
       <c r="J22" t="n">
-        <v>54.43464134455434</v>
+        <v>54.43464134455436</v>
       </c>
       <c r="K22" t="n">
-        <v>86.5844236207531</v>
+        <v>86.58442362075313</v>
       </c>
       <c r="W22" t="n">
-        <v>16.75497371290091</v>
+        <v>16.754973712901</v>
       </c>
       <c r="X22" t="n">
-        <v>-8009.531316887499</v>
+        <v>-8009.531316887551</v>
       </c>
       <c r="Y22" t="n">
-        <v>63.42875406905142</v>
+        <v>63.4287671630544</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.608567983255995e-08</v>
+        <v>3.608570330841947e-08</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.7420350641531359</v>
+        <v>0.7420350236077491</v>
       </c>
     </row>
   </sheetData>
@@ -5477,7 +5477,7 @@
         <v>253.4470000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>323.6833219809552</v>
+        <v>323.6832933532662</v>
       </c>
       <c r="D2" t="n">
         <v>5.01385e-07</v>
@@ -5486,37 +5486,37 @@
         <v>-73.41</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2296364909577362</v>
+        <v>0.2296364909577347</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6078580228780566</v>
+        <v>0.6078580228780426</v>
       </c>
       <c r="H2" t="n">
         <v>1.237907571267598</v>
       </c>
       <c r="I2" t="n">
-        <v>1.994196354650039</v>
+        <v>1.994196354650042</v>
       </c>
       <c r="J2" t="n">
-        <v>19.43486932483383</v>
+        <v>19.43486932483385</v>
       </c>
       <c r="K2" t="n">
-        <v>84.66028256898838</v>
+        <v>84.66028256898839</v>
       </c>
       <c r="W2" t="n">
-        <v>10.6990312958025</v>
+        <v>10.69903129580252</v>
       </c>
       <c r="X2" t="n">
-        <v>-7302.501598697544</v>
+        <v>-7302.501598697563</v>
       </c>
       <c r="Y2" t="n">
-        <v>252.1795368991039</v>
+        <v>252.1795256643442</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.500194215210243e-09</v>
+        <v>4.500190411904655e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9255377633340059</v>
+        <v>0.9255377308356948</v>
       </c>
     </row>
     <row r="3">
@@ -5527,7 +5527,7 @@
         <v>172.7979999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>313.5667666526824</v>
+        <v>313.5667765536845</v>
       </c>
       <c r="D3" t="n">
         <v>5.09218e-07</v>
@@ -5539,16 +5539,16 @@
         <v>0.1196414127941215</v>
       </c>
       <c r="G3" t="n">
-        <v>0.462278794935522</v>
+        <v>0.4622787949355223</v>
       </c>
       <c r="H3" t="n">
-        <v>1.242468645785523</v>
+        <v>1.242468645785527</v>
       </c>
       <c r="I3" t="n">
-        <v>2.195021400136902</v>
+        <v>2.195021400136893</v>
       </c>
       <c r="J3" t="n">
-        <v>25.67780053149527</v>
+        <v>25.67780053149538</v>
       </c>
       <c r="K3" t="n">
         <v>85.72490414119909</v>
@@ -5557,16 +5557,16 @@
         <v>13.37734026843357</v>
       </c>
       <c r="X3" t="n">
-        <v>-7870.419776766566</v>
+        <v>-7870.419776766567</v>
       </c>
       <c r="Y3" t="n">
-        <v>230.7278090774557</v>
+        <v>230.7277942078681</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.272025430990645e-09</v>
+        <v>8.272026085956584e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8894968651357756</v>
+        <v>0.8894968520962707</v>
       </c>
     </row>
     <row r="4">
@@ -5586,28 +5586,28 @@
         <v>-76.93000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01821994632036216</v>
+        <v>0.01821994632035714</v>
       </c>
       <c r="G4" t="n">
         <v>0.5148373473266725</v>
       </c>
       <c r="H4" t="n">
-        <v>1.210613048401512</v>
+        <v>1.210613048401513</v>
       </c>
       <c r="I4" t="n">
-        <v>2.215830137990696</v>
+        <v>2.215830137990695</v>
       </c>
       <c r="J4" t="n">
-        <v>29.6830906363262</v>
+        <v>29.68309063632618</v>
       </c>
       <c r="K4" t="n">
-        <v>85.87143116814933</v>
+        <v>85.87143116814934</v>
       </c>
       <c r="W4" t="n">
-        <v>13.85385184086968</v>
+        <v>13.8538518408697</v>
       </c>
       <c r="X4" t="n">
-        <v>-7842.511579781048</v>
+        <v>-7842.511579781059</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>2.583984295924121e-06</v>
+        <v>2.583738004072247e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7552828372831227</v>
+        <v>0.7552930952056649</v>
       </c>
     </row>
     <row r="5">
@@ -5629,7 +5629,7 @@
         <v>151.967</v>
       </c>
       <c r="C5" t="n">
-        <v>457.0052237107581</v>
+        <v>457.0052091682127</v>
       </c>
       <c r="D5" t="n">
         <v>5.03645e-07</v>
@@ -5638,37 +5638,37 @@
         <v>-77.367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5804019335957445</v>
+        <v>0.5804019335958471</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9604235352681523</v>
+        <v>0.9604235352681583</v>
       </c>
       <c r="H5" t="n">
-        <v>1.774213394500648</v>
+        <v>1.774213394500634</v>
       </c>
       <c r="I5" t="n">
-        <v>2.864324209810046</v>
+        <v>2.864324209810041</v>
       </c>
       <c r="J5" t="n">
-        <v>35.39999241015102</v>
+        <v>35.39999241015119</v>
       </c>
       <c r="K5" t="n">
         <v>86.31820763514392</v>
       </c>
       <c r="W5" t="n">
-        <v>15.54050007974512</v>
+        <v>15.54050007974514</v>
       </c>
       <c r="X5" t="n">
-        <v>-8701.709860191046</v>
+        <v>-8701.709860191064</v>
       </c>
       <c r="Y5" t="n">
-        <v>62.85769452869913</v>
+        <v>62.85771194006414</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.417970883099724e-09</v>
+        <v>4.417973424885522e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8765965063282908</v>
+        <v>0.8765964720471099</v>
       </c>
     </row>
     <row r="6">
@@ -5679,7 +5679,7 @@
         <v>144.878</v>
       </c>
       <c r="C6" t="n">
-        <v>317.920333750284</v>
+        <v>317.9203143559882</v>
       </c>
       <c r="D6" t="n">
         <v>5.01405e-07</v>
@@ -5688,19 +5688,19 @@
         <v>-77.703</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03819542857772485</v>
+        <v>0.03819542857774064</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4234819453490237</v>
+        <v>0.4234819453490309</v>
       </c>
       <c r="H6" t="n">
-        <v>1.37744107307523</v>
+        <v>1.377441073075244</v>
       </c>
       <c r="I6" t="n">
-        <v>2.334803817236022</v>
+        <v>2.334803817236031</v>
       </c>
       <c r="J6" t="n">
-        <v>35.11137570502797</v>
+        <v>35.111375705028</v>
       </c>
       <c r="K6" t="n">
         <v>86.13165010017671</v>
@@ -5709,16 +5709,16 @@
         <v>14.78891432840433</v>
       </c>
       <c r="X6" t="n">
-        <v>-8118.921871447683</v>
+        <v>-8118.921871447685</v>
       </c>
       <c r="Y6" t="n">
-        <v>199.7382618915078</v>
+        <v>199.7382843361201</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.627806507445807e-09</v>
+        <v>7.627809981544667e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8892077299740936</v>
+        <v>0.8892077086344362</v>
       </c>
     </row>
     <row r="7">
@@ -5729,7 +5729,7 @@
         <v>143.576</v>
       </c>
       <c r="C7" t="n">
-        <v>310.1760714150536</v>
+        <v>310.1760860919221</v>
       </c>
       <c r="D7" t="n">
         <v>4.99915e-07</v>
@@ -5741,16 +5741,16 @@
         <v>0.3275613662899805</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8520832758368355</v>
+        <v>0.8520832758368463</v>
       </c>
       <c r="H7" t="n">
-        <v>1.642845625566089</v>
+        <v>1.642845625566081</v>
       </c>
       <c r="I7" t="n">
-        <v>2.611538870481448</v>
+        <v>2.61153887048145</v>
       </c>
       <c r="J7" t="n">
-        <v>36.76602825141157</v>
+        <v>36.7660282514116</v>
       </c>
       <c r="K7" t="n">
         <v>86.44123434496925</v>
@@ -5762,13 +5762,13 @@
         <v>-8744.574638608035</v>
       </c>
       <c r="Y7" t="n">
-        <v>200.1258072265054</v>
+        <v>200.1257964697823</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.266994107913307e-09</v>
+        <v>7.266994050244653e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8943795164601346</v>
+        <v>0.8943795200699068</v>
       </c>
     </row>
     <row r="8">
@@ -5779,7 +5779,7 @@
         <v>136.6940000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>360.460017708268</v>
+        <v>360.4599905139353</v>
       </c>
       <c r="D8" t="n">
         <v>4.98705e-07</v>
@@ -5788,37 +5788,37 @@
         <v>-78.23399999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1454714267210917</v>
+        <v>0.1454714267210942</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4344866750626211</v>
+        <v>0.4344866750626167</v>
       </c>
       <c r="H8" t="n">
-        <v>1.386862764621113</v>
+        <v>1.386862764621114</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5373564854663</v>
+        <v>2.537356485466336</v>
       </c>
       <c r="J8" t="n">
-        <v>38.7730148817938</v>
+        <v>38.77301488179385</v>
       </c>
       <c r="K8" t="n">
-        <v>86.29102253757358</v>
+        <v>86.2910225375736</v>
       </c>
       <c r="W8" t="n">
-        <v>15.42628003873503</v>
+        <v>15.42628003873508</v>
       </c>
       <c r="X8" t="n">
-        <v>-8232.455344380243</v>
+        <v>-8232.455344380274</v>
       </c>
       <c r="Y8" t="n">
-        <v>140.2920926504446</v>
+        <v>140.2921059291924</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.322911086374246e-09</v>
+        <v>5.322910733349516e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8929410544962458</v>
+        <v>0.8929410355136588</v>
       </c>
     </row>
     <row r="9">
@@ -5829,7 +5829,7 @@
         <v>135.736</v>
       </c>
       <c r="C9" t="n">
-        <v>367.9301536037434</v>
+        <v>367.9301358934236</v>
       </c>
       <c r="D9" t="n">
         <v>4.97863e-07</v>
@@ -5838,16 +5838,16 @@
         <v>-78.468</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2193189354326392</v>
+        <v>0.2193189354326349</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7878455389818507</v>
+        <v>0.7878455389818217</v>
       </c>
       <c r="H9" t="n">
-        <v>1.592082700881541</v>
+        <v>1.592082700881537</v>
       </c>
       <c r="I9" t="n">
-        <v>2.377560165337943</v>
+        <v>2.377560165337948</v>
       </c>
       <c r="J9" t="n">
         <v>37.22386935567619</v>
@@ -5859,16 +5859,16 @@
         <v>16.51117767689291</v>
       </c>
       <c r="X9" t="n">
-        <v>-8721.625051795852</v>
+        <v>-8721.625051795854</v>
       </c>
       <c r="Y9" t="n">
-        <v>126.1254858314337</v>
+        <v>126.1254885601283</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.015497944676026e-09</v>
+        <v>5.015497005153904e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8935478057307703</v>
+        <v>0.893547794083649</v>
       </c>
     </row>
     <row r="10">
@@ -5879,7 +5879,7 @@
         <v>130.203</v>
       </c>
       <c r="C10" t="n">
-        <v>460.4555701481956</v>
+        <v>460.455096822582</v>
       </c>
       <c r="D10" t="n">
         <v>4.97235e-07</v>
@@ -5891,13 +5891,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6777930583759576</v>
+        <v>0.6777930583759516</v>
       </c>
       <c r="H10" t="n">
-        <v>1.523320713106424</v>
+        <v>1.52332071310645</v>
       </c>
       <c r="I10" t="n">
-        <v>2.611409048472505</v>
+        <v>2.611409048472506</v>
       </c>
       <c r="J10" t="n">
         <v>42.25804798728812</v>
@@ -5906,19 +5906,19 @@
         <v>86.42366930959109</v>
       </c>
       <c r="W10" t="n">
-        <v>16.0000165272244</v>
+        <v>16.00001652722441</v>
       </c>
       <c r="X10" t="n">
-        <v>-8311.733703603246</v>
+        <v>-8311.733703603248</v>
       </c>
       <c r="Y10" t="n">
-        <v>25.92151326303559</v>
+        <v>25.92257639795785</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.611210191295035e-09</v>
+        <v>3.611270798175282e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8845680238162228</v>
+        <v>0.8845671013620756</v>
       </c>
     </row>
     <row r="11">
@@ -5929,7 +5929,7 @@
         <v>127.462</v>
       </c>
       <c r="C11" t="n">
-        <v>402.0098709142263</v>
+        <v>402.0098531626217</v>
       </c>
       <c r="D11" t="n">
         <v>4.96745e-07</v>
@@ -5938,37 +5938,37 @@
         <v>-78.842</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04852635772667549</v>
+        <v>0.04852635772667459</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8344308259248309</v>
+        <v>0.834430825924802</v>
       </c>
       <c r="H11" t="n">
-        <v>1.519708120697381</v>
+        <v>1.519708120697412</v>
       </c>
       <c r="I11" t="n">
-        <v>2.598031221256674</v>
+        <v>2.598031221256627</v>
       </c>
       <c r="J11" t="n">
-        <v>43.38457532545887</v>
+        <v>43.38457532545906</v>
       </c>
       <c r="K11" t="n">
-        <v>86.47190368232027</v>
+        <v>86.47190368232026</v>
       </c>
       <c r="W11" t="n">
         <v>16.21932612958744</v>
       </c>
       <c r="X11" t="n">
-        <v>-8319.005571557916</v>
+        <v>-8319.005571557913</v>
       </c>
       <c r="Y11" t="n">
-        <v>78.7297734199192</v>
+        <v>78.72977514248063</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.152595767305368e-09</v>
+        <v>4.152594842544937e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8924075463604643</v>
+        <v>0.8924075676162064</v>
       </c>
     </row>
   </sheetData>
@@ -6125,7 +6125,7 @@
         <v>204.199</v>
       </c>
       <c r="C2" t="n">
-        <v>333.7383590532926</v>
+        <v>333.7383608644214</v>
       </c>
       <c r="D2" t="n">
         <v>5.0472e-07</v>
@@ -6137,34 +6137,34 @@
         <v>0.3156890011984848</v>
       </c>
       <c r="G2" t="n">
-        <v>0.97285090925156</v>
+        <v>0.9728509092516643</v>
       </c>
       <c r="H2" t="n">
-        <v>1.440676296746758</v>
+        <v>1.440676296746729</v>
       </c>
       <c r="I2" t="n">
-        <v>2.284959637321605</v>
+        <v>2.28495963732162</v>
       </c>
       <c r="J2" t="n">
-        <v>33.28894429570712</v>
+        <v>33.2889442957073</v>
       </c>
       <c r="K2" t="n">
-        <v>86.03281935299277</v>
+        <v>86.0328193529928</v>
       </c>
       <c r="W2" t="n">
-        <v>14.41935528366748</v>
+        <v>14.41935528366756</v>
       </c>
       <c r="X2" t="n">
-        <v>-8998.037819848076</v>
+        <v>-8998.037819848139</v>
       </c>
       <c r="Y2" t="n">
-        <v>227.8923884778532</v>
+        <v>227.8923895345061</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.174809799371125e-09</v>
+        <v>7.174809964956378e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8949663818215458</v>
+        <v>0.8949663816539296</v>
       </c>
     </row>
     <row r="3">
@@ -6175,7 +6175,7 @@
         <v>176.8770000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>387.5551363556407</v>
+        <v>387.5551377991939</v>
       </c>
       <c r="D3" t="n">
         <v>5.04653e-07</v>
@@ -6184,37 +6184,37 @@
         <v>-76.874</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02214201925965265</v>
+        <v>0.02214201925966368</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04633567291082438</v>
+        <v>0.0463356729108244</v>
       </c>
       <c r="H3" t="n">
-        <v>1.104321058262387</v>
+        <v>1.104321058262383</v>
       </c>
       <c r="I3" t="n">
-        <v>1.864130830717051</v>
+        <v>1.864130830717049</v>
       </c>
       <c r="J3" t="n">
-        <v>29.9758687866024</v>
+        <v>29.97586878660229</v>
       </c>
       <c r="K3" t="n">
-        <v>85.86164679763668</v>
+        <v>85.86164679763669</v>
       </c>
       <c r="W3" t="n">
-        <v>13.82098318058108</v>
+        <v>13.8209831805811</v>
       </c>
       <c r="X3" t="n">
-        <v>-8186.697565978693</v>
+        <v>-8186.697565978709</v>
       </c>
       <c r="Y3" t="n">
-        <v>160.9870642315289</v>
+        <v>160.9870642212932</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.711205719375123e-09</v>
+        <v>6.711205824871637e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8772008645347179</v>
+        <v>0.877200865836673</v>
       </c>
     </row>
     <row r="4">
@@ -6225,7 +6225,7 @@
         <v>173.34</v>
       </c>
       <c r="C4" t="n">
-        <v>400.9949357415367</v>
+        <v>400.9949052429997</v>
       </c>
       <c r="D4" t="n">
         <v>5.03772e-07</v>
@@ -6234,37 +6234,37 @@
         <v>-77.217</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3550266579802169</v>
+        <v>0.3550266579802111</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6614387944018564</v>
+        <v>0.6614387944018605</v>
       </c>
       <c r="H4" t="n">
-        <v>1.71518255369683</v>
+        <v>1.715182553696835</v>
       </c>
       <c r="I4" t="n">
-        <v>2.511868491765952</v>
+        <v>2.511868491765958</v>
       </c>
       <c r="J4" t="n">
-        <v>43.59092517424482</v>
+        <v>43.59092517424479</v>
       </c>
       <c r="K4" t="n">
-        <v>86.19508813400054</v>
+        <v>86.19508813400053</v>
       </c>
       <c r="W4" t="n">
-        <v>15.03622972663303</v>
+        <v>15.03622972663297</v>
       </c>
       <c r="X4" t="n">
-        <v>-8805.342610140813</v>
+        <v>-8805.342610140771</v>
       </c>
       <c r="Y4" t="n">
-        <v>141.1293764231992</v>
+        <v>141.1293827993325</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.334030138377831e-09</v>
+        <v>6.334023530058953e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8754536965500936</v>
+        <v>0.8754537716249041</v>
       </c>
     </row>
     <row r="5">
@@ -6275,7 +6275,7 @@
         <v>170.826</v>
       </c>
       <c r="C5" t="n">
-        <v>392.2677837302621</v>
+        <v>392.2677956072337</v>
       </c>
       <c r="D5" t="n">
         <v>5.02732e-07</v>
@@ -6287,10 +6287,10 @@
         <v>0.2483070555288152</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5682759174516555</v>
+        <v>0.5682759174516346</v>
       </c>
       <c r="H5" t="n">
-        <v>1.539298469417471</v>
+        <v>1.539298469417475</v>
       </c>
       <c r="I5" t="n">
         <v>2.192189168530405</v>
@@ -6299,22 +6299,22 @@
         <v>36.54324884832494</v>
       </c>
       <c r="K5" t="n">
-        <v>86.40674426826318</v>
+        <v>86.40674426826317</v>
       </c>
       <c r="W5" t="n">
-        <v>15.92445628612508</v>
+        <v>15.92445628612504</v>
       </c>
       <c r="X5" t="n">
-        <v>-9242.403888453036</v>
+        <v>-9242.403888453009</v>
       </c>
       <c r="Y5" t="n">
-        <v>143.348287769841</v>
+        <v>143.3482890806727</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.117988579171726e-09</v>
+        <v>6.117990287798686e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8794014137901353</v>
+        <v>0.8794014118903722</v>
       </c>
     </row>
     <row r="6">
@@ -6325,7 +6325,7 @@
         <v>163.6229999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>383.3607839776258</v>
+        <v>383.3607684871413</v>
       </c>
       <c r="D6" t="n">
         <v>5.01979e-07</v>
@@ -6343,28 +6343,28 @@
         <v>1.244973010066469</v>
       </c>
       <c r="I6" t="n">
-        <v>2.073670120981009</v>
+        <v>2.073670120981036</v>
       </c>
       <c r="J6" t="n">
-        <v>37.46227441948014</v>
+        <v>37.46227441948036</v>
       </c>
       <c r="K6" t="n">
-        <v>86.1408049396007</v>
+        <v>86.14080493960067</v>
       </c>
       <c r="W6" t="n">
-        <v>14.8241035214749</v>
+        <v>14.82410352147485</v>
       </c>
       <c r="X6" t="n">
-        <v>-8456.181561102565</v>
+        <v>-8456.181561102536</v>
       </c>
       <c r="Y6" t="n">
-        <v>145.5312488458853</v>
+        <v>145.5312537347509</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.871513314987725e-09</v>
+        <v>5.871511624042273e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8840918118655955</v>
+        <v>0.8840918210820785</v>
       </c>
     </row>
     <row r="7">
@@ -6375,7 +6375,7 @@
         <v>163.093</v>
       </c>
       <c r="C7" t="n">
-        <v>387.6260250837857</v>
+        <v>387.6260568424495</v>
       </c>
       <c r="D7" t="n">
         <v>5.01564e-07</v>
@@ -6384,16 +6384,16 @@
         <v>-77.88200000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2097552089747076</v>
+        <v>0.2097552089747126</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6296495062564021</v>
+        <v>0.6296495062564023</v>
       </c>
       <c r="H7" t="n">
-        <v>1.273188133789402</v>
+        <v>1.273188133789445</v>
       </c>
       <c r="I7" t="n">
-        <v>2.014345571950377</v>
+        <v>2.014345571950383</v>
       </c>
       <c r="J7" t="n">
         <v>35.25798837604948</v>
@@ -6402,19 +6402,19 @@
         <v>86.40851752037459</v>
       </c>
       <c r="W7" t="n">
-        <v>15.93233944722355</v>
+        <v>15.93233944722353</v>
       </c>
       <c r="X7" t="n">
-        <v>-9008.67653005546</v>
+        <v>-9008.676530055445</v>
       </c>
       <c r="Y7" t="n">
-        <v>134.3057081927186</v>
+        <v>134.3056969287446</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.606485186376758e-09</v>
+        <v>5.606490240188069e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8848035359512456</v>
+        <v>0.8848034966660651</v>
       </c>
     </row>
     <row r="8">
@@ -6425,7 +6425,7 @@
         <v>159.327</v>
       </c>
       <c r="C8" t="n">
-        <v>455.9313743831524</v>
+        <v>455.9314294807543</v>
       </c>
       <c r="D8" t="n">
         <v>5.01307e-07</v>
@@ -6434,37 +6434,37 @@
         <v>-78.09</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3753911060973815</v>
+        <v>0.3753911060973607</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7870533273630577</v>
+        <v>0.7870533273630415</v>
       </c>
       <c r="H8" t="n">
-        <v>1.268733421460422</v>
+        <v>1.268733421460517</v>
       </c>
       <c r="I8" t="n">
         <v>1.973124901537699</v>
       </c>
       <c r="J8" t="n">
-        <v>35.83401562066883</v>
+        <v>35.83401562066882</v>
       </c>
       <c r="K8" t="n">
         <v>86.43720129708646</v>
       </c>
       <c r="W8" t="n">
-        <v>16.06094456924135</v>
+        <v>16.06094456924136</v>
       </c>
       <c r="X8" t="n">
-        <v>-8959.763870917543</v>
+        <v>-8959.763870917552</v>
       </c>
       <c r="Y8" t="n">
-        <v>57.65119156154392</v>
+        <v>57.65115229916918</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.211153819740203e-09</v>
+        <v>4.211155008352932e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8805665605047152</v>
+        <v>0.8805665506616956</v>
       </c>
     </row>
     <row r="9">
@@ -6475,7 +6475,7 @@
         <v>153.55</v>
       </c>
       <c r="C9" t="n">
-        <v>397.0440654776713</v>
+        <v>397.0440513982285</v>
       </c>
       <c r="D9" t="n">
         <v>5.01034e-07</v>
@@ -6487,16 +6487,16 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6091395131324718</v>
+        <v>0.6091395131324647</v>
       </c>
       <c r="H9" t="n">
         <v>1.266061034339221</v>
       </c>
       <c r="I9" t="n">
-        <v>2.338117364586253</v>
+        <v>2.338117364586335</v>
       </c>
       <c r="J9" t="n">
-        <v>40.54930417069693</v>
+        <v>40.54930417069688</v>
       </c>
       <c r="K9" t="n">
         <v>86.28508447384245</v>
@@ -6508,13 +6508,13 @@
         <v>-8452.194266275221</v>
       </c>
       <c r="Y9" t="n">
-        <v>110.7907600203852</v>
+        <v>110.7907705044067</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.797901593959666e-09</v>
+        <v>4.797901020649383e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8901034585781992</v>
+        <v>0.8901034637515034</v>
       </c>
     </row>
     <row r="10">
@@ -6525,7 +6525,7 @@
         <v>149.8440000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>429.3531783039456</v>
+        <v>429.3531806957795</v>
       </c>
       <c r="D10" t="n">
         <v>5.01037e-07</v>
@@ -6534,37 +6534,37 @@
         <v>-78.43000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1766026344237576</v>
+        <v>0.176602634423757</v>
       </c>
       <c r="G10" t="n">
         <v>0.6449775118365028</v>
       </c>
       <c r="H10" t="n">
-        <v>1.327372377665219</v>
+        <v>1.327372377665214</v>
       </c>
       <c r="I10" t="n">
         <v>2.236264268371305</v>
       </c>
       <c r="J10" t="n">
-        <v>41.98405620538083</v>
+        <v>41.98405620538085</v>
       </c>
       <c r="K10" t="n">
         <v>86.32324995252912</v>
       </c>
       <c r="W10" t="n">
-        <v>15.56187115866204</v>
+        <v>15.56187115866207</v>
       </c>
       <c r="X10" t="n">
-        <v>-8434.84913626253</v>
+        <v>-8434.849136262545</v>
       </c>
       <c r="Y10" t="n">
-        <v>72.71740707250895</v>
+        <v>72.71743914145695</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.262832680057284e-09</v>
+        <v>4.262838451441043e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8868177966141216</v>
+        <v>0.8868177457776283</v>
       </c>
     </row>
     <row r="11">
@@ -6575,7 +6575,7 @@
         <v>147.658</v>
       </c>
       <c r="C11" t="n">
-        <v>458.4268044693984</v>
+        <v>458.4267345226313</v>
       </c>
       <c r="D11" t="n">
         <v>5.00963e-07</v>
@@ -6584,37 +6584,37 @@
         <v>-78.592</v>
       </c>
       <c r="F11" t="n">
-        <v>0.284421217697096</v>
+        <v>0.2844212176971112</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8095565444205217</v>
+        <v>0.8095565444205075</v>
       </c>
       <c r="H11" t="n">
         <v>1.655394521131121</v>
       </c>
       <c r="I11" t="n">
-        <v>2.718188531627107</v>
+        <v>2.718188531627082</v>
       </c>
       <c r="J11" t="n">
-        <v>58.51830501035526</v>
+        <v>58.51830501035592</v>
       </c>
       <c r="K11" t="n">
         <v>86.48826426941312</v>
       </c>
       <c r="W11" t="n">
-        <v>16.29508015012644</v>
+        <v>16.2950801501264</v>
       </c>
       <c r="X11" t="n">
-        <v>-8755.166632520968</v>
+        <v>-8755.166632520941</v>
       </c>
       <c r="Y11" t="n">
-        <v>37.62722075934894</v>
+        <v>37.62738841525666</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.793623224996956e-09</v>
+        <v>3.793639736104032e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8849402216654799</v>
+        <v>0.8849400528368321</v>
       </c>
     </row>
     <row r="12">
@@ -6625,7 +6625,7 @@
         <v>146.007</v>
       </c>
       <c r="C12" t="n">
-        <v>456.3851345786028</v>
+        <v>456.3851974000868</v>
       </c>
       <c r="D12" t="n">
         <v>5.00917e-07</v>
@@ -6634,37 +6634,37 @@
         <v>-78.74299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5619376580030291</v>
+        <v>0.5619376580030427</v>
       </c>
       <c r="G12" t="n">
-        <v>1.016750498543256</v>
+        <v>1.016750498543238</v>
       </c>
       <c r="H12" t="n">
-        <v>1.291088286448889</v>
+        <v>1.291088286448895</v>
       </c>
       <c r="I12" t="n">
-        <v>1.943797504102476</v>
+        <v>1.943797504102452</v>
       </c>
       <c r="J12" t="n">
-        <v>39.39722636911135</v>
+        <v>39.39722636911133</v>
       </c>
       <c r="K12" t="n">
         <v>86.602996634245</v>
       </c>
       <c r="W12" t="n">
-        <v>16.84679782633561</v>
+        <v>16.84679782633566</v>
       </c>
       <c r="X12" t="n">
-        <v>-8967.316715429086</v>
+        <v>-8967.316715429122</v>
       </c>
       <c r="Y12" t="n">
-        <v>33.9692222050665</v>
+        <v>33.96914128174099</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.709304132998158e-09</v>
+        <v>3.709305837328845e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8852089676178069</v>
+        <v>0.8852088334534824</v>
       </c>
     </row>
     <row r="13">
@@ -6675,7 +6675,7 @@
         <v>143.929</v>
       </c>
       <c r="C13" t="n">
-        <v>488.2389712823329</v>
+        <v>488.2350551226262</v>
       </c>
       <c r="D13" t="n">
         <v>5.00883e-07</v>
@@ -6687,13 +6687,13 @@
         <v>0.611085245803213</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8730512035772793</v>
+        <v>0.8730512035771731</v>
       </c>
       <c r="H13" t="n">
-        <v>1.503027664106945</v>
+        <v>1.503027664106958</v>
       </c>
       <c r="I13" t="n">
-        <v>2.355345401316294</v>
+        <v>2.355345401316339</v>
       </c>
       <c r="J13" t="n">
         <v>45.29807484081643</v>
@@ -6702,19 +6702,19 @@
         <v>86.71849331651104</v>
       </c>
       <c r="W13" t="n">
-        <v>17.44110982551324</v>
+        <v>17.44110982551321</v>
       </c>
       <c r="X13" t="n">
-        <v>-9203.16118004487</v>
+        <v>-9203.161180044854</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.09894328438015956</v>
+        <v>0.09983599959110891</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.815731746779896e-09</v>
+        <v>3.815398138985539e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8746576657290869</v>
+        <v>0.8746636193992441</v>
       </c>
     </row>
     <row r="14">
@@ -6725,7 +6725,7 @@
         <v>137.064</v>
       </c>
       <c r="C14" t="n">
-        <v>434.2215184145222</v>
+        <v>434.2217547232589</v>
       </c>
       <c r="D14" t="n">
         <v>5.00936e-07</v>
@@ -6734,37 +6734,37 @@
         <v>-78.985</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1066815669347054</v>
+        <v>0.1066815669347174</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4700025549762474</v>
+        <v>0.4700025549762662</v>
       </c>
       <c r="H14" t="n">
-        <v>1.355883184469666</v>
+        <v>1.35588318446967</v>
       </c>
       <c r="I14" t="n">
         <v>2.572368269561976</v>
       </c>
       <c r="J14" t="n">
-        <v>53.05740581592507</v>
+        <v>53.05740581592509</v>
       </c>
       <c r="K14" t="n">
         <v>86.29088641881872</v>
       </c>
       <c r="W14" t="n">
-        <v>15.42571233335039</v>
+        <v>15.4257123333504</v>
       </c>
       <c r="X14" t="n">
-        <v>-7986.190497144414</v>
+        <v>-7986.190497144417</v>
       </c>
       <c r="Y14" t="n">
-        <v>46.80144374133224</v>
+        <v>46.80120308276325</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.741252969916298e-09</v>
+        <v>3.741258648928313e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8903701046201471</v>
+        <v>0.8903698164404517</v>
       </c>
     </row>
     <row r="15">
@@ -6784,28 +6784,28 @@
         <v>-79.127</v>
       </c>
       <c r="F15" t="n">
-        <v>0.111647529898037</v>
+        <v>0.1116475298980408</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6689203519740923</v>
+        <v>0.6689203519740471</v>
       </c>
       <c r="H15" t="n">
-        <v>1.267260897898484</v>
+        <v>1.267260897898485</v>
       </c>
       <c r="I15" t="n">
-        <v>2.449199406064878</v>
+        <v>2.449199406064877</v>
       </c>
       <c r="J15" t="n">
-        <v>47.38617085675377</v>
+        <v>47.38617085675396</v>
       </c>
       <c r="K15" t="n">
         <v>86.50371673617262</v>
       </c>
       <c r="W15" t="n">
-        <v>16.36727953793666</v>
+        <v>16.36727953793667</v>
       </c>
       <c r="X15" t="n">
-        <v>-8419.750097659607</v>
+        <v>-8419.750097659613</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>1.333391361176151e-06</v>
+        <v>1.333158525952509e-06</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8516630899017905</v>
+        <v>0.8516912918057065</v>
       </c>
     </row>
     <row r="16">
@@ -6836,19 +6836,19 @@
         <v>-79.258</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3003178330651065</v>
+        <v>0.3003178330651026</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5285805268160026</v>
+        <v>0.5285805268159798</v>
       </c>
       <c r="H16" t="n">
-        <v>1.23920266819028</v>
+        <v>1.239202668190281</v>
       </c>
       <c r="I16" t="n">
         <v>2.117464031181024</v>
       </c>
       <c r="J16" t="n">
-        <v>43.47005633813709</v>
+        <v>43.47005633813728</v>
       </c>
       <c r="K16" t="n">
         <v>86.42903280883154</v>
@@ -6865,10 +6865,10 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>1.293232785149028e-06</v>
+        <v>1.293510595181526e-06</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8562847747424579</v>
+        <v>0.8562521822003075</v>
       </c>
     </row>
     <row r="17">
@@ -6888,28 +6888,28 @@
         <v>-79.361</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2558097757365574</v>
+        <v>0.2558097757365806</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6016751344865429</v>
+        <v>0.6016751344865271</v>
       </c>
       <c r="H17" t="n">
-        <v>1.289778889475776</v>
+        <v>1.289778889475759</v>
       </c>
       <c r="I17" t="n">
-        <v>2.396437244033415</v>
+        <v>2.396437244033414</v>
       </c>
       <c r="J17" t="n">
-        <v>48.83467347061129</v>
+        <v>48.83467347061132</v>
       </c>
       <c r="K17" t="n">
         <v>86.54830245463963</v>
       </c>
       <c r="W17" t="n">
-        <v>16.57921874263137</v>
+        <v>16.57921874263133</v>
       </c>
       <c r="X17" t="n">
-        <v>-8367.410371942011</v>
+        <v>-8367.410371941982</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -6917,10 +6917,10 @@
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>1.261495630592835e-06</v>
+        <v>1.261680200820417e-06</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8600427131116327</v>
+        <v>0.8600206575437374</v>
       </c>
     </row>
     <row r="18">
@@ -6940,28 +6940,28 @@
         <v>-79.467</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3584431059084611</v>
+        <v>0.3584431059084465</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5862267431410751</v>
+        <v>0.5862267431410932</v>
       </c>
       <c r="H18" t="n">
-        <v>1.682633211736269</v>
+        <v>1.682633211736147</v>
       </c>
       <c r="I18" t="n">
         <v>2.306320364720206</v>
       </c>
       <c r="J18" t="n">
-        <v>50.56519977932956</v>
+        <v>50.56519977932982</v>
       </c>
       <c r="K18" t="n">
         <v>86.58297226724598</v>
       </c>
       <c r="W18" t="n">
-        <v>16.74784028843792</v>
+        <v>16.74784028843795</v>
       </c>
       <c r="X18" t="n">
-        <v>-8372.141872889862</v>
+        <v>-8372.141872889877</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>1.230586387078175e-06</v>
+        <v>1.230158693345426e-06</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8638017003769267</v>
+        <v>0.8638494747524976</v>
       </c>
     </row>
     <row r="19">
@@ -6983,7 +6983,7 @@
         <v>130.161</v>
       </c>
       <c r="C19" t="n">
-        <v>377.3320098041998</v>
+        <v>377.3320222364162</v>
       </c>
       <c r="D19" t="n">
         <v>5.01147e-07</v>
@@ -6992,37 +6992,37 @@
         <v>-79.596</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3455968090130568</v>
+        <v>0.3455968090130529</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9200174715224655</v>
+        <v>0.9200174715224405</v>
       </c>
       <c r="H19" t="n">
-        <v>1.767535232060444</v>
+        <v>1.767535232060372</v>
       </c>
       <c r="I19" t="n">
-        <v>2.956776949068005</v>
+        <v>2.956776949068001</v>
       </c>
       <c r="J19" t="n">
         <v>73.33580906515812</v>
       </c>
       <c r="K19" t="n">
-        <v>86.76825808540362</v>
+        <v>86.7682580854036</v>
       </c>
       <c r="W19" t="n">
-        <v>17.71026477324596</v>
+        <v>17.7102647732459</v>
       </c>
       <c r="X19" t="n">
-        <v>-8793.046607036948</v>
+        <v>-8793.046607036911</v>
       </c>
       <c r="Y19" t="n">
-        <v>81.90682373251711</v>
+        <v>81.90681925676233</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.970662628894026e-09</v>
+        <v>3.970664117041469e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.902757749613458</v>
+        <v>0.9027577359702366</v>
       </c>
     </row>
     <row r="20">
@@ -7033,7 +7033,7 @@
         <v>126.241</v>
       </c>
       <c r="C20" t="n">
-        <v>395.8857910650998</v>
+        <v>395.8857757989766</v>
       </c>
       <c r="D20" t="n">
         <v>5.01156e-07</v>
@@ -7042,37 +7042,37 @@
         <v>-79.693</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2911520566826355</v>
+        <v>0.291152056682672</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5552695067037177</v>
+        <v>0.5552695067037131</v>
       </c>
       <c r="H20" t="n">
         <v>1.10456850307801</v>
       </c>
       <c r="I20" t="n">
-        <v>2.046627014585492</v>
+        <v>2.046627014585496</v>
       </c>
       <c r="J20" t="n">
-        <v>41.55609873971333</v>
+        <v>41.55609873971334</v>
       </c>
       <c r="K20" t="n">
         <v>86.51465982914073</v>
       </c>
       <c r="W20" t="n">
-        <v>16.41879627757449</v>
+        <v>16.41879627757448</v>
       </c>
       <c r="X20" t="n">
-        <v>-8030.453118528424</v>
+        <v>-8030.453118528411</v>
       </c>
       <c r="Y20" t="n">
-        <v>87.26921127112581</v>
+        <v>87.26922213222399</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.22853880313042e-08</v>
+        <v>2.22853803538781e-08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.7832100861549512</v>
+        <v>0.7832101144408083</v>
       </c>
     </row>
     <row r="21">
@@ -7092,28 +7092,28 @@
         <v>-79.821</v>
       </c>
       <c r="F21" t="n">
-        <v>0.250671080922325</v>
+        <v>0.2506710809223208</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6470678688595063</v>
+        <v>0.6470678688594389</v>
       </c>
       <c r="H21" t="n">
-        <v>1.296146435994921</v>
+        <v>1.296146435994859</v>
       </c>
       <c r="I21" t="n">
-        <v>2.33436541593751</v>
+        <v>2.334365415937509</v>
       </c>
       <c r="J21" t="n">
-        <v>48.09008211628269</v>
+        <v>48.09008211628271</v>
       </c>
       <c r="K21" t="n">
-        <v>86.54094038033492</v>
+        <v>86.54094038033493</v>
       </c>
       <c r="W21" t="n">
-        <v>16.54384682346686</v>
+        <v>16.54384682346692</v>
       </c>
       <c r="X21" t="n">
-        <v>-8010.580184951246</v>
+        <v>-8010.58018495128</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>1.149276738290599e-06</v>
+        <v>1.148847195129947e-06</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8741729828158392</v>
+        <v>0.8742300708293216</v>
       </c>
     </row>
     <row r="22">
@@ -7135,7 +7135,7 @@
         <v>120.958</v>
       </c>
       <c r="C22" t="n">
-        <v>242.6668779791709</v>
+        <v>242.6668837434536</v>
       </c>
       <c r="D22" t="n">
         <v>5.014219999999999e-07</v>
@@ -7144,37 +7144,37 @@
         <v>-79.92</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1393148318971744</v>
+        <v>0.139314831897184</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5807451093120737</v>
+        <v>0.5807451093120736</v>
       </c>
       <c r="H22" t="n">
-        <v>1.328568527433896</v>
+        <v>1.328568527433865</v>
       </c>
       <c r="I22" t="n">
-        <v>2.608520608892386</v>
+        <v>2.608520608892389</v>
       </c>
       <c r="J22" t="n">
-        <v>66.17594065249925</v>
+        <v>66.17594065249892</v>
       </c>
       <c r="K22" t="n">
-        <v>86.47140388244669</v>
+        <v>86.47140388244671</v>
       </c>
       <c r="W22" t="n">
-        <v>16.2170229625122</v>
+        <v>16.21702296251223</v>
       </c>
       <c r="X22" t="n">
-        <v>-7761.130699727876</v>
+        <v>-7761.130699727893</v>
       </c>
       <c r="Y22" t="n">
-        <v>206.0151794279648</v>
+        <v>206.0151819898355</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.30284402484601e-09</v>
+        <v>6.302845122770817e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9301641275216251</v>
+        <v>0.9301641327239726</v>
       </c>
     </row>
   </sheetData>
@@ -7340,16 +7340,16 @@
         <v>-72.634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09775238428660057</v>
+        <v>0.09775238428660177</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7116576783443929</v>
+        <v>0.7116576783443902</v>
       </c>
       <c r="H2" t="n">
         <v>1.141752670121127</v>
       </c>
       <c r="I2" t="n">
-        <v>2.074780039713145</v>
+        <v>2.074780039713136</v>
       </c>
       <c r="J2" t="n">
         <v>16.46094679366934</v>
@@ -7361,7 +7361,7 @@
         <v>10.0067712903218</v>
       </c>
       <c r="X2" t="n">
-        <v>-6504.174744469758</v>
+        <v>-6504.174744469757</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>1.611346149556508e-05</v>
+        <v>1.611346142095591e-05</v>
       </c>
       <c r="AB2" t="n">
         <v>0.5000000000000001</v>
@@ -7383,7 +7383,7 @@
         <v>170.455</v>
       </c>
       <c r="C3" t="n">
-        <v>307.6917454527425</v>
+        <v>307.6917798475012</v>
       </c>
       <c r="D3" t="n">
         <v>5.40305e-07</v>
@@ -7395,34 +7395,34 @@
         <v>0.1869081556360942</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5929183646290453</v>
+        <v>0.5929183646290123</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3172577339898</v>
+        <v>1.317257733989801</v>
       </c>
       <c r="I3" t="n">
         <v>2.138832426653552</v>
       </c>
       <c r="J3" t="n">
-        <v>21.2745031554246</v>
+        <v>21.27450315542455</v>
       </c>
       <c r="K3" t="n">
-        <v>85.31756945895515</v>
+        <v>85.31756945895513</v>
       </c>
       <c r="W3" t="n">
-        <v>12.2090796213082</v>
+        <v>12.20907962130819</v>
       </c>
       <c r="X3" t="n">
-        <v>-7000.486509476262</v>
+        <v>-7000.486509476255</v>
       </c>
       <c r="Y3" t="n">
-        <v>220.2713085346376</v>
+        <v>220.2713064375686</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.998855821040033e-09</v>
+        <v>7.998866396504864e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8920745773425226</v>
+        <v>0.8920745180675131</v>
       </c>
     </row>
     <row r="4">
@@ -7433,7 +7433,7 @@
         <v>158.9570000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>300.2928279138742</v>
+        <v>300.2928279715659</v>
       </c>
       <c r="D4" t="n">
         <v>5.35659e-07</v>
@@ -7442,37 +7442,37 @@
         <v>-76.13800000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3500517204795346</v>
+        <v>0.3500517204795259</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6996287674581867</v>
+        <v>0.6996287674581835</v>
       </c>
       <c r="H4" t="n">
-        <v>1.422923069521735</v>
+        <v>1.422923069521878</v>
       </c>
       <c r="I4" t="n">
-        <v>1.881800688283441</v>
+        <v>1.881800688283531</v>
       </c>
       <c r="J4" t="n">
-        <v>22.62407950232634</v>
+        <v>22.62407950232632</v>
       </c>
       <c r="K4" t="n">
         <v>85.85794459005777</v>
       </c>
       <c r="W4" t="n">
-        <v>13.8085867696154</v>
+        <v>13.80858676961539</v>
       </c>
       <c r="X4" t="n">
-        <v>-7709.912167855526</v>
+        <v>-7709.912167855524</v>
       </c>
       <c r="Y4" t="n">
-        <v>220.9215905703833</v>
+        <v>220.9215901461214</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.908621478266132e-09</v>
+        <v>9.908621196519139e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8809801679421293</v>
+        <v>0.8809801698427002</v>
       </c>
     </row>
     <row r="5">
@@ -7483,7 +7483,7 @@
         <v>153.12</v>
       </c>
       <c r="C5" t="n">
-        <v>290.28846621865</v>
+        <v>290.2884542971939</v>
       </c>
       <c r="D5" t="n">
         <v>5.30925e-07</v>
@@ -7492,37 +7492,37 @@
         <v>-76.696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3216325080779493</v>
+        <v>0.3216325080779491</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7262974791148865</v>
+        <v>0.7262974791148866</v>
       </c>
       <c r="H5" t="n">
-        <v>1.385765969599591</v>
+        <v>1.385765969599639</v>
       </c>
       <c r="I5" t="n">
         <v>1.893332204520736</v>
       </c>
       <c r="J5" t="n">
-        <v>25.07318979280422</v>
+        <v>25.07318979280419</v>
       </c>
       <c r="K5" t="n">
         <v>86.08631888573478</v>
       </c>
       <c r="W5" t="n">
-        <v>14.61709321768785</v>
+        <v>14.61709321768788</v>
       </c>
       <c r="X5" t="n">
-        <v>-8039.545069267775</v>
+        <v>-8039.545069267796</v>
       </c>
       <c r="Y5" t="n">
-        <v>222.8676787012344</v>
+        <v>222.867691458066</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.946108326433836e-09</v>
+        <v>8.946109092832398e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8913342300585392</v>
+        <v>0.8913342301674744</v>
       </c>
     </row>
     <row r="6">
@@ -7533,7 +7533,7 @@
         <v>150.159</v>
       </c>
       <c r="C6" t="n">
-        <v>282.3453121881905</v>
+        <v>282.3453017022407</v>
       </c>
       <c r="D6" t="n">
         <v>5.27303e-07</v>
@@ -7542,16 +7542,16 @@
         <v>-77.13800000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4231827061669879</v>
+        <v>0.4231827061669897</v>
       </c>
       <c r="G6" t="n">
         <v>0.8664650559238887</v>
       </c>
       <c r="H6" t="n">
-        <v>1.687802618607461</v>
+        <v>1.687802618607475</v>
       </c>
       <c r="I6" t="n">
-        <v>2.296423059158444</v>
+        <v>2.296423059158386</v>
       </c>
       <c r="J6" t="n">
         <v>31.16312837963968</v>
@@ -7560,19 +7560,19 @@
         <v>86.35350537499718</v>
       </c>
       <c r="W6" t="n">
-        <v>15.69134364300222</v>
+        <v>15.69134364300223</v>
       </c>
       <c r="X6" t="n">
-        <v>-8539.226460839291</v>
+        <v>-8539.226460839292</v>
       </c>
       <c r="Y6" t="n">
-        <v>224.7749118053001</v>
+        <v>224.7749314090922</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.036364808205926e-09</v>
+        <v>9.036368531952542e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8934104973528855</v>
+        <v>0.8934104787618273</v>
       </c>
     </row>
     <row r="7">
@@ -7583,7 +7583,7 @@
         <v>143.3390000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>275.8369465036677</v>
+        <v>275.8369422682491</v>
       </c>
       <c r="D7" t="n">
         <v>5.2461e-07</v>
@@ -7592,37 +7592,37 @@
         <v>-77.485</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0664872769086961</v>
+        <v>0.0664872769086889</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7093968994475335</v>
+        <v>0.709396899447529</v>
       </c>
       <c r="H7" t="n">
-        <v>1.382848833060943</v>
+        <v>1.382848833060945</v>
       </c>
       <c r="I7" t="n">
-        <v>2.269400803864905</v>
+        <v>2.269400803864906</v>
       </c>
       <c r="J7" t="n">
-        <v>31.25696630349673</v>
+        <v>31.25696630349663</v>
       </c>
       <c r="K7" t="n">
-        <v>86.15776587493272</v>
+        <v>86.15776587493271</v>
       </c>
       <c r="W7" t="n">
-        <v>14.88974008794273</v>
+        <v>14.88974008794271</v>
       </c>
       <c r="X7" t="n">
-        <v>-7943.922326265624</v>
+        <v>-7943.922326265613</v>
       </c>
       <c r="Y7" t="n">
-        <v>223.0535162443924</v>
+        <v>223.053513727177</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.009662984263437e-09</v>
+        <v>8.00966189747138e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9028878973696812</v>
+        <v>0.9028878946488863</v>
       </c>
     </row>
     <row r="8">
@@ -7633,7 +7633,7 @@
         <v>139.069</v>
       </c>
       <c r="C8" t="n">
-        <v>270.6415675273945</v>
+        <v>270.6415627922646</v>
       </c>
       <c r="D8" t="n">
         <v>5.22457e-07</v>
@@ -7642,37 +7642,37 @@
         <v>-77.798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1435917165607293</v>
+        <v>0.1435917165607309</v>
       </c>
       <c r="G8" t="n">
         <v>0.4676814026646209</v>
       </c>
       <c r="H8" t="n">
-        <v>1.233637622650597</v>
+        <v>1.233637622650582</v>
       </c>
       <c r="I8" t="n">
-        <v>2.209853001165884</v>
+        <v>2.209853001165882</v>
       </c>
       <c r="J8" t="n">
-        <v>30.80413627735691</v>
+        <v>30.80413627735696</v>
       </c>
       <c r="K8" t="n">
         <v>86.20263531704791</v>
       </c>
       <c r="W8" t="n">
-        <v>15.06620187371839</v>
+        <v>15.0662018737184</v>
       </c>
       <c r="X8" t="n">
-        <v>-7915.945534897673</v>
+        <v>-7915.94553489768</v>
       </c>
       <c r="Y8" t="n">
-        <v>223.231093909834</v>
+        <v>223.231113745769</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.769866838194908e-09</v>
+        <v>8.76987585486621e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8989800812589358</v>
+        <v>0.8989800166137683</v>
       </c>
     </row>
     <row r="9">
@@ -7683,7 +7683,7 @@
         <v>137.652</v>
       </c>
       <c r="C9" t="n">
-        <v>263.4319410469334</v>
+        <v>263.4319516075745</v>
       </c>
       <c r="D9" t="n">
         <v>5.20873e-07</v>
@@ -7692,37 +7692,37 @@
         <v>-78.066</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4863849597300355</v>
+        <v>0.4863849597300345</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9677087449909744</v>
+        <v>0.9677087449909394</v>
       </c>
       <c r="H9" t="n">
-        <v>1.68876618002486</v>
+        <v>1.688766180024898</v>
       </c>
       <c r="I9" t="n">
-        <v>2.737051272546962</v>
+        <v>2.737051272546963</v>
       </c>
       <c r="J9" t="n">
-        <v>41.67158222566433</v>
+        <v>41.67158222566452</v>
       </c>
       <c r="K9" t="n">
-        <v>86.42234109702724</v>
+        <v>86.42234109702723</v>
       </c>
       <c r="W9" t="n">
-        <v>15.99406103152173</v>
+        <v>15.99406103152172</v>
       </c>
       <c r="X9" t="n">
-        <v>-8313.244926148822</v>
+        <v>-8313.244926148809</v>
       </c>
       <c r="Y9" t="n">
-        <v>221.1800551701652</v>
+        <v>221.1800412600217</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.482622911118262e-09</v>
+        <v>7.482622162022436e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9105021387614715</v>
+        <v>0.9105021321915807</v>
       </c>
     </row>
     <row r="10">
@@ -7733,7 +7733,7 @@
         <v>130.743</v>
       </c>
       <c r="C10" t="n">
-        <v>257.7315705111645</v>
+        <v>257.7315694622065</v>
       </c>
       <c r="D10" t="n">
         <v>5.19572e-07</v>
@@ -7742,37 +7742,37 @@
         <v>-78.333</v>
       </c>
       <c r="F10" t="n">
-        <v>0.133576586155218</v>
+        <v>0.1335765861552119</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5004093939842542</v>
+        <v>0.5004093939842404</v>
       </c>
       <c r="H10" t="n">
-        <v>1.321593093252559</v>
+        <v>1.321593093252602</v>
       </c>
       <c r="I10" t="n">
-        <v>2.404818545583846</v>
+        <v>2.404818545583855</v>
       </c>
       <c r="J10" t="n">
-        <v>39.86063127368425</v>
+        <v>39.86063127368432</v>
       </c>
       <c r="K10" t="n">
-        <v>86.2101776795749</v>
+        <v>86.21017767957491</v>
       </c>
       <c r="W10" t="n">
-        <v>15.09627396283187</v>
+        <v>15.0962739628319</v>
       </c>
       <c r="X10" t="n">
-        <v>-7692.415457396726</v>
+        <v>-7692.415457396745</v>
       </c>
       <c r="Y10" t="n">
-        <v>221.3412966422295</v>
+        <v>221.341295233972</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.8410061893477e-09</v>
+        <v>7.841005734167045e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.910109379973956</v>
+        <v>0.9101093783175064</v>
       </c>
     </row>
     <row r="11">
@@ -7783,7 +7783,7 @@
         <v>127.131</v>
       </c>
       <c r="C11" t="n">
-        <v>253.5332798399539</v>
+        <v>253.5332866608391</v>
       </c>
       <c r="D11" t="n">
         <v>5.18468e-07</v>
@@ -7792,37 +7792,37 @@
         <v>-78.536</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1382706410385817</v>
+        <v>0.1382706410385759</v>
       </c>
       <c r="G11" t="n">
-        <v>0.581409056877447</v>
+        <v>0.5814090568774418</v>
       </c>
       <c r="H11" t="n">
-        <v>1.137981876614404</v>
+        <v>1.1379818766144</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2387694904972</v>
+        <v>2.238769490497187</v>
       </c>
       <c r="J11" t="n">
-        <v>37.62158200193961</v>
+        <v>37.62158200193963</v>
       </c>
       <c r="K11" t="n">
         <v>86.23391246743091</v>
       </c>
       <c r="W11" t="n">
-        <v>15.19169150364624</v>
+        <v>15.19169150364622</v>
       </c>
       <c r="X11" t="n">
-        <v>-7635.581378916427</v>
+        <v>-7635.581378916412</v>
       </c>
       <c r="Y11" t="n">
-        <v>219.3866016645426</v>
+        <v>219.3865848151568</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.313061727398261e-09</v>
+        <v>7.313059073461233e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9168531593108472</v>
+        <v>0.916853160596305</v>
       </c>
     </row>
   </sheetData>
@@ -7979,7 +7979,7 @@
         <v>204.609</v>
       </c>
       <c r="C2" t="n">
-        <v>333.7421800405776</v>
+        <v>333.7421794098832</v>
       </c>
       <c r="D2" t="n">
         <v>5.190239999999999e-07</v>
@@ -7988,37 +7988,37 @@
         <v>-75.535</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4341269836425564</v>
+        <v>0.4341269836425922</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8770698217290915</v>
+        <v>0.8770698217291029</v>
       </c>
       <c r="H2" t="n">
         <v>1.611166485128293</v>
       </c>
       <c r="I2" t="n">
-        <v>2.726171321750013</v>
+        <v>2.726171321750026</v>
       </c>
       <c r="J2" t="n">
-        <v>34.44217657680807</v>
+        <v>34.44217657680806</v>
       </c>
       <c r="K2" t="n">
         <v>85.95011125627252</v>
       </c>
       <c r="W2" t="n">
-        <v>14.12392554478488</v>
+        <v>14.12392554478492</v>
       </c>
       <c r="X2" t="n">
-        <v>-8799.586962586653</v>
+        <v>-8799.58696258668</v>
       </c>
       <c r="Y2" t="n">
-        <v>227.2043173257353</v>
+        <v>227.2043131232952</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.415790909173874e-09</v>
+        <v>7.415790427308462e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.892209389826914</v>
+        <v>0.8922093913877586</v>
       </c>
     </row>
     <row r="3">
@@ -8029,7 +8029,7 @@
         <v>180.717</v>
       </c>
       <c r="C3" t="n">
-        <v>406.6459735239791</v>
+        <v>406.645966932743</v>
       </c>
       <c r="D3" t="n">
         <v>5.19621e-07</v>
@@ -8038,37 +8038,37 @@
         <v>-76.41800000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4074856843798644</v>
+        <v>0.4074856843798806</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8052893662018898</v>
+        <v>0.8052893662019398</v>
       </c>
       <c r="H3" t="n">
-        <v>1.505632555887714</v>
+        <v>1.505632555887814</v>
       </c>
       <c r="I3" t="n">
-        <v>2.183018310677797</v>
+        <v>2.1830183106778</v>
       </c>
       <c r="J3" t="n">
-        <v>29.9661756648014</v>
+        <v>29.96617566480117</v>
       </c>
       <c r="K3" t="n">
         <v>86.09480031582621</v>
       </c>
       <c r="W3" t="n">
-        <v>14.64893791468133</v>
+        <v>14.64893791468135</v>
       </c>
       <c r="X3" t="n">
-        <v>-8712.207715790601</v>
+        <v>-8712.20771579061</v>
       </c>
       <c r="Y3" t="n">
-        <v>139.8248128091584</v>
+        <v>139.8248299101751</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.131392653100676e-09</v>
+        <v>6.131394480100796e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8761863054589144</v>
+        <v>0.8761863025301915</v>
       </c>
     </row>
     <row r="4">
@@ -8079,7 +8079,7 @@
         <v>172.316</v>
       </c>
       <c r="C4" t="n">
-        <v>397.8591615662288</v>
+        <v>397.8591614596535</v>
       </c>
       <c r="D4" t="n">
         <v>5.18674e-07</v>
@@ -8091,13 +8091,13 @@
         <v>0.2029816572770876</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7437107576065484</v>
+        <v>0.7437107576065481</v>
       </c>
       <c r="H4" t="n">
-        <v>1.363498654623092</v>
+        <v>1.363498654623129</v>
       </c>
       <c r="I4" t="n">
-        <v>2.599642291862426</v>
+        <v>2.59964229186243</v>
       </c>
       <c r="J4" t="n">
         <v>39.29648469481174</v>
@@ -8112,13 +8112,13 @@
         <v>-8459.159807644928</v>
       </c>
       <c r="Y4" t="n">
-        <v>141.394852709049</v>
+        <v>141.3948503124371</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.936200708988308e-09</v>
+        <v>5.936200339332325e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8804858813101721</v>
+        <v>0.8804858817833203</v>
       </c>
     </row>
     <row r="5">
@@ -8129,7 +8129,7 @@
         <v>169.34</v>
       </c>
       <c r="C5" t="n">
-        <v>530.7556491734686</v>
+        <v>530.7557444438736</v>
       </c>
       <c r="D5" t="n">
         <v>5.17863e-07</v>
@@ -8138,37 +8138,37 @@
         <v>-77.03700000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4437706076916035</v>
+        <v>0.4437706076916083</v>
       </c>
       <c r="G5" t="n">
         <v>0.6937116245526209</v>
       </c>
       <c r="H5" t="n">
-        <v>1.454849245616604</v>
+        <v>1.45484924561656</v>
       </c>
       <c r="I5" t="n">
-        <v>1.879215365228066</v>
+        <v>1.879215365227958</v>
       </c>
       <c r="J5" t="n">
-        <v>30.44454441905064</v>
+        <v>30.44454441905067</v>
       </c>
       <c r="K5" t="n">
-        <v>86.20353949558505</v>
+        <v>86.20353949558503</v>
       </c>
       <c r="W5" t="n">
-        <v>15.06980062195729</v>
+        <v>15.06980062195727</v>
       </c>
       <c r="X5" t="n">
-        <v>-8694.053340036611</v>
+        <v>-8694.053340036593</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.205207069750095</v>
+        <v>1.205147383560811</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.204855398689917e-09</v>
+        <v>4.204859647325554e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8627178882205535</v>
+        <v>0.8627178039481953</v>
       </c>
     </row>
     <row r="6">
@@ -8179,7 +8179,7 @@
         <v>167.161</v>
       </c>
       <c r="C6" t="n">
-        <v>517.3195051347097</v>
+        <v>517.3194277707649</v>
       </c>
       <c r="D6" t="n">
         <v>5.17232e-07</v>
@@ -8188,37 +8188,37 @@
         <v>-77.259</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4189759137374585</v>
+        <v>0.4189759137374952</v>
       </c>
       <c r="G6" t="n">
-        <v>1.222558228199029</v>
+        <v>1.222558228199021</v>
       </c>
       <c r="H6" t="n">
-        <v>1.616154031587023</v>
+        <v>1.616154031586944</v>
       </c>
       <c r="I6" t="n">
-        <v>2.675854820872687</v>
+        <v>2.675854820872656</v>
       </c>
       <c r="J6" t="n">
-        <v>43.52718987594177</v>
+        <v>43.52718987594187</v>
       </c>
       <c r="K6" t="n">
         <v>86.46264421811694</v>
       </c>
       <c r="W6" t="n">
-        <v>16.17676239454528</v>
+        <v>16.1767623945453</v>
       </c>
       <c r="X6" t="n">
-        <v>-9257.356887068754</v>
+        <v>-9257.356887068769</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.418480364888201</v>
+        <v>7.418662130836812</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.010189250164338e-09</v>
+        <v>4.010208331381286e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8682984528808602</v>
+        <v>0.8682981579817073</v>
       </c>
     </row>
     <row r="7">
@@ -8229,7 +8229,7 @@
         <v>158.897</v>
       </c>
       <c r="C7" t="n">
-        <v>396.6151230536615</v>
+        <v>396.6151359336719</v>
       </c>
       <c r="D7" t="n">
         <v>5.16748e-07</v>
@@ -8238,7 +8238,7 @@
         <v>-77.473</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2287810479190074</v>
+        <v>0.2287810479190225</v>
       </c>
       <c r="G7" t="n">
         <v>0.2909553693014067</v>
@@ -8247,28 +8247,28 @@
         <v>1.194053249113096</v>
       </c>
       <c r="I7" t="n">
-        <v>1.881690882143798</v>
+        <v>1.881690882143863</v>
       </c>
       <c r="J7" t="n">
-        <v>32.24413141500671</v>
+        <v>32.24413141500663</v>
       </c>
       <c r="K7" t="n">
-        <v>85.98322467867696</v>
+        <v>85.98322467867695</v>
       </c>
       <c r="W7" t="n">
         <v>14.24074725219623</v>
       </c>
       <c r="X7" t="n">
-        <v>-7971.611483143059</v>
+        <v>-7971.611483143056</v>
       </c>
       <c r="Y7" t="n">
-        <v>123.5819524822922</v>
+        <v>123.5819518491335</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.580689771780757e-09</v>
+        <v>5.580690799047449e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8813409558600329</v>
+        <v>0.8813409613014896</v>
       </c>
     </row>
     <row r="8">
@@ -8279,7 +8279,7 @@
         <v>155.76</v>
       </c>
       <c r="C8" t="n">
-        <v>389.398452558566</v>
+        <v>389.3984397813338</v>
       </c>
       <c r="D8" t="n">
         <v>5.16463e-07</v>
@@ -8288,19 +8288,19 @@
         <v>-77.65900000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09326881776994159</v>
+        <v>0.09326881776994167</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5352377549858983</v>
+        <v>0.535237754985895</v>
       </c>
       <c r="H8" t="n">
-        <v>1.312222876269671</v>
+        <v>1.312222876269708</v>
       </c>
       <c r="I8" t="n">
-        <v>2.138215954275578</v>
+        <v>2.138215954275574</v>
       </c>
       <c r="J8" t="n">
-        <v>36.09636256477264</v>
+        <v>36.09636256477265</v>
       </c>
       <c r="K8" t="n">
         <v>86.10727891488591</v>
@@ -8312,13 +8312,13 @@
         <v>-8138.293414799076</v>
       </c>
       <c r="Y8" t="n">
-        <v>124.7574524670185</v>
+        <v>124.757452678464</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.54003427037018e-09</v>
+        <v>5.540033973945719e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8830618283321697</v>
+        <v>0.8830618083046421</v>
       </c>
     </row>
     <row r="9">
@@ -8338,28 +8338,28 @@
         <v>-77.81100000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3206300146548768</v>
+        <v>0.3206300146548778</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6425562784706773</v>
+        <v>0.6425562784706809</v>
       </c>
       <c r="H9" t="n">
-        <v>1.402216861111823</v>
+        <v>1.402216861111815</v>
       </c>
       <c r="I9" t="n">
-        <v>2.392039409126852</v>
+        <v>2.392039409126843</v>
       </c>
       <c r="J9" t="n">
-        <v>41.39457995253967</v>
+        <v>41.39457995254021</v>
       </c>
       <c r="K9" t="n">
         <v>86.24132441411275</v>
       </c>
       <c r="W9" t="n">
-        <v>15.22173524286037</v>
+        <v>15.22173524286035</v>
       </c>
       <c r="X9" t="n">
-        <v>-8346.133023764769</v>
+        <v>-8346.133023764758</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -8367,10 +8367,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>2.115043053145326e-06</v>
+        <v>2.11541369864559e-06</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7872666669690823</v>
+        <v>0.7872399332937411</v>
       </c>
     </row>
     <row r="10">
@@ -8390,28 +8390,28 @@
         <v>-77.982</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4704757754080797</v>
+        <v>0.4704757754081003</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9385174736945496</v>
+        <v>0.9385174736945442</v>
       </c>
       <c r="H10" t="n">
-        <v>1.741258981043819</v>
+        <v>1.741258981043794</v>
       </c>
       <c r="I10" t="n">
-        <v>2.367071551321159</v>
+        <v>2.367071551321134</v>
       </c>
       <c r="J10" t="n">
         <v>42.7925121795191</v>
       </c>
       <c r="K10" t="n">
-        <v>86.57823194614254</v>
+        <v>86.57823194614255</v>
       </c>
       <c r="W10" t="n">
-        <v>16.72458364745447</v>
+        <v>16.72458364745453</v>
       </c>
       <c r="X10" t="n">
-        <v>-9121.422450275599</v>
+        <v>-9121.422450275631</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>2.000572738836259e-06</v>
+        <v>1.947955430033344e-06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7955462512158019</v>
+        <v>0.7994682982430225</v>
       </c>
     </row>
     <row r="11">
@@ -8433,7 +8433,7 @@
         <v>147.194</v>
       </c>
       <c r="C11" t="n">
-        <v>358.3160349785629</v>
+        <v>358.3160326345661</v>
       </c>
       <c r="D11" t="n">
         <v>5.16208e-07</v>
@@ -8442,37 +8442,37 @@
         <v>-78.142</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06426427450633361</v>
+        <v>0.06426427450631776</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6147806978837342</v>
+        <v>0.6147806978838863</v>
       </c>
       <c r="H11" t="n">
-        <v>1.304585700646868</v>
+        <v>1.304585700646849</v>
       </c>
       <c r="I11" t="n">
-        <v>2.263897460490562</v>
+        <v>2.263897460490561</v>
       </c>
       <c r="J11" t="n">
         <v>39.61757183780524</v>
       </c>
       <c r="K11" t="n">
-        <v>86.23403615487634</v>
+        <v>86.23403615487635</v>
       </c>
       <c r="W11" t="n">
-        <v>15.19219189203601</v>
+        <v>15.19219189203606</v>
       </c>
       <c r="X11" t="n">
-        <v>-8143.608376541416</v>
+        <v>-8143.608376541447</v>
       </c>
       <c r="Y11" t="n">
-        <v>141.1282560027825</v>
+        <v>141.1282295936746</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.637330948850109e-09</v>
+        <v>5.637328373294426e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8923681297970864</v>
+        <v>0.8923681419669789</v>
       </c>
     </row>
     <row r="12">
@@ -8483,7 +8483,7 @@
         <v>144.9469999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>393.2511289055929</v>
+        <v>393.251124107029</v>
       </c>
       <c r="D12" t="n">
         <v>5.15941e-07</v>
@@ -8492,19 +8492,19 @@
         <v>-78.27</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3100808111512601</v>
+        <v>0.3100808111512414</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7215574700022996</v>
+        <v>0.7215574700022934</v>
       </c>
       <c r="H12" t="n">
         <v>1.399708717458724</v>
       </c>
       <c r="I12" t="n">
-        <v>2.068831105715563</v>
+        <v>2.068831105715564</v>
       </c>
       <c r="J12" t="n">
-        <v>39.81076461623726</v>
+        <v>39.81076461623734</v>
       </c>
       <c r="K12" t="n">
         <v>86.27555474661604</v>
@@ -8513,16 +8513,16 @@
         <v>15.36203429133054</v>
       </c>
       <c r="X12" t="n">
-        <v>-8155.639213459574</v>
+        <v>-8155.639213459578</v>
       </c>
       <c r="Y12" t="n">
-        <v>99.59046985793617</v>
+        <v>99.59047323973897</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.69699916975905e-09</v>
+        <v>4.696999101536326e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8907493303389157</v>
+        <v>0.8907493327725793</v>
       </c>
     </row>
     <row r="13">
@@ -8533,7 +8533,7 @@
         <v>145.48</v>
       </c>
       <c r="C13" t="n">
-        <v>424.5484234291735</v>
+        <v>424.5483651997986</v>
       </c>
       <c r="D13" t="n">
         <v>5.16025e-07</v>
@@ -8542,13 +8542,13 @@
         <v>-78.407</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2778815103829188</v>
+        <v>0.277881510382923</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8456813308983444</v>
+        <v>0.8456813308983667</v>
       </c>
       <c r="H13" t="n">
-        <v>1.465722789624489</v>
+        <v>1.465722789624584</v>
       </c>
       <c r="I13" t="n">
         <v>2.307784678470119</v>
@@ -8557,22 +8557,22 @@
         <v>41.08126219608315</v>
       </c>
       <c r="K13" t="n">
-        <v>86.61406644922589</v>
+        <v>86.6140664492259</v>
       </c>
       <c r="W13" t="n">
-        <v>16.90200504411959</v>
+        <v>16.90200504411962</v>
       </c>
       <c r="X13" t="n">
-        <v>-8934.495273070181</v>
+        <v>-8934.495273070197</v>
       </c>
       <c r="Y13" t="n">
-        <v>63.07391247671142</v>
+        <v>63.07397179061735</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.273598507811043e-09</v>
+        <v>4.27359698217387e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8849312902537186</v>
+        <v>0.8849313545254478</v>
       </c>
     </row>
     <row r="14">
@@ -8592,28 +8592,28 @@
         <v>-78.548</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3793314305432155</v>
+        <v>0.3793314305432402</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7224578856322302</v>
+        <v>0.7224578856322497</v>
       </c>
       <c r="H14" t="n">
-        <v>1.407974108401413</v>
+        <v>1.407974108401417</v>
       </c>
       <c r="I14" t="n">
-        <v>2.440022047394589</v>
+        <v>2.440022047394597</v>
       </c>
       <c r="J14" t="n">
-        <v>47.52595568656239</v>
+        <v>47.52595568656245</v>
       </c>
       <c r="K14" t="n">
         <v>86.41195667456248</v>
       </c>
       <c r="W14" t="n">
-        <v>15.94765071620183</v>
+        <v>15.94765071620184</v>
       </c>
       <c r="X14" t="n">
-        <v>-8314.579168769395</v>
+        <v>-8314.579168769402</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -8621,10 +8621,10 @@
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>1.583197135291149e-06</v>
+        <v>1.583286270231736e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8304214642819526</v>
+        <v>0.8304042260370988</v>
       </c>
     </row>
     <row r="15">
@@ -8635,7 +8635,7 @@
         <v>137.995</v>
       </c>
       <c r="C15" t="n">
-        <v>409.5404736692715</v>
+        <v>409.5404367406712</v>
       </c>
       <c r="D15" t="n">
         <v>5.15982e-07</v>
@@ -8644,19 +8644,19 @@
         <v>-78.654</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1850079808415546</v>
+        <v>0.1850079808415682</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6211224989523683</v>
+        <v>0.6211224989523778</v>
       </c>
       <c r="H15" t="n">
-        <v>1.440378818762587</v>
+        <v>1.440378818762599</v>
       </c>
       <c r="I15" t="n">
-        <v>2.28793299546794</v>
+        <v>2.287932995467975</v>
       </c>
       <c r="J15" t="n">
-        <v>42.33021315199902</v>
+        <v>42.33021315199939</v>
       </c>
       <c r="K15" t="n">
         <v>86.36764732155075</v>
@@ -8668,13 +8668,13 @@
         <v>-8125.317972457186</v>
       </c>
       <c r="Y15" t="n">
-        <v>69.20627253984094</v>
+        <v>69.20634213582717</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.174501091509376e-09</v>
+        <v>4.174503577685571e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8907022372085974</v>
+        <v>0.890702277343011</v>
       </c>
     </row>
     <row r="16">
@@ -8685,7 +8685,7 @@
         <v>136.198</v>
       </c>
       <c r="C16" t="n">
-        <v>419.169734472589</v>
+        <v>419.1697330259964</v>
       </c>
       <c r="D16" t="n">
         <v>5.15883e-07</v>
@@ -8697,34 +8697,34 @@
         <v>0.2763925948041334</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5953812507390878</v>
+        <v>0.5953812507390521</v>
       </c>
       <c r="H16" t="n">
-        <v>1.454093701839376</v>
+        <v>1.454093701839388</v>
       </c>
       <c r="I16" t="n">
-        <v>2.267031003926022</v>
+        <v>2.267031003925959</v>
       </c>
       <c r="J16" t="n">
-        <v>43.71138836166046</v>
+        <v>43.71138836166045</v>
       </c>
       <c r="K16" t="n">
         <v>86.39923131988029</v>
       </c>
       <c r="W16" t="n">
-        <v>15.89114278155018</v>
+        <v>15.89114278155021</v>
       </c>
       <c r="X16" t="n">
-        <v>-8119.982157234307</v>
+        <v>-8119.982157234324</v>
       </c>
       <c r="Y16" t="n">
-        <v>80.11166277418602</v>
+        <v>80.11166866743098</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.826632434904228e-08</v>
+        <v>1.826633089816727e-08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.7905655511727179</v>
+        <v>0.7905655280317965</v>
       </c>
     </row>
     <row r="17">
@@ -8744,19 +8744,19 @@
         <v>-78.913</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2915081464087915</v>
+        <v>0.2915081464087833</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9061904908275671</v>
+        <v>0.9061904908274884</v>
       </c>
       <c r="H17" t="n">
-        <v>1.60067523840496</v>
+        <v>1.600675238404946</v>
       </c>
       <c r="I17" t="n">
-        <v>2.830325477844451</v>
+        <v>2.830325477844452</v>
       </c>
       <c r="J17" t="n">
-        <v>59.84232123027933</v>
+        <v>59.8423212302792</v>
       </c>
       <c r="K17" t="n">
         <v>86.56823354229601</v>
@@ -8765,7 +8765,7 @@
         <v>16.67574058292641</v>
       </c>
       <c r="X17" t="n">
-        <v>-8464.497698882653</v>
+        <v>-8464.497698882655</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>1.423873628367312e-06</v>
+        <v>1.424566020301487e-06</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8463346620118506</v>
+        <v>0.8462592525752697</v>
       </c>
     </row>
     <row r="18">
@@ -8787,7 +8787,7 @@
         <v>128.85</v>
       </c>
       <c r="C18" t="n">
-        <v>498.3512950132838</v>
+        <v>498.3515375097577</v>
       </c>
       <c r="D18" t="n">
         <v>5.16125e-07</v>
@@ -8796,37 +8796,37 @@
         <v>-79.03</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08553367608119777</v>
+        <v>0.08553367608119912</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4511436861560143</v>
+        <v>0.4511436861560666</v>
       </c>
       <c r="H18" t="n">
-        <v>1.209508652176592</v>
+        <v>1.209508652176575</v>
       </c>
       <c r="I18" t="n">
-        <v>2.274208323575305</v>
+        <v>2.274208323575353</v>
       </c>
       <c r="J18" t="n">
-        <v>45.02317040776452</v>
+        <v>45.02317040776396</v>
       </c>
       <c r="K18" t="n">
-        <v>86.19605984370624</v>
+        <v>86.19605984370621</v>
       </c>
       <c r="W18" t="n">
-        <v>15.04008201906049</v>
+        <v>15.0400820190604</v>
       </c>
       <c r="X18" t="n">
-        <v>-7507.542129849154</v>
+        <v>-7507.542129849103</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.318141355633743</v>
+        <v>4.318009393599073</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.918891604463265e-08</v>
+        <v>3.918925375065649e-08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.7140455141465991</v>
+        <v>0.7140448729314802</v>
       </c>
     </row>
     <row r="19">
@@ -8837,7 +8837,7 @@
         <v>128.679</v>
       </c>
       <c r="C19" t="n">
-        <v>420.4362557923385</v>
+        <v>420.4364991920662</v>
       </c>
       <c r="D19" t="n">
         <v>5.16195e-07</v>
@@ -8846,19 +8846,19 @@
         <v>-79.139</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2598098467772489</v>
+        <v>0.2598098467772512</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6718184631646174</v>
+        <v>0.6718184631646248</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9773069703928212</v>
+        <v>0.9773069703928023</v>
       </c>
       <c r="I19" t="n">
         <v>2.146576179141718</v>
       </c>
       <c r="J19" t="n">
-        <v>37.403737808341</v>
+        <v>37.40373780834123</v>
       </c>
       <c r="K19" t="n">
         <v>86.37119903640611</v>
@@ -8867,16 +8867,16 @@
         <v>15.76805951364126</v>
       </c>
       <c r="X19" t="n">
-        <v>-7814.228678086119</v>
+        <v>-7814.228678086121</v>
       </c>
       <c r="Y19" t="n">
-        <v>40.83394559870862</v>
+        <v>40.8335755980548</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.653105197658538e-09</v>
+        <v>3.653094124068158e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8940978275469788</v>
+        <v>0.8940978773476441</v>
       </c>
     </row>
     <row r="20">
@@ -8887,7 +8887,7 @@
         <v>125.838</v>
       </c>
       <c r="C20" t="n">
-        <v>381.9111972965312</v>
+        <v>381.911199175964</v>
       </c>
       <c r="D20" t="n">
         <v>5.16325e-07</v>
@@ -8896,37 +8896,37 @@
         <v>-79.258</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02535125707845608</v>
+        <v>0.02535125707846865</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5387538266961881</v>
+        <v>0.5387538266962301</v>
       </c>
       <c r="H20" t="n">
-        <v>1.336427828124159</v>
+        <v>1.336427828124124</v>
       </c>
       <c r="I20" t="n">
-        <v>2.549917302944029</v>
+        <v>2.549917302944014</v>
       </c>
       <c r="J20" t="n">
-        <v>54.77269454172064</v>
+        <v>54.7726945417211</v>
       </c>
       <c r="K20" t="n">
         <v>86.3154575967724</v>
       </c>
       <c r="W20" t="n">
-        <v>15.52886908561989</v>
+        <v>15.52886908561991</v>
       </c>
       <c r="X20" t="n">
-        <v>-7611.576853225756</v>
+        <v>-7611.576853225773</v>
       </c>
       <c r="Y20" t="n">
-        <v>75.83070001575803</v>
+        <v>75.83071427145259</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.080322871783889e-09</v>
+        <v>4.080323724053289e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8990971811547871</v>
+        <v>0.8990971783762893</v>
       </c>
     </row>
     <row r="21">
@@ -8937,7 +8937,7 @@
         <v>123.924</v>
       </c>
       <c r="C21" t="n">
-        <v>383.8729147054056</v>
+        <v>383.8729355730983</v>
       </c>
       <c r="D21" t="n">
         <v>5.16501e-07</v>
@@ -8946,37 +8946,37 @@
         <v>-79.37</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2436970921242774</v>
+        <v>0.2436970921242972</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6682560515821906</v>
+        <v>0.6682560515821812</v>
       </c>
       <c r="H21" t="n">
-        <v>1.339842451990955</v>
+        <v>1.339842451990981</v>
       </c>
       <c r="I21" t="n">
-        <v>2.487079147596895</v>
+        <v>2.487079147596893</v>
       </c>
       <c r="J21" t="n">
-        <v>55.49866911638667</v>
+        <v>55.49866911638694</v>
       </c>
       <c r="K21" t="n">
         <v>86.38709435375804</v>
       </c>
       <c r="W21" t="n">
-        <v>15.83761802685178</v>
+        <v>15.83761802685179</v>
       </c>
       <c r="X21" t="n">
-        <v>-7688.220450246899</v>
+        <v>-7688.220450246908</v>
       </c>
       <c r="Y21" t="n">
-        <v>69.3957914278527</v>
+        <v>69.39571167565212</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.008907648031505e-09</v>
+        <v>4.008903726244124e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8987504464267437</v>
+        <v>0.8987504861957519</v>
       </c>
     </row>
     <row r="22">
@@ -8987,7 +8987,7 @@
         <v>121.6420000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>367.4489439492795</v>
+        <v>367.4489576011801</v>
       </c>
       <c r="D22" t="n">
         <v>5.16635e-07</v>
@@ -8999,34 +8999,34 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5600702658062693</v>
+        <v>0.5600702658062751</v>
       </c>
       <c r="H22" t="n">
-        <v>1.335431596250833</v>
+        <v>1.335431596250831</v>
       </c>
       <c r="I22" t="n">
-        <v>2.386473134667395</v>
+        <v>2.386473134667374</v>
       </c>
       <c r="J22" t="n">
-        <v>49.06020133975996</v>
+        <v>49.06020133975994</v>
       </c>
       <c r="K22" t="n">
-        <v>86.31899829893688</v>
+        <v>86.31899829893689</v>
       </c>
       <c r="W22" t="n">
-        <v>15.54384732010938</v>
+        <v>15.54384732010939</v>
       </c>
       <c r="X22" t="n">
-        <v>-7461.779420541887</v>
+        <v>-7461.779420541895</v>
       </c>
       <c r="Y22" t="n">
-        <v>81.53535160518707</v>
+        <v>81.53399829411991</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.184498841114459e-09</v>
+        <v>4.18452288903893e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9008264610054592</v>
+        <v>0.9008253041846258</v>
       </c>
     </row>
   </sheetData>
@@ -9183,7 +9183,7 @@
         <v>230.223</v>
       </c>
       <c r="C2" t="n">
-        <v>318.6762908569275</v>
+        <v>318.676294701301</v>
       </c>
       <c r="D2" t="n">
         <v>5.48405e-07</v>
@@ -9192,16 +9192,16 @@
         <v>-71.477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08917540533169541</v>
+        <v>0.08917540533169116</v>
       </c>
       <c r="G2" t="n">
         <v>0.3471414323388183</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1459857028003</v>
+        <v>1.145985702800317</v>
       </c>
       <c r="I2" t="n">
-        <v>1.954132397868006</v>
+        <v>1.954132397868003</v>
       </c>
       <c r="J2" t="n">
         <v>13.54704243204864</v>
@@ -9210,19 +9210,19 @@
         <v>83.23478723234156</v>
       </c>
       <c r="W2" t="n">
-        <v>8.429781238972879</v>
+        <v>8.429781238972884</v>
       </c>
       <c r="X2" t="n">
-        <v>-5414.041814868423</v>
+        <v>-5414.041814868425</v>
       </c>
       <c r="Y2" t="n">
-        <v>223.6363416046415</v>
+        <v>223.6363367675561</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.341432782033877e-09</v>
+        <v>3.341432760764105e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9390762822440303</v>
+        <v>0.9390762770541593</v>
       </c>
     </row>
     <row r="3">
@@ -9233,7 +9233,7 @@
         <v>155.771</v>
       </c>
       <c r="C3" t="n">
-        <v>281.2050578839725</v>
+        <v>281.2050418088222</v>
       </c>
       <c r="D3" t="n">
         <v>5.56439e-07</v>
@@ -9242,19 +9242,19 @@
         <v>-74.845</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0184069568974506</v>
+        <v>0.01840695689741802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6847044382186773</v>
+        <v>0.6847044382186913</v>
       </c>
       <c r="H3" t="n">
-        <v>1.456079963214183</v>
+        <v>1.456079963214203</v>
       </c>
       <c r="I3" t="n">
-        <v>2.191634385802108</v>
+        <v>2.191634385802081</v>
       </c>
       <c r="J3" t="n">
-        <v>18.62958177097708</v>
+        <v>18.62958177097705</v>
       </c>
       <c r="K3" t="n">
         <v>85.08416256317115</v>
@@ -9263,16 +9263,16 @@
         <v>11.62673141074112</v>
       </c>
       <c r="X3" t="n">
-        <v>-6445.594085121489</v>
+        <v>-6445.59408512149</v>
       </c>
       <c r="Y3" t="n">
-        <v>231.3452517081248</v>
+        <v>231.3452642404183</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.069067949366617e-09</v>
+        <v>8.06906772960169e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8999087974728303</v>
+        <v>0.8999088043071136</v>
       </c>
     </row>
     <row r="4">
@@ -9283,7 +9283,7 @@
         <v>142.388</v>
       </c>
       <c r="C4" t="n">
-        <v>274.9206344129435</v>
+        <v>274.9206300011541</v>
       </c>
       <c r="D4" t="n">
         <v>5.48945e-07</v>
@@ -9292,37 +9292,37 @@
         <v>-76.01000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3604533760222052</v>
+        <v>0.3604533760221865</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7743064445909836</v>
+        <v>0.7743064445909724</v>
       </c>
       <c r="H4" t="n">
-        <v>1.497126154862834</v>
+        <v>1.497126154862831</v>
       </c>
       <c r="I4" t="n">
-        <v>2.627842470879877</v>
+        <v>2.627842470879866</v>
       </c>
       <c r="J4" t="n">
         <v>23.87766911889256</v>
       </c>
       <c r="K4" t="n">
-        <v>85.70517038129283</v>
+        <v>85.70517038129285</v>
       </c>
       <c r="W4" t="n">
-        <v>13.3156451929969</v>
+        <v>13.31564519299691</v>
       </c>
       <c r="X4" t="n">
-        <v>-7146.132424742581</v>
+        <v>-7146.132424742593</v>
       </c>
       <c r="Y4" t="n">
-        <v>227.2879308200891</v>
+        <v>227.2879322893289</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.837082347473839e-09</v>
+        <v>8.837082017584867e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8952620395798013</v>
+        <v>0.8952620368498381</v>
       </c>
     </row>
     <row r="5">
@@ -9333,7 +9333,7 @@
         <v>134.357</v>
       </c>
       <c r="C5" t="n">
-        <v>272.340117382444</v>
+        <v>272.3401181617656</v>
       </c>
       <c r="D5" t="n">
         <v>5.42322e-07</v>
@@ -9342,37 +9342,37 @@
         <v>-76.693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2608720242752646</v>
+        <v>0.2608720242752559</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4951698017334251</v>
+        <v>0.4951698017334252</v>
       </c>
       <c r="H5" t="n">
-        <v>1.15293708568749</v>
+        <v>1.152937085687482</v>
       </c>
       <c r="I5" t="n">
         <v>1.886380745785861</v>
       </c>
       <c r="J5" t="n">
-        <v>22.43295414845267</v>
+        <v>22.43295414845264</v>
       </c>
       <c r="K5" t="n">
-        <v>85.79608932309401</v>
+        <v>85.79608932309402</v>
       </c>
       <c r="W5" t="n">
-        <v>13.60469582453691</v>
+        <v>13.60469582453696</v>
       </c>
       <c r="X5" t="n">
-        <v>-7146.513889313306</v>
+        <v>-7146.513889313336</v>
       </c>
       <c r="Y5" t="n">
-        <v>222.6717965081064</v>
+        <v>222.6717959665643</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.373627419559294e-09</v>
+        <v>8.373627470565421e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8998280601798566</v>
+        <v>0.8998280595011753</v>
       </c>
     </row>
     <row r="6">
@@ -9383,7 +9383,7 @@
         <v>131.894</v>
       </c>
       <c r="C6" t="n">
-        <v>262.8184441995215</v>
+        <v>262.8184458762306</v>
       </c>
       <c r="D6" t="n">
         <v>5.37384e-07</v>
@@ -9392,37 +9392,37 @@
         <v>-77.176</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2971080407960572</v>
+        <v>0.2971080407960646</v>
       </c>
       <c r="G6" t="n">
-        <v>1.138437418711877</v>
+        <v>1.138437418711925</v>
       </c>
       <c r="H6" t="n">
-        <v>1.509783129603516</v>
+        <v>1.509783129603517</v>
       </c>
       <c r="I6" t="n">
-        <v>2.560692240341428</v>
+        <v>2.560692240341429</v>
       </c>
       <c r="J6" t="n">
-        <v>28.59713413647124</v>
+        <v>28.5971341364712</v>
       </c>
       <c r="K6" t="n">
-        <v>86.1322096647157</v>
+        <v>86.13220966471569</v>
       </c>
       <c r="W6" t="n">
-        <v>14.79106039914917</v>
+        <v>14.79106039914915</v>
       </c>
       <c r="X6" t="n">
-        <v>-7685.932461853346</v>
+        <v>-7685.932461853336</v>
       </c>
       <c r="Y6" t="n">
-        <v>224.7462366581939</v>
+        <v>224.746234501729</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.043829150533915e-09</v>
+        <v>8.04382904514534e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9060893027203227</v>
+        <v>0.9060893016988211</v>
       </c>
     </row>
     <row r="7">
@@ -9433,7 +9433,7 @@
         <v>126.794</v>
       </c>
       <c r="C7" t="n">
-        <v>256.3464491092914</v>
+        <v>256.3464469035407</v>
       </c>
       <c r="D7" t="n">
         <v>5.34091e-07</v>
@@ -9442,37 +9442,37 @@
         <v>-77.55500000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08846537671712368</v>
+        <v>0.08846537671713303</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5108913846030761</v>
+        <v>0.5108913846030665</v>
       </c>
       <c r="H7" t="n">
-        <v>1.130939646268442</v>
+        <v>1.130939646268487</v>
       </c>
       <c r="I7" t="n">
         <v>2.022654159692959</v>
       </c>
       <c r="J7" t="n">
-        <v>25.80948698569293</v>
+        <v>25.80948698569296</v>
       </c>
       <c r="K7" t="n">
         <v>86.09283679408355</v>
       </c>
       <c r="W7" t="n">
-        <v>14.6415533226027</v>
+        <v>14.64155332260268</v>
       </c>
       <c r="X7" t="n">
-        <v>-7469.247115082168</v>
+        <v>-7469.247115082159</v>
       </c>
       <c r="Y7" t="n">
-        <v>223.9275679417528</v>
+        <v>223.9275708134445</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.727730312684295e-09</v>
+        <v>7.727730387311628e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9110341542815975</v>
+        <v>0.9110341551006097</v>
       </c>
     </row>
     <row r="8">
@@ -9483,7 +9483,7 @@
         <v>121.5</v>
       </c>
       <c r="C8" t="n">
-        <v>250.596257992918</v>
+        <v>250.596257380253</v>
       </c>
       <c r="D8" t="n">
         <v>5.31622e-07</v>
@@ -9495,34 +9495,34 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4546049582765402</v>
+        <v>0.4546049582765499</v>
       </c>
       <c r="H8" t="n">
         <v>1.075151414504331</v>
       </c>
       <c r="I8" t="n">
-        <v>1.985898241251778</v>
+        <v>1.985898241251807</v>
       </c>
       <c r="J8" t="n">
-        <v>27.01572125230378</v>
+        <v>27.0157212523038</v>
       </c>
       <c r="K8" t="n">
-        <v>86.01793341948847</v>
+        <v>86.01793341948849</v>
       </c>
       <c r="W8" t="n">
-        <v>14.36527923318814</v>
+        <v>14.36527923318819</v>
       </c>
       <c r="X8" t="n">
-        <v>-7190.513920025728</v>
+        <v>-7190.51392002576</v>
       </c>
       <c r="Y8" t="n">
-        <v>222.9776757650925</v>
+        <v>222.9776767171154</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.606002976191019e-09</v>
+        <v>7.606003275399738e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9141653567392408</v>
+        <v>0.9141653542667639</v>
       </c>
     </row>
     <row r="9">
@@ -9533,7 +9533,7 @@
         <v>119.83</v>
       </c>
       <c r="C9" t="n">
-        <v>242.8081298746673</v>
+        <v>242.808119433828</v>
       </c>
       <c r="D9" t="n">
         <v>5.29846e-07</v>
@@ -9542,37 +9542,37 @@
         <v>-78.14400000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1549357653185952</v>
+        <v>0.1549357653185919</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6998680887728033</v>
+        <v>0.699868088772796</v>
       </c>
       <c r="H9" t="n">
-        <v>1.539827081477487</v>
+        <v>1.53982708147742</v>
       </c>
       <c r="I9" t="n">
-        <v>2.564392866790091</v>
+        <v>2.564392866789976</v>
       </c>
       <c r="J9" t="n">
-        <v>34.00297576992922</v>
+        <v>34.00297576992923</v>
       </c>
       <c r="K9" t="n">
-        <v>86.26989989713512</v>
+        <v>86.2698998971351</v>
       </c>
       <c r="W9" t="n">
-        <v>15.33867958993862</v>
+        <v>15.33867958993858</v>
       </c>
       <c r="X9" t="n">
-        <v>-7597.017364114158</v>
+        <v>-7597.017364114135</v>
       </c>
       <c r="Y9" t="n">
-        <v>224.117781748786</v>
+        <v>224.1177968247004</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.507951925369305e-09</v>
+        <v>7.507952627214874e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.916976180910871</v>
+        <v>0.916976192834606</v>
       </c>
     </row>
     <row r="10">
@@ -9583,7 +9583,7 @@
         <v>116.121</v>
       </c>
       <c r="C10" t="n">
-        <v>238.6319366151209</v>
+        <v>238.6319458119767</v>
       </c>
       <c r="D10" t="n">
         <v>5.28564e-07</v>
@@ -9592,16 +9592,16 @@
         <v>-78.361</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08806292461510733</v>
+        <v>0.08806292461510291</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6883682539826083</v>
+        <v>0.6883682539826219</v>
       </c>
       <c r="H10" t="n">
-        <v>1.237438892053168</v>
+        <v>1.237438892053175</v>
       </c>
       <c r="I10" t="n">
-        <v>2.252080060144379</v>
+        <v>2.252080060144384</v>
       </c>
       <c r="J10" t="n">
         <v>33.00930684280635</v>
@@ -9610,19 +9610,19 @@
         <v>86.27825604431004</v>
       </c>
       <c r="W10" t="n">
-        <v>15.37321574682725</v>
+        <v>15.37321574682724</v>
       </c>
       <c r="X10" t="n">
-        <v>-7510.588681929537</v>
+        <v>-7510.58868192953</v>
       </c>
       <c r="Y10" t="n">
-        <v>222.7389122939269</v>
+        <v>222.7388959233915</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.38618453373546e-09</v>
+        <v>7.386183340816521e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9195498165967417</v>
+        <v>0.9195498027059763</v>
       </c>
     </row>
     <row r="11">
@@ -9642,28 +9642,28 @@
         <v>-78.563</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3470963104992334</v>
+        <v>0.3470963104992353</v>
       </c>
       <c r="G11" t="n">
-        <v>0.964366898429819</v>
+        <v>0.9643668984297553</v>
       </c>
       <c r="H11" t="n">
-        <v>1.528700134325663</v>
+        <v>1.528700134325659</v>
       </c>
       <c r="I11" t="n">
-        <v>2.54653247517536</v>
+        <v>2.546532475175336</v>
       </c>
       <c r="J11" t="n">
-        <v>34.09323503542841</v>
+        <v>34.09323503542848</v>
       </c>
       <c r="K11" t="n">
         <v>86.57205587394866</v>
       </c>
       <c r="W11" t="n">
-        <v>16.69437940080897</v>
+        <v>16.69437940080894</v>
       </c>
       <c r="X11" t="n">
-        <v>-8100.325238554351</v>
+        <v>-8100.325238554336</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -9671,10 +9671,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>1.351561634035653e-06</v>
+        <v>1.352979360048473e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8580267901229111</v>
+        <v>0.8578680129768219</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,6 +1125,566 @@
       </c>
       <c r="AD11" t="n">
         <v>0.8820897532340063</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>202.047</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>344.391113968732</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.21535e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-75.191</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1916114932947508</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6401405543196615</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.325163521322319</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.15728535615622</v>
+      </c>
+      <c r="L12" t="n">
+        <v>26.42594023751873</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.75144313712272</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13.4612130265655</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-8425.382353354793</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>229.9006078340155</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.390464970288625e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8754728802098124</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>191.839</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9494771018624378</v>
+      </c>
+      <c r="D13" t="n">
+        <v>403.3256387227924</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.171126728779103</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.16844e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-75.92</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3163862155468708</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6672988410120961</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.244488088691967</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.135214841455913</v>
+      </c>
+      <c r="L13" t="n">
+        <v>27.89517354074306</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.95358244905579</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.13608209517033</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-8648.783113050877</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>157.4216700417161</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.638798901483142e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8738426742760733</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>185.659</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9188901592203793</v>
+      </c>
+      <c r="D14" t="n">
+        <v>441.9545613422773</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.283292580488599</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.14064e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-76.389</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3418126842168303</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.787324305454534</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.280089896848301</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.335561143644852</v>
+      </c>
+      <c r="L14" t="n">
+        <v>33.42687872252122</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.16898640496976</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.93348098541377</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-9004.449998165865</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>110.0034760628821</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.493802419722268e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8733102946857125</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>177.7169999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.879582473384905</v>
+      </c>
+      <c r="D15" t="n">
+        <v>398.9997393890193</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.158565721371212</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.12067e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-76.751</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.03866112505641388</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.631088982005509</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.058926213036913</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.975505547908519</v>
+      </c>
+      <c r="L15" t="n">
+        <v>30.19127106272634</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.1096533110838</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.70503950702535</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8715.851842118578</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>146.8711746844227</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6.317673909073686e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.876056313288321</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>173.469</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8585576623260923</v>
+      </c>
+      <c r="D16" t="n">
+        <v>390.0525450344726</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.132585973370632</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.10734e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-77.038</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1590480294086399</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.530346475396146</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.200895437514181</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.805119031982562</v>
+      </c>
+      <c r="L16" t="n">
+        <v>31.15138677097838</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.20104291829934</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.05986807852182</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8804.112573257327</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>148.8850777608197</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.257609979652605e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8792938015861804</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>168.0309999999999</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8316431325384684</v>
+      </c>
+      <c r="D17" t="n">
+        <v>454.4291438453985</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.319514718624991</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.09842e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-77.322</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1420233111535636</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8076149251994346</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.495643479595357</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.574670224228298</v>
+      </c>
+      <c r="L17" t="n">
+        <v>45.8717916872337</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.18963722131049</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.01465623900593</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8647.549253121884</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>74.72344333841052</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.443498897225976e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8795519533581874</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>162.943</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8064608729652013</v>
+      </c>
+      <c r="D18" t="n">
+        <v>462.789221501918</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.343789670322143</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5.09092e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-77.54900000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.07830713619269372</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.3071860725068022</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.398477207138516</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.015642289022921</v>
+      </c>
+      <c r="L18" t="n">
+        <v>37.09347506303033</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.10652505823431</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.69318818376991</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-8328.152260697079</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>60.56518800376531</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.45412765456922e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8764884642052987</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>163.156</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8075150831242235</v>
+      </c>
+      <c r="D19" t="n">
+        <v>392.9621903175844</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.141034638754536</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.08651e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-77.782</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4164939112962885</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.133297331941555</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.621305872901055</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.692652910741343</v>
+      </c>
+      <c r="L19" t="n">
+        <v>50.22657284326226</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.61123063991427</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.88782801410665</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-9523.735254483508</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>125.1098427284256</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.438060306922006e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8841174214021877</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>155.971</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7719540502952282</v>
+      </c>
+      <c r="D20" t="n">
+        <v>406.7885075627921</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.181181775786832</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.082609999999999e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-77.98099999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1617325119238919</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.759705859251338</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.565502145397079</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.578594925231223</v>
+      </c>
+      <c r="L20" t="n">
+        <v>52.00445736814253</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.344032132899</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15.65057452743505</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-8663.694647733459</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>105.4024575105026</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.277030531419358e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8807965602109382</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>152.0339999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7524684850554569</v>
+      </c>
+      <c r="D21" t="n">
+        <v>445.8208587260186</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.294519053027877</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.08056e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-78.173</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2072955141396304</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5454724906845972</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.33197094309005</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.143726058355128</v>
+      </c>
+      <c r="L21" t="n">
+        <v>41.38384227129446</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.2630169763801</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.3103481549823</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-8351.490980495342</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>58.64887275879467</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.236679430119911e-09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8820898919335342</v>
       </c>
     </row>
   </sheetData>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,6 +3017,1182 @@
       </c>
       <c r="AD22" t="n">
         <v>0.7951882469836797</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>204.684</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>333.0270055230043</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.21634e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-75.754</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3164903587282932</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7778741743617876</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.461623813279092</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.422465636962534</v>
+      </c>
+      <c r="L23" t="n">
+        <v>33.32976497281615</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.96837537932797</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.1881230881079</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-8745.798358997863</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>223.0084257518495</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.410451186857469e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8919967224851825</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>178.233</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8707715307498387</v>
+      </c>
+      <c r="D24" t="n">
+        <v>387.3411747194574</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.16309238679054</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.21579e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.58</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.01391882359777785</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.403249382259977</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.333960457939073</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.169164727500503</v>
+      </c>
+      <c r="L24" t="n">
+        <v>31.46758390179824</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.90677899824207</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.97390290455383</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-8194.01702800314</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>157.4197792984946</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.407610361741133e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8703510827243802</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>177.282</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8661253444333703</v>
+      </c>
+      <c r="D25" t="n">
+        <v>562.3228867377552</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.688520382467637</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.20277e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.88500000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5934229774499765</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.030465497959012</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.694160515413319</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.955486472502577</v>
+      </c>
+      <c r="L25" t="n">
+        <v>47.28654211276874</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.48824651819594</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.29499757508112</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-9494.247686904198</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>10.24486587007457</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.787937415089337e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.710725352612355</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>172.5309999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8429139551699201</v>
+      </c>
+      <c r="D26" t="n">
+        <v>529.6243125367926</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.590334428599989</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.19107e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-77.10599999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4028511991794392</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.023299975134475</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.674980028094982</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.732742359244883</v>
+      </c>
+      <c r="L26" t="n">
+        <v>42.47204809449417</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.48646823592057</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.28672959154239</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-9370.291333677133</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.3241789192435256</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.416717263785596e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8598474793700015</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>166.1299999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8116413593637017</v>
+      </c>
+      <c r="D27" t="n">
+        <v>387.7967054166649</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.164460235912842</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.18404e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-77.31999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3520387347631234</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8529723944084484</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.466325014602286</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.064087515445013</v>
+      </c>
+      <c r="L27" t="n">
+        <v>35.23849248096204</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.37210788369279</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.77202025658535</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-8952.996738374826</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>138.0677664450951</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>6.341418106734412e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8774412708113917</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>162.554</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7941705262746476</v>
+      </c>
+      <c r="D28" t="n">
+        <v>376.4243365919004</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.130311747543544</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.179499999999999e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-77.48999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3488996412597922</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7785537313279134</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.708690601594952</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.586390090860013</v>
+      </c>
+      <c r="L28" t="n">
+        <v>45.90821696265915</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.28400188530301</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.39705343960712</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-8631.120644864357</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>144.0083830735583</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>6.259567105913664e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8811408785020909</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>160.9569999999999</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7863682554571921</v>
+      </c>
+      <c r="D29" t="n">
+        <v>374.4413740723473</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.124357388027147</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.17457e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-77.657</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4801645341277064</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8020454599199758</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.542292289407025</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.349117361662363</v>
+      </c>
+      <c r="L29" t="n">
+        <v>36.99527892414148</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.47985200944004</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.25604123245145</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9043.424900618773</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>141.2392074967616</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>6.269338301692185e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8814009762837013</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>153.128</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7481190518066875</v>
+      </c>
+      <c r="D30" t="n">
+        <v>366.9710401942912</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.10192577210962</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.17208e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.816</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.0347117543051103</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1886290392761678</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.150009958138461</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.784617603478775</v>
+      </c>
+      <c r="L30" t="n">
+        <v>31.75053460318937</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.11077642405689</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14.70929904195229</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8037.031378340022</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>142.9133812711353</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>6.054268481942603e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8849298881465186</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>151.991</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7425641476617614</v>
+      </c>
+      <c r="D31" t="n">
+        <v>404.9511613765343</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.215970941277198</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.17053e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-77.97199999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1947439123320832</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.552344498660277</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.264832899068977</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.251803367504654</v>
+      </c>
+      <c r="L31" t="n">
+        <v>38.65799346646835</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.25853183561949</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>15.29194246146117</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8291.427047402467</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>98.40913603165963</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.899836276904541e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8847337800179376</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>149.975</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7327148189404152</v>
+      </c>
+      <c r="D32" t="n">
+        <v>365.2469915445549</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.096748868671928</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.16953e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-78.111</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.06022194818207346</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4863690710485205</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.420237270551522</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.229680908051382</v>
+      </c>
+      <c r="L32" t="n">
+        <v>39.82159364052011</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.29610157160081</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>15.44749275968521</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-8296.650322649351</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>135.5089098159176</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>5.663009758989823e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.889901826217492</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>146.2569999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7145502335307105</v>
+      </c>
+      <c r="D33" t="n">
+        <v>355.030200382946</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.066070302092729</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.16839e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-78.25</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1309157165111011</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.6414333786593798</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.371880245353843</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.355753039203926</v>
+      </c>
+      <c r="L33" t="n">
+        <v>40.67715977940261</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.34556247412981</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>15.65714622017713</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-8334.538598439181</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>141.7022465247036</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>5.832578499962812e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8912410472249038</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>147.52</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7207207207207208</v>
+      </c>
+      <c r="D34" t="n">
+        <v>386.5370120516294</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.160677679711259</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5.16651e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-78.372</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5461594089392623</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.5893925544402342</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.359832687388742</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.384702482976529</v>
+      </c>
+      <c r="L34" t="n">
+        <v>37.79114712261118</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.585848616647</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>16.76198348291727</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-8876.970806251993</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>104.5847558314836</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>5.136520999938164e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8865342650504305</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>144.762</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7072462918449902</v>
+      </c>
+      <c r="D35" t="n">
+        <v>380.2100530506711</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.141679343552238</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.16679e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-78.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3809619793428616</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9402104195210098</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.696242951974511</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.651337386673217</v>
+      </c>
+      <c r="L35" t="n">
+        <v>56.81998852543433</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.52793233680912</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>16.48171443191585</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-8637.506802509266</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>105.7573635614998</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.865615713464103e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8918869719684813</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6830040452600106</v>
+      </c>
+      <c r="D36" t="n">
+        <v>375.3800280398298</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.127175940132278</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.16595e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-78.61499999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2204231327090239</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7173105553115798</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.082566153931102</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.010475568240903</v>
+      </c>
+      <c r="L36" t="n">
+        <v>35.49957492604278</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.31645639209577</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>15.53309137840044</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-8033.735733587318</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>107.1930919853709</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.887624187810668e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8929718632103733</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>138.576</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6770240956791933</v>
+      </c>
+      <c r="D37" t="n">
+        <v>411.7915779642389</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.236511067075591</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5.16497e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-78.729</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1734043090905769</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.6431014296704793</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.364292639675652</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.284857464935117</v>
+      </c>
+      <c r="L37" t="n">
+        <v>39.69687123002108</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.39821187978181</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>15.88663313036996</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-8154.107755845103</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>65.43123283614408</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.23095565099949e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8891324480553866</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>136.36</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6661976510132692</v>
+      </c>
+      <c r="D38" t="n">
+        <v>367.7910198302857</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.104387973740106</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5.16677e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-78.84099999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1023786923017589</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.5201476579457887</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.476600907347289</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.99587827967409</v>
+      </c>
+      <c r="L38" t="n">
+        <v>40.23086948456863</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.42057155683021</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>15.98613355001057</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-8133.899800027616</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>106.6031485407682</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.97938461285699e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8926286522661564</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>136.257</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6656944363018115</v>
+      </c>
+      <c r="D39" t="n">
+        <v>415.4012112236608</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.247349927587078</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5.16473e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-78.952</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3572676105965167</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7560890507750961</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.564623957796175</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.57863812318887</v>
+      </c>
+      <c r="L39" t="n">
+        <v>52.53009133940348</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.58516089805744</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>16.75859976177421</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-8471.952024295244</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>78.53894212244809</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.850502738646332e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.790534747744792</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>134.044</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6548826483750561</v>
+      </c>
+      <c r="D40" t="n">
+        <v>333.8276888130184</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.002404259344544</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5.16867e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-79.07299999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2099367862275081</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8880466162554762</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.51531017510031</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.495265419909244</v>
+      </c>
+      <c r="L40" t="n">
+        <v>46.63374388710874</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.54973313037206</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>16.58611008233738</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-8294.412934411406</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>132.1394400731704</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>5.234154284672732e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.901170161063104</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>129.803</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6341629047702799</v>
+      </c>
+      <c r="D41" t="n">
+        <v>467.0374295778074</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.402401072082264</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5.16924e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-79.17700000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0136815459439828</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5536990957905706</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.51414977389177</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.532969187758172</v>
+      </c>
+      <c r="L41" t="n">
+        <v>54.16953460278455</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.39231169106921</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>15.8605827269193</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-7830.255058443121</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>23.12892322752857</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.449353073360224e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.7537757322678628</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>130.119</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6357067479627133</v>
+      </c>
+      <c r="D42" t="n">
+        <v>360.079115643257</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.081230980285723</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5.16894e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-79.301</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3635656862472216</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8332025941300015</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.27405768837931</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.377995221933312</v>
+      </c>
+      <c r="L42" t="n">
+        <v>49.28280867385168</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.61496854372024</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>16.9065198492662</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-8297.645628534912</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>119.6879432405711</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.266384180022669e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.7941595694737776</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>126.468</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6178694963944419</v>
+      </c>
+      <c r="D43" t="n">
+        <v>356.1223834070836</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.069349865029141</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5.17013e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-79.40300000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1041033060454829</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5901341396294604</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.32611772515657</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.970034417693592</v>
+      </c>
+      <c r="L43" t="n">
+        <v>39.4832497715412</v>
+      </c>
+      <c r="M43" t="n">
+        <v>86.50872653162848</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>16.39082409335788</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7948.453721050384</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>119.3616963016755</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.262534013321325e-08</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.795188307249609</v>
       </c>
     </row>
   </sheetData>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3789,6 +5525,1182 @@
       </c>
       <c r="AD22" t="n">
         <v>0.9004620741576727</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>210.712</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>341.6979188593349</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.25343e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-74.611</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2720457344516437</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5572529293546007</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.099907237109436</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.045591311831987</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.12159672972395</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.39536472822121</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.41626554165463</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7840.929782597527</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>224.8295300798852</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.226362303369192e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8910256367845035</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>183.956</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.873020995481985</v>
+      </c>
+      <c r="D24" t="n">
+        <v>363.6497547221265</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.064243399363016</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.20708e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.012</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2268987737245975</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6368823274303759</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.268729063557225</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.197811681729848</v>
+      </c>
+      <c r="L24" t="n">
+        <v>30.24769433494263</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.74484201939345</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.44025355411804</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-8066.219127042916</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>191.0133012066292</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.905520432140107e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8754645405653402</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>180.083</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8546404571168231</v>
+      </c>
+      <c r="D25" t="n">
+        <v>387.0542433685881</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.132738076546275</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.178079999999999e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.523</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3630593732499043</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9972396494370659</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.575740765283397</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.361346673380483</v>
+      </c>
+      <c r="L25" t="n">
+        <v>33.66970051690188</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.21932323919701</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.1328988631492</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8984.526394492013</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>159.9096871759979</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>6.912902421749697e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8751243143808325</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>172.3580000000001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.817979042484529</v>
+      </c>
+      <c r="D26" t="n">
+        <v>393.2590386044641</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.150896791871756</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.15806e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-76.84699999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.04427324000057926</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4288234263283882</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.088016781281365</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.048388617719314</v>
+      </c>
+      <c r="L26" t="n">
+        <v>32.7164915695606</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.94346905743005</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.10072163318455</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8216.205625040062</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>146.898476784162</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.370403006032022e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8771097177957955</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>170.711</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8101626865104978</v>
+      </c>
+      <c r="D27" t="n">
+        <v>390.2476932266832</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.142083904196486</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.1463e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-77.111</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1632241141875192</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6023929228274406</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.394722846961592</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.979967496398638</v>
+      </c>
+      <c r="L27" t="n">
+        <v>31.58056057728472</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.2339946905055</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.1920241406363</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-8778.693107569135</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>142.0637608296033</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.750435092777831e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8829233951345242</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>168.984</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8019666654011162</v>
+      </c>
+      <c r="D28" t="n">
+        <v>383.2824838252924</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.121699789992214</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.13615e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-77.367</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5699435146274735</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.011273201742432</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.685503940553962</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.68329661960172</v>
+      </c>
+      <c r="L28" t="n">
+        <v>45.98694219481419</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.51320910630089</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16.41194814785253</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9402.657814577411</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>142.564527343569</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.679722261742771e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8863457807567284</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>165.126</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7836573142488324</v>
+      </c>
+      <c r="D29" t="n">
+        <v>458.7931325398323</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.342686353113849</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.130670000000001e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-77.59399999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3388034996971831</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.996716435955491</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.814657303785136</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.666723339112169</v>
+      </c>
+      <c r="L29" t="n">
+        <v>47.82694045758274</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.55911649603661</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.63145015458909</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9405.307126144156</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>59.02803660977627</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.354464015178583e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.877652969565531</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>156.348</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7419985572724858</v>
+      </c>
+      <c r="D30" t="n">
+        <v>383.7329874695934</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.123018216647561</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.1277e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.816</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2366907644341796</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4167899803093619</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.129201596139296</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.943290000706262</v>
+      </c>
+      <c r="L30" t="n">
+        <v>35.19957650124807</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.07449723841991</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14.57293642754102</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8063.108053185894</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>130.3980433726214</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.66070795484045e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8841113566439921</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7370249439993923</v>
+      </c>
+      <c r="D31" t="n">
+        <v>388.2974267404322</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.13637632923448</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.12321e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-77.991</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2206160237111546</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7543313861075586</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.532648826214294</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.682490663789457</v>
+      </c>
+      <c r="L31" t="n">
+        <v>52.62256582177207</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.36674037246492</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>15.7486573898104</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8648.107996158202</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>119.8477807925455</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5.308820471443502e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.886266047014231</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>153.829</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7300438513231331</v>
+      </c>
+      <c r="D32" t="n">
+        <v>444.3917420657357</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.300539797108557</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.12047e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-78.163</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4091694089847748</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5744778662563396</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.549948974767799</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.231253077970798</v>
+      </c>
+      <c r="L32" t="n">
+        <v>41.34519349762449</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.56369146988663</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>16.65364594434083</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-9064.751095793925</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>56.6753550132556</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4.234785720362304e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8817952064412825</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>151.853</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7206661224799727</v>
+      </c>
+      <c r="D33" t="n">
+        <v>386.1374916957523</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.13005514632564</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.11952e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-78.35299999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6372594814608188</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9660936609081548</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.48128779744172</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.827935325292888</v>
+      </c>
+      <c r="L33" t="n">
+        <v>48.61631945073572</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.68660525809</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>17.27288744915598</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-9312.487903245345</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>110.297681648891</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.87472494368755e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.891165036856356</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>148.809</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7062198640798815</v>
+      </c>
+      <c r="D34" t="n">
+        <v>381.7390210001143</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.11718275099376</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5.11746e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-78.512</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.579661632834932</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6343058820088076</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.512314145170923</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.317249196402248</v>
+      </c>
+      <c r="L34" t="n">
+        <v>44.43721378107116</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.622170643838</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>16.9426513207141</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-9025.273366936079</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>110.1488631683879</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.861647875658643e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8921368038671557</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>143.251</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6798426288013971</v>
+      </c>
+      <c r="D35" t="n">
+        <v>451.2434631894565</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.320591780880052</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.11511e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-78.64400000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.09589835926551953</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8394914168343167</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.570705945470442</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.536366543814996</v>
+      </c>
+      <c r="L35" t="n">
+        <v>50.956289445696</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.4417932709521</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>16.08172519812722</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-8441.386468294122</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>33.86162467763149</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.775523952693485e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.885454606201231</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>139.908</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6639773719579332</v>
+      </c>
+      <c r="D36" t="n">
+        <v>427.3617248965816</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.250700403219346</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.11432e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-78.77500000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1115059899106161</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8241650984262513</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.488049813722304</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.285879891882137</v>
+      </c>
+      <c r="L36" t="n">
+        <v>46.01942209834789</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.4416045225037</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>16.08086997576169</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-8347.666635147372</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>53.72914852306968</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.96730562527593e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8890166425849961</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>140.885</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6686140324234026</v>
+      </c>
+      <c r="D37" t="n">
+        <v>442.8690835133963</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.296083643095614</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5.11416e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-78.937</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4647135923414618</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.6639705578297354</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.68547061524846</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.385794665227607</v>
+      </c>
+      <c r="L37" t="n">
+        <v>47.47124749764789</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.72236432383684</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>17.46175350010711</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-9018.367276180579</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>33.02976585294689</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.6646680318347e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8885971133413211</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>134.765</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.63956964956908</v>
+      </c>
+      <c r="D38" t="n">
+        <v>396.6406713053481</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.160793348198972</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5.11313e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-79.042</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3477365262142145</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.5529316491965903</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.204506388140443</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.041631753494221</v>
+      </c>
+      <c r="L38" t="n">
+        <v>42.44051890048005</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.41701922497259</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>15.97024282799256</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-8112.33179844505</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>75.44823366840062</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.181996194230989e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8940987670535485</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>131.494</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6240460913474317</v>
+      </c>
+      <c r="D39" t="n">
+        <v>366.5796940402226</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.072818047191943</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5.11395e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-79.161</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2065324107509542</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5120631779318133</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.252374548146775</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.457918192885649</v>
+      </c>
+      <c r="L39" t="n">
+        <v>56.97753812005433</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.28313144161756</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>15.3934375115313</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-7723.15535826667</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>100.7692414989428</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>4.389025232489526e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8998750556155107</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>129.931</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.616628383765519</v>
+      </c>
+      <c r="D40" t="n">
+        <v>416.9211306037764</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.220145361129367</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5.11415e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-79.30200000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1330858811668914</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4570632257040505</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.092793376310215</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.848939700136615</v>
+      </c>
+      <c r="L40" t="n">
+        <v>40.30521752203354</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.40867727258966</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>15.9330500226619</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-7925.510388842426</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>45.59883408696484</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.748221195700228e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8931764030270641</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>128.692</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6107483199817761</v>
+      </c>
+      <c r="D41" t="n">
+        <v>397.202793076122</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.162438432174463</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5.113180000000001e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-79.41500000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1297665175197009</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5657355249873937</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.344986339498661</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.153225000437606</v>
+      </c>
+      <c r="L41" t="n">
+        <v>46.44978303970057</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.51583409920416</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>16.42434358446329</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-8100.256490752329</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>91.77194030896482</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.983976772289966e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.7636309787707771</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>125.114</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5937677968032194</v>
+      </c>
+      <c r="D42" t="n">
+        <v>396.9955233739875</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.161831844628286</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5.11435e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-79.544</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1017203708429481</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5672137690783452</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.378751875987282</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.549378574614653</v>
+      </c>
+      <c r="L42" t="n">
+        <v>62.86242267236146</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.38509718954566</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>15.82884480380971</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-7709.902032735069</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>93.03111347132511</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.626765849711758e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.7343990254680249</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>125.383</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.595044420820836</v>
+      </c>
+      <c r="D43" t="n">
+        <v>393.297396083376</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.151009047395699</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5.11423e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-79.65600000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1306278689324751</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.632874884593983</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.4767764927858</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.393417089662365</v>
+      </c>
+      <c r="L43" t="n">
+        <v>55.48930023729062</v>
+      </c>
+      <c r="M43" t="n">
+        <v>86.64470537406686</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>17.05670425805519</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-8259.885288528591</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>55.98905151635061</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.687047499124076e-09</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.9004621972677983</v>
       </c>
     </row>
   </sheetData>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4505,6 +7417,566 @@
       </c>
       <c r="AD11" t="n">
         <v>0.92252475723238</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>238.871</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>325.7049731563766</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.87922e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-75.291</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.02101189782293665</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4416031295047559</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.253422903089767</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.829554929011708</v>
+      </c>
+      <c r="L12" t="n">
+        <v>27.53106510200568</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.34901167197907</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.29198442932581</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-8200.373625341748</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>242.1785808988342</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.0568605612986e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9328979490642934</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>173.854</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7278154317602389</v>
+      </c>
+      <c r="D13" t="n">
+        <v>304.1970270758579</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9339649441883335</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.87782e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-77.417</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2022948526187776</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4694093191168597</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.216195771550984</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.026329615081373</v>
+      </c>
+      <c r="L13" t="n">
+        <v>31.413838079155</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.28775760729498</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.41267457729695</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-9107.587728673425</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>237.7114903220558</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.437096324568277e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9005567520160501</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>158.3100000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6627426518916069</v>
+      </c>
+      <c r="D14" t="n">
+        <v>482.954627828173</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.482797831263995</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.84144e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-78.038</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0577051984630322</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6753350119726891</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.462949880787509</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.228208201846877</v>
+      </c>
+      <c r="L14" t="n">
+        <v>38.26377739692784</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.29597584401212</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>15.44696695383032</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8814.495803533346</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>42.75314916788184</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.750906368241167e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8816567695562842</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>154.839</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6482117963252131</v>
+      </c>
+      <c r="D15" t="n">
+        <v>446.709143098156</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.37151465256775</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.81253e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-78.372</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2463898255991757</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9327750449122383</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.58182927075096</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.348649979974319</v>
+      </c>
+      <c r="L15" t="n">
+        <v>36.85928415814359</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.61836106409478</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16.92352028285748</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-9534.062981448962</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>72.57093426314468</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.21130179896689e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8834008086826522</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>147.86</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6189951898723578</v>
+      </c>
+      <c r="D16" t="n">
+        <v>368.9668498255512</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.132825348811619</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.79014e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-78.628</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.07711677239394175</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.3715025133735476</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.273188192489151</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.099177526153221</v>
+      </c>
+      <c r="L16" t="n">
+        <v>38.39836110295906</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.41644623323495</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.96768259864628</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8820.97147336844</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>144.8544544199808</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.140868590765824e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8954711303316567</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>144.188</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6036228759455939</v>
+      </c>
+      <c r="D17" t="n">
+        <v>371.2024190474932</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.139689134771892</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.77705e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-78.854</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1261868149208869</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5286105061370348</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.324726675540119</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.196136895677293</v>
+      </c>
+      <c r="L17" t="n">
+        <v>39.55111887077848</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.46781189788122</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.20048960678876</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8822.490523328337</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>135.3112369998083</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.823013576349e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8979351306034531</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>140.3050000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5873672400584418</v>
+      </c>
+      <c r="D18" t="n">
+        <v>287.0887483015436</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8814380250918286</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.76467e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-79.038</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1536918080742441</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5838540321391755</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.284295879553887</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.160212447265749</v>
+      </c>
+      <c r="L18" t="n">
+        <v>40.39249237444132</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.51486193447968</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.41975076668421</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-8812.921887403641</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>214.8042785166869</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>6.641242705775471e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9109186072599155</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5672517802495907</v>
+      </c>
+      <c r="D19" t="n">
+        <v>280.8981827421281</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8624313593371631</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.7574e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-79.248</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.07135794233975419</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8777163556382003</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.005117324541387</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.968314970434821</v>
+      </c>
+      <c r="L19" t="n">
+        <v>38.33821509162608</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.51034475496964</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.39844369081007</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-8660.448950401082</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>213.5984532662007</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.46172908367481e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9144262548162821</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>131.688</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.551293375922569</v>
+      </c>
+      <c r="D20" t="n">
+        <v>416.7549660407801</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.279547444431218</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.74943e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-79.428</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1746615813686714</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5400528925217368</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.180900667657341</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.229148017613615</v>
+      </c>
+      <c r="L20" t="n">
+        <v>39.61458506589467</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.59874183786719</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16.82567386277451</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-8761.127318496148</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>67.32813421914891</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.659839296772036e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.897803684055882</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>128.871</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5395003997973803</v>
+      </c>
+      <c r="D21" t="n">
+        <v>265.4492471235441</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8149990605028231</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.74377e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-79.59099999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1638014264097591</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6202505999003139</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.442115668568622</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.397534574039566</v>
+      </c>
+      <c r="L21" t="n">
+        <v>44.05801338712176</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.70715520511527</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17.38092384372242</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-8935.364647830284</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>214.9768742996576</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.196319133341197e-09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9225247772999374</v>
       </c>
     </row>
   </sheetData>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5837,6 +9309,1182 @@
       </c>
       <c r="AD22" t="n">
         <v>0.7420350641531359</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>204.016</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>339.7673915117572</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.74437e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-77.244</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.01505260537279031</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5655120172916673</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9205681126079864</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.894376023837155</v>
+      </c>
+      <c r="L23" t="n">
+        <v>32.21984490610738</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.09884029082535</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.66415516767532</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-9168.045261675235</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>227.62971714997</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>6.765482074525139e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8973218597833352</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>179.986</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8822151203827152</v>
+      </c>
+      <c r="D24" t="n">
+        <v>545.4437429207192</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.605344587347914</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.76221e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-77.97</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4191208280561057</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8201220516463859</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.525928095295393</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.9048124304223</v>
+      </c>
+      <c r="L24" t="n">
+        <v>36.42205966339107</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.44781561778335</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16.10906020334771</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-9613.249141578946</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>5.090451761353048</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.154361632402995e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8635068304305556</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>170.772</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8370519959218884</v>
+      </c>
+      <c r="D25" t="n">
+        <v>413.9794960654182</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.218420326398783</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.76744e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-78.206</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.148343751965978</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.460859548954253</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.482466634266912</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.299662476454884</v>
+      </c>
+      <c r="L25" t="n">
+        <v>41.90094506884206</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.31932891105522</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.54524737775506</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-9084.445695273291</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>131.6847420848823</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.778710150289327e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8789352768825712</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>168.457</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8257048466786917</v>
+      </c>
+      <c r="D26" t="n">
+        <v>406.6017607657085</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.196706249403685</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.76995e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-78.354</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5705037793441028</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6994848286068229</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.805597269583352</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.26883989469789</v>
+      </c>
+      <c r="L26" t="n">
+        <v>38.7007161889357</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.58067505465303</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.73656181709891</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-9693.609583300173</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>132.7331384905397</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5.695351405186227e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8813365588996349</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>162.661</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7972953101717511</v>
+      </c>
+      <c r="D27" t="n">
+        <v>406.273815992463</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.195741045615922</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.77418e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-78.51900000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.07890459733344735</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5738289258654301</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.510745159853823</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.556603467005759</v>
+      </c>
+      <c r="L27" t="n">
+        <v>49.81846626164151</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.46714595864921</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.19742807996264</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-9243.747570538662</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>125.6010440117387</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.601616685752391e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8798569496078067</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>157.551</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7722482550388203</v>
+      </c>
+      <c r="D28" t="n">
+        <v>399.7025901384902</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.176400679182478</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.77759e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-78.667</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.04213691763952981</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7224552129789302</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.221023638015037</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.186944186748772</v>
+      </c>
+      <c r="L28" t="n">
+        <v>40.61644537722056</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.38348824761646</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.82178401732196</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-8893.081304166308</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>126.2454138186359</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.591008823193338e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8820880148708538</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>154.458</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7570876793976944</v>
+      </c>
+      <c r="D29" t="n">
+        <v>454.5802129485559</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.33791595163371</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.7825e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-78.82599999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.349101888686514</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7620699783851991</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.298825080717362</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.26071803139541</v>
+      </c>
+      <c r="L29" t="n">
+        <v>46.39635713656086</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.46683111339421</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.1959810410846</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-8995.914981161315</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>62.85782621046351</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.318404936688555e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8807108876398066</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>152.2860000000001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7464414555721122</v>
+      </c>
+      <c r="D30" t="n">
+        <v>447.7860395649757</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.317919408253398</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.78731e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-78.97</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4075924077423284</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9835335769783613</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.312075041667175</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.589177724402965</v>
+      </c>
+      <c r="L30" t="n">
+        <v>53.92067172313102</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.58083054750514</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>16.73732475235289</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-9195.303952956219</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>63.21275819828529</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.264236366324386e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8824390453702067</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>147.229</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7216541839855696</v>
+      </c>
+      <c r="D31" t="n">
+        <v>377.5822051909706</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.111296182694168</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.79115e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-79.095</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.5001868411509414</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.286568009590191</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.049070432317442</v>
+      </c>
+      <c r="L31" t="n">
+        <v>43.02720445839577</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.47075669293119</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>16.21404156567568</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8779.878118726641</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>130.2489308556262</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5.411212777996565e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8896215836910858</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>144.8179999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7098364834130653</v>
+      </c>
+      <c r="D32" t="n">
+        <v>364.443028444642</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.072625088661667</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.7943e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-79.22799999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2337142179290277</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5323350461727298</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.237320821564611</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.108321369535186</v>
+      </c>
+      <c r="L32" t="n">
+        <v>43.83966456460248</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.52072046388217</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>16.44746716044814</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-8809.539496702882</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>137.5253713015156</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>5.423682791954497e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8927123748996728</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>143.027</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7010577601756723</v>
+      </c>
+      <c r="D33" t="n">
+        <v>376.6154028300266</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.108450699622227</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.79687e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-79.342</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1592045218196064</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8947502627080933</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.688218308443864</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.712888023685589</v>
+      </c>
+      <c r="L33" t="n">
+        <v>58.79283257010831</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.68044798971583</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>17.24077723915688</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-9158.797661151482</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>119.6276056669041</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>5.017775697294179e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8923761709504064</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>139.073</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6816769272998198</v>
+      </c>
+      <c r="D34" t="n">
+        <v>363.5623564540439</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.070033103637208</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.80072e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-79.452</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1572133842226027</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7072554046623157</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.257823541983323</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.239179019831898</v>
+      </c>
+      <c r="L34" t="n">
+        <v>45.80761059439575</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.59022587957202</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>16.78355249768229</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-8804.542669663162</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>127.6784655278801</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>5.078501443711879e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8951702284522829</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>136.257</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6678740883067994</v>
+      </c>
+      <c r="D35" t="n">
+        <v>449.0170870207647</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.321542614854572</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.80283e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-79.551</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2501873502243586</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.67539835044602</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.382011292104346</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.071594947626012</v>
+      </c>
+      <c r="L35" t="n">
+        <v>41.86916415303664</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.56760377659262</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>16.67267363786399</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-8648.770055613189</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>36.91706038227231</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.884979178744533e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8849941540699663</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>134.838</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.660918751470473</v>
+      </c>
+      <c r="D36" t="n">
+        <v>440.1753553419092</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.29551971830904</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.80562e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-79.65000000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3972886743752359</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7942993864004582</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.482844013892448</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.253182020333484</v>
+      </c>
+      <c r="L36" t="n">
+        <v>47.57070443616836</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.66078674449373</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>17.1390355636008</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-8816.12815654298</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>40.50137619520073</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.755648406632066e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8892991741132735</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>132.256</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6482628813426399</v>
+      </c>
+      <c r="D37" t="n">
+        <v>434.3350075823903</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.278330464998024</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.80718e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-79.752</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4474656213682247</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.6285925599346665</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.480539308420188</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.185479715788673</v>
+      </c>
+      <c r="L37" t="n">
+        <v>47.96414807483092</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.6944385266701</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>17.31391071908502</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-8819.790180277114</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>41.96540858969528</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.717144591561439e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8913861930648297</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>131.183</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6430034899223589</v>
+      </c>
+      <c r="D38" t="n">
+        <v>428.2355587257581</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.260378627920624</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.81131e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-79.858</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4294887429324486</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.07634533454852</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.674459009976527</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.451967401807525</v>
+      </c>
+      <c r="L38" t="n">
+        <v>56.309871010769</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.77865078601783</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>17.76752271114627</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-8974.515075371022</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>43.32440942517029</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.767885052608444e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8910214825866947</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>125.34</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6143635793271117</v>
+      </c>
+      <c r="D39" t="n">
+        <v>422.1333534979912</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.242418678319175</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.81229e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-79.967</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.05588083585556246</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4661930612116028</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.16929152529535</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.149914982014107</v>
+      </c>
+      <c r="L39" t="n">
+        <v>44.78677304149863</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.42938387225493</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>16.02569019930992</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-7959.370109641308</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>44.42855496384536</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.670666051254952e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8933290900848907</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>125.903</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6171231668104463</v>
+      </c>
+      <c r="D40" t="n">
+        <v>417.4664820477009</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.228683188784627</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.81515e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-80.075</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.09746330265341825</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6404602328060932</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.434250629492077</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.266192964293286</v>
+      </c>
+      <c r="L40" t="n">
+        <v>45.40427527818315</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.69524674808844</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>17.3181544759351</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-8556.044908255617</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>44.9376489790598</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.653886942361388e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8950390226704255</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>124.379</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6096531644576896</v>
+      </c>
+      <c r="D41" t="n">
+        <v>412.6612349702912</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.214540433483628</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.8177e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-80.164</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.469219301124402</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8706687167730299</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.612526565466324</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.318028826892607</v>
+      </c>
+      <c r="L41" t="n">
+        <v>52.42411698485977</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.8068756115899</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>17.92490429093083</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-8782.753613832576</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>45.2562653823698</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.5918961981375e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8976405750522507</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>121.612</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5960905027056702</v>
+      </c>
+      <c r="D42" t="n">
+        <v>423.788533881223</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.247290188724771</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.82033e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-80.258</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2156900627528445</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6784744603553857</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.573425921757229</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.255773469270133</v>
+      </c>
+      <c r="L42" t="n">
+        <v>47.30255336691628</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.76109712077206</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>17.67102547793088</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-8563.080911208064</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>29.40586241969301</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.362962966298479e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8978746927360731</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>118.135</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5790477217473138</v>
+      </c>
+      <c r="D43" t="n">
+        <v>420.0459190327686</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.23627496200804</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.82364e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-80.37</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1124222209022626</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8083180241574842</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.223807543020327</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.272915579511114</v>
+      </c>
+      <c r="L43" t="n">
+        <v>54.43464134455436</v>
+      </c>
+      <c r="M43" t="n">
+        <v>86.58442362075313</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>16.754973712901</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-8009.531316887551</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>63.4287671630544</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.608570330841947e-08</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.7420350236077491</v>
       </c>
     </row>
   </sheetData>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6553,6 +11201,566 @@
       </c>
       <c r="AD11" t="n">
         <v>0.8924075463604643</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>253.4470000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>323.6832933532662</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.01385e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-73.41</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2296364909577347</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6078580228780426</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.237907571267598</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.994196354650042</v>
+      </c>
+      <c r="L12" t="n">
+        <v>19.43486932483385</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.66028256898839</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.69903129580252</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-7302.501598697563</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>252.1795256643442</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.500190411904655e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9255377308356948</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>172.7979999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6817914593583665</v>
+      </c>
+      <c r="D13" t="n">
+        <v>313.5667765536845</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9687456318959886</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.09218e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-76.122</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1196414127941215</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4622787949355223</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.242468645785527</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.195021400136893</v>
+      </c>
+      <c r="L13" t="n">
+        <v>25.67780053149538</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.72490414119909</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.37734026843357</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7870.419776766567</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>230.7277942078681</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.272026085956584e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8894968520962707</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>155.4710000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6134260811925176</v>
+      </c>
+      <c r="D14" t="n">
+        <v>312.26748257082</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9647315415504406</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.06645e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-76.93000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.01821994632035714</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5148373473266725</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.210613048401513</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.215830137990695</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29.68309063632618</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.87143116814934</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.8538518408697</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7842.511579781059</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>219.9569518310108</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.36215672633458e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8871616101566138</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>151.967</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5996007054729391</v>
+      </c>
+      <c r="D15" t="n">
+        <v>457.0052091682127</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.411890012715113</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.03645e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-77.367</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5804019335958471</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9604235352681583</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.774213394500634</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.864324209810041</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35.39999241015119</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.31820763514392</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.54050007974514</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8701.709860191064</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>62.85771194006414</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.417973424885522e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8765964720471099</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>144.878</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5716303605882098</v>
+      </c>
+      <c r="D16" t="n">
+        <v>317.9203143559882</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9821956241930958</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.01405e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-77.703</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.03819542857774064</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4234819453490309</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.377441073075244</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.334803817236031</v>
+      </c>
+      <c r="L16" t="n">
+        <v>35.111375705028</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.13165010017671</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.78891432840433</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8118.921871447685</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>199.7382843361201</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.627809981544667e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8892077086344362</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>143.576</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5664931918704896</v>
+      </c>
+      <c r="D17" t="n">
+        <v>310.1760860919221</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9582702983480756</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.99915e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-77.97499999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3275613662899805</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8520832758368463</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.642845625566081</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.61153887048145</v>
+      </c>
+      <c r="L17" t="n">
+        <v>36.7660282514116</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.44123434496925</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.07919295827195</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8744.574638608035</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>200.1257964697823</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.266994050244653e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8943795200699068</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>136.6940000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5393395857911123</v>
+      </c>
+      <c r="D18" t="n">
+        <v>360.4599905139353</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.113619386344204</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.98705e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-78.23399999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1454714267210942</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4344866750626167</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.386862764621114</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.537356485466336</v>
+      </c>
+      <c r="L18" t="n">
+        <v>38.77301488179385</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.2910225375736</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15.42628003873508</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-8232.455344380274</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>140.2921059291924</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.322910733349516e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8929410355136588</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>135.736</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5355597028175514</v>
+      </c>
+      <c r="D19" t="n">
+        <v>367.9301358934236</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.13669794965867</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.97863e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-78.468</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2193189354326349</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7878455389818217</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.592082700881537</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.377560165337948</v>
+      </c>
+      <c r="L19" t="n">
+        <v>37.22386935567619</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.53411292493462</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.51117767689291</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-8721.625051795854</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>126.1254885601283</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.015497005153904e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.893547794083649</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>130.203</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5137287085662878</v>
+      </c>
+      <c r="D20" t="n">
+        <v>460.455096822582</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.422548232416938</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.97235e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-78.67400000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6777930583759516</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.52332071310645</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.611409048472506</v>
+      </c>
+      <c r="L20" t="n">
+        <v>42.25804798728812</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.42366930959109</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16.00001652722441</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-8311.733703603248</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>25.92257639795785</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.611270798175282e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8845671013620756</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>127.462</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.50291382419204</v>
+      </c>
+      <c r="D21" t="n">
+        <v>402.0098531626217</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.241985179395312</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.96745e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-78.842</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.04852635772667459</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.834430825924802</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.519708120697412</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.598031221256627</v>
+      </c>
+      <c r="L21" t="n">
+        <v>43.38457532545906</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.47190368232026</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>16.21932612958744</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-8319.005571557913</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>78.72977514248063</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.152594842544937e-09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8924075676162064</v>
       </c>
     </row>
   </sheetData>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7885,6 +13093,1182 @@
       </c>
       <c r="AD22" t="n">
         <v>0.9301641275216251</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>204.199</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>333.7383608644214</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.0472e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-76.01000000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3156890011984848</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9728509092516643</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.440676296746729</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.28495963732162</v>
+      </c>
+      <c r="L23" t="n">
+        <v>33.2889442957073</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.0328193529928</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.41935528366756</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-8998.037819848139</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>227.8923895345061</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.174809964956378e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8949663816539296</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>176.8770000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8661991488694857</v>
+      </c>
+      <c r="D24" t="n">
+        <v>387.5551377991939</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.161254393397812</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.04653e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.874</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.02214201925966368</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0463356729108244</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.104321058262383</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.864130830717049</v>
+      </c>
+      <c r="L24" t="n">
+        <v>29.97586878660229</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.86164679763669</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.8209831805811</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-8186.697565978709</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>160.9870642212932</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.711205824871637e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.877200865836673</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>173.34</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8488778103712559</v>
+      </c>
+      <c r="D25" t="n">
+        <v>400.9949052429997</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.201524763903005</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.03772e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-77.217</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3550266579802111</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6614387944018605</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.715182553696835</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.511868491765958</v>
+      </c>
+      <c r="L25" t="n">
+        <v>43.59092517424479</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.19508813400053</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.03622972663297</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8805.342610140771</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>141.1293827993325</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>6.334023530058953e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8754537716249041</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>170.826</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8365662907262034</v>
+      </c>
+      <c r="D26" t="n">
+        <v>392.2677956072337</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.175375208864855</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.02732e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-77.474</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2483070555288152</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5682759174516346</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.539298469417475</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.192189168530405</v>
+      </c>
+      <c r="L26" t="n">
+        <v>36.54324884832494</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.40674426826317</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.92445628612504</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-9242.403888453009</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>143.3482890806727</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.117990287798686e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8794014118903722</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>163.6229999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8012918770415133</v>
+      </c>
+      <c r="D27" t="n">
+        <v>383.3607684871413</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.1486865564216</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.01979e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-77.679</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4928887963228729</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.244973010066469</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.073670120981036</v>
+      </c>
+      <c r="L27" t="n">
+        <v>37.46227441948036</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.14080493960067</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14.82410352147485</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-8456.181561102536</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>145.5312537347509</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5.871511624042273e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8840918210820785</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>163.093</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7986963697177756</v>
+      </c>
+      <c r="D28" t="n">
+        <v>387.6260568424495</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.161466892323833</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.01564e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-77.88200000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2097552089747126</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6296495062564023</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.273188133789445</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.014345571950383</v>
+      </c>
+      <c r="L28" t="n">
+        <v>35.25798837604948</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.40851752037459</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.93233944722353</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9008.676530055445</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>134.3056969287446</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.606490240188069e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8848034966660651</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>159.327</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7802535761683458</v>
+      </c>
+      <c r="D29" t="n">
+        <v>455.9314294807543</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.366134322407045</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.01307e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-78.09</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3753911060973607</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7870533273630415</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.268733421460517</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.973124901537699</v>
+      </c>
+      <c r="L29" t="n">
+        <v>35.83401562066882</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.43720129708646</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.06094456924136</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-8959.763870917552</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>57.65115229916918</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.211155008352932e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8805665506616956</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>153.55</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7519625463396004</v>
+      </c>
+      <c r="D30" t="n">
+        <v>397.0440513982285</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.189686586731708</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.01034e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-78.264</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6091395131324647</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.266061034339221</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.338117364586335</v>
+      </c>
+      <c r="L30" t="n">
+        <v>40.54930417069688</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.28508447384245</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>15.40155300398406</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8452.194266275221</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>110.7907705044067</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.797901020649383e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8901034637515034</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>149.8440000000001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7338135838079525</v>
+      </c>
+      <c r="D31" t="n">
+        <v>429.3531806957795</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.286496342774935</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.01037e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-78.43000000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.176602634423757</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6449775118365028</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.327372377665214</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.236264268371305</v>
+      </c>
+      <c r="L31" t="n">
+        <v>41.98405620538085</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.32324995252912</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>15.56187115866207</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8434.849136262545</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>72.71743914145695</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.262838451441043e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8868177457776283</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>147.658</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7231083403934397</v>
+      </c>
+      <c r="D32" t="n">
+        <v>458.4267345226313</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.373611152566497</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.00963e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-78.592</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2844212176971112</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8095565444205075</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.655394521131121</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.718188531627082</v>
+      </c>
+      <c r="L32" t="n">
+        <v>58.51830501035592</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.48826426941312</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>16.2950801501264</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-8755.166632520941</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>37.62738841525666</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.793639736104032e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8849400528368321</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>146.007</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7150230902208142</v>
+      </c>
+      <c r="D33" t="n">
+        <v>456.3851974000868</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.367493974075967</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.00917e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-78.74299999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5619376580030427</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.016750498543238</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.291088286448895</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.943797504102452</v>
+      </c>
+      <c r="L33" t="n">
+        <v>39.39722636911133</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.602996634245</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>16.84679782633566</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-8967.316715429122</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>33.96914128174099</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.709305837328845e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8852088334534824</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>143.929</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7048467426383087</v>
+      </c>
+      <c r="D34" t="n">
+        <v>488.2350551226262</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.462927587521076</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5.00883e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-78.86799999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.611085245803213</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8730512035771731</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.503027664106958</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.355345401316339</v>
+      </c>
+      <c r="L34" t="n">
+        <v>45.29807484081643</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.71849331651104</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>17.44110982551321</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-9203.161180044854</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.09983599959110891</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.815398138985539e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8746636193992441</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>137.064</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6712275770204558</v>
+      </c>
+      <c r="D35" t="n">
+        <v>434.2217547232589</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.301084339236801</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.00936e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-78.985</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1066815669347174</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4700025549762662</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.35588318446967</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.572368269561976</v>
+      </c>
+      <c r="L35" t="n">
+        <v>53.05740581592509</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.29088641881872</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>15.4257123333504</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-7986.190497144417</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>46.80120308276325</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.741258648928313e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8903698164404517</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>136.907</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6704587191905939</v>
+      </c>
+      <c r="D36" t="n">
+        <v>472.2271924731223</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.414962281381135</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.00865e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-79.127</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1116475298980408</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6689203519740471</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.267260897898485</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.449199406064877</v>
+      </c>
+      <c r="L36" t="n">
+        <v>47.38617085675396</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.50371673617262</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>16.36727953793667</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-8419.750097659613</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>38.74187877525371</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.10402156217653e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.7393170396286174</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>133.383</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6532010440795502</v>
+      </c>
+      <c r="D37" t="n">
+        <v>430.4652881634638</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.289828616190564</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5.00941e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-79.258</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3003178330651026</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5285805268159798</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.239202668190281</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.117464031181024</v>
+      </c>
+      <c r="L37" t="n">
+        <v>43.47005633813728</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.42903280883154</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>16.02411061962765</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-8153.537225727913</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>41.58779412051921</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.619818882363888e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8925317037144216</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>132.185</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.647334218091176</v>
+      </c>
+      <c r="D38" t="n">
+        <v>408.415484254263</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.223759483915541</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5.0099e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-79.361</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2558097757365806</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6016751344865271</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.289778889475759</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.396437244033414</v>
+      </c>
+      <c r="L38" t="n">
+        <v>48.83467347061132</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.54830245463963</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>16.57921874263133</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-8367.410371941982</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>59.42578592663762</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.750722453399486e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8968471932599683</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6412372244722062</v>
+      </c>
+      <c r="D39" t="n">
+        <v>408.7009244287902</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.22461476520172</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5.01015e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-79.467</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3584431059084465</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5862267431410932</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.682633211736147</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.306320364720206</v>
+      </c>
+      <c r="L39" t="n">
+        <v>50.56519977932982</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.58297226724598</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>16.74784028843795</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-8372.141872889877</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>54.45780556621189</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.673828985799426e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.896830286597542</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>130.161</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6374223184246741</v>
+      </c>
+      <c r="D40" t="n">
+        <v>377.3320222364162</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.130622267272729</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5.01147e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-79.596</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3455968090130529</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9200174715224405</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.767535232060372</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.956776949068001</v>
+      </c>
+      <c r="L40" t="n">
+        <v>73.33580906515812</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.7682580854036</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>17.7102647732459</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-8793.046607036911</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>81.90681925676233</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.970664117041469e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9027577359702366</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>126.241</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6182253585962716</v>
+      </c>
+      <c r="D41" t="n">
+        <v>395.8857757989766</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.186215977011411</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5.01156e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-79.693</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.291152056682672</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5552695067037131</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.10456850307801</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.046627014585496</v>
+      </c>
+      <c r="L41" t="n">
+        <v>41.55609873971334</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.51465982914073</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>16.41879627757448</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-8030.453118528411</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>87.26922213222399</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.22853803538781e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.7832101144408083</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>123.382</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6042243105989746</v>
+      </c>
+      <c r="D42" t="n">
+        <v>451.1148506520688</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.351702122236199</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5.01346e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-79.821</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2506710809223208</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6470678688594389</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.296146435994859</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.334365415937509</v>
+      </c>
+      <c r="L42" t="n">
+        <v>48.09008211628271</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.54094038033493</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>16.54384682346692</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-8010.58018495128</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.04967709830088678</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.481363870285527e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8860227373724798</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>120.958</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5923535374805949</v>
+      </c>
+      <c r="D43" t="n">
+        <v>242.6668837434536</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7271171438456101</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5.014219999999999e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-79.92</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.139314831897184</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5807451093120736</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.328568527433865</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.608520608892389</v>
+      </c>
+      <c r="L43" t="n">
+        <v>66.17594065249892</v>
+      </c>
+      <c r="M43" t="n">
+        <v>86.47140388244671</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>16.21702296251223</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7761.130699727893</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>206.0151819898355</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>6.302845122770817e-09</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.9301641327239726</v>
       </c>
     </row>
   </sheetData>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8601,6 +14985,566 @@
       </c>
       <c r="AD11" t="n">
         <v>0.9168531593108472</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>236.601</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>314.2880750676807</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.34048e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-72.634</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.09775238428660177</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7116576783443902</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.141752670121127</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.074780039713136</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16.46094679366934</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.29324554001242</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.0067712903218</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6504.174744469757</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>239.3090178209063</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.330900965159795e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9325419929460405</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>170.455</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7204322889590494</v>
+      </c>
+      <c r="D13" t="n">
+        <v>307.6917798475012</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9790119455892209</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.40305e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-75.205</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1869081556360942</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5929183646290123</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.317257733989801</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.138832426653552</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.27450315542455</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.31756945895513</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.20907962130819</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7000.486509476255</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>220.2713064375686</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.998866396504864e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8920745180675131</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>158.9570000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6718357065270225</v>
+      </c>
+      <c r="D14" t="n">
+        <v>300.2928279715659</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9554700028211347</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.35659e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-76.13800000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3500517204795259</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6996287674581835</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.422923069521878</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.881800688283531</v>
+      </c>
+      <c r="L14" t="n">
+        <v>22.62407950232632</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.85794459005777</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.80858676961539</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7709.912167855524</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>220.9215901461214</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.908621196519139e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8809801698427002</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>153.12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6471654811264534</v>
+      </c>
+      <c r="D15" t="n">
+        <v>290.2884542971939</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9236381438738376</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.30925e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-76.696</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3216325080779491</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7262974791148866</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.385765969599639</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.893332204520736</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.07318979280419</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.08631888573478</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.61709321768788</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8039.545069267796</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>222.867691458066</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.946109092832398e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8913342301674744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>150.159</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6346507411211282</v>
+      </c>
+      <c r="D16" t="n">
+        <v>282.3453017022407</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8983646663699816</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.27303e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-77.13800000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4231827061669897</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8664650559238887</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.687802618607475</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.296423059158386</v>
+      </c>
+      <c r="L16" t="n">
+        <v>31.16312837963968</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.35350537499718</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.69134364300223</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8539.226460839292</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>224.7749314090922</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.036368531952542e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8934104787618273</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>143.3390000000001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6058258418180822</v>
+      </c>
+      <c r="D17" t="n">
+        <v>275.8369422682491</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.877656405540836</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.2461e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-77.485</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0664872769086889</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.709396899447529</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.382848833060945</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.269400803864906</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31.25696630349663</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.15776587493271</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14.88974008794271</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-7943.922326265613</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>223.053513727177</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.00966189747138e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9028878946488863</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>139.069</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5877785808174945</v>
+      </c>
+      <c r="D18" t="n">
+        <v>270.6415627922646</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8611257768338265</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5.22457e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-77.798</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1435917165607309</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4676814026646209</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.233637622650582</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.209853001165882</v>
+      </c>
+      <c r="L18" t="n">
+        <v>30.80413627735696</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.20263531704791</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15.0662018737184</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-7915.94553489768</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>223.231113745769</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.76987585486621e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8989800166137683</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>137.652</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5817895951411872</v>
+      </c>
+      <c r="D19" t="n">
+        <v>263.4319516075745</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8381862771944034</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.20873e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-78.066</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4863849597300345</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9677087449909394</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.688766180024898</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.737051272546963</v>
+      </c>
+      <c r="L19" t="n">
+        <v>41.67158222566452</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.42234109702723</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.99406103152172</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-8313.244926148809</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>221.1800412600217</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.482622162022436e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9105021321915807</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>130.743</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.552588535128761</v>
+      </c>
+      <c r="D20" t="n">
+        <v>257.7315694622065</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8200488338817977</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.19572e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-78.333</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1335765861552119</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5004093939842404</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.321593093252602</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.404818545583855</v>
+      </c>
+      <c r="L20" t="n">
+        <v>39.86063127368432</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.21017767957491</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15.0962739628319</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-7692.415457396745</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>221.341295233972</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.841005734167045e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9101093783175064</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>127.131</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5373223274626905</v>
+      </c>
+      <c r="D21" t="n">
+        <v>253.5332866608391</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8066907616722069</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.18468e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-78.536</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1382706410385759</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5814090568774418</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.1379818766144</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.238769490497187</v>
+      </c>
+      <c r="L21" t="n">
+        <v>37.62158200193963</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.23391246743091</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.19169150364622</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-7635.581378916412</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>219.3865848151568</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.313059073461233e-09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.916853160596305</v>
       </c>
     </row>
   </sheetData>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9933,6 +16877,1182 @@
       </c>
       <c r="AD22" t="n">
         <v>0.9008264610054592</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>204.609</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>333.7421794098832</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.190239999999999e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-75.535</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4341269836425922</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8770698217291029</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.611166485128293</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.726171321750026</v>
+      </c>
+      <c r="L23" t="n">
+        <v>34.44217657680806</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.95011125627252</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.12392554478492</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-8799.58696258668</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>227.2043131232952</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.415790427308462e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8922093913877586</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>180.717</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8832309429203994</v>
+      </c>
+      <c r="D24" t="n">
+        <v>406.645966932743</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.218443433346564</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.19621e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.41800000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4074856843798806</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8052893662019398</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.505632555887814</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.1830183106778</v>
+      </c>
+      <c r="L24" t="n">
+        <v>29.96617566480117</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.09480031582621</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.64893791468135</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-8712.20771579061</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>139.8248299101751</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.131394480100796e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8761863025301915</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>172.316</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8421721429653635</v>
+      </c>
+      <c r="D25" t="n">
+        <v>397.8591614596535</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.192115309377858</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.18674e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.767</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2029816572770876</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7437107576065481</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.363498654623129</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.59964229186243</v>
+      </c>
+      <c r="L25" t="n">
+        <v>39.29648469481174</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.05397946992426</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.49692457470197</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8459.159807644928</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>141.3948503124371</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.936200339332325e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8804858817833203</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>169.34</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8276273282211437</v>
+      </c>
+      <c r="D26" t="n">
+        <v>530.7557444438736</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.590316649164172</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.17863e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-77.03700000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4437706076916083</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6937116245526209</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.45484924561656</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.879215365227958</v>
+      </c>
+      <c r="L26" t="n">
+        <v>30.44454441905067</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.20353949558503</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.06980062195727</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8694.053340036593</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.205147383560811</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.204859647325554e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8627178039481953</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>167.161</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8169777478019051</v>
+      </c>
+      <c r="D27" t="n">
+        <v>517.3194277707649</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.550057079046705</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.17232e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-77.259</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4189759137374952</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.222558228199021</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.616154031586944</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.675854820872656</v>
+      </c>
+      <c r="L27" t="n">
+        <v>43.52718987594187</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.46264421811694</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.1767623945453</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-9257.356887068769</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>7.418662130836812</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.010208331381286e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8682981579817073</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>158.897</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7765885176116398</v>
+      </c>
+      <c r="D28" t="n">
+        <v>396.6151359336719</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.188387804726869</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.16748e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-77.473</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2287810479190225</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2909553693014067</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.194053249113096</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.881690882143863</v>
+      </c>
+      <c r="L28" t="n">
+        <v>32.24413141500663</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.98322467867695</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14.24074725219623</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-7971.611483143056</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>123.5819518491335</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.580690799047449e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8813409613014896</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>155.76</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7612568362095512</v>
+      </c>
+      <c r="D29" t="n">
+        <v>389.3984397813338</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.166764238400615</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.16463e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-77.65900000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.09326881776994167</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.535237754985895</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.312222876269708</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.138215954275574</v>
+      </c>
+      <c r="L29" t="n">
+        <v>36.09636256477265</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.10727891488591</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14.69604241525118</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-8138.293414799076</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>124.757452678464</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>5.540033973945719e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8830618083046421</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>153.4829999999999</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7501282934768263</v>
+      </c>
+      <c r="D30" t="n">
+        <v>444.8348879999961</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.332869848176053</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.162660000000001e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.81100000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3206300146548778</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6425562784706809</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.402216861111815</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.392039409126843</v>
+      </c>
+      <c r="L30" t="n">
+        <v>41.39457995254021</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.24132441411275</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>15.22173524286035</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8346.133023764758</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>61.77698254469293</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.277483822442116e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8818519893888688</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>152.814</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7468586425817048</v>
+      </c>
+      <c r="D31" t="n">
+        <v>376.5265656188095</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.128195921428262</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.16143e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-77.982</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4704757754081003</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9385174736945442</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.741258981043794</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.367071551321134</v>
+      </c>
+      <c r="L31" t="n">
+        <v>42.7925121795191</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.57823194614255</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>16.72458364745453</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-9121.422450275631</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>127.0033199933496</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5.512282369337972e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8865535176475393</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>147.194</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7193916201144623</v>
+      </c>
+      <c r="D32" t="n">
+        <v>358.3160326345661</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.073631248133316</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.16208e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-78.142</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.06426427450631776</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.6147806978838863</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.304585700646849</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.263897460490561</v>
+      </c>
+      <c r="L32" t="n">
+        <v>39.61757183780524</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.23403615487635</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>15.19219189203606</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-8143.608376541447</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>141.1282295936746</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>5.637328373294426e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8923681419669789</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>144.9469999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7084096984981109</v>
+      </c>
+      <c r="D33" t="n">
+        <v>393.251124107029</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.178308132350452</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.15941e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-78.27</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3100808111512414</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7215574700022934</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.399708717458724</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.068831105715564</v>
+      </c>
+      <c r="L33" t="n">
+        <v>39.81076461623734</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.27555474661604</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>15.36203429133054</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-8155.639213459578</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>99.59047323973897</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.696999101536326e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8907493327725793</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>145.48</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7110146669990081</v>
+      </c>
+      <c r="D34" t="n">
+        <v>424.5483651997986</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.272084834918011</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5.16025e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-78.407</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.277881510382923</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8456813308983667</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.465722789624584</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.307784678470119</v>
+      </c>
+      <c r="L34" t="n">
+        <v>41.08126219608315</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.6140664492259</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>16.90200504411962</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-8934.495273070197</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>63.07397179061735</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.27359698217387e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8849313545254478</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>140.832</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6882981687022566</v>
+      </c>
+      <c r="D35" t="n">
+        <v>377.5184782903183</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.131168014057556</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.16003e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-78.548</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3793314305432402</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.7224578856322497</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.407974108401417</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.440022047394597</v>
+      </c>
+      <c r="L35" t="n">
+        <v>47.52595568656245</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.41195667456248</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>15.94765071620184</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-8314.579168769402</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>106.7119085090865</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.963138603268788e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8905431226099229</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>137.995</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6744326984638995</v>
+      </c>
+      <c r="D36" t="n">
+        <v>409.5404367406712</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.22711620528401</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.15982e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-78.654</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1850079808415682</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6211224989523778</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.440378818762599</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.287932995467975</v>
+      </c>
+      <c r="L36" t="n">
+        <v>42.33021315199939</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.36764732155075</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>15.75260017528404</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-8125.317972457186</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>69.20634213582717</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.174503577685571e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.890702277343011</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>136.198</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6656500935931459</v>
+      </c>
+      <c r="D37" t="n">
+        <v>419.1697330259964</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.255968705445517</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5.15883e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-78.79600000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2763925948041334</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5953812507390521</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.454093701839388</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.267031003925959</v>
+      </c>
+      <c r="L37" t="n">
+        <v>43.71138836166045</v>
+      </c>
+      <c r="M37" t="n">
+        <v>86.39923131988029</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>15.89114278155021</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-8119.982157234324</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>80.11166866743098</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.826633089816727e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.7905655280317965</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>135.462</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6620529888714576</v>
+      </c>
+      <c r="D38" t="n">
+        <v>407.7646517665256</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.221795376561415</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5.16019e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-78.913</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2915081464087833</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9061904908274884</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.600675238404946</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.830325477844452</v>
+      </c>
+      <c r="L38" t="n">
+        <v>59.8423212302792</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.56823354229601</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>16.67574058292641</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-8464.497698882655</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>61.95133803269718</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.932269727715567e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8943499637294982</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>128.85</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6297376948228085</v>
+      </c>
+      <c r="D39" t="n">
+        <v>498.3515375097577</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.49322311729052</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5.16125e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-79.03</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.08553367608119912</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4511436861560666</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.209508652176575</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.274208323575353</v>
+      </c>
+      <c r="L39" t="n">
+        <v>45.02317040776396</v>
+      </c>
+      <c r="M39" t="n">
+        <v>86.19605984370621</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>15.0400820190604</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-7507.542129849103</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.318009393599073</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.918925375065649e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.7140448729314802</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>128.679</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6289019544594812</v>
+      </c>
+      <c r="D40" t="n">
+        <v>420.4364991920662</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.259764348442484</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5.16195e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-79.139</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2598098467772512</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6718184631646248</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9773069703928023</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.146576179141718</v>
+      </c>
+      <c r="L40" t="n">
+        <v>37.40373780834123</v>
+      </c>
+      <c r="M40" t="n">
+        <v>86.37119903640611</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>15.76805951364126</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-7814.228678086121</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>40.8335755980548</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.653094124068158e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8940978773476441</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>125.838</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.615016934738941</v>
+      </c>
+      <c r="D41" t="n">
+        <v>381.911199175964</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.144330032995087</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5.16325e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-79.258</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.02535125707846865</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5387538266962301</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.336427828124124</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.549917302944014</v>
+      </c>
+      <c r="L41" t="n">
+        <v>54.7726945417211</v>
+      </c>
+      <c r="M41" t="n">
+        <v>86.3154575967724</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>15.52886908561991</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-7611.576853225773</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>75.83071427145259</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.080323724053289e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8990971783762893</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>123.924</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6056625075143325</v>
+      </c>
+      <c r="D42" t="n">
+        <v>383.8729355730983</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.150208032595267</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5.16501e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-79.37</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2436970921242972</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6682560515821812</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.339842451990981</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.487079147596893</v>
+      </c>
+      <c r="L42" t="n">
+        <v>55.49866911638694</v>
+      </c>
+      <c r="M42" t="n">
+        <v>86.38709435375804</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>15.83761802685179</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-7688.220450246908</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>69.39571167565212</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.008903726244124e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8987504861957519</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>121.6420000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5945095279288793</v>
+      </c>
+      <c r="D43" t="n">
+        <v>367.4489576011801</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.100996458556412</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5.16635e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-79.488</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5600702658062751</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.335431596250831</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.386473134667374</v>
+      </c>
+      <c r="L43" t="n">
+        <v>49.06020133975994</v>
+      </c>
+      <c r="M43" t="n">
+        <v>86.31899829893689</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>15.54384732010939</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7461.779420541895</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>81.53399829411991</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.18452288903893e-09</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.9008253041846258</v>
       </c>
     </row>
   </sheetData>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.9223818708683649</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>230.223</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>318.676294701301</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.48405e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-71.477</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.08917540533169116</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3471414323388183</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.145985702800317</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.954132397868003</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.54704243204864</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.23478723234156</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.429781238972884</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5414.041814868425</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>223.6363367675561</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.341432760764105e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9390762770541593</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>155.771</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6766092006445926</v>
+      </c>
+      <c r="D13" t="n">
+        <v>281.2050418088222</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8824159389464438</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.56439e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-74.845</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.01840695689741802</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6847044382186913</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.456079963214203</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.191634385802081</v>
+      </c>
+      <c r="L13" t="n">
+        <v>18.62958177097705</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.08416256317115</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.62673141074112</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6445.59408512149</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>231.3452642404183</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.06906772960169e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8999088043071136</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>142.388</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6184786055259468</v>
+      </c>
+      <c r="D14" t="n">
+        <v>274.9206300011541</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8626955772121061</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.48945e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-76.01000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3604533760221865</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7743064445909724</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.497126154862831</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.627842470879866</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.87766911889256</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.70517038129285</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.31564519299691</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7146.132424742593</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>227.2879322893289</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.837082017584867e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8952620368498381</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>134.357</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5835950361171562</v>
+      </c>
+      <c r="D15" t="n">
+        <v>272.3401181617656</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8545979813686274</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.42322e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-76.693</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2608720242752559</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4951698017334252</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.152937085687482</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.886380745785861</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22.43295414845264</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.79608932309402</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.60469582453696</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-7146.513889313336</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>222.6717959665643</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.373627470565421e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8998280595011753</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>131.894</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5728967131867799</v>
+      </c>
+      <c r="D16" t="n">
+        <v>262.8184458762306</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8247191593669474</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.37384e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-77.176</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2971080407960646</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.138437418711925</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.509783129603517</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.560692240341429</v>
+      </c>
+      <c r="L16" t="n">
+        <v>28.5971341364712</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.13220966471569</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.79106039914915</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-7685.932461853336</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>224.746234501729</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.04382904514534e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9060893016988211</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>126.794</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.550744278373577</v>
+      </c>
+      <c r="D17" t="n">
+        <v>256.3464469035407</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8044101527658881</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.34091e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-77.55500000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.08846537671713303</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5108913846030665</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.130939646268487</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.022654159692959</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25.80948698569296</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.09283679408355</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14.64155332260268</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-7469.247115082159</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>223.9275708134445</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.727730387311628e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9110341551006097</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5277491823145386</v>
+      </c>
+      <c r="D18" t="n">
+        <v>250.596257380253</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7863661701449735</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5.31622e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-77.863</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4546049582765499</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.075151414504331</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.985898241251807</v>
+      </c>
+      <c r="L18" t="n">
+        <v>27.0157212523038</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.01793341948849</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.36527923318819</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-7190.51392002576</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>222.9776767171154</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.606003275399738e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9141653542667639</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>119.83</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5204953458168822</v>
+      </c>
+      <c r="D19" t="n">
+        <v>242.808119433828</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7619271451031991</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.29846e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-78.14400000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1549357653185919</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.699868088772796</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.53982708147742</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.564392866789976</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.00297576992923</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.2698998971351</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.33867958993858</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-7597.017364114135</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>224.1177968247004</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.507952627214874e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.916976192834606</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>116.121</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5043848790086134</v>
+      </c>
+      <c r="D20" t="n">
+        <v>238.6319458119767</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7488223936946712</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.28564e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-78.361</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.08806292461510291</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6883682539826219</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.237438892053175</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.252080060144384</v>
+      </c>
+      <c r="L20" t="n">
+        <v>33.00930684280635</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.27825604431004</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15.37321574682724</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-7510.58868192953</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>222.7388959233915</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.386183340816521e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9195498027059763</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>116.015</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5039244558536726</v>
+      </c>
+      <c r="D21" t="n">
+        <v>234.6635426187714</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7363696218406338</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.27423e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-78.563</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3470963104992353</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9643668984297553</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.528700134325659</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.546532475175336</v>
+      </c>
+      <c r="L21" t="n">
+        <v>34.09323503542848</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.57205587394866</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>16.69437940080894</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-8100.325238554336</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>221.6827423832186</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.249341720811328e-09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9223818606242553</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 57.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1685,6 +1685,566 @@
       </c>
       <c r="AD21" t="n">
         <v>0.8820898919335342</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>202.047</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>344.3911103236727</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5.21535e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-75.191</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.1916114932947444</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6401405543196917</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.325163521322319</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.157285356156221</v>
+      </c>
+      <c r="L22" t="n">
+        <v>26.42594023751873</v>
+      </c>
+      <c r="M22" t="n">
+        <v>85.75144313712272</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>13.46121302656552</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-8425.382353354806</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>229.9006229273865</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.390468004277009e-09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.8754728658495474</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>191.839</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9494771018624378</v>
+      </c>
+      <c r="D23" t="n">
+        <v>403.3256277427941</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.171126709292038</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.16844e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-75.92</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3163862155468708</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6672988410120807</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.244488088691967</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.135214841455913</v>
+      </c>
+      <c r="L23" t="n">
+        <v>27.89517354074312</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.95358244905577</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.1360820951703</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-8648.783113050857</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>157.4216849829879</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>6.638799756616554e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8738426745704772</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>185.659</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9188901592203793</v>
+      </c>
+      <c r="D24" t="n">
+        <v>441.9545660513697</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.283292607744732</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.14064e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.389</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3418126842168111</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7873243054545538</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.280089896848315</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.335561143644852</v>
+      </c>
+      <c r="L24" t="n">
+        <v>33.42687872252122</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.16898640496976</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.93348098541376</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-9004.449998165856</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>110.0034723264628</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5.493802959491138e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8733102871555355</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>177.7169999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.879582473384905</v>
+      </c>
+      <c r="D25" t="n">
+        <v>398.9996810371522</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.15856556419867</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.12067e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.751</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.03866112505642204</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6310889820055303</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.058926213036916</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.975505547908519</v>
+      </c>
+      <c r="L25" t="n">
+        <v>30.19127106272634</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.1096533110838</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.70503950702534</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8715.851842118569</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>146.8712818462355</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>6.317668841206807e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8760565206763249</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>173.469</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8585576623260923</v>
+      </c>
+      <c r="D26" t="n">
+        <v>390.052536981051</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.132585961973478</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.10734e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-77.038</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1590480294086417</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.530346475396138</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.200895437514181</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.805119031982555</v>
+      </c>
+      <c r="L26" t="n">
+        <v>31.15138677097848</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.20104291829934</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.05986807852183</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8804.112573257338</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>148.8850888462575</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.257610626092362e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8792937976244373</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>168.0309999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8316431325384684</v>
+      </c>
+      <c r="D27" t="n">
+        <v>454.4291070522619</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.319514625755499</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.09842e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-77.322</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1420233111535582</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8076149251994229</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.495643479595357</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.574670224228278</v>
+      </c>
+      <c r="L27" t="n">
+        <v>45.87179168723365</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.18963722131048</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.01465623900591</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-8647.549253121873</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>74.7234850520715</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.443499102394953e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8795519684794557</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>162.943</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8064608729652013</v>
+      </c>
+      <c r="D28" t="n">
+        <v>462.7892024750278</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.343789629296992</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.09092e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-77.54900000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.07830713619269164</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3071860725067974</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.398477207138512</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.015642289022849</v>
+      </c>
+      <c r="L28" t="n">
+        <v>37.09347506303033</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.10652505823433</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14.69318818376992</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-8328.152260697088</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>60.56521440817603</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.454127271989648e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8764884833998486</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>163.156</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8075150831242235</v>
+      </c>
+      <c r="D29" t="n">
+        <v>392.9621891418261</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.141034647417305</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.08651e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-77.782</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4164939112962919</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.133297331941555</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.621305872901047</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.6926529107413</v>
+      </c>
+      <c r="L29" t="n">
+        <v>50.22657284326222</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.61123063991427</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.88782801410668</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-9523.735254483521</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>125.1098390792133</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>5.438059972178863e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8841174156044891</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>155.971</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7719540502952282</v>
+      </c>
+      <c r="D30" t="n">
+        <v>406.7885019146118</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.181181771888059</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.082609999999999e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-77.98099999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1617325119238948</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.759705859251338</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.565502145397057</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.578594925231208</v>
+      </c>
+      <c r="L30" t="n">
+        <v>52.00445736814248</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.344032132899</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>15.65057452743505</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8663.69464773346</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>105.4024587408428</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.277029393332828e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8807965771361188</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>152.0339999999999</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7524684850554569</v>
+      </c>
+      <c r="D31" t="n">
+        <v>445.8212054726692</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.29452007356888</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.08056e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-78.173</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2072955141396269</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.5454724906845655</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.331970943090006</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.143726058355128</v>
+      </c>
+      <c r="L31" t="n">
+        <v>41.38384227129414</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.26301697638011</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>15.31034815498231</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8351.490980495348</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>58.64875837894973</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.236703469673262e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8820897532340063</v>
       </c>
     </row>
   </sheetData>
@@ -1698,7 +2258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4193,6 +4753,1182 @@
       </c>
       <c r="AD43" t="n">
         <v>0.795188307249609</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>204.684</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>333.0270070311045</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.21634e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-75.754</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.3164903587282908</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.7778741743617645</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.461623813279092</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.422465636962559</v>
+      </c>
+      <c r="L44" t="n">
+        <v>33.32976497281621</v>
+      </c>
+      <c r="M44" t="n">
+        <v>85.96837537932797</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>14.1881230881079</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-8745.798358997865</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>223.0084259902413</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>7.410451648377995e-09</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8919967201928634</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>178.233</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.8707715307498387</v>
+      </c>
+      <c r="D45" t="n">
+        <v>387.3411781734849</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.163092391895134</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.21579e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-76.58</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.0139188235977812</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.4032493822599827</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.333960457939073</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.169164727500518</v>
+      </c>
+      <c r="L45" t="n">
+        <v>31.46758390179824</v>
+      </c>
+      <c r="M45" t="n">
+        <v>85.90677899824207</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>13.97390290455378</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-8194.017028003105</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>157.4197865639987</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>7.407614133219286e-09</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8703510490126979</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>177.282</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8661253444333703</v>
+      </c>
+      <c r="D46" t="n">
+        <v>562.32287473126</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.688520338768619</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.20277e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-76.88500000000001</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.5934229774499764</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.030465497959012</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.694160515413292</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.955486472502589</v>
+      </c>
+      <c r="L46" t="n">
+        <v>47.28654211276875</v>
+      </c>
+      <c r="M46" t="n">
+        <v>86.48824651819594</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>16.29499757508114</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-9494.247686904209</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>10.24488972037106</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.78794012638793e-08</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.7107253094663536</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>172.5309999999999</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8429139551699201</v>
+      </c>
+      <c r="D47" t="n">
+        <v>529.6243631490713</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.590334573374719</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5.19107e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-77.10599999999999</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.4028511991794416</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.023299975134411</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.674980028094986</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.7327423592449</v>
+      </c>
+      <c r="L47" t="n">
+        <v>42.47204809449438</v>
+      </c>
+      <c r="M47" t="n">
+        <v>86.48646823592055</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>16.28672959154234</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-9370.291333677103</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.3241863592358062</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>4.41672142289782e-09</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8598474278637736</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>166.1299999999999</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8116413593637017</v>
+      </c>
+      <c r="D48" t="n">
+        <v>387.7967086525374</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.164460240356175</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5.18404e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-77.31999999999999</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.3520387347631234</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.8529723944085141</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.466325014602316</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.06408751544502</v>
+      </c>
+      <c r="L48" t="n">
+        <v>35.23849248096194</v>
+      </c>
+      <c r="M48" t="n">
+        <v>86.37210788369278</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>15.7720202565853</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-8952.996738374797</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>138.0677563262086</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>6.34141649426861e-09</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8774412860110926</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>162.554</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7941705262746476</v>
+      </c>
+      <c r="D49" t="n">
+        <v>376.4243304700689</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.130311724042582</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5.179499999999999e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-77.48999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.3488996412597917</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.7785537313279486</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.708690601594925</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.586390090859982</v>
+      </c>
+      <c r="L49" t="n">
+        <v>45.90821696265915</v>
+      </c>
+      <c r="M49" t="n">
+        <v>86.28400188530301</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>15.39705343960711</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-8631.120644864346</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>144.0083939977964</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>6.259567773943016e-09</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8811408823484378</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>160.9569999999999</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7863682554571921</v>
+      </c>
+      <c r="D50" t="n">
+        <v>374.4413837960556</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.124357412133494</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.17457e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-77.657</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.4801645341277065</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.8020454599199882</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.542292289407071</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.349117361662359</v>
+      </c>
+      <c r="L50" t="n">
+        <v>36.99527892414145</v>
+      </c>
+      <c r="M50" t="n">
+        <v>86.47985200944004</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>16.25604123245146</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-9043.424900618778</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>141.2392026920833</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>6.269339490577508e-09</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8814009597784864</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>153.128</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7481190518066875</v>
+      </c>
+      <c r="D51" t="n">
+        <v>366.9710549971194</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.101925811568923</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5.17208e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-77.816</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.03471175430512569</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1886290392761659</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.150009958138471</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1.784617603478716</v>
+      </c>
+      <c r="L51" t="n">
+        <v>31.75053460318929</v>
+      </c>
+      <c r="M51" t="n">
+        <v>86.11077642405689</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>14.70929904195229</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-8037.031378340025</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>142.9133771970071</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>6.054270864660105e-09</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8849298712682626</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>151.991</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7425641476617614</v>
+      </c>
+      <c r="D52" t="n">
+        <v>404.9512013180006</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.215971055705336</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.17053e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-77.97199999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1947439123320832</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.5523444986602706</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.264832899069007</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.251803367504679</v>
+      </c>
+      <c r="L52" t="n">
+        <v>38.65799346646809</v>
+      </c>
+      <c r="M52" t="n">
+        <v>86.25853183561952</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>15.29194246146126</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-8291.427047402522</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>98.40911146387889</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>4.899836239363002e-09</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8847338045899777</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>149.975</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7327148189404152</v>
+      </c>
+      <c r="D53" t="n">
+        <v>365.2470051404855</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.096748904530652</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.16953e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-78.111</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.06022194818207349</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.4863690710485331</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.420237270551536</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.22968090805138</v>
+      </c>
+      <c r="L53" t="n">
+        <v>39.82159364052018</v>
+      </c>
+      <c r="M53" t="n">
+        <v>86.2961015716008</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>15.44749275968518</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-8296.650322649335</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>135.5088901740925</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>5.663009006004826e-09</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8899018259419662</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>146.2569999999999</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.7145502335307105</v>
+      </c>
+      <c r="D54" t="n">
+        <v>355.0302112074004</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.066070329768303</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5.16839e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-78.25</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.1309157165110802</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.6414333786593623</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.371880245353843</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.355753039203927</v>
+      </c>
+      <c r="L54" t="n">
+        <v>40.67715977940247</v>
+      </c>
+      <c r="M54" t="n">
+        <v>86.34556247412979</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>15.65714622017708</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-8334.538598439145</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>141.7022340288969</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>5.832578046703131e-09</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.891241047460964</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>147.52</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.7207207207207208</v>
+      </c>
+      <c r="D55" t="n">
+        <v>386.5370260168108</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.160677716389255</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.16651e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-78.372</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.5461594089392622</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.5893925544401728</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.359832687388762</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.384702482976528</v>
+      </c>
+      <c r="L55" t="n">
+        <v>37.79114712261124</v>
+      </c>
+      <c r="M55" t="n">
+        <v>86.58584861664701</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>16.76198348291728</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-8876.970806251997</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>104.5847440824063</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>5.136521040146e-09</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8865342640098314</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>144.762</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.7072462918449902</v>
+      </c>
+      <c r="D56" t="n">
+        <v>380.210065905066</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.141679376980842</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5.16679e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-78.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.3809619793428631</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.940210419520971</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.696242951974511</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.651337386673285</v>
+      </c>
+      <c r="L56" t="n">
+        <v>56.81998852543433</v>
+      </c>
+      <c r="M56" t="n">
+        <v>86.52793233680913</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>16.48171443191587</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-8637.506802509282</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>105.7573589779639</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>4.86561674479868e-09</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8918869563566058</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6830040452600106</v>
+      </c>
+      <c r="D57" t="n">
+        <v>375.3800781796061</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.127176085585593</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5.16595e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-78.61499999999999</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.2204231327090241</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.7173105553115233</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.082566153931112</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.010475568240889</v>
+      </c>
+      <c r="L57" t="n">
+        <v>35.49957492604283</v>
+      </c>
+      <c r="M57" t="n">
+        <v>86.31645639209579</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>15.53309137840044</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-8033.735733587318</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>107.1930694323915</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>4.887625925854153e-09</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8929718765991993</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>138.576</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6770240956791933</v>
+      </c>
+      <c r="D58" t="n">
+        <v>411.7916117839802</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.236511163028646</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5.16497e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-78.729</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1734043090905827</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.6431014296704807</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.364292639675629</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.284857464935116</v>
+      </c>
+      <c r="L58" t="n">
+        <v>39.69687123002117</v>
+      </c>
+      <c r="M58" t="n">
+        <v>86.39821187978183</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>15.88663313037</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-8154.107755845124</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>65.4312068768817</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>4.230956079471146e-09</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8891324299389712</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>136.36</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.6661976510132692</v>
+      </c>
+      <c r="D59" t="n">
+        <v>367.7910074746194</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.104387931637833</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5.16677e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-78.84099999999999</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1023786923017569</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.5201476579457995</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.476600907347314</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1.995878279674151</v>
+      </c>
+      <c r="L59" t="n">
+        <v>40.23086948456863</v>
+      </c>
+      <c r="M59" t="n">
+        <v>86.4205715568302</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>15.98613355001055</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-8133.899800027603</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>106.6031614154839</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>4.979385093718369e-09</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8926286489021307</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>136.257</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6656944363018115</v>
+      </c>
+      <c r="D60" t="n">
+        <v>415.4012094342916</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.247349916565456</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5.16473e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-78.952</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.3572676105965221</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.7560890507750943</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.56462395779619</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.578638123188831</v>
+      </c>
+      <c r="L60" t="n">
+        <v>52.53009133940343</v>
+      </c>
+      <c r="M60" t="n">
+        <v>86.58516089805744</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>16.7585997617742</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-8471.952024295244</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>78.53895455267042</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.850504210320341e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.7905346964649813</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>134.044</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.6548826483750561</v>
+      </c>
+      <c r="D61" t="n">
+        <v>333.8276886751332</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.002404254391158</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5.16867e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-79.07299999999999</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.2099367862275081</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.8880466162554737</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.515310175100335</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.495265419909257</v>
+      </c>
+      <c r="L61" t="n">
+        <v>46.63374388710879</v>
+      </c>
+      <c r="M61" t="n">
+        <v>86.54973313037205</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>16.5861100823373</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-8294.412934411361</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>132.139441229088</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>5.234154315022335e-09</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.9011701638633079</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>129.803</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.6341629047702799</v>
+      </c>
+      <c r="D62" t="n">
+        <v>467.0369166354093</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.402399525488899</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5.16924e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-79.17700000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.01368154594398414</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.5536990957905542</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.514149773891765</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.532969187758171</v>
+      </c>
+      <c r="L62" t="n">
+        <v>54.16953460278456</v>
+      </c>
+      <c r="M62" t="n">
+        <v>86.39231169106921</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>15.86058272691931</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-7830.255058443125</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>23.12963728663417</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.449391648522401e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.7537748643487034</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>130.119</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.6357067479627133</v>
+      </c>
+      <c r="D63" t="n">
+        <v>360.0790886762683</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.081230894414029</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5.16894e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-79.301</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.3635656862472247</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8332025941300015</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.274057688379306</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.377995221933312</v>
+      </c>
+      <c r="L63" t="n">
+        <v>49.2828086738517</v>
+      </c>
+      <c r="M63" t="n">
+        <v>86.61496854372025</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>16.90651984926625</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-8297.645628534941</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>119.6879713770479</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.266384538245927e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.7941595699682489</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>126.468</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.6178694963944419</v>
+      </c>
+      <c r="D64" t="n">
+        <v>356.1223838441292</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.069349861498973</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5.17013e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-79.40300000000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.1041033060454893</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.5901341396295071</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.326117725156579</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1.970034417693584</v>
+      </c>
+      <c r="L64" t="n">
+        <v>39.48324977154112</v>
+      </c>
+      <c r="M64" t="n">
+        <v>86.50872653162848</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>16.39082409335788</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-7948.453721050384</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>119.3617090422799</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.262536145671332e-08</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.7951882469836797</v>
       </c>
     </row>
   </sheetData>
@@ -4206,7 +5942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6701,6 +8437,1182 @@
       </c>
       <c r="AD43" t="n">
         <v>0.9004621972677983</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>210.712</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>341.6979069834582</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.25343e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-74.611</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.2720457344516501</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.5572529293545954</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.099907237109413</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.045591311832009</v>
+      </c>
+      <c r="L44" t="n">
+        <v>23.12159672972388</v>
+      </c>
+      <c r="M44" t="n">
+        <v>85.3953647282212</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>12.4162655416546</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-7840.929782597505</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>224.8295459526351</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>7.226363242135862e-09</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8910256327095495</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>183.956</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.873020995481985</v>
+      </c>
+      <c r="D45" t="n">
+        <v>363.6497639271059</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.064243463290252</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.20708e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-76.012</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.2268987737245904</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.6368823274303386</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.268729063557205</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.197811681729863</v>
+      </c>
+      <c r="L45" t="n">
+        <v>30.24769433494262</v>
+      </c>
+      <c r="M45" t="n">
+        <v>85.74484201939346</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>13.44025355411804</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-8066.219127042919</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>191.0132913280065</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>7.905519892743868e-09</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.875464542001318</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>180.083</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8546404571168231</v>
+      </c>
+      <c r="D46" t="n">
+        <v>387.0542451777099</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.132738121209643</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.178079999999999e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-76.523</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.3630593732499043</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.9972396494370661</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.575740765283392</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.361346673380489</v>
+      </c>
+      <c r="L46" t="n">
+        <v>33.66970051690187</v>
+      </c>
+      <c r="M46" t="n">
+        <v>86.21932323919702</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>15.13289886314923</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-8984.526394492035</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>159.9096847103525</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>6.9129023585624e-09</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.875124314175641</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>172.3580000000001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.817979042484529</v>
+      </c>
+      <c r="D47" t="n">
+        <v>393.2590477592757</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.150896858663854</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5.15806e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-76.84699999999999</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.04427324000057927</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.4288234263283882</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.088016781281395</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.048388617719308</v>
+      </c>
+      <c r="L47" t="n">
+        <v>32.71649156956062</v>
+      </c>
+      <c r="M47" t="n">
+        <v>85.94346905743005</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>14.10072163318455</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-8216.205625040062</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>146.8984825696081</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>6.370404615978873e-09</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8771097234591843</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>170.711</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8101626865104978</v>
+      </c>
+      <c r="D48" t="n">
+        <v>390.2476918822101</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.142083939955483</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5.1463e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-77.111</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.1632241141875213</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.6023929228274145</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.394722846961558</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.979967496398626</v>
+      </c>
+      <c r="L48" t="n">
+        <v>31.58056057728474</v>
+      </c>
+      <c r="M48" t="n">
+        <v>86.23399469050551</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>15.19202414063634</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-8778.693107569165</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>142.06375932202</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>5.750435024820161e-09</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.88292339022861</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>168.984</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.8019666654011162</v>
+      </c>
+      <c r="D49" t="n">
+        <v>383.2824836663607</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.121699828512311</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5.13615e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-77.367</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5699435146274544</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.011273201742436</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.685503940553962</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.683296619601748</v>
+      </c>
+      <c r="L49" t="n">
+        <v>45.9869421948146</v>
+      </c>
+      <c r="M49" t="n">
+        <v>86.51320910630089</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>16.41194814785252</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-9402.657814577398</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>142.5645284873783</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>5.67972254819635e-09</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8863457788451515</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>165.126</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7836573142488324</v>
+      </c>
+      <c r="D50" t="n">
+        <v>458.7931246357018</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.34268637664764</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.130670000000001e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-77.59399999999999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.3388034996971831</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9967164359554841</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.814657303785062</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.666723339112187</v>
+      </c>
+      <c r="L50" t="n">
+        <v>47.8269404575823</v>
+      </c>
+      <c r="M50" t="n">
+        <v>86.55911649603661</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>16.63145015458909</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-9405.307126144153</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>59.02804183650778</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>4.354462815013564e-09</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8776529971076544</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>156.348</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7419985572724858</v>
+      </c>
+      <c r="D51" t="n">
+        <v>383.7329921473025</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.123018269368209</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5.1277e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-77.816</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.2366907644341785</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.4167899803093497</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.129201596139299</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1.943290000706279</v>
+      </c>
+      <c r="L51" t="n">
+        <v>35.19957650124805</v>
+      </c>
+      <c r="M51" t="n">
+        <v>86.07449723841992</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>14.57293642754105</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-8063.108053185911</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>130.3980580756192</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>5.660710440691972e-09</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8841113583034919</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7370249439993923</v>
+      </c>
+      <c r="D52" t="n">
+        <v>388.2974362593066</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.136376396587364</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.12321e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-77.991</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.2206160237111593</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.7543313861075586</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.532648826214313</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.682490663789457</v>
+      </c>
+      <c r="L52" t="n">
+        <v>52.62256582177227</v>
+      </c>
+      <c r="M52" t="n">
+        <v>86.36674037246492</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>15.74865738981043</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-8648.107996158215</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>119.8477767958207</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>5.308821479569965e-09</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8862660386991242</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>153.829</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7300438513231331</v>
+      </c>
+      <c r="D53" t="n">
+        <v>444.3917867001123</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.300539972934706</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.12047e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-78.163</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.4091694089847645</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.574477866256307</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.549948974767799</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.231253077970797</v>
+      </c>
+      <c r="L53" t="n">
+        <v>41.34519349762449</v>
+      </c>
+      <c r="M53" t="n">
+        <v>86.56369146988662</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>16.65364594434075</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-9064.751095793868</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>56.67532839650912</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>4.23478689178182e-09</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.881795207234946</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>151.853</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.7206661224799727</v>
+      </c>
+      <c r="D54" t="n">
+        <v>386.1374707202639</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.130055124215195</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5.11952e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-78.35299999999999</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.637259481460802</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9660936609081621</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.48128779744172</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.827935325292888</v>
+      </c>
+      <c r="L54" t="n">
+        <v>48.61631945073621</v>
+      </c>
+      <c r="M54" t="n">
+        <v>86.68660525809</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>17.27288744915598</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-9312.487903245348</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>110.2976991947266</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>4.874724432965449e-09</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8911650437145543</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>148.809</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.7062198640798815</v>
+      </c>
+      <c r="D55" t="n">
+        <v>381.7389685892621</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.117182636438397</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.11746e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-78.512</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.5796616328349538</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.6343058820088262</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.512314145170895</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.317249196402199</v>
+      </c>
+      <c r="L55" t="n">
+        <v>44.43721378107117</v>
+      </c>
+      <c r="M55" t="n">
+        <v>86.622170643838</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>16.94265132071409</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-9025.273366936073</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>110.1489081230043</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>4.861646727016281e-09</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8921368282840895</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>143.251</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6798426288013971</v>
+      </c>
+      <c r="D56" t="n">
+        <v>451.2434607063406</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.320591819510868</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5.11511e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-78.64400000000001</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.09589835926551951</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.8394914168343394</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.570705945470481</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.536366543814996</v>
+      </c>
+      <c r="L56" t="n">
+        <v>50.956289445696</v>
+      </c>
+      <c r="M56" t="n">
+        <v>86.4417932709521</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>16.08172519812724</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-8441.386468294138</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>33.8616555052066</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.775526732847771e-09</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8854545555268637</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>139.908</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6639773719579332</v>
+      </c>
+      <c r="D57" t="n">
+        <v>427.361725617272</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.250700448797191</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5.11432e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-78.77500000000001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1115059899106077</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.8241650984262582</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.488049813722304</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.285879891882056</v>
+      </c>
+      <c r="L57" t="n">
+        <v>46.01942209834783</v>
+      </c>
+      <c r="M57" t="n">
+        <v>86.44160452250371</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>16.08086997576172</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-8347.666635147394</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>53.72911812333076</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>3.967303247131936e-09</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8890166261869491</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>140.885</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6686140324234026</v>
+      </c>
+      <c r="D58" t="n">
+        <v>442.8692696758281</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.296084232957469</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5.11416e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-78.937</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.4647135923414617</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.6639705578297351</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.685470615248416</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.385794665227607</v>
+      </c>
+      <c r="L58" t="n">
+        <v>47.47124749764816</v>
+      </c>
+      <c r="M58" t="n">
+        <v>86.72236432383686</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>17.46175350010721</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-9018.367276180637</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>33.02922131950001</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>3.664617131412577e-09</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8885975038958073</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>134.765</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.63956964956908</v>
+      </c>
+      <c r="D59" t="n">
+        <v>396.6407040101756</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.160793484255604</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5.11313e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-79.042</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.3477365262141789</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.5529316491965853</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.204506388140444</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.041631753494224</v>
+      </c>
+      <c r="L59" t="n">
+        <v>42.44051890047962</v>
+      </c>
+      <c r="M59" t="n">
+        <v>86.41701922497259</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>15.97024282799256</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-8112.331798445049</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>75.44817053871354</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>4.181993003410859e-09</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8940987488573682</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>131.494</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6240460913474317</v>
+      </c>
+      <c r="D60" t="n">
+        <v>366.5796757216426</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.072818030867801</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5.11395e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-79.161</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.206532410750953</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.5120631779318011</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.252374548146723</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.457918192885649</v>
+      </c>
+      <c r="L60" t="n">
+        <v>56.97753812005435</v>
+      </c>
+      <c r="M60" t="n">
+        <v>86.28313144161756</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>15.3934375115313</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-7723.155358266668</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>100.7692571054653</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>4.389025473516373e-09</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8998750496540887</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>129.931</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.616628383765519</v>
+      </c>
+      <c r="D61" t="n">
+        <v>416.9211472387407</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.220145452219361</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5.11415e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-79.30200000000001</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.1330858811668987</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.4570632257041024</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.092793376310215</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.848939700136619</v>
+      </c>
+      <c r="L61" t="n">
+        <v>40.30521752203344</v>
+      </c>
+      <c r="M61" t="n">
+        <v>86.40867727258967</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>15.93305002266193</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-7925.510388842446</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>45.59886413900296</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>3.748221525319169e-09</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8931765201238405</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>128.692</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.6107483199817761</v>
+      </c>
+      <c r="D62" t="n">
+        <v>397.2027845337354</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.162438447575753</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5.113180000000001e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-79.41500000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.1297665175197009</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.565735524987386</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.344986339498656</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.153225000437529</v>
+      </c>
+      <c r="L62" t="n">
+        <v>46.44978303970022</v>
+      </c>
+      <c r="M62" t="n">
+        <v>86.51583409920414</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>16.42434358446324</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-8100.256490752301</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>91.7719657082217</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.983980878070751e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.7636308922401035</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>125.114</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.5937677968032194</v>
+      </c>
+      <c r="D63" t="n">
+        <v>396.9955436015437</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.161831944205507</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5.11435e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-79.544</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1017203708429545</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.5672137690783522</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.37875187598734</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.549378574614573</v>
+      </c>
+      <c r="L63" t="n">
+        <v>62.86242267236202</v>
+      </c>
+      <c r="M63" t="n">
+        <v>86.38509718954563</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>15.82884480380962</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-7709.902032735014</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>93.03109718082503</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>4.6267670528128e-08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.7343990011673772</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>125.383</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.595044420820836</v>
+      </c>
+      <c r="D64" t="n">
+        <v>393.2974255438315</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.151009173617418</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5.11423e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-79.65600000000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.1306278689324792</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.6328748845939941</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.4767764927858</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.393417089662345</v>
+      </c>
+      <c r="L64" t="n">
+        <v>55.48930023729125</v>
+      </c>
+      <c r="M64" t="n">
+        <v>86.64470537406686</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>17.05670425805519</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-8259.885288528591</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>55.98906642483281</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>3.687056364749095e-09</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.9004620741576727</v>
       </c>
     </row>
   </sheetData>
@@ -6714,7 +9626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7977,6 +10889,566 @@
       </c>
       <c r="AD21" t="n">
         <v>0.9225247772999374</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>238.871</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>325.7049933330659</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.87922e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-75.291</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.02101189782293583</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.4416031295047814</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.253422903089771</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.829554929011778</v>
+      </c>
+      <c r="L22" t="n">
+        <v>27.53106510200563</v>
+      </c>
+      <c r="M22" t="n">
+        <v>85.34901167197908</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>12.29198442932583</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-8200.373625341766</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>242.1786016804024</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.056861174184744e-09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9328979066333302</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>173.854</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7278154317602389</v>
+      </c>
+      <c r="D23" t="n">
+        <v>304.1970272889869</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9339648869856747</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.87782e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-77.417</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2022948526187804</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.4694093191168598</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.216195771550979</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.026329615081339</v>
+      </c>
+      <c r="L23" t="n">
+        <v>31.41383807915502</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.28775760729498</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15.41267457729695</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-9107.587728673427</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>237.7114894748159</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.43709630984683e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9005567507759799</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>158.3100000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6627426518916069</v>
+      </c>
+      <c r="D24" t="n">
+        <v>482.9546466120261</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.482797797079386</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.84144e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-78.038</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.05770519846303718</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6753350119727103</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.46294988078753</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.228208201846874</v>
+      </c>
+      <c r="L24" t="n">
+        <v>38.26377739692781</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.29597584401212</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15.44696695383033</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-8814.495803533349</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>42.75312280156238</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.75090618562822e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8816567426619194</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>154.839</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6482117963252131</v>
+      </c>
+      <c r="D25" t="n">
+        <v>446.7091493264989</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.371514586728163</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.81253e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-78.372</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2463898255991757</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9327750449122331</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.581829270750887</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.348649979974415</v>
+      </c>
+      <c r="L25" t="n">
+        <v>36.85928415814353</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.61836106409478</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.92352028285748</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-9534.062981448962</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>72.57092775892666</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.211302805758928e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8834007791854758</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>147.86</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6189951898723578</v>
+      </c>
+      <c r="D26" t="n">
+        <v>368.9668466882758</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.132825269003384</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.79014e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-78.628</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.07711677239392996</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3715025133735628</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.273188192489151</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.099177526153265</v>
+      </c>
+      <c r="L26" t="n">
+        <v>38.39836110295903</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.41644623323495</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.96768259864628</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8820.971473368434</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>144.8544539254593</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>5.140868309727292e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.895471127643144</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>144.188</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.6036228759455939</v>
+      </c>
+      <c r="D27" t="n">
+        <v>371.2024076802504</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.139689029270297</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.77705e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-78.854</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1261868149208826</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5286105061370255</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.324726675539995</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.196136895677287</v>
+      </c>
+      <c r="L27" t="n">
+        <v>39.5511188707784</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.46781189788122</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.20048960678877</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-8822.49052332835</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>135.3112536506113</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.823014132585008e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8979351380162091</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>140.3050000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.5873672400584418</v>
+      </c>
+      <c r="D28" t="n">
+        <v>287.0887637740387</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8814380179933615</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.76467e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-79.038</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1536918080742448</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.583854032139182</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.284295879553938</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.160212447265749</v>
+      </c>
+      <c r="L28" t="n">
+        <v>40.39249237444133</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.51486193447968</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16.41975076668417</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-8812.921887403612</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>214.804272242354</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>6.641244788193796e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9109185952838685</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5672517802495907</v>
+      </c>
+      <c r="D29" t="n">
+        <v>280.8981722421294</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8624312736737286</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.7574e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-79.248</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.07135794233975726</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8777163556381857</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.005117324541387</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.968314970434818</v>
+      </c>
+      <c r="L29" t="n">
+        <v>38.33821509162608</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.51034475496964</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.39844369081006</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-8660.448950401082</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>213.5984595748785</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>6.461728324893254e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9144262595446954</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>131.688</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.551293375922569</v>
+      </c>
+      <c r="D30" t="n">
+        <v>416.7538539347299</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.279543950708049</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.74943e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-79.428</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1746615813686714</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.5400528925217504</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.180900667657328</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.229148017613586</v>
+      </c>
+      <c r="L30" t="n">
+        <v>39.61458506589467</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.59874183786719</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>16.82567386277453</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8761.127318496159</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>67.3293447905464</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.659841981598257e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8978041382884377</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>128.871</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5395003997973803</v>
+      </c>
+      <c r="D31" t="n">
+        <v>265.4492455068826</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8149990050518942</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.74377e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-79.59099999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1638014264097569</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6202505999003254</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.442115668568615</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.397534574039562</v>
+      </c>
+      <c r="L31" t="n">
+        <v>44.05801338712136</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.70715520511527</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>17.38092384372241</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8935.364647830273</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>214.9768873844445</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.196321570933123e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.92252475723238</v>
       </c>
     </row>
   </sheetData>
@@ -7990,7 +11462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10485,6 +13957,1182 @@
       </c>
       <c r="AD43" t="n">
         <v>0.7420350236077491</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>204.016</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>339.7673869785584</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4.74437e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-77.244</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.01505260537279031</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.5655120172916728</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.9205681126079903</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.894376023837155</v>
+      </c>
+      <c r="L44" t="n">
+        <v>32.21984490610736</v>
+      </c>
+      <c r="M44" t="n">
+        <v>86.09884029082536</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>14.66415516767536</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-9168.045261675268</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>227.6297222373055</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>6.765482307061953e-09</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8973218605203542</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>179.986</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.8822151203827152</v>
+      </c>
+      <c r="D45" t="n">
+        <v>545.4438493538568</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.605344922019482</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4.76221e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-77.97</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.4191208280561204</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.8201220516463597</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.525928095295496</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.904812430422271</v>
+      </c>
+      <c r="L45" t="n">
+        <v>36.42205966339108</v>
+      </c>
+      <c r="M45" t="n">
+        <v>86.44781561778335</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>16.10906020334769</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-9613.249141578935</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>5.090338729739035</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4.15435445458743e-09</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8635069527063824</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>170.772</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8370519959218884</v>
+      </c>
+      <c r="D46" t="n">
+        <v>413.9794444903621</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.218420190859834</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4.76744e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-78.206</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.1483437519659716</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.4608595489542529</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.482466634266881</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.299662476454889</v>
+      </c>
+      <c r="L46" t="n">
+        <v>41.90094506884159</v>
+      </c>
+      <c r="M46" t="n">
+        <v>86.31932891105524</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>15.54524737775507</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-9084.445695273294</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>131.6848470811086</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>5.778712682824706e-09</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8789352997023815</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>168.457</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8257048466786917</v>
+      </c>
+      <c r="D47" t="n">
+        <v>406.6017632401113</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.196706272652857</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4.76995e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-78.354</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5705037793440886</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.6994848286068222</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.805597269583298</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.268839894697855</v>
+      </c>
+      <c r="L47" t="n">
+        <v>38.70071618893611</v>
+      </c>
+      <c r="M47" t="n">
+        <v>86.58067505465303</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>16.73656181709892</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-9693.609583300185</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>132.7331362219924</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>5.695351319661394e-09</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8813365593857625</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>162.661</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.7972953101717511</v>
+      </c>
+      <c r="D48" t="n">
+        <v>406.2738152706561</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.195741059445163</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4.77418e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-78.51900000000001</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.07890459733344933</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.5738289258654355</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.510745159853829</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.556603467005762</v>
+      </c>
+      <c r="L48" t="n">
+        <v>49.81846626164148</v>
+      </c>
+      <c r="M48" t="n">
+        <v>86.46714595864923</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>16.19742807996265</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-9243.747570538677</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>125.6010462418734</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>5.601616956506803e-09</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8798569487772685</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>157.551</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7722482550388203</v>
+      </c>
+      <c r="D49" t="n">
+        <v>399.7025898207946</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.176400693943055</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4.77759e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-78.667</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.04213691763952598</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.7224552129789223</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.221023638015017</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.186944186748775</v>
+      </c>
+      <c r="L49" t="n">
+        <v>40.61644537722049</v>
+      </c>
+      <c r="M49" t="n">
+        <v>86.38348824761647</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>15.821784017322</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-8893.081304166333</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>126.2454133521194</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>5.591008815793764e-09</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8820880142600872</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>154.458</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7570876793976944</v>
+      </c>
+      <c r="D50" t="n">
+        <v>454.5802147907395</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.337915974906169</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.7825e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-78.82599999999999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.3491018886865117</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.7620699783851993</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.298825080717381</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.260718031395355</v>
+      </c>
+      <c r="L50" t="n">
+        <v>46.39635713656119</v>
+      </c>
+      <c r="M50" t="n">
+        <v>86.46683111339421</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>16.1959810410846</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-8995.914981161315</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>62.85781446360237</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>4.318403669988344e-09</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8807109063840068</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>152.2860000000001</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7464414555721122</v>
+      </c>
+      <c r="D51" t="n">
+        <v>447.7860286787588</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.31791939379696</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4.78731e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-78.97</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.4075924077423179</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9835335769783613</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.312075041667159</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.58917772440293</v>
+      </c>
+      <c r="L51" t="n">
+        <v>53.92067172313116</v>
+      </c>
+      <c r="M51" t="n">
+        <v>86.58083054750514</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>16.73732475235285</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-9195.303952956188</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>63.21278608061525</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>4.26423877519813e-09</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8824390103783448</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>147.229</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7216541839855696</v>
+      </c>
+      <c r="D52" t="n">
+        <v>377.5822135698467</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.111296222181779</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4.79115e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-79.095</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.5001868411509627</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.286568009590114</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.049070432317442</v>
+      </c>
+      <c r="L52" t="n">
+        <v>43.02720445839579</v>
+      </c>
+      <c r="M52" t="n">
+        <v>86.47075669293118</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>16.2140415656756</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-8779.878118726585</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>130.2489205555841</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>5.411212466037764e-09</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8896215833422135</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>144.8179999999999</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7098364834130653</v>
+      </c>
+      <c r="D53" t="n">
+        <v>364.4430241317015</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.072625090278898</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4.7943e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-79.22799999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.2337142179290318</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.5323350461727602</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.237320821564642</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.108321369535127</v>
+      </c>
+      <c r="L53" t="n">
+        <v>43.8396645646021</v>
+      </c>
+      <c r="M53" t="n">
+        <v>86.52072046388218</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>16.44746716044817</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-8809.539496702904</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>137.5253703308194</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>5.423682510497587e-09</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8927123680662962</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>143.027</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.7010577601756723</v>
+      </c>
+      <c r="D54" t="n">
+        <v>376.6154018659058</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.108450711573659</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4.79687e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-79.342</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.1592045218196105</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.8947502627080397</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.688218308443864</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.712888023685584</v>
+      </c>
+      <c r="L54" t="n">
+        <v>58.79283257010837</v>
+      </c>
+      <c r="M54" t="n">
+        <v>86.68044798971584</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>17.24077723915691</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-9158.797661151497</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>119.627608249827</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>5.017775854070988e-09</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8923761719398211</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>139.073</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6816769272998198</v>
+      </c>
+      <c r="D55" t="n">
+        <v>363.5623590380698</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.070033125518939</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.80072e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-79.452</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1572133842226058</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.7072554046623214</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.257823541983323</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.239179019831915</v>
+      </c>
+      <c r="L55" t="n">
+        <v>45.80761059439564</v>
+      </c>
+      <c r="M55" t="n">
+        <v>86.59022587957202</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>16.78355249768228</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-8804.542669663158</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>127.6784616255033</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>5.078501271788473e-09</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8951702270571552</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>136.257</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6678740883067994</v>
+      </c>
+      <c r="D56" t="n">
+        <v>449.0170728057246</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.321542590649116</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4.80283e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-79.551</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.2501873502243557</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.6753983504459924</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.38201129210432</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.071594947626012</v>
+      </c>
+      <c r="L56" t="n">
+        <v>41.86916415303637</v>
+      </c>
+      <c r="M56" t="n">
+        <v>86.56760377659262</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>16.672673637864</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-8648.770055613191</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>36.91710871632608</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.884984844326481e-09</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.884994070974946</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>134.838</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.660918751470473</v>
+      </c>
+      <c r="D57" t="n">
+        <v>440.1754265398313</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.295519945142967</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4.80562e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-79.65000000000001</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.3972886743752337</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.7942993864004355</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.482844013892421</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.253182020333465</v>
+      </c>
+      <c r="L57" t="n">
+        <v>47.5707044361684</v>
+      </c>
+      <c r="M57" t="n">
+        <v>86.66078674449373</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>17.13903556360076</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-8816.128156542951</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>40.5012012620049</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>3.755630694943536e-09</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8892993532787845</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>132.256</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6482628813426399</v>
+      </c>
+      <c r="D58" t="n">
+        <v>434.3350146136094</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.278330502747808</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.80718e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-79.752</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.4474656213682003</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.6285925599346588</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.480539308420189</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.185479715788673</v>
+      </c>
+      <c r="L58" t="n">
+        <v>47.96414807483088</v>
+      </c>
+      <c r="M58" t="n">
+        <v>86.6944385266701</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>17.31391071908497</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-8819.790180277078</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>41.96535895806021</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>3.717141678169611e-09</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8913862327854897</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>131.183</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.6430034899223589</v>
+      </c>
+      <c r="D59" t="n">
+        <v>428.2356030756833</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.260378775266938</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4.81131e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-79.858</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.4294887429324541</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.07634533454852</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.674459009976488</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.451967401807524</v>
+      </c>
+      <c r="L59" t="n">
+        <v>56.30987101076902</v>
+      </c>
+      <c r="M59" t="n">
+        <v>86.77865078601785</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>17.76752271114635</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-8974.515075371071</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>43.32431791440263</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>3.767883063831334e-09</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8910213894939077</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>125.34</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6143635793271117</v>
+      </c>
+      <c r="D60" t="n">
+        <v>422.1333723723887</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.242418750446546</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4.81229e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-79.967</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.05588083585556243</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.4661930612116133</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.169291525295366</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.149914982014108</v>
+      </c>
+      <c r="L60" t="n">
+        <v>44.78677304149869</v>
+      </c>
+      <c r="M60" t="n">
+        <v>86.42938387225492</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>16.02569019930987</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-7959.370109641281</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>44.42852924781555</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>3.670667510141318e-09</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8933290145824563</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>125.903</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.6171231668104463</v>
+      </c>
+      <c r="D61" t="n">
+        <v>417.4665126141884</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.228683295140782</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4.81515e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-80.075</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.09746330265341353</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.6404602328060933</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.434250629492104</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.266192964293285</v>
+      </c>
+      <c r="L61" t="n">
+        <v>45.40427527818311</v>
+      </c>
+      <c r="M61" t="n">
+        <v>86.69524674808845</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>17.31815447593515</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-8556.044908255646</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>44.93749015511537</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>3.653871920749278e-09</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8950390687044602</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>124.379</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.6096531644576896</v>
+      </c>
+      <c r="D62" t="n">
+        <v>412.6613142454954</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.214540683010101</v>
+      </c>
+      <c r="F62" t="n">
+        <v>4.8177e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-80.164</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.4692193011243914</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.8706687167730387</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.612526565466353</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.318028826892592</v>
+      </c>
+      <c r="L62" t="n">
+        <v>52.42411698486022</v>
+      </c>
+      <c r="M62" t="n">
+        <v>86.80687561158989</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>17.92490429093078</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-8782.753613832549</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>45.25610951578229</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>3.59188969117282e-09</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8976406298994852</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>121.612</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.5960905027056702</v>
+      </c>
+      <c r="D63" t="n">
+        <v>423.7886358527908</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.247290505487905</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4.82033e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-80.258</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.2156900627528431</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.6784744603553692</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.573425921757229</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.255773469270077</v>
+      </c>
+      <c r="L63" t="n">
+        <v>47.30255336691651</v>
+      </c>
+      <c r="M63" t="n">
+        <v>86.76109712077208</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>17.67102547793089</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-8563.08091120807</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>29.40565046205502</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>3.362952695954367e-09</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8978748610500724</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>118.135</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.5790477217473138</v>
+      </c>
+      <c r="D64" t="n">
+        <v>420.0459236117385</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.236274991979281</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4.82364e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-80.37</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.1124222209022645</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.8083180241574554</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.223807543020304</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.272915579511115</v>
+      </c>
+      <c r="L64" t="n">
+        <v>54.43464134455434</v>
+      </c>
+      <c r="M64" t="n">
+        <v>86.5844236207531</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>16.75497371290091</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-8009.531316887499</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>63.42875406905142</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>3.608567983255995e-08</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.7420350641531359</v>
       </c>
     </row>
   </sheetData>
@@ -10498,7 +15146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11761,6 +16409,566 @@
       </c>
       <c r="AD21" t="n">
         <v>0.8924075676162064</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>253.4470000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>323.6833219809552</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5.01385e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-73.41</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2296364909577362</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6078580228780566</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.237907571267598</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.994196354650039</v>
+      </c>
+      <c r="L22" t="n">
+        <v>19.43486932483383</v>
+      </c>
+      <c r="M22" t="n">
+        <v>84.66028256898838</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>10.6990312958025</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-7302.501598697544</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>252.1795368991039</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.500194215210243e-09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9255377633340059</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>172.7979999999999</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.6817914593583665</v>
+      </c>
+      <c r="D23" t="n">
+        <v>313.5667666526824</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9687455156281792</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.09218e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-76.122</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1196414127941215</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.462278794935522</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.242468645785523</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.195021400136902</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25.67780053149527</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.72490414119909</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.37734026843357</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7870.419776766566</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>230.7278090774557</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.272025430990645e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8894968651357756</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>155.4710000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6134260811925176</v>
+      </c>
+      <c r="D24" t="n">
+        <v>312.2674715528693</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9647314221869066</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.06645e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.93000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.01821994632036216</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5148373473266725</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.210613048401512</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.215830137990696</v>
+      </c>
+      <c r="L24" t="n">
+        <v>29.6830906363262</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.87143116814933</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.85385184086968</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7842.511579781048</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>219.9569714188642</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.362157906860891e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8871616245921441</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>151.967</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5996007054729391</v>
+      </c>
+      <c r="D25" t="n">
+        <v>457.0052237107581</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.411889932770918</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.03645e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-77.367</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5804019335957445</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9604235352681523</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.774213394500648</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.864324209810046</v>
+      </c>
+      <c r="L25" t="n">
+        <v>35.39999241015102</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.31820763514392</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.54050007974512</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8701.709860191046</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>62.85769452869913</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.417970883099724e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8765965063282908</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>144.878</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5716303605882098</v>
+      </c>
+      <c r="D26" t="n">
+        <v>317.920333750284</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9821955972417687</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.01405e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-77.703</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.03819542857772485</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4234819453490237</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.37744107307523</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.334803817236022</v>
+      </c>
+      <c r="L26" t="n">
+        <v>35.11137570502797</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.13165010017671</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.78891432840433</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8118.921871447683</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>199.7382618915078</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.627806507445807e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8892077299740936</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>143.576</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.5664931918704896</v>
+      </c>
+      <c r="D27" t="n">
+        <v>310.1760714150536</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.958270168251992</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.99915e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-77.97499999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3275613662899805</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8520832758368355</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.642845625566089</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.611538870481448</v>
+      </c>
+      <c r="L27" t="n">
+        <v>36.76602825141157</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.44123434496925</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.07919295827195</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-8744.574638608035</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>200.1258072265054</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.266994107913307e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8943795164601346</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>136.6940000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.5393395857911123</v>
+      </c>
+      <c r="D28" t="n">
+        <v>360.460017708268</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.11361937186704</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.98705e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-78.23399999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1454714267210917</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4344866750626211</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.386862764621113</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.5373564854663</v>
+      </c>
+      <c r="L28" t="n">
+        <v>38.7730148817938</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.29102253757358</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.42628003873503</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-8232.455344380243</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>140.2920926504446</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>5.322911086374246e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8929410544962458</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>135.736</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5355597028175514</v>
+      </c>
+      <c r="D29" t="n">
+        <v>367.9301536037434</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.136697903840074</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.97863e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-78.468</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2193189354326392</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7878455389818507</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.592082700881541</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.377560165337943</v>
+      </c>
+      <c r="L29" t="n">
+        <v>37.22386935567619</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.53411292493462</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.51117767689291</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-8721.625051795852</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>126.1254858314337</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>5.015497944676026e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8935478057307703</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>130.203</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5137287085662878</v>
+      </c>
+      <c r="D30" t="n">
+        <v>460.4555701481956</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.422549568912568</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.97235e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-78.67400000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6777930583759576</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.523320713106424</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.611409048472505</v>
+      </c>
+      <c r="L30" t="n">
+        <v>42.25804798728812</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.42366930959109</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>16.0000165272244</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8311.733703603246</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>25.92151326303559</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.611210191295035e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8845680238162228</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>127.462</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.50291382419204</v>
+      </c>
+      <c r="D31" t="n">
+        <v>402.0098709142263</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.24198512439229</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.96745e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-78.842</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.04852635772667549</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8344308259248309</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.519708120697381</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.598031221256674</v>
+      </c>
+      <c r="L31" t="n">
+        <v>43.38457532545887</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.47190368232027</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>16.21932612958744</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8319.005571557916</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>78.7297734199192</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.152595767305368e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8924075463604643</v>
       </c>
     </row>
   </sheetData>
@@ -11774,7 +16982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14269,6 +19477,1182 @@
       </c>
       <c r="AD43" t="n">
         <v>0.9301641327239726</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>204.199</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>333.7383590532926</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.0472e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-76.01000000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.3156890011984848</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.97285090925156</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.440676296746758</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.284959637321605</v>
+      </c>
+      <c r="L44" t="n">
+        <v>33.28894429570712</v>
+      </c>
+      <c r="M44" t="n">
+        <v>86.03281935299277</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>14.41935528366748</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-8998.037819848076</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>227.8923884778532</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>7.174809799371125e-09</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.8949663818215458</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>176.8770000000001</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.8661991488694857</v>
+      </c>
+      <c r="D45" t="n">
+        <v>387.5551363556407</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.161254395374295</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.04653e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-76.874</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.02214201925965265</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.04633567291082438</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.104321058262387</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.864130830717051</v>
+      </c>
+      <c r="L45" t="n">
+        <v>29.9758687866024</v>
+      </c>
+      <c r="M45" t="n">
+        <v>85.86164679763668</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>13.82098318058108</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-8186.697565978693</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>160.9870642315289</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>6.711205719375123e-09</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8772008645347179</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>173.34</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8488778103712559</v>
+      </c>
+      <c r="D46" t="n">
+        <v>400.9949357415367</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.201524861808002</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.03772e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-77.217</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.3550266579802169</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.6614387944018564</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.71518255369683</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.511868491765952</v>
+      </c>
+      <c r="L46" t="n">
+        <v>43.59092517424482</v>
+      </c>
+      <c r="M46" t="n">
+        <v>86.19508813400054</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>15.03622972663303</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-8805.342610140813</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>141.1293764231992</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>6.334030138377831e-09</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8754536965500936</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>170.826</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8365662907262034</v>
+      </c>
+      <c r="D47" t="n">
+        <v>392.2677837302621</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.175375179655699</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5.02732e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-77.474</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.2483070555288152</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.5682759174516555</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.539298469417471</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.192189168530405</v>
+      </c>
+      <c r="L47" t="n">
+        <v>36.54324884832494</v>
+      </c>
+      <c r="M47" t="n">
+        <v>86.40674426826318</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>15.92445628612508</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-9242.403888453036</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>143.348287769841</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>6.117988579171726e-09</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8794014137901353</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>163.6229999999999</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8012918770415133</v>
+      </c>
+      <c r="D48" t="n">
+        <v>383.3607839776258</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.148686609070338</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5.01979e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-77.679</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.4928887963228729</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.244973010066469</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.073670120981009</v>
+      </c>
+      <c r="L48" t="n">
+        <v>37.46227441948014</v>
+      </c>
+      <c r="M48" t="n">
+        <v>86.1408049396007</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>14.8241035214749</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-8456.181561102565</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>145.5312488458853</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>5.871513314987725e-09</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8840918118655955</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>163.093</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7986963697177756</v>
+      </c>
+      <c r="D49" t="n">
+        <v>387.6260250837857</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.161466803466509</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5.01564e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-77.88200000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.2097552089747076</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.6296495062564021</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.273188133789402</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2.014345571950377</v>
+      </c>
+      <c r="L49" t="n">
+        <v>35.25798837604948</v>
+      </c>
+      <c r="M49" t="n">
+        <v>86.40851752037459</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>15.93233944722355</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-9008.67653005546</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>134.3057081927186</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>5.606485186376758e-09</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8848035359512456</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>159.327</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7802535761683458</v>
+      </c>
+      <c r="D50" t="n">
+        <v>455.9313743831524</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.366134164728567</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.01307e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-78.09</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.3753911060973815</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.7870533273630577</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.268733421460422</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1.973124901537699</v>
+      </c>
+      <c r="L50" t="n">
+        <v>35.83401562066883</v>
+      </c>
+      <c r="M50" t="n">
+        <v>86.43720129708646</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>16.06094456924135</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-8959.763870917543</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>57.65119156154392</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>4.211153819740203e-09</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8805665605047152</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>153.55</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7519625463396004</v>
+      </c>
+      <c r="D51" t="n">
+        <v>397.0440654776713</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.189686635374958</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5.01034e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-78.264</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.6091395131324718</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.266061034339221</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.338117364586253</v>
+      </c>
+      <c r="L51" t="n">
+        <v>40.54930417069693</v>
+      </c>
+      <c r="M51" t="n">
+        <v>86.28508447384245</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>15.40155300398406</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-8452.194266275221</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>110.7907600203852</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>4.797901593959666e-09</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8901034585781992</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>149.8440000000001</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7338135838079525</v>
+      </c>
+      <c r="D52" t="n">
+        <v>429.3531783039456</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.28649634258969</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.01037e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-78.43000000000001</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1766026344237576</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.6449775118365028</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.327372377665219</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.236264268371305</v>
+      </c>
+      <c r="L52" t="n">
+        <v>41.98405620538083</v>
+      </c>
+      <c r="M52" t="n">
+        <v>86.32324995252912</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>15.56187115866204</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-8434.84913626253</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>72.71740707250895</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>4.262832680057284e-09</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8868177966141216</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>147.658</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7231083403934397</v>
+      </c>
+      <c r="D53" t="n">
+        <v>458.4268044693984</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.373611369606438</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.00963e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-78.592</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.284421217697096</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.8095565444205217</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.655394521131121</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.718188531627107</v>
+      </c>
+      <c r="L53" t="n">
+        <v>58.51830501035526</v>
+      </c>
+      <c r="M53" t="n">
+        <v>86.48826426941312</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>16.29508015012644</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-8755.166632520968</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>37.62722075934894</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.793623224996956e-09</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8849402216654799</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>146.007</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.7150230902208142</v>
+      </c>
+      <c r="D54" t="n">
+        <v>456.3851345786028</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.367493793261342</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5.00917e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-78.74299999999999</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.5619376580030291</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.016750498543256</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.291088286448889</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1.943797504102476</v>
+      </c>
+      <c r="L54" t="n">
+        <v>39.39722636911135</v>
+      </c>
+      <c r="M54" t="n">
+        <v>86.602996634245</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>16.84679782633561</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-8967.316715429086</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>33.9692222050665</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>3.709304132998158e-09</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8852089676178069</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>143.929</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.7048467426383087</v>
+      </c>
+      <c r="D55" t="n">
+        <v>488.2389712823329</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.462939329681216</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.00883e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-78.86799999999999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.611085245803213</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.8730512035772793</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.503027664106945</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.355345401316294</v>
+      </c>
+      <c r="L55" t="n">
+        <v>45.29807484081643</v>
+      </c>
+      <c r="M55" t="n">
+        <v>86.71849331651104</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>17.44110982551324</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-9203.16118004487</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.09894328438015956</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.815731746779896e-09</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8746576657290869</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>137.064</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6712275770204558</v>
+      </c>
+      <c r="D56" t="n">
+        <v>434.2215184145222</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.30108363823166</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5.00936e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-78.985</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1066815669347054</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.4700025549762474</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.355883184469666</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.572368269561976</v>
+      </c>
+      <c r="L56" t="n">
+        <v>53.05740581592507</v>
+      </c>
+      <c r="M56" t="n">
+        <v>86.29088641881872</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>15.42571233335039</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-7986.190497144414</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>46.80144374133224</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.741252969916298e-09</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.8903701046201471</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>136.907</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6704587191905939</v>
+      </c>
+      <c r="D57" t="n">
+        <v>472.2271827423729</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.414962259903021</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5.00865e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-79.127</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.111647529898037</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.6689203519740923</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.267260897898484</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.449199406064878</v>
+      </c>
+      <c r="L57" t="n">
+        <v>47.38617085675377</v>
+      </c>
+      <c r="M57" t="n">
+        <v>86.50371673617262</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>16.36727953793666</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-8419.750097659607</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>38.74202198668218</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>3.10405115555302e-08</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.7393164225662986</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>133.383</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6532010440795502</v>
+      </c>
+      <c r="D58" t="n">
+        <v>430.4654591808757</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.28982913561979</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5.00941e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-79.258</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.3003178330651065</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5285805268160026</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.23920266819028</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.117464031181024</v>
+      </c>
+      <c r="L58" t="n">
+        <v>43.47005633813709</v>
+      </c>
+      <c r="M58" t="n">
+        <v>86.42903280883154</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>16.02411061962765</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-8153.537225727913</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>41.58738430973423</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>3.619800435831877e-09</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.8925315090164336</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>132.185</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.647334218091176</v>
+      </c>
+      <c r="D59" t="n">
+        <v>408.4152512876064</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.223758792504847</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5.0099e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-79.361</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.2558097757365574</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.6016751344865429</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.289778889475776</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.396437244033415</v>
+      </c>
+      <c r="L59" t="n">
+        <v>48.83467347061129</v>
+      </c>
+      <c r="M59" t="n">
+        <v>86.54830245463963</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>16.57921874263137</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-8367.410371942011</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>59.4260252167246</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>3.750722480465142e-09</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.8968473166157009</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6412372244722062</v>
+      </c>
+      <c r="D60" t="n">
+        <v>408.7009082824634</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.224614723467255</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5.01015e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-79.467</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.3584431059084611</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.5862267431410751</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.682633211736269</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.306320364720206</v>
+      </c>
+      <c r="L60" t="n">
+        <v>50.56519977932956</v>
+      </c>
+      <c r="M60" t="n">
+        <v>86.58297226724598</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>16.74784028843792</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-8372.141872889862</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>54.45781094140037</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>3.673832597592769e-09</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.8968301483162585</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>130.161</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.6374223184246741</v>
+      </c>
+      <c r="D61" t="n">
+        <v>377.3320098041998</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.130622236156995</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5.01147e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-79.596</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.3455968090130568</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.9200174715224655</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1.767535232060444</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.956776949068005</v>
+      </c>
+      <c r="L61" t="n">
+        <v>73.33580906515812</v>
+      </c>
+      <c r="M61" t="n">
+        <v>86.76825808540362</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>17.71026477324596</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-8793.046607036948</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>81.90682373251711</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>3.970662628894026e-09</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.902757749613458</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>126.241</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.6182253585962716</v>
+      </c>
+      <c r="D62" t="n">
+        <v>395.8857910650998</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.186216029191548</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5.01156e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-79.693</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.2911520566826355</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.5552695067037177</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.10456850307801</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.046627014585492</v>
+      </c>
+      <c r="L62" t="n">
+        <v>41.55609873971333</v>
+      </c>
+      <c r="M62" t="n">
+        <v>86.51465982914073</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>16.41879627757449</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-8030.453118528424</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>87.26921127112581</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.22853880313042e-08</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.7832100861549512</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>123.382</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.6042243105989746</v>
+      </c>
+      <c r="D63" t="n">
+        <v>451.1256477273816</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.35173448148747</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5.01346e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-79.821</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.250671080922325</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.6470678688595063</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.296146435994921</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.33436541593751</v>
+      </c>
+      <c r="L63" t="n">
+        <v>48.09008211628269</v>
+      </c>
+      <c r="M63" t="n">
+        <v>86.54094038033492</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>16.54384682346686</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-8010.580184951246</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0.05004860170751397</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>3.483605191908451e-09</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8859829277459923</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>120.958</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.5923535374805949</v>
+      </c>
+      <c r="D64" t="n">
+        <v>242.6668779791709</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7271171305196623</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5.014219999999999e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-79.92</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.1393148318971744</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.5807451093120737</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.328568527433896</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.608520608892386</v>
+      </c>
+      <c r="L64" t="n">
+        <v>66.17594065249925</v>
+      </c>
+      <c r="M64" t="n">
+        <v>86.47140388244669</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>16.2170229625122</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-7761.130699727876</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>206.0151794279648</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>6.30284402484601e-09</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.9301641275216251</v>
       </c>
     </row>
   </sheetData>
@@ -14282,7 +20666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15545,6 +21929,566 @@
       </c>
       <c r="AD21" t="n">
         <v>0.916853160596305</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>236.601</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>314.2880971985944</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5.34048e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-72.634</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.09775238428660057</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.7116576783443929</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.141752670121127</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.074780039713145</v>
+      </c>
+      <c r="L22" t="n">
+        <v>16.46094679366934</v>
+      </c>
+      <c r="M22" t="n">
+        <v>84.29324554001242</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>10.0067712903218</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-6504.174744469758</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>239.3089239005637</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.330897575188572e-09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.932541978469257</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>170.455</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7204322889590494</v>
+      </c>
+      <c r="D23" t="n">
+        <v>307.6917454527425</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9790117672140675</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.40305e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-75.205</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1869081556360942</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5929183646290453</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.3172577339898</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.138832426653552</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21.2745031554246</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.31756945895515</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.2090796213082</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7000.486509476262</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>220.2713085346376</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.998855821040033e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8920745773425226</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>158.9570000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6718357065270225</v>
+      </c>
+      <c r="D24" t="n">
+        <v>300.2928279138742</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9554699353571866</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.35659e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.13800000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3500517204795346</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6996287674581867</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.422923069521735</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.881800688283441</v>
+      </c>
+      <c r="L24" t="n">
+        <v>22.62407950232634</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.85794459005777</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.8085867696154</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7709.912167855526</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>220.9215905703833</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.908621478266132e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8809801679421293</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>153.12</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6471654811264534</v>
+      </c>
+      <c r="D25" t="n">
+        <v>290.28846621865</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9236381167665432</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.30925e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.696</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3216325080779493</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7262974791148865</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.385765969599591</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.893332204520736</v>
+      </c>
+      <c r="L25" t="n">
+        <v>25.07318979280422</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.08631888573478</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.61709321768785</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8039.545069267775</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>222.8676787012344</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.946108326433836e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8913342300585392</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>150.159</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6346507411211282</v>
+      </c>
+      <c r="D26" t="n">
+        <v>282.3453121881905</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8983646364748593</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.27303e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-77.13800000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4231827061669879</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8664650559238887</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.687802618607461</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.296423059158444</v>
+      </c>
+      <c r="L26" t="n">
+        <v>31.16312837963968</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.35350537499718</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.69134364300222</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8539.226460839291</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>224.7749118053001</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.036364808205926e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8934104973528855</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>143.3390000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.6058258418180822</v>
+      </c>
+      <c r="D27" t="n">
+        <v>275.8369465036677</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8776563572160039</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.2461e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-77.485</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0664872769086961</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7093968994475335</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.382848833060943</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.269400803864905</v>
+      </c>
+      <c r="L27" t="n">
+        <v>31.25696630349673</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.15776587493272</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14.88974008794273</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-7943.922326265624</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>223.0535162443924</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.009662984263437e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9028878973696812</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>139.069</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.5877785808174945</v>
+      </c>
+      <c r="D28" t="n">
+        <v>270.6415675273945</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8611257312629939</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.22457e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-77.798</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1435917165607293</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4676814026646209</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.233637622650597</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.209853001165884</v>
+      </c>
+      <c r="L28" t="n">
+        <v>30.80413627735691</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.20263531704791</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.06620187371839</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-7915.945534897673</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>223.231093909834</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.769866838194908e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8989800812589358</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>137.652</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5817895951411872</v>
+      </c>
+      <c r="D29" t="n">
+        <v>263.4319410469334</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8381861845708855</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.20873e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-78.066</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4863849597300355</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9677087449909744</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.68876618002486</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.737051272546962</v>
+      </c>
+      <c r="L29" t="n">
+        <v>41.67158222566433</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.42234109702724</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>15.99406103152173</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-8313.244926148822</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>221.1800551701652</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.482622911118262e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9105021387614715</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>130.743</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.552588535128761</v>
+      </c>
+      <c r="D30" t="n">
+        <v>257.7315705111645</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8200487794747994</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.19572e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-78.333</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.133576586155218</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.5004093939842542</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.321593093252559</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.404818545583846</v>
+      </c>
+      <c r="L30" t="n">
+        <v>39.86063127368425</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.2101776795749</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>15.09627396283187</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-7692.415457396726</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>221.3412966422295</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.8410061893477e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.910109379973956</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>127.131</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5373223274626905</v>
+      </c>
+      <c r="D31" t="n">
+        <v>253.5332798399539</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8066906831656103</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.18468e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-78.536</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1382706410385817</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.581409056877447</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.137981876614404</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.2387694904972</v>
+      </c>
+      <c r="L31" t="n">
+        <v>37.62158200193961</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.23391246743091</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>15.19169150364624</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-7635.581378916427</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>219.3866016645426</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.313061727398261e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9168531593108472</v>
       </c>
     </row>
   </sheetData>
@@ -15558,7 +22502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18053,6 +24997,1182 @@
       </c>
       <c r="AD43" t="n">
         <v>0.9008253041846258</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B44" t="n">
+        <v>204.609</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>333.7421800405776</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.190239999999999e-07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-75.535</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.4341269836425564</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8770698217290915</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.611166485128293</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.726171321750013</v>
+      </c>
+      <c r="L44" t="n">
+        <v>34.44217657680807</v>
+      </c>
+      <c r="M44" t="n">
+        <v>85.95011125627252</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>14.12392554478488</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-8799.586962586653</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>227.2043173257353</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>7.415790909173874e-09</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.892209389826914</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B45" t="n">
+        <v>180.717</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.8832309429203994</v>
+      </c>
+      <c r="D45" t="n">
+        <v>406.6459735239791</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.218443450793476</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.19621e-07</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-76.41800000000001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.4074856843798644</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.8052893662018898</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.505632555887714</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.183018310677797</v>
+      </c>
+      <c r="L45" t="n">
+        <v>29.9661756648014</v>
+      </c>
+      <c r="M45" t="n">
+        <v>86.09480031582621</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>14.64893791468133</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-8712.207715790601</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>139.8248128091584</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>6.131392653100676e-09</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0.8761863054589144</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B46" t="n">
+        <v>172.316</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8421721429653635</v>
+      </c>
+      <c r="D46" t="n">
+        <v>397.8591615662288</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.192115307444374</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.18674e-07</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-76.767</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.2029816572770876</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.7437107576065484</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.363498654623092</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.599642291862426</v>
+      </c>
+      <c r="L46" t="n">
+        <v>39.29648469481174</v>
+      </c>
+      <c r="M46" t="n">
+        <v>86.05397946992426</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>14.49692457470197</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-8459.159807644928</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>141.394852709049</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>5.936200708988308e-09</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.8804858813101721</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B47" t="n">
+        <v>169.34</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.8276273282211437</v>
+      </c>
+      <c r="D47" t="n">
+        <v>530.7556491734686</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.590316360697762</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5.17863e-07</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-77.03700000000001</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.4437706076916035</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.6937116245526209</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.454849245616604</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.879215365228066</v>
+      </c>
+      <c r="L47" t="n">
+        <v>30.44454441905064</v>
+      </c>
+      <c r="M47" t="n">
+        <v>86.20353949558505</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>15.06980062195729</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-8694.053340036611</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.205207069750095</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>4.204855398689917e-09</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.8627178882205535</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B48" t="n">
+        <v>167.161</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.8169777478019051</v>
+      </c>
+      <c r="D48" t="n">
+        <v>517.3195051347097</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.550057307924974</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5.17232e-07</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-77.259</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.4189759137374585</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.222558228199029</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.616154031587023</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.675854820872687</v>
+      </c>
+      <c r="L48" t="n">
+        <v>43.52718987594177</v>
+      </c>
+      <c r="M48" t="n">
+        <v>86.46264421811694</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>16.17676239454528</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-9257.356887068754</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>7.418480364888201</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>4.010189250164338e-09</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.8682984528808602</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B49" t="n">
+        <v>158.897</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.7765885176116398</v>
+      </c>
+      <c r="D49" t="n">
+        <v>396.6151230536615</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.188387763888399</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5.16748e-07</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-77.473</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.2287810479190074</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2909553693014067</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.194053249113096</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.881690882143798</v>
+      </c>
+      <c r="L49" t="n">
+        <v>32.24413141500671</v>
+      </c>
+      <c r="M49" t="n">
+        <v>85.98322467867696</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>14.24074725219623</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-7971.611483143059</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>123.5819524822922</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>5.580689771780757e-09</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.8813409558600329</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="n">
+        <v>155.76</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.7612568362095512</v>
+      </c>
+      <c r="D50" t="n">
+        <v>389.398452558566</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.166764274480443</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5.16463e-07</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-77.65900000000001</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.09326881776994159</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.5352377549858983</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.312222876269671</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.138215954275578</v>
+      </c>
+      <c r="L50" t="n">
+        <v>36.09636256477264</v>
+      </c>
+      <c r="M50" t="n">
+        <v>86.10727891488591</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>14.69604241525118</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-8138.293414799076</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>124.7574524670185</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>5.54003427037018e-09</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.8830618283321697</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>153.4829999999999</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.7501282934768263</v>
+      </c>
+      <c r="D51" t="n">
+        <v>444.83487911816</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.332869819044375</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5.162660000000001e-07</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-77.81100000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.3206300146548768</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.6425562784706773</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.402216861111823</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2.392039409126852</v>
+      </c>
+      <c r="L51" t="n">
+        <v>41.39457995253967</v>
+      </c>
+      <c r="M51" t="n">
+        <v>86.24132441411275</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>15.22173524286037</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-8346.133023764769</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>61.77698442399143</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>4.277482654160997e-09</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.8818520109864552</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B52" t="n">
+        <v>152.814</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.7468586425817048</v>
+      </c>
+      <c r="D52" t="n">
+        <v>376.5265905355797</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.128195993954975</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.16143e-07</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-77.982</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.4704757754080797</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.9385174736945496</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.741258981043819</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.367071551321159</v>
+      </c>
+      <c r="L52" t="n">
+        <v>42.7925121795191</v>
+      </c>
+      <c r="M52" t="n">
+        <v>86.57823194614254</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>16.72458364745447</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>-9121.422450275599</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>127.0033660591474</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>5.512283067736537e-09</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.8865536720272756</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B53" t="n">
+        <v>147.194</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.7193916201144623</v>
+      </c>
+      <c r="D53" t="n">
+        <v>358.3160349785629</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.073631253127781</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.16208e-07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-78.142</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.06426427450633361</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.6147806978837342</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1.304585700646868</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2.263897460490562</v>
+      </c>
+      <c r="L53" t="n">
+        <v>39.61757183780524</v>
+      </c>
+      <c r="M53" t="n">
+        <v>86.23403615487634</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>15.19219189203601</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>-8143.608376541416</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>141.1282560027825</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>5.637330948850109e-09</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.8923681297970864</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B54" t="n">
+        <v>144.9469999999999</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.7084096984981109</v>
+      </c>
+      <c r="D54" t="n">
+        <v>393.2511289055929</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.178308144501783</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5.15941e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-78.27</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.3100808111512601</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.7215574700022996</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.399708717458724</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2.068831105715563</v>
+      </c>
+      <c r="L54" t="n">
+        <v>39.81076461623726</v>
+      </c>
+      <c r="M54" t="n">
+        <v>86.27555474661604</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>15.36203429133054</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-8155.639213459574</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>99.59046985793617</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>4.69699916975905e-09</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.8907493303389157</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B55" t="n">
+        <v>145.48</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.7110146669990081</v>
+      </c>
+      <c r="D55" t="n">
+        <v>424.5484234291735</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.272085006988195</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.16025e-07</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-78.407</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.2778815103829188</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.8456813308983444</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.465722789624489</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.307784678470119</v>
+      </c>
+      <c r="L55" t="n">
+        <v>41.08126219608315</v>
+      </c>
+      <c r="M55" t="n">
+        <v>86.61406644922589</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>16.90200504411959</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>-8934.495273070181</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>63.07391247671142</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>4.273598507811043e-09</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.8849312902537186</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B56" t="n">
+        <v>140.832</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6882981687022566</v>
+      </c>
+      <c r="D56" t="n">
+        <v>377.5191314109251</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.131169968881443</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5.16003e-07</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-78.548</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.3793314305432155</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.7224578856322302</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.407974108401413</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2.440022047394589</v>
+      </c>
+      <c r="L56" t="n">
+        <v>47.52595568656239</v>
+      </c>
+      <c r="M56" t="n">
+        <v>86.41195667456248</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>15.94765071620183</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>-8314.579168769395</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>106.711260715675</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>4.963075074059891e-09</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.890544204048319</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" t="n">
+        <v>137.995</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6744326984638995</v>
+      </c>
+      <c r="D57" t="n">
+        <v>409.5404736692715</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.227116313615133</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5.15982e-07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-78.654</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1850079808415546</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.6211224989523683</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.440378818762587</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.28793299546794</v>
+      </c>
+      <c r="L57" t="n">
+        <v>42.33021315199902</v>
+      </c>
+      <c r="M57" t="n">
+        <v>86.36764732155075</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>15.75260017528404</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-8125.317972457186</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>69.20627253984094</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>4.174501091509376e-09</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.8907022372085974</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>136.198</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6656500935931459</v>
+      </c>
+      <c r="D58" t="n">
+        <v>419.169734472589</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.255968707406492</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5.15883e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-78.79600000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.2763925948041334</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5953812507390878</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.454093701839376</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2.267031003926022</v>
+      </c>
+      <c r="L58" t="n">
+        <v>43.71138836166046</v>
+      </c>
+      <c r="M58" t="n">
+        <v>86.39923131988029</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>15.89114278155018</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>-8119.982157234307</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>80.11166277418602</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.826632434904228e-08</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.7905655511727179</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B59" t="n">
+        <v>135.462</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.6620529888714576</v>
+      </c>
+      <c r="D59" t="n">
+        <v>407.7649126601494</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.221796155974567</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5.16019e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-78.913</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.2915081464087915</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.9061904908275671</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.60067523840496</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.830325477844451</v>
+      </c>
+      <c r="L59" t="n">
+        <v>59.84232123027933</v>
+      </c>
+      <c r="M59" t="n">
+        <v>86.56823354229601</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>16.67574058292641</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>-8464.497698882653</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>61.95069215369865</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>3.932244104051688e-09</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0.894350259057036</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B60" t="n">
+        <v>128.85</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.6297376948228085</v>
+      </c>
+      <c r="D60" t="n">
+        <v>498.3512950132838</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.493222387870459</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5.16125e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-79.03</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.08553367608119777</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.4511436861560143</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.209508652176592</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.274208323575305</v>
+      </c>
+      <c r="L60" t="n">
+        <v>45.02317040776452</v>
+      </c>
+      <c r="M60" t="n">
+        <v>86.19605984370624</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>15.04008201906049</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>-7507.542129849154</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>4.318141355633743</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>3.918891604463265e-08</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.7140455141465991</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B61" t="n">
+        <v>128.679</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.6289019544594812</v>
+      </c>
+      <c r="D61" t="n">
+        <v>420.4362557923385</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.259763616757164</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5.16195e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-79.139</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.2598098467772489</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.6718184631646174</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.9773069703928212</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.146576179141718</v>
+      </c>
+      <c r="L61" t="n">
+        <v>37.403737808341</v>
+      </c>
+      <c r="M61" t="n">
+        <v>86.37119903640611</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>15.76805951364126</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>-7814.228678086119</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>40.83394559870862</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>3.653105197658538e-09</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.8940978275469788</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B62" t="n">
+        <v>125.838</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.615016934738941</v>
+      </c>
+      <c r="D62" t="n">
+        <v>381.9111972965312</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.144330025201181</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5.16325e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-79.258</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.02535125707845608</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.5387538266961881</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1.336427828124159</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.549917302944029</v>
+      </c>
+      <c r="L62" t="n">
+        <v>54.77269454172064</v>
+      </c>
+      <c r="M62" t="n">
+        <v>86.3154575967724</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>15.52886908561989</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-7611.576853225756</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>75.83070001575803</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>4.080322871783889e-09</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8990971811547871</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B63" t="n">
+        <v>123.924</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.6056625075143325</v>
+      </c>
+      <c r="D63" t="n">
+        <v>383.8729147054056</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.150207967895257</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5.16501e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-79.37</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.2436970921242774</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.6682560515821906</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.339842451990955</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.487079147596895</v>
+      </c>
+      <c r="L63" t="n">
+        <v>55.49866911638667</v>
+      </c>
+      <c r="M63" t="n">
+        <v>86.38709435375804</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>15.83761802685178</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>-7688.220450246899</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>69.3957914278527</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>4.008907648031505e-09</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.8987504464267437</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B64" t="n">
+        <v>121.6420000000001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.5945095279288793</v>
+      </c>
+      <c r="D64" t="n">
+        <v>367.4489439492795</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.100996415570257</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5.16635e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-79.488</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.5600702658062693</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.335431596250833</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2.386473134667395</v>
+      </c>
+      <c r="L64" t="n">
+        <v>49.06020133975996</v>
+      </c>
+      <c r="M64" t="n">
+        <v>86.31899829893688</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>15.54384732010938</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-7461.779420541887</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>81.53535160518707</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>4.184498841114459e-09</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.9008264610054592</v>
       </c>
     </row>
   </sheetData>
@@ -18066,7 +26186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19331,6 +27451,566 @@
         <v>0.9223818606242553</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>230.223</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>318.6762908569275</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5.48405e-07</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-71.477</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.08917540533169541</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.3471414323388183</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.1459857028003</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.954132397868006</v>
+      </c>
+      <c r="L22" t="n">
+        <v>13.54704243204864</v>
+      </c>
+      <c r="M22" t="n">
+        <v>83.23478723234156</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.429781238972879</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-5414.041814868423</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>223.6363416046415</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.341432782033877e-09</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9390762822440303</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>155.771</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.6766092006445926</v>
+      </c>
+      <c r="D23" t="n">
+        <v>281.2050578839725</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8824160000350387</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.56439e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-74.845</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0184069568974506</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6847044382186773</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.456079963214183</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.191634385802108</v>
+      </c>
+      <c r="L23" t="n">
+        <v>18.62958177097708</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.08416256317115</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.62673141074112</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6445.594085121489</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>231.3452517081248</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.069067949366617e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8999087974728303</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>142.388</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6184786055259468</v>
+      </c>
+      <c r="D24" t="n">
+        <v>274.9206344129435</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8626956014634031</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.48945e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.01000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3604533760222052</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.7743064445909836</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.497126154862834</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.627842470879877</v>
+      </c>
+      <c r="L24" t="n">
+        <v>23.87766911889256</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.70517038129283</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.3156451929969</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7146.132424742581</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>227.2879308200891</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.837082347473839e-09</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8952620395798013</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="n">
+        <v>134.357</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5835950361171562</v>
+      </c>
+      <c r="D25" t="n">
+        <v>272.340117382444</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8545979892326332</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.42322e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.693</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2608720242752646</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4951698017334251</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.15293708568749</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.886380745785861</v>
+      </c>
+      <c r="L25" t="n">
+        <v>22.43295414845267</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.79608932309401</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.60469582453691</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-7146.513889313306</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>222.6717965081064</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.373627419559294e-09</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8998280601798566</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>131.894</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5728967131867799</v>
+      </c>
+      <c r="D26" t="n">
+        <v>262.8184441995215</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8247191640545236</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.37384e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-77.176</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2971080407960572</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.138437418711877</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.509783129603516</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.560692240341428</v>
+      </c>
+      <c r="L26" t="n">
+        <v>28.59713413647124</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.1322096647157</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.79106039914917</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-7685.932461853346</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>224.7462366581939</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.043829150533915e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9060893027203227</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>126.794</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.550744278373577</v>
+      </c>
+      <c r="D27" t="n">
+        <v>256.3464491092914</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8044101693915483</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.34091e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-77.55500000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.08846537671712368</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5108913846030761</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.130939646268442</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.022654159692959</v>
+      </c>
+      <c r="L27" t="n">
+        <v>25.80948698569293</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.09283679408355</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14.6415533226027</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-7469.247115082168</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>223.9275679417528</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.727730312684295e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9110341542815975</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.5277491823145386</v>
+      </c>
+      <c r="D28" t="n">
+        <v>250.596257992918</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.786366181553887</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.31622e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-77.863</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4546049582765402</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.075151414504331</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.985898241251778</v>
+      </c>
+      <c r="L28" t="n">
+        <v>27.01572125230378</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.01793341948847</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14.36527923318814</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-7190.513920025728</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>222.9776757650925</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.606002976191019e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9141653567392408</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="n">
+        <v>119.83</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5204953458168822</v>
+      </c>
+      <c r="D29" t="n">
+        <v>242.8081298746673</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7619271870579106</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.29846e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-78.14400000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1549357653185952</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.6998680887728033</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.539827081477487</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.564392866790091</v>
+      </c>
+      <c r="L29" t="n">
+        <v>34.00297576992922</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.26989989713512</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>15.33867958993862</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-7597.017364114158</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>224.117781748786</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.507951925369305e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.916976180910871</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>116.121</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5043848790086134</v>
+      </c>
+      <c r="D30" t="n">
+        <v>238.6319366151209</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7488223738685875</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.28564e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-78.361</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.08806292461510733</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6883682539826083</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.237438892053168</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.252080060144379</v>
+      </c>
+      <c r="L30" t="n">
+        <v>33.00930684280635</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.27825604431004</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>15.37321574682725</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-7510.588681929537</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>222.7389122939269</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.38618453373546e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9195498165967417</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" t="n">
+        <v>116.015</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5039244558536726</v>
+      </c>
+      <c r="D31" t="n">
+        <v>234.6635320537154</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7363695975709397</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5.27423e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-78.563</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3470963104992334</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.964366898429819</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.528700134325663</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.54653247517536</v>
+      </c>
+      <c r="L31" t="n">
+        <v>34.09323503542841</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.57205587394866</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>16.69437940080897</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8100.325238554351</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>221.6827575007765</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.249342579418549e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9223818708683649</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
